--- a/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
+++ b/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <color rgb="00D03B3B"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F3E4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,22 +74,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -536,94 +550,110 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>5151</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HEXTAR</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.006500000000000001</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>15707400</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="H2" t="n">
-        <v>50.93</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" s="7" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1662000</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>61.52</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 61.52未超买，现价高于50日均线约29.5%，技术面信号可靠性较高。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0170</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>KANGER</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>8980400</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="H3" t="n">
-        <v>40.85</v>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="7" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.1089</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>5215300</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>65.62</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 65.62偏高但未超买，现价远高于50日均线，信号可靠性中等。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -633,42 +663,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CTOS</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.0641</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>1483400</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.11</v>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>47301600</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0.13</v>
       </c>
       <c r="H4" t="n">
-        <v>39.53</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>37.22</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0.223</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr"/>
+      <c r="M4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -678,42 +708,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0170</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GIIB</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>-0.0141</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1165800</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.05</v>
+          <t>KANGER</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>-0.3333</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>26006300</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>34.14</v>
       </c>
       <c r="H5" t="n">
-        <v>64.88</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
+        <v>35.25</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.581</v>
+      <c r="J5" s="9" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.023</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -723,42 +753,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>879300</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.04</v>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>-0.0141</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>17978800</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0.23</v>
       </c>
       <c r="H6" t="n">
-        <v>59.81</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>4.904</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>4.796</v>
+        <v>64.94</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.273</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,45 +798,2014 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>13698000</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>43.87</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DATASONIC</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>9064200</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H8" t="n">
+        <v>47.51</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ICONIC</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>8296300</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H9" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>7255800</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H10" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.0263</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>6399400</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H11" t="n">
+        <v>49.13</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>6061100</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H12" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0476</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>5575900</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H13" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7120</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AXTERIA</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>2608200</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H14" t="n">
+        <v>85.94</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5932</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BPURI</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>2384900</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H15" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0478</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NWEBHD</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>2287100</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>2091000</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AVANGAAD</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>1930000</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H18" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>1806700</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H19" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>2.714</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>2.749</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>1720300</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H20" t="n">
+        <v>50.93</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>1558800</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H21" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>4.795</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>1520700</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H22" t="n">
+        <v>62.72</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>1346500</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H23" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>1337900</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H24" t="n">
+        <v>52.51</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>2.108</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>-0.0172</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>1315500</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H25" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>1.271</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TDM</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>1279400</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="H26" t="n">
+        <v>52.51</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>1211300</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H27" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>1170900</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>50.78</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>1146300</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H29" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>4.794</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>1134900</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>-0.004500000000000001</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>1133600</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H31" t="n">
+        <v>64.81999999999999</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>2.031</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>1.837</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>1018700</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H32" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>1017600</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H33" t="n">
+        <v>40.02</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0399</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>1012000</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H34" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>989800</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H35" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>962900</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>3.012</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>2.881</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>0112</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>MIKROMB</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D37" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>959000</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H37" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
         <v>0.64</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="K37" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>916700</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H38" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>7.293</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>7.587</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>835500</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H39" t="n">
+        <v>53.12</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>830700</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H40" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E41" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G7" s="5" t="n">
+      <c r="F41" s="11" t="n">
+        <v>795800</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H41" t="n">
+        <v>79.91</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5125</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PANTECH</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>785600</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>773500</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H43" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>1.823</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>745000</v>
+      </c>
+      <c r="G44" s="12" t="n">
         <v>0.23</v>
       </c>
-      <c r="H7" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0.631</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>90.12</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>3.153</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>2.672</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>693500</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H45" t="n">
+        <v>47.94</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>1.731</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>672200</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H46" t="n">
+        <v>68.38</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>659200</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H47" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>648000</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H48" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>552900</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H49" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>531200</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H50" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>508700</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H51" t="n">
+        <v>53.45</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>1.258</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M7"/>
+  <autoFilter ref="A1:M51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
+++ b/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="4">
@@ -96,9 +96,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -557,28 +557,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.645</v>
+        <v>1.11</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0488</v>
+        <v>0.099</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1662000</v>
+        <v>7307100</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.32</v>
+        <v>1.13</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>61.52</v>
+        <v>65.28</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.588</v>
+        <v>0.866</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.498</v>
+        <v>0.667</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,62 +598,54 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 61.52未超买，现价高于50日均线约29.5%，技术面信号可靠性较高。</t>
+          <t>SAR转多信号，RSI 65.28偏高但未超买，现价1.11远高于50日均线0.667，技术面信号可靠性较强。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>0455</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>BUSCAP</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0.1089</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>5215300</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>65.62</v>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>🎯 SAR 转多</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>SAR转多信号，RSI 65.62偏高但未超买，现价远高于50日均线，信号可靠性中等。</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0138</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>-0.0588</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>48914800</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H3" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -663,39 +655,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>0170</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>KANGER</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0</v>
+        <v>-0.3333</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>47301600</v>
+        <v>26781200</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.13</v>
+        <v>35.15</v>
       </c>
       <c r="H4" t="n">
-        <v>37.22</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.25</v>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.095</v>
+        <v>0.019</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.223</v>
+        <v>0.023</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -708,39 +700,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0170</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KANGER</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>-0.3333</v>
+        <v>0.345</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>-0.0282</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>26006300</v>
+        <v>21557500</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>34.14</v>
+        <v>0.27</v>
       </c>
       <c r="H5" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.49</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.019</v>
+        <v>0.325</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.023</v>
+        <v>0.273</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -753,28 +745,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>-0.0141</v>
+        <v>0.435</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.1154</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>17978800</v>
+        <v>19655800</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.23</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
-        <v>64.94</v>
+        <v>43.05</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -782,10 +774,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.325</v>
+        <v>0.455</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.273</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -798,28 +790,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.44</v>
+        <v>0.115</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>0.1282</v>
+        <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>13698000</v>
+        <v>12987300</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.05</v>
+        <v>2.58</v>
       </c>
       <c r="H7" t="n">
-        <v>43.87</v>
+        <v>70.39</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -827,10 +819,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.455</v>
+        <v>0.103</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -843,39 +835,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>0.0185</v>
+        <v>0.705</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>9064200</v>
+        <v>12240100</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1.43</v>
+        <v>0.53</v>
       </c>
       <c r="H8" t="n">
-        <v>47.51</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.279</v>
+        <v>0.674</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.282</v>
+        <v>0.581</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -888,39 +880,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>8296300</v>
+        <v>10225300</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="H9" t="n">
-        <v>70.39</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.84</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.103</v>
+        <v>0.279</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.282</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -933,39 +925,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.19</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>7255800</v>
+        <v>6420800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="H10" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.65</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.674</v>
+        <v>0.186</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.581</v>
+        <v>0.187</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -978,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.0263</v>
+        <v>0.28</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>6399400</v>
+        <v>6135200</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.35</v>
+        <v>0.53</v>
       </c>
       <c r="H11" t="n">
-        <v>49.13</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.33</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.185</v>
+        <v>0.283</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.187</v>
+        <v>0.279</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1023,40 +1015,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0.0182</v>
+        <v>0.235</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>6061100</v>
+        <v>5995900</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.53</v>
+        <v>0.32</v>
       </c>
       <c r="H12" t="n">
-        <v>48.33</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
+        <v>57.33</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J12" s="9" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>0.279</v>
-      </c>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="9" t="n"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
     </row>
@@ -1068,36 +1056,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E13" s="10" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5575900</v>
+        <v>5048700</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="H13" t="n">
-        <v>54.46</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
+        <v>30.77</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
+      <c r="J13" s="9" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0.068</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
     </row>
@@ -1109,40 +1101,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0</v>
+        <v>0.205</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0.025</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>2608200</v>
+        <v>4388100</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H14" t="n">
-        <v>85.94</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>0.122</v>
-      </c>
+        <v>0.17</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
     </row>
@@ -1154,39 +1139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>-0.0222</v>
+        <v>0.11</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>2384900</v>
+        <v>4299200</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2.21</v>
+        <v>0.25</v>
       </c>
       <c r="H15" t="n">
-        <v>45.54</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.82</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.223</v>
+        <v>0.125</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.23</v>
+        <v>0.144</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1199,33 +1184,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0.025</v>
+        <v>0.38</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>2287100</v>
+        <v>4279000</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
+        <v>0.62</v>
+      </c>
+      <c r="H16" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.37</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
     </row>
@@ -1237,39 +1229,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>-0.0104</v>
+        <v>0.295</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>2091000</v>
+        <v>4156500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.1</v>
+        <v>1.17</v>
       </c>
       <c r="H17" t="n">
-        <v>62.06</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
+        <v>49.15</v>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.446</v>
+        <v>0.295</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.398</v>
+        <v>0.295</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1282,39 +1274,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E18" s="10" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E18" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>1930000</v>
+        <v>4106300</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="H18" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.94</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.295</v>
+        <v>0.145</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.295</v>
+        <v>0.122</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1327,39 +1319,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>-0.0075</v>
+        <v>0.48</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1806700</v>
+        <v>3717000</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H19" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
+        <v>63.86</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>2.714</v>
+        <v>0.446</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>2.749</v>
+        <v>0.398</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1372,28 +1364,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.775</v>
+        <v>0.82</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>-0.0061</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1720300</v>
+        <v>3409300</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="H20" t="n">
-        <v>50.93</v>
+        <v>53.1</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1401,10 +1393,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.774</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.775</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1417,28 +1409,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>-0.002</v>
+        <v>2.2</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1558800</v>
+        <v>3370300</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="H21" t="n">
-        <v>57.51</v>
+        <v>64.05</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1446,10 +1438,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>4.9</v>
+        <v>2.03</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>4.795</v>
+        <v>1.837</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1462,39 +1454,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>1520700</v>
+        <v>3091500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="H22" t="n">
-        <v>62.72</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.71</v>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.61</v>
+        <v>0.387</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.587</v>
+        <v>0.401</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1507,28 +1499,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.445</v>
+        <v>0.15</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>0.0114</v>
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1346500</v>
+        <v>3056500</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H23" t="n">
-        <v>54.88</v>
+        <v>37.77</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1536,10 +1528,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.432</v>
+        <v>0.153</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.416</v>
+        <v>0.172</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1552,28 +1544,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E24" s="10" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E24" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>1337900</v>
+        <v>2860300</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="H24" t="n">
-        <v>52.51</v>
+        <v>50.93</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1581,10 +1573,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>2.108</v>
+        <v>0.774</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>2.225</v>
+        <v>0.775</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1597,39 +1589,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>-0.0172</v>
+        <v>0.635</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>0.0325</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1315500</v>
+        <v>2772300</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.13</v>
+        <v>0.53</v>
       </c>
       <c r="H25" t="n">
-        <v>33.47</v>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.38</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1.19</v>
+        <v>0.587</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1.271</v>
+        <v>0.498</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1642,28 +1634,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TDM</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>0.0513</v>
+        <v>0.495</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1279400</v>
+        <v>2601600</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>3.52</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>52.51</v>
+        <v>72.61</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1671,10 +1663,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.201</v>
+        <v>0.441</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.214</v>
+        <v>0.343</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1687,39 +1679,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E27" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.22</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>1211300</v>
+        <v>2449500</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.13</v>
+        <v>2.27</v>
       </c>
       <c r="H27" t="n">
-        <v>49.94</v>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.54</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.335</v>
+        <v>0.223</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.339</v>
+        <v>0.23</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1732,39 +1724,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0</v>
+        <v>4.78</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1170900</v>
+        <v>2403900</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.6</v>
+        <v>0.11</v>
       </c>
       <c r="H28" t="n">
-        <v>50.78</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.52</v>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.904</v>
+        <v>4.734</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.898</v>
+        <v>4.795</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1777,39 +1769,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>0.0064</v>
+        <v>2.63</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>-0.015</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1146300</v>
+        <v>2296000</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="H29" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
+        <v>41.22</v>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>4.73</v>
+        <v>2.712</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>4.794</v>
+        <v>2.749</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1822,39 +1814,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
+        <v>1.52</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>1134900</v>
+        <v>2212300</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="H30" t="n">
-        <v>43.12</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.65</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.988</v>
+        <v>1.556</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.993</v>
+        <v>1.822</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1867,28 +1859,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>-0.004500000000000001</v>
+        <v>0.905</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>1133600</v>
+        <v>2171500</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.04</v>
+        <v>1.12</v>
       </c>
       <c r="H31" t="n">
-        <v>64.81999999999999</v>
+        <v>50.78</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1896,10 +1888,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>2.031</v>
+        <v>0.904</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1.837</v>
+        <v>0.898</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1912,28 +1904,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>-0.0111</v>
+        <v>0.44</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>1018700</v>
+        <v>2145000</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="H32" t="n">
-        <v>46.14</v>
+        <v>32.84</v>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
@@ -1941,10 +1933,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.453</v>
+        <v>0.469</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.471</v>
+        <v>0.585</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1957,28 +1949,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>0.0164</v>
+        <v>2.16</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1017600</v>
+        <v>2058400</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H33" t="n">
-        <v>40.02</v>
+        <v>53.36</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1986,10 +1978,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1.277</v>
+        <v>2.109</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.469</v>
+        <v>2.225</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2002,39 +1994,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>-0.0122</v>
+        <v>0.53</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>1012000</v>
+        <v>2028400</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="H34" t="n">
-        <v>35.62</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.91</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.435</v>
+        <v>0.471</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.452</v>
+        <v>0.441</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2047,28 +2039,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>-0.0083</v>
+        <v>4.97</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>989800</v>
+        <v>2002700</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H35" t="n">
-        <v>55.64</v>
+        <v>56.08</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2076,10 +2068,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.575</v>
+        <v>4.898</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.552</v>
+        <v>4.794</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2092,28 +2084,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>0.01</v>
+        <v>0.965</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>962900</v>
+        <v>1999500</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="H36" t="n">
-        <v>52.29</v>
+        <v>69.03</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2121,10 +2113,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>3.012</v>
+        <v>0.888</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>2.881</v>
+        <v>0.782</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2137,28 +2129,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>-0.0156</v>
+        <v>0.665</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>959000</v>
+        <v>1900400</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="H37" t="n">
-        <v>45.12</v>
+        <v>62.72</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2166,10 +2158,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.631</v>
+        <v>0.587</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2182,39 +2174,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>-0.0028</v>
+        <v>0.44</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>916700</v>
+        <v>1899800</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H38" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.81</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>7.293</v>
+        <v>0.452</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>7.587</v>
+        <v>0.471</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2227,39 +2219,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>-0.0064</v>
+        <v>0.595</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>835500</v>
+        <v>1805000</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="H39" t="n">
-        <v>53.12</v>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.64</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.771</v>
+        <v>0.575</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.771</v>
+        <v>0.552</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2272,39 +2264,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>-0.0061</v>
+        <v>7.09</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>-0.0028</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>830700</v>
+        <v>1802500</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H40" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.4</v>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.8179999999999999</v>
+        <v>7.293</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>7.587</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2317,28 +2309,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E41" s="10" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E41" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>795800</v>
+        <v>1792800</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="H41" t="n">
-        <v>79.91</v>
+        <v>53.62</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2346,10 +2338,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.471</v>
+        <v>0.431</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.441</v>
+        <v>0.416</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2362,39 +2354,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PANTECH</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>0.0075</v>
+        <v>0.4</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>785600</v>
+        <v>1779100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>2.8</v>
+        <v>0.89</v>
       </c>
       <c r="H42" t="n">
-        <v>61.24</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.27</v>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.661</v>
+        <v>0.434</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.661</v>
+        <v>0.452</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2407,28 +2399,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>0.0132</v>
+        <v>1.24</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>773500</v>
+        <v>1740600</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="H43" t="n">
-        <v>41.73</v>
+        <v>40.02</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2436,10 +2428,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.557</v>
+        <v>1.277</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1.823</v>
+        <v>1.469</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2452,39 +2444,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0.008699999999999999</v>
+        <v>1.15</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>745000</v>
+        <v>1659700</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="H44" t="n">
-        <v>90.12</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.03</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>3.153</v>
+        <v>1.191</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>2.672</v>
+        <v>1.272</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2497,28 +2489,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>-0.006</v>
+        <v>0.35</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>693500</v>
+        <v>1608100</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.11</v>
+        <v>1.89</v>
       </c>
       <c r="H45" t="n">
-        <v>47.94</v>
+        <v>70.63</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2526,10 +2518,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>1.65</v>
+        <v>0.335</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1.731</v>
+        <v>0.319</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2542,28 +2534,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>FPI</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>0.008100000000000001</v>
+        <v>1.16</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>672200</v>
+        <v>1594700</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.79</v>
       </c>
       <c r="H46" t="n">
-        <v>68.38</v>
+        <v>65.13</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2571,10 +2563,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.131</v>
+        <v>1.096</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>1.071</v>
+        <v>1.099</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2587,28 +2579,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>-0.0052</v>
+        <v>0.29</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>659200</v>
+        <v>1510100</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="H47" t="n">
-        <v>69.03</v>
+        <v>38.02</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2616,10 +2608,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.888</v>
+        <v>0.308</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.782</v>
+        <v>0.352</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2632,39 +2624,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.78</v>
+        <v>0.3</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>648000</v>
+        <v>1495600</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H48" t="n">
-        <v>57.65</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.44</v>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.75</v>
+        <v>0.306</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.699</v>
+        <v>0.304</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2677,39 +2669,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.945</v>
       </c>
       <c r="E49" s="17" t="n">
-        <v>0.0053</v>
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>552900</v>
+        <v>1481300</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0.13</v>
       </c>
       <c r="H49" t="n">
-        <v>57.27</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.12</v>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.904</v>
+        <v>0.988</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.953</v>
+        <v>0.993</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2722,28 +2714,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>-0.0105</v>
+        <v>0.645</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>531200</v>
+        <v>1452300</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H50" t="n">
-        <v>51.71</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2751,10 +2743,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.944</v>
+        <v>0.629</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.9</v>
+        <v>0.62</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2767,45 +2759,1613 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>-0.0155</v>
+        <v>2.61</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>508700</v>
+        <v>1423400</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="H51" t="n">
-        <v>53.45</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.27</v>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.258</v>
+        <v>2.596</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.137</v>
+        <v>2.571</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>1405000</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H52" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.04650000000000001</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>1390900</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H53" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>1.254</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>1.136</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>1368700</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H54" t="n">
+        <v>53.12</v>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>1351300</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H55" t="n">
+        <v>40.78</v>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TDM</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>1320300</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="H56" t="n">
+        <v>52.51</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0113</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MMSV</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>1271100</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H57" t="n">
+        <v>61.06</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>1237500</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H58" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>3.011</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>2.881</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>1224700</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H59" t="n">
+        <v>47.34</v>
+      </c>
+      <c r="I59" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>1214100</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>52.36</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>1187200</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H61" t="n">
+        <v>90.12</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>3.153</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>2.672</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.0241</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>1173000</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H62" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>1.647</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>1.731</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5125</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PANTECH</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>1159700</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="H63" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="14" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0456</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MMCS</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>1118300</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H64" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>1004800</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H65" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>959000</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H66" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>-0.006500000000000001</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>936900</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H67" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>927200</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H68" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>913500</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H69" t="n">
+        <v>44.93</v>
+      </c>
+      <c r="I69" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>887800</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H70" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>839800</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H71" t="n">
+        <v>67.55</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="14" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>826400</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H72" t="n">
+        <v>72.51000000000001</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>812400</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H73" t="n">
+        <v>53.11</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>10.096</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="14" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>796300</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>1.633</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="14" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>782700</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H75" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="I75" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="14" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>755400</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H76" t="n">
+        <v>45.59</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>5.529</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="14" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>727900</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="n"/>
+      <c r="K77" s="9" t="n"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="14" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>710900</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H78" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>687600</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H79" t="n">
+        <v>56.13</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="14" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>650700</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H80" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>2.609</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>2.599</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>625800</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>1.215</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="14" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>614600</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H82" t="n">
+        <v>68.64</v>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>604600</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H83" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>1.269</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="14" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>TMK</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>560900</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H84" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>2.849</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>531500</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H85" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>4.492</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>4.452</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="14" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>524700</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H86" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>1.197</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M51"/>
+  <autoFilter ref="A1:M86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
+++ b/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$115</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.099</v>
+        <v>0.1089</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>7307100</v>
+        <v>8112500</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>65.28</v>
+        <v>65.62</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.866</v>
+        <v>0.867</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.667</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 65.28偏高但未超买，现价1.11远高于50日均线0.667，技术面信号可靠性较强。</t>
+          <t>SAR转多信号，RSI 65.62偏高但未超买，现价1.12远高于50日均线0.667，信号可靠性一般。</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         <v>-0.0588</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>48914800</v>
+        <v>49387900</v>
       </c>
       <c r="G3" s="12" t="n">
         <v>0.13</v>
@@ -670,10 +670,10 @@
         <v>-0.3333</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>26781200</v>
+        <v>26884700</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>35.15</v>
+        <v>35.29</v>
       </c>
       <c r="H4" t="n">
         <v>35.25</v>
@@ -709,19 +709,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.345</v>
+        <v>0.35</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>-0.0282</v>
+        <v>-0.0141</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>21557500</v>
+        <v>22161700</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H5" t="n">
-        <v>62.49</v>
+        <v>64.94</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -760,10 +760,10 @@
         <v>0.1154</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>19655800</v>
+        <v>21813400</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="H6" t="n">
         <v>43.05</v>
@@ -790,39 +790,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>0</v>
+        <v>0.7</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-0.0141</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>12987300</v>
+        <v>14208900</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>2.58</v>
+        <v>0.62</v>
       </c>
       <c r="H7" t="n">
-        <v>70.39</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.88</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.103</v>
+        <v>0.674</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,39 +835,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.12</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>12240100</v>
+        <v>14133400</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.53</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.66</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.674</v>
+        <v>0.103</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.581</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.28</v>
+        <v>0.275</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0185</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>10225300</v>
+        <v>10606400</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="H9" t="n">
-        <v>49.84</v>
+        <v>47.51</v>
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
@@ -925,39 +925,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>6420800</v>
+        <v>9731000</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.35</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>53.65</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.71</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.186</v>
+        <v>0.387</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.187</v>
+        <v>0.401</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.0182</v>
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>6135200</v>
+        <v>9264100</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="H11" t="n">
-        <v>48.33</v>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.67</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.283</v>
+        <v>0.441</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.279</v>
+        <v>0.343</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,36 +1015,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0.0217</v>
+        <v>6.95</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.0225</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>5995900</v>
+        <v>7810200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.32</v>
+        <v>0.48</v>
       </c>
       <c r="H12" t="n">
-        <v>57.33</v>
+        <v>26.6</v>
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
+      <c r="J12" s="9" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>7.584</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
     </row>
@@ -1056,28 +1060,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5048700</v>
+        <v>7060200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.43</v>
+        <v>0.61</v>
       </c>
       <c r="H13" t="n">
-        <v>30.77</v>
+        <v>48.33</v>
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
@@ -1085,10 +1089,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.057</v>
+        <v>0.283</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.068</v>
+        <v>0.279</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1101,33 +1105,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>0.025</v>
+        <v>0.185</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>4388100</v>
+        <v>6470800</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
+        <v>0.36</v>
+      </c>
+      <c r="H14" t="n">
+        <v>49.13</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.187</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
     </row>
@@ -1139,39 +1150,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>0.0476</v>
+        <v>0.82</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>4299200</v>
+        <v>6467300</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="H15" t="n">
-        <v>36.82</v>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.1</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.125</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.144</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1184,40 +1195,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>0.0133</v>
+        <v>0.23</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>4279000</v>
+        <v>6346900</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.62</v>
+        <v>0.33</v>
       </c>
       <c r="H16" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>0.37</v>
-      </c>
+        <v>54.46</v>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
     </row>
@@ -1229,39 +1236,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>4156500</v>
+        <v>6067500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>1.17</v>
+        <v>0.88</v>
       </c>
       <c r="H17" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.8</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.295</v>
+        <v>0.374</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.295</v>
+        <v>0.37</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1274,39 +1281,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.215</v>
+        <v>0.045</v>
       </c>
       <c r="E18" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>4106300</v>
+        <v>6058700</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0.51</v>
       </c>
       <c r="H18" t="n">
-        <v>85.94</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.77</v>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.145</v>
+        <v>0.057</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.122</v>
+        <v>0.068</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1319,28 +1326,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="E19" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>3717000</v>
+        <v>5028900</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="H19" t="n">
-        <v>63.86</v>
+        <v>39.44</v>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
@@ -1348,10 +1355,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.446</v>
+        <v>0.306</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.398</v>
+        <v>0.304</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1364,28 +1371,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>-0.0061</v>
+        <v>0.775</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>3409300</v>
+        <v>4766500</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="H20" t="n">
-        <v>53.1</v>
+        <v>50.93</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1393,10 +1400,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.774</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.775</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1424,10 +1431,10 @@
         <v>-0.009000000000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>3370300</v>
+        <v>4567700</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="H21" t="n">
         <v>64.05</v>
@@ -1454,40 +1461,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.38</v>
+        <v>0.205</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>0.0133</v>
+        <v>0.025</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>3091500</v>
+        <v>4434300</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H22" t="n">
-        <v>36.71</v>
+        <v>0.17</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J22" s="9" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>0.401</v>
-      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1499,39 +1499,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
+        <v>0.11</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>3056500</v>
+        <v>4324300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H23" t="n">
-        <v>37.77</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.82</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.153</v>
+        <v>0.125</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.172</v>
+        <v>0.144</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1544,28 +1544,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.775</v>
+        <v>0.215</v>
       </c>
       <c r="E24" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2860300</v>
+        <v>4168800</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.18</v>
+        <v>0.52</v>
       </c>
       <c r="H24" t="n">
-        <v>50.93</v>
+        <v>85.94</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.774</v>
+        <v>0.145</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.775</v>
+        <v>0.122</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1589,39 +1589,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0.0325</v>
+        <v>0.295</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>2772300</v>
+        <v>4156500</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.53</v>
+        <v>1.17</v>
       </c>
       <c r="H25" t="n">
-        <v>60.38</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.587</v>
+        <v>0.295</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.498</v>
+        <v>0.295</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1634,39 +1634,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.495</v>
+        <v>0.475</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>-0.01</v>
+        <v>-0.0104</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>2601600</v>
+        <v>4056700</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H26" t="n">
-        <v>72.61</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.06</v>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.441</v>
+        <v>0.446</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.343</v>
+        <v>0.398</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1679,39 +1679,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>-0.0222</v>
+        <v>4.75</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>2449500</v>
+        <v>3874000</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>2.27</v>
+        <v>0.18</v>
       </c>
       <c r="H27" t="n">
-        <v>45.54</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.86</v>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.223</v>
+        <v>4.731</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.23</v>
+        <v>4.795</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1724,28 +1724,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>4.78</v>
+        <v>0.865</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>0.0149</v>
+        <v>0.0058</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>2403900</v>
+        <v>3634200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="H28" t="n">
-        <v>53.52</v>
+        <v>47.34</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>4.734</v>
+        <v>0.867</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>4.795</v>
+        <v>0.868</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1769,39 +1769,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>-0.015</v>
+        <v>2.18</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0.014</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>2296000</v>
+        <v>3389800</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H29" t="n">
-        <v>41.22</v>
-      </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.97</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>2.712</v>
+        <v>2.111</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>2.749</v>
+        <v>2.225</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1814,28 +1814,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>1.52</v>
+        <v>0.635</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>0.0066</v>
+        <v>0.0325</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>2212300</v>
+        <v>3313100</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.15</v>
+        <v>0.64</v>
       </c>
       <c r="H30" t="n">
-        <v>40.65</v>
+        <v>60.38</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>1.556</v>
+        <v>0.587</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1.822</v>
+        <v>0.498</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1859,28 +1859,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>0</v>
+        <v>4.97</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2171500</v>
+        <v>3296100</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.12</v>
+        <v>0.16</v>
       </c>
       <c r="H31" t="n">
-        <v>50.78</v>
+        <v>56.08</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.904</v>
+        <v>4.898</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.898</v>
+        <v>4.794</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1904,39 +1904,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.44</v>
+        <v>0.155</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>-0.0112</v>
+        <v>-0.0313</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2145000</v>
+        <v>3214600</v>
       </c>
       <c r="G32" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H32" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="K32" s="9" t="n">
         <v>0.15</v>
-      </c>
-      <c r="H32" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>0.585</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1949,28 +1949,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.145</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>2058400</v>
+        <v>3103200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="H33" t="n">
-        <v>53.36</v>
+        <v>32.87</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>2.109</v>
+        <v>0.152</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>2.225</v>
+        <v>0.172</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1994,28 +1994,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>0</v>
+        <v>0.965</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>2028400</v>
+        <v>3078300</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.47</v>
+        <v>0.04</v>
       </c>
       <c r="H34" t="n">
-        <v>79.91</v>
+        <v>69.03</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.471</v>
+        <v>0.888</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.441</v>
+        <v>0.782</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2039,28 +2039,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>FPI</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>-0.006</v>
+        <v>1.17</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>0.0174</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2002700</v>
+        <v>2981200</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.1</v>
+        <v>7.08</v>
       </c>
       <c r="H35" t="n">
-        <v>56.08</v>
+        <v>66.55</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>4.898</v>
+        <v>1.097</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>4.794</v>
+        <v>1.099</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2084,28 +2084,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.965</v>
+        <v>0.525</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>-0.0052</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>1999500</v>
+        <v>2881300</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.03</v>
+        <v>0.66</v>
       </c>
       <c r="H36" t="n">
-        <v>69.03</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.888</v>
+        <v>0.471</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.782</v>
+        <v>0.441</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2129,39 +2129,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>0</v>
+        <v>2.64</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>1900400</v>
+        <v>2701800</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="H37" t="n">
-        <v>62.72</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42</v>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.61</v>
+        <v>2.713</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.587</v>
+        <v>2.749</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2174,28 +2174,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>-0.0222</v>
+        <v>0.665</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1899800</v>
+        <v>2582900</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.05</v>
+        <v>0.58</v>
       </c>
       <c r="H38" t="n">
-        <v>44.81</v>
+        <v>62.72</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.452</v>
+        <v>0.61</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.471</v>
+        <v>0.587</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2219,28 +2219,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>-0.0083</v>
+        <v>1.51</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1805000</v>
+        <v>2553000</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H39" t="n">
-        <v>55.64</v>
+        <v>39.52</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.575</v>
+        <v>1.556</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.552</v>
+        <v>1.822</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2264,39 +2264,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>7.09</v>
+        <v>0.44</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>-0.0028</v>
+        <v>-0.0112</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1802500</v>
+        <v>2539700</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="H40" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>32.84</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>7.293</v>
+        <v>0.469</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>7.587</v>
+        <v>0.585</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2309,28 +2309,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1792800</v>
+        <v>2449500</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.25</v>
+        <v>2.27</v>
       </c>
       <c r="H41" t="n">
-        <v>53.62</v>
+        <v>45.54</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.431</v>
+        <v>0.223</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.416</v>
+        <v>0.23</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2354,39 +2354,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>-0.0244</v>
+        <v>0.905</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1779100</v>
+        <v>2444300</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.89</v>
+        <v>1.26</v>
       </c>
       <c r="H42" t="n">
-        <v>34.27</v>
-      </c>
-      <c r="I42" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.78</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.434</v>
+        <v>0.904</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.452</v>
+        <v>0.898</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2399,28 +2399,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>0.0164</v>
+        <v>0.445</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1740600</v>
+        <v>2352000</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="H43" t="n">
-        <v>40.02</v>
+        <v>46.14</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.277</v>
+        <v>0.453</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1.469</v>
+        <v>0.471</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2444,28 +2444,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1.15</v>
+        <v>2.59</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>-0.0086</v>
+        <v>-0.0077</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1659700</v>
+        <v>2321800</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="H44" t="n">
-        <v>35.03</v>
+        <v>49.9</v>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>1.191</v>
+        <v>2.594</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1.272</v>
+        <v>2.57</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2489,28 +2489,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>0</v>
+        <v>1.24</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>1608100</v>
+        <v>2299000</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1.89</v>
+        <v>0.29</v>
       </c>
       <c r="H45" t="n">
-        <v>70.63</v>
+        <v>40.02</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.335</v>
+        <v>1.277</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.319</v>
+        <v>1.469</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2534,39 +2534,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FPI</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.21</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>1594700</v>
+        <v>2242100</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>3.79</v>
+        <v>0.23</v>
       </c>
       <c r="H46" t="n">
-        <v>65.13</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.42</v>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.096</v>
+        <v>0.22</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>1.099</v>
+        <v>0.26</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2579,39 +2579,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>0.0357</v>
+        <v>1.16</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1510100</v>
+        <v>2240900</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="H47" t="n">
-        <v>38.02</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.73</v>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.308</v>
+        <v>1.192</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.352</v>
+        <v>1.272</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2624,39 +2624,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1495600</v>
+        <v>2166300</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H48" t="n">
-        <v>39.44</v>
-      </c>
-      <c r="I48" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.49</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.306</v>
+        <v>0.575</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.304</v>
+        <v>0.552</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2669,39 +2669,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>0.001</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1481300</v>
+        <v>2101100</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H49" t="n">
-        <v>43.12</v>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.87</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.988</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.993</v>
+        <v>10.094</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2714,28 +2714,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>0.0125</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1452300</v>
+        <v>2043900</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="H50" t="n">
-        <v>66.40000000000001</v>
+        <v>52.36</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.629</v>
+        <v>0.402</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.62</v>
+        <v>0.385</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2759,39 +2759,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>2.61</v>
+        <v>0.645</v>
       </c>
       <c r="E51" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1423400</v>
+        <v>2035800</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="H51" t="n">
-        <v>51.27</v>
-      </c>
-      <c r="I51" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.40000000000001</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>2.596</v>
+        <v>0.629</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2.571</v>
+        <v>0.62</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0.0152</v>
+        <v>0.44</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1405000</v>
+        <v>1947500</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="H52" t="n">
-        <v>49.94</v>
-      </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.62</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.335</v>
+        <v>0.431</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.339</v>
+        <v>0.416</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2849,28 +2849,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>-0.04650000000000001</v>
+        <v>0.285</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1390900</v>
+        <v>1922600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="H53" t="n">
-        <v>49.86</v>
+        <v>35.46</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>1.254</v>
+        <v>0.308</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>1.136</v>
+        <v>0.352</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2894,39 +2894,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.78</v>
+        <v>0.345</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>-0.0064</v>
+        <v>-0.0143</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1368700</v>
+        <v>1889700</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.19</v>
+        <v>2.22</v>
       </c>
       <c r="H54" t="n">
-        <v>53.12</v>
-      </c>
-      <c r="I54" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.06999999999999</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.771</v>
+        <v>0.334</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.771</v>
+        <v>0.319</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2939,28 +2939,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.215</v>
+        <v>0.78</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>-0.0227</v>
+        <v>-0.0064</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1351300</v>
+        <v>1858500</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H55" t="n">
-        <v>40.78</v>
+        <v>53.12</v>
       </c>
       <c r="I55" s="15" t="inlineStr">
         <is>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.221</v>
+        <v>0.771</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.26</v>
+        <v>0.771</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2984,28 +2984,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TDM</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>0.0513</v>
+        <v>1.27</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1320300</v>
+        <v>1828700</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>3.63</v>
+        <v>0.54</v>
       </c>
       <c r="H56" t="n">
-        <v>52.51</v>
+        <v>53.45</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.201</v>
+        <v>1.258</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.214</v>
+        <v>1.137</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3029,28 +3029,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>0.0161</v>
+        <v>0.835</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1271100</v>
+        <v>1820000</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1.56</v>
+        <v>0.37</v>
       </c>
       <c r="H57" t="n">
-        <v>61.06</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.295</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.293</v>
+        <v>0.783</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3074,39 +3074,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>0.0066</v>
+        <v>0.4</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1237500</v>
+        <v>1811400</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.38</v>
+        <v>0.91</v>
       </c>
       <c r="H58" t="n">
-        <v>51.88</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.27</v>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>3.011</v>
+        <v>0.434</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>2.881</v>
+        <v>0.452</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3119,39 +3119,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.865</v>
+        <v>3.48</v>
       </c>
       <c r="E59" s="16" t="n">
-        <v>0.0058</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1224700</v>
+        <v>1790500</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.06</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="I59" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>90.12</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.867</v>
+        <v>3.153</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.868</v>
+        <v>2.672</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3164,39 +3164,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>0.0125</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1214100</v>
+        <v>1679700</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="H60" t="n">
-        <v>52.36</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.54</v>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.402</v>
+        <v>0.987</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.385</v>
+        <v>0.993</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3209,28 +3209,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="E61" s="16" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.375</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1187200</v>
+        <v>1664700</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.37</v>
+        <v>1.37</v>
       </c>
       <c r="H61" t="n">
-        <v>90.12</v>
+        <v>66.98</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>3.153</v>
+        <v>0.346</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>2.672</v>
+        <v>0.355</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3254,28 +3254,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>PANTECH</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>-0.0241</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>0.0299</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1173000</v>
+        <v>1552500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.18</v>
+        <v>5.52</v>
       </c>
       <c r="H62" t="n">
-        <v>45.12</v>
+        <v>68.31</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.647</v>
+        <v>0.663</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1.731</v>
+        <v>0.662</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3299,28 +3299,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PANTECH</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E63" s="16" t="n">
-        <v>0.0149</v>
+        <v>3.01</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1159700</v>
+        <v>1533600</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>4.13</v>
+        <v>0.47</v>
       </c>
       <c r="H63" t="n">
-        <v>63.93</v>
+        <v>51.04</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.662</v>
+        <v>3.009</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.661</v>
+        <v>2.88</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3344,28 +3344,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.38</v>
+        <v>1.29</v>
       </c>
       <c r="E64" s="16" t="n">
-        <v>0.0133</v>
+        <v>0.0157</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1118300</v>
+        <v>1533400</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.92</v>
+        <v>0.49</v>
       </c>
       <c r="H64" t="n">
-        <v>68.75</v>
+        <v>56.73</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.346</v>
+        <v>1.269</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.355</v>
+        <v>1.27</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3389,39 +3389,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>-0.0053</v>
+        <v>0.33</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1004800</v>
+        <v>1527300</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="H65" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.02</v>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.944</v>
+        <v>0.335</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.9</v>
+        <v>0.339</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3434,28 +3434,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.63</v>
+        <v>0.305</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>-0.0156</v>
+        <v>-0.0161</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>959000</v>
+        <v>1486000</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.44</v>
+        <v>1.83</v>
       </c>
       <c r="H66" t="n">
-        <v>45.12</v>
+        <v>56.04</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.64</v>
+        <v>0.294</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.631</v>
+        <v>0.293</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3479,28 +3479,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>-0.006500000000000001</v>
+        <v>1.69</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>0.0242</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>936900</v>
+        <v>1477900</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H67" t="n">
-        <v>55.85</v>
+        <v>57.22</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.749</v>
+        <v>1.635</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.699</v>
+        <v>1.667</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3524,39 +3524,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E68" s="16" t="n">
-        <v>0.0198</v>
+        <v>0.335</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>-0.029</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>927200</v>
+        <v>1411700</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.24</v>
+        <v>0.92</v>
       </c>
       <c r="H68" t="n">
-        <v>41.44</v>
-      </c>
-      <c r="I68" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.81</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.523</v>
+        <v>0.32</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.554</v>
+        <v>0.33</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3569,39 +3569,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>0</v>
+        <v>1.63</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>-0.0181</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>913500</v>
+        <v>1401700</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="H69" t="n">
-        <v>44.93</v>
-      </c>
-      <c r="I69" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.02</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.726</v>
+        <v>1.648</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.724</v>
+        <v>1.731</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3614,28 +3614,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>0.0119</v>
+        <v>0.265</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>887800</v>
+        <v>1400000</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.33</v>
+        <v>1.32</v>
       </c>
       <c r="H70" t="n">
-        <v>42.56</v>
+        <v>34.28</v>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.861</v>
+        <v>0.274</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.918</v>
+        <v>0.283</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3659,28 +3659,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1.24</v>
+        <v>5.27</v>
       </c>
       <c r="E71" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>839800</v>
+        <v>1372300</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>0.08</v>
       </c>
       <c r="H71" t="n">
-        <v>67.55</v>
+        <v>45.91</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>1.13</v>
+        <v>5.351</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>1.071</v>
+        <v>5.53</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3704,39 +3704,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E72" s="17" t="n">
-        <v>0</v>
+        <v>0.455</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>826400</v>
+        <v>1350600</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H72" t="n">
-        <v>72.51000000000001</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.55</v>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.485</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.783</v>
+        <v>0.473</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3749,39 +3749,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.7</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>812400</v>
+        <v>1342900</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="H73" t="n">
-        <v>53.11</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.93</v>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>10</v>
+        <v>0.726</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>10.096</v>
+        <v>0.724</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3794,28 +3794,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>TDM</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.67</v>
+        <v>0.21</v>
       </c>
       <c r="E74" s="16" t="n">
-        <v>0.0121</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>796300</v>
+        <v>1320400</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.1</v>
+        <v>3.63</v>
       </c>
       <c r="H74" t="n">
-        <v>54.81</v>
+        <v>57.22</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.633</v>
+        <v>0.201</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.667</v>
+        <v>0.214</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3839,28 +3839,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>-0.0083</v>
+        <v>0.505</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>782700</v>
+        <v>1307100</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="H75" t="n">
-        <v>48.01</v>
+        <v>34.5</v>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
@@ -3868,10 +3868,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.605</v>
+        <v>0.522</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.618</v>
+        <v>0.554</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3884,28 +3884,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>-0.0019</v>
+        <v>1.25</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>755400</v>
+        <v>1250800</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="H76" t="n">
-        <v>45.59</v>
+        <v>68.38</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3913,10 +3913,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>5.35</v>
+        <v>1.131</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>5.529</v>
+        <v>1.071</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3929,33 +3929,40 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.715</v>
+        <v>0.31</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>-0.0138</v>
+        <v>-0.0462</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>727900</v>
+        <v>1206800</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I77" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J77" s="9" t="n"/>
-      <c r="K77" s="9" t="n"/>
+        <v>0.74</v>
+      </c>
+      <c r="H77" t="n">
+        <v>52.43</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>0.324</v>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
     </row>
@@ -3967,39 +3974,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E78" s="16" t="n">
-        <v>0.0244</v>
+        <v>0.595</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>710900</v>
+        <v>1158700</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="H78" t="n">
-        <v>47.38</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.18</v>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.27</v>
+        <v>0.605</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.318</v>
+        <v>0.618</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4012,28 +4019,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>0</v>
+        <v>2.09</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>687600</v>
+        <v>1148800</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="H79" t="n">
-        <v>56.13</v>
+        <v>47.17</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4041,10 +4048,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.904</v>
+        <v>2.105</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.953</v>
+        <v>2.115</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4057,39 +4064,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>-0.0037</v>
+        <v>0.855</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>650700</v>
+        <v>1143400</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.12</v>
+        <v>0.42</v>
       </c>
       <c r="H80" t="n">
-        <v>55.29</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.32</v>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>2.609</v>
+        <v>0.861</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>2.599</v>
+        <v>0.918</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4102,28 +4109,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>-0.0077</v>
+        <v>0.63</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>625800</v>
+        <v>1106900</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H81" t="n">
-        <v>59.53</v>
+        <v>69.45</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -4131,10 +4138,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.246</v>
+        <v>0.623</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.215</v>
+        <v>0.613</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4147,39 +4154,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.805</v>
+        <v>0.34</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>614600</v>
+        <v>1063400</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="H82" t="n">
-        <v>68.64</v>
-      </c>
-      <c r="I82" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.96</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.751</v>
+        <v>0.337</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.68</v>
+        <v>0.343</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4192,28 +4199,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.29</v>
+        <v>6.95</v>
       </c>
       <c r="E83" s="16" t="n">
-        <v>0.0157</v>
+        <v>0.0131</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>604600</v>
+        <v>1062300</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="H83" t="n">
-        <v>56.73</v>
+        <v>44.89</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4221,10 +4228,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.269</v>
+        <v>6.998</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.27</v>
+        <v>7.437</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4237,28 +4244,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>0.0168</v>
+        <v>0.465</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>-0.0312</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>560900</v>
+        <v>1054600</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
       <c r="H84" t="n">
-        <v>63.38</v>
+        <v>54</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -4266,10 +4273,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>2.849</v>
+        <v>0.457</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>2.855</v>
+        <v>0.449</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4282,28 +4289,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>4.7</v>
+        <v>3.94</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>-0.0042</v>
+        <v>-0.0125</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>531500</v>
+        <v>1044100</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="H85" t="n">
-        <v>59.69</v>
+        <v>56.72</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4311,10 +4318,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>4.492</v>
+        <v>3.851</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>4.452</v>
+        <v>3.379</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4327,45 +4334,1343 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>524700</v>
+        <v>1024200</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="H86" t="n">
-        <v>58.56</v>
-      </c>
-      <c r="I86" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.71</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>1.289</v>
+        <v>0.944</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.197</v>
+        <v>0.9</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H87" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>2.611</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>2.599</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="14" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>959000</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H88" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="14" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>956400</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H89" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="I89" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>1.409</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>1.447</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="14" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>-0.006500000000000001</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>944400</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H90" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>-0.0207</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>911700</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I91" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n"/>
+      <c r="K91" s="9" t="n"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="14" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>-0.0231</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>870300</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H92" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>1.244</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>1.214</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>864900</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H93" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>7.411</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>7.755</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="14" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>829700</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H94" t="n">
+        <v>50</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>6.338</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>6.588</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>797100</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H95" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="14" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>791500</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H96" t="n">
+        <v>59.68</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>6.446</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>6.068</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="14" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>774000</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H97" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="14" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>770000</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H98" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>4.492</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>4.452</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>699400</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H99" t="n">
+        <v>60.37</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>4.043</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>3.707</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>-0.0308</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>697000</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H100" t="n">
+        <v>39.32</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>-0.0286</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>696800</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H101" t="n">
+        <v>55.24</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>1.311</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="14" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>695200</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H102" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="I102" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>1.197</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>659800</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H103" t="n">
+        <v>68.64</v>
+      </c>
+      <c r="I103" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CLOUDPT</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>658600</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H104" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>IHH</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>649700</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H105" t="n">
+        <v>45.92</v>
+      </c>
+      <c r="I105" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>7.892</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>7.914</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>-0.0263</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>635600</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H106" t="n">
+        <v>50.52</v>
+      </c>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>TMK</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>597900</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H107" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>2.849</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>565200</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H108" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>559300</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H109" t="n">
+        <v>57.26</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>552800</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H110" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="I110" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>548300</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H111" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>5.814</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>6.046</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E112" s="16" t="n">
+        <v>0.004099999999999999</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>541200</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H112" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="I112" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>2.431</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>4863</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>521600</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H113" t="n">
+        <v>59.38</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>7.872</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>7.867</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>520200</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H114" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>3.849</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>3.776</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>510900</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H115" t="n">
+        <v>68.29000000000001</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M86"/>
+  <autoFilter ref="A1:M115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
+++ b/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M115"/>
+  <dimension ref="A1:M139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -557,95 +557,103 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>4213100</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>60.96</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 60.96未超买，现价高于50日均线约28.5%，技术面信号可靠性较高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>0455</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>BUSCAP</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.1089</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>8112500</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>65.62</v>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="D3" s="3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.1485</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>9468100</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>66.91</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>🎯 SAR 转多</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>SAR转多信号，RSI 65.62偏高但未超买，现价1.12远高于50日均线0.667，信号可靠性一般。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>-0.0588</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>49387900</v>
-      </c>
-      <c r="G3" s="12" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H3" t="n">
-        <v>36.06</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 66.91接近超买区，现价1.16远高于50日均线0.668，技术面偏强。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -655,39 +663,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0170</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KANGER</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>-0.3333</v>
+        <v>-0.0588</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>26884700</v>
+        <v>56279200</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>35.29</v>
+        <v>0.15</v>
       </c>
       <c r="H4" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.06</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.019</v>
+        <v>0.095</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.023</v>
+        <v>0.223</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -700,39 +708,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0170</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>KANGER</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>-0.0141</v>
+        <v>-0.3333</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>22161700</v>
+        <v>27002700</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.28</v>
+        <v>35.44</v>
       </c>
       <c r="H5" t="n">
-        <v>64.94</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.25</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.325</v>
+        <v>0.019</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.273</v>
+        <v>0.023</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -754,19 +762,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.435</v>
+        <v>0.425</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.1154</v>
+        <v>0.0897</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>21813400</v>
+        <v>23978900</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="H6" t="n">
-        <v>43.05</v>
+        <v>41.34</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -774,7 +782,7 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0.5679999999999999</v>
@@ -790,39 +798,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>-0.0141</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>14208900</v>
+        <v>23281300</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.62</v>
+        <v>0.29</v>
       </c>
       <c r="H7" t="n">
-        <v>64.88</v>
-      </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.94</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.674</v>
+        <v>0.325</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.581</v>
+        <v>0.273</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,39 +843,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0.0435</v>
+        <v>0.04</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>-0.1111</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>14133400</v>
+        <v>18783300</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="H8" t="n">
-        <v>73.66</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.36</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.103</v>
+        <v>0.056</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,28 +888,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.0185</v>
+        <v>0.695</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>-0.0211</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>10606400</v>
+        <v>16305800</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.67</v>
+        <v>0.71</v>
       </c>
       <c r="H9" t="n">
-        <v>47.51</v>
+        <v>62.97</v>
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
@@ -909,10 +917,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.279</v>
+        <v>0.673</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.282</v>
+        <v>0.581</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,39 +933,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>0.0133</v>
+        <v>0.0435</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>9731000</v>
+        <v>14362300</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.85</v>
       </c>
       <c r="H10" t="n">
-        <v>36.71</v>
-      </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.66</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.387</v>
+        <v>0.103</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.401</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -985,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>9264100</v>
+        <v>11479600</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="H11" t="n">
         <v>74.67</v>
@@ -1015,28 +1023,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.0225</v>
+        <v>0.275</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>7810200</v>
+        <v>11203400</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.48</v>
+        <v>1.76</v>
       </c>
       <c r="H12" t="n">
-        <v>26.6</v>
+        <v>47.51</v>
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
@@ -1044,10 +1052,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>7.28</v>
+        <v>0.279</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>7.584</v>
+        <v>0.282</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,28 +1068,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0.0182</v>
+        <v>6.91</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>-0.0281</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>7060200</v>
+        <v>11174200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="H13" t="n">
-        <v>48.33</v>
+        <v>25.49</v>
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
@@ -1089,10 +1097,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.283</v>
+        <v>7.276</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.279</v>
+        <v>7.583</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,28 +1113,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.185</v>
+        <v>0.96</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.0263</v>
+        <v>-0.0103</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>6470800</v>
+        <v>10872700</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.36</v>
+        <v>0.14</v>
       </c>
       <c r="H14" t="n">
-        <v>49.13</v>
+        <v>67.83</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -1134,10 +1142,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.185</v>
+        <v>0.887</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.187</v>
+        <v>0.782</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,39 +1158,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>-0.0061</v>
+        <v>0.38</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>6467300</v>
+        <v>9767500</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.41</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.71</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.387</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.401</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1195,36 +1203,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0</v>
+        <v>0.82</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>6346900</v>
+        <v>9215300</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.33</v>
+        <v>0.58</v>
       </c>
       <c r="H16" t="n">
-        <v>54.46</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
+        <v>53.1</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
     </row>
@@ -1236,39 +1248,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0.0133</v>
+        <v>0.465</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>-0.0312</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6067500</v>
+        <v>7681000</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.88</v>
+        <v>0.36</v>
       </c>
       <c r="H17" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.75</v>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.374</v>
+        <v>0.445</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.37</v>
+        <v>0.398</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1281,28 +1293,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.045</v>
+        <v>0.275</v>
       </c>
       <c r="E18" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>6058700</v>
+        <v>7553900</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.51</v>
+        <v>0.66</v>
       </c>
       <c r="H18" t="n">
-        <v>30.77</v>
+        <v>46</v>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
@@ -1310,10 +1322,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.057</v>
+        <v>0.283</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.068</v>
+        <v>0.279</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1326,39 +1338,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="E19" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5028900</v>
+        <v>7382600</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.26</v>
+        <v>0.58</v>
       </c>
       <c r="H19" t="n">
-        <v>39.44</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.77</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.306</v>
+        <v>0.153</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.304</v>
+        <v>0.172</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1371,39 +1383,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.775</v>
+        <v>0.3</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>4766500</v>
+        <v>6882500</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="H20" t="n">
-        <v>50.93</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.44</v>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.774</v>
+        <v>0.306</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.775</v>
+        <v>0.304</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1416,28 +1428,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.19</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>4567700</v>
+        <v>6550900</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.16</v>
+        <v>0.36</v>
       </c>
       <c r="H21" t="n">
-        <v>64.05</v>
+        <v>53.65</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1445,10 +1457,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>2.03</v>
+        <v>0.186</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.837</v>
+        <v>0.187</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1461,25 +1473,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>0.025</v>
+        <v>0.23</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>4434300</v>
+        <v>6518900</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
+      </c>
+      <c r="H22" t="n">
+        <v>54.46</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -1499,28 +1514,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.11</v>
+        <v>0.865</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.0476</v>
+        <v>0.0058</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>4324300</v>
+        <v>6244500</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="H23" t="n">
-        <v>36.82</v>
+        <v>47.34</v>
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
@@ -1528,10 +1543,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.125</v>
+        <v>0.867</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.144</v>
+        <v>0.868</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1544,28 +1559,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>4168800</v>
+        <v>6227500</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.52</v>
+        <v>0.9</v>
       </c>
       <c r="H24" t="n">
-        <v>85.94</v>
+        <v>58.8</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1573,10 +1588,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.145</v>
+        <v>0.374</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.122</v>
+        <v>0.37</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1589,39 +1604,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.295</v>
+        <v>0.215</v>
       </c>
       <c r="E25" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4156500</v>
+        <v>5771300</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.17</v>
+        <v>0.72</v>
       </c>
       <c r="H25" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.94</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.295</v>
+        <v>0.145</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.295</v>
+        <v>0.122</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1634,39 +1649,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>-0.0104</v>
+        <v>0.775</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4056700</v>
+        <v>5599300</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.19</v>
+        <v>0.36</v>
       </c>
       <c r="H26" t="n">
-        <v>62.06</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.93</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.446</v>
+        <v>0.774</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.398</v>
+        <v>0.775</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1679,40 +1694,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>4.75</v>
+        <v>0.205</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.025</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>3874000</v>
+        <v>5152400</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H27" t="n">
-        <v>50.86</v>
+        <v>0.2</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J27" s="9" t="n">
-        <v>4.731</v>
-      </c>
-      <c r="K27" s="9" t="n">
-        <v>4.795</v>
-      </c>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
     </row>
@@ -1724,39 +1732,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>0.0058</v>
+        <v>2.22</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3634200</v>
+        <v>5050900</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H28" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.62</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.867</v>
+        <v>2.032</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.868</v>
+        <v>1.837</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1769,28 +1777,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>0.014</v>
+        <v>0.53</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>3389800</v>
+        <v>4895200</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.27</v>
+        <v>1.13</v>
       </c>
       <c r="H29" t="n">
-        <v>54.97</v>
+        <v>79.91</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1798,10 +1806,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>2.111</v>
+        <v>0.471</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>2.225</v>
+        <v>0.441</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1814,28 +1822,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.635</v>
+        <v>2.17</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>0.0325</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3313100</v>
+        <v>4597900</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.64</v>
+        <v>0.37</v>
       </c>
       <c r="H30" t="n">
-        <v>60.38</v>
+        <v>54.18</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1843,10 +1851,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.587</v>
+        <v>2.11</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.498</v>
+        <v>2.225</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1859,36 +1867,36 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>-0.006</v>
+        <v>4.73</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>0.0042</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3296100</v>
+        <v>4452100</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="H31" t="n">
-        <v>56.08</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.91</v>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>4.898</v>
+        <v>4.729</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>4.794</v>
@@ -1904,39 +1912,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>-0.0313</v>
+        <v>0.11</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3214600</v>
+        <v>4444300</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="H32" t="n">
-        <v>48.93</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.82</v>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.159</v>
+        <v>0.125</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.15</v>
+        <v>0.144</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1949,39 +1957,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>-0.0333</v>
+        <v>0.295</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3103200</v>
+        <v>4156500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.24</v>
+        <v>1.17</v>
       </c>
       <c r="H33" t="n">
-        <v>32.87</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.152</v>
+        <v>0.295</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.172</v>
+        <v>0.295</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1994,28 +2002,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.965</v>
+        <v>0.43</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>-0.0052</v>
+        <v>-0.0337</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3078300</v>
+        <v>3903300</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.04</v>
+        <v>0.27</v>
       </c>
       <c r="H34" t="n">
-        <v>69.03</v>
+        <v>31.06</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2023,10 +2031,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.888</v>
+        <v>0.468</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.782</v>
+        <v>0.585</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2048,19 +2056,19 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>0.0174</v>
+        <v>0.0261</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2981200</v>
+        <v>3813100</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>7.08</v>
+        <v>9.06</v>
       </c>
       <c r="H35" t="n">
-        <v>66.55</v>
+        <v>67.86</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2068,7 +2076,7 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>1.097</v>
+        <v>1.098</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>1.099</v>
@@ -2084,28 +2092,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.525</v>
+        <v>0.475</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0104</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>2881300</v>
+        <v>3514800</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.66</v>
+        <v>1.33</v>
       </c>
       <c r="H36" t="n">
-        <v>76.73999999999999</v>
+        <v>58.14</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2113,10 +2121,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.471</v>
+        <v>0.458</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.441</v>
+        <v>0.449</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2129,39 +2137,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.64</v>
+        <v>4.97</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>-0.0112</v>
+        <v>-0.006</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>2701800</v>
+        <v>3324700</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="H37" t="n">
-        <v>42</v>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.08</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2.713</v>
+        <v>4.898</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.749</v>
+        <v>4.794</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2174,28 +2182,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>0.025</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2582900</v>
+        <v>3316300</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.58</v>
+        <v>0.28</v>
       </c>
       <c r="H38" t="n">
-        <v>62.72</v>
+        <v>53.97</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2203,10 +2211,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.61</v>
+        <v>0.403</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.587</v>
+        <v>0.385</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2219,28 +2227,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>1.51</v>
+        <v>0.16</v>
       </c>
       <c r="E39" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2553000</v>
+        <v>3245500</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="H39" t="n">
-        <v>39.52</v>
+        <v>51.28</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2248,10 +2256,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>1.556</v>
+        <v>0.159</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>1.822</v>
+        <v>0.15</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2264,28 +2272,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>-0.0112</v>
+        <v>1.51</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2539700</v>
+        <v>3097500</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H40" t="n">
-        <v>32.84</v>
+        <v>39.52</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2293,10 +2301,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.469</v>
+        <v>1.556</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.585</v>
+        <v>1.822</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2309,39 +2317,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.22</v>
+        <v>2.64</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>-0.0222</v>
+        <v>-0.0112</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>2449500</v>
+        <v>3059700</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>2.27</v>
+        <v>0.31</v>
       </c>
       <c r="H41" t="n">
-        <v>45.54</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42</v>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.223</v>
+        <v>2.713</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.23</v>
+        <v>2.749</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2354,28 +2362,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0.001</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2444300</v>
+        <v>2938900</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1.26</v>
+        <v>0.25</v>
       </c>
       <c r="H42" t="n">
-        <v>50.78</v>
+        <v>48.87</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2383,10 +2391,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.904</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.898</v>
+        <v>10.094</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2399,28 +2407,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.445</v>
+        <v>0.66</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>-0.0111</v>
+        <v>-0.0075</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2352000</v>
+        <v>2846400</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.06</v>
+        <v>0.64</v>
       </c>
       <c r="H43" t="n">
-        <v>46.14</v>
+        <v>61.52</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2428,10 +2436,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.453</v>
+        <v>0.609</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.471</v>
+        <v>0.587</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2444,39 +2452,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>-0.0077</v>
+        <v>1.22</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2321800</v>
+        <v>2807700</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="H44" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="I44" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.11</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>2.594</v>
+        <v>1.275</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>2.57</v>
+        <v>1.469</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2489,39 +2497,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>0.0164</v>
+        <v>1.14</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2299000</v>
+        <v>2757700</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="H45" t="n">
-        <v>40.02</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.47</v>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>1.277</v>
+        <v>1.19</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1.469</v>
+        <v>1.271</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2534,28 +2542,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.21</v>
+        <v>2.59</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>-0.0455</v>
+        <v>-0.0077</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2242100</v>
+        <v>2690800</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="H46" t="n">
-        <v>38.42</v>
+        <v>49.9</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
@@ -2563,10 +2571,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.22</v>
+        <v>2.594</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.26</v>
+        <v>2.57</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2579,39 +2587,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1.16</v>
+        <v>0.645</v>
       </c>
       <c r="E47" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2240900</v>
+        <v>2536700</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H47" t="n">
-        <v>36.73</v>
-      </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.40000000000001</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>1.192</v>
+        <v>0.629</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>1.272</v>
+        <v>0.62</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2624,28 +2632,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>-0.0167</v>
+        <v>0.905</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2166300</v>
+        <v>2474100</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.11</v>
+        <v>1.28</v>
       </c>
       <c r="H48" t="n">
-        <v>54.49</v>
+        <v>50.78</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2653,10 +2661,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.575</v>
+        <v>0.904</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.552</v>
+        <v>0.898</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2669,28 +2677,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>0.001</v>
+        <v>0.22</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2101100</v>
+        <v>2454500</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.18</v>
+        <v>2.27</v>
       </c>
       <c r="H49" t="n">
-        <v>48.87</v>
+        <v>45.54</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2698,10 +2706,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>9.994999999999999</v>
+        <v>0.223</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>10.094</v>
+        <v>0.23</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2714,28 +2722,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>0.0125</v>
+        <v>0.595</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2043900</v>
+        <v>2448200</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="H50" t="n">
-        <v>52.36</v>
+        <v>55.64</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2743,10 +2751,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.402</v>
+        <v>0.575</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.385</v>
+        <v>0.552</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2759,28 +2767,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>0</v>
+        <v>0.445</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2035800</v>
+        <v>2362000</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>66.40000000000001</v>
+        <v>46.14</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -2788,10 +2796,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.629</v>
+        <v>0.453</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.62</v>
+        <v>0.471</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2804,28 +2812,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.44</v>
+        <v>0.835</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1947500</v>
+        <v>2344800</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.27</v>
+        <v>0.48</v>
       </c>
       <c r="H52" t="n">
-        <v>53.62</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2833,10 +2841,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.431</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.416</v>
+        <v>0.783</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2849,39 +2857,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>0.0179</v>
+        <v>0.21</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1922600</v>
+        <v>2342800</v>
       </c>
       <c r="G53" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H53" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="I53" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K53" s="9" t="n">
         <v>0.26</v>
-      </c>
-      <c r="H53" t="n">
-        <v>35.46</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J53" s="9" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="K53" s="9" t="n">
-        <v>0.352</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2894,28 +2902,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>-0.0143</v>
+        <v>0.44</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1889700</v>
+        <v>2308400</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>2.22</v>
+        <v>0.33</v>
       </c>
       <c r="H54" t="n">
-        <v>64.06999999999999</v>
+        <v>53.62</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -2923,10 +2931,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.334</v>
+        <v>0.431</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.319</v>
+        <v>0.416</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2939,39 +2947,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.78</v>
+        <v>0.365</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>-0.0064</v>
+        <v>-0.0267</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1858500</v>
+        <v>2221500</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.26</v>
+        <v>1.82</v>
       </c>
       <c r="H55" t="n">
-        <v>53.12</v>
-      </c>
-      <c r="I55" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.14</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.771</v>
+        <v>0.345</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.771</v>
+        <v>0.355</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2984,39 +2992,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>-0.0155</v>
+        <v>0.95</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1828700</v>
+        <v>2117900</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.54</v>
+        <v>0.18</v>
       </c>
       <c r="H56" t="n">
-        <v>53.45</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.89</v>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>1.258</v>
+        <v>0.988</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.137</v>
+        <v>0.993</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3029,28 +3037,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.835</v>
+        <v>1.24</v>
       </c>
       <c r="E57" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1820000</v>
+        <v>2115000</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.37</v>
+        <v>0.2</v>
       </c>
       <c r="H57" t="n">
-        <v>72.51000000000001</v>
+        <v>67.55</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3058,10 +3066,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.8129999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.783</v>
+        <v>1.071</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3074,39 +3082,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>-0.0244</v>
+        <v>0.63</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1811400</v>
+        <v>2100300</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="H58" t="n">
-        <v>34.27</v>
-      </c>
-      <c r="I58" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.45</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.434</v>
+        <v>0.623</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.452</v>
+        <v>0.613</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3119,28 +3127,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>0.008699999999999999</v>
+        <v>1.28</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1790500</v>
+        <v>2054900</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H59" t="n">
-        <v>90.12</v>
+        <v>54.43</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3148,10 +3156,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>3.153</v>
+        <v>1.258</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>2.672</v>
+        <v>1.137</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3164,39 +3172,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>-0.0053</v>
+        <v>0.29</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1679700</v>
+        <v>2010500</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="H60" t="n">
-        <v>42.54</v>
-      </c>
-      <c r="I60" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.02</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.987</v>
+        <v>0.308</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.993</v>
+        <v>0.352</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3209,28 +3217,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>0</v>
+        <v>3.47</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1664700</v>
+        <v>2004000</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>1.37</v>
+        <v>0.62</v>
       </c>
       <c r="H61" t="n">
-        <v>66.98</v>
+        <v>89.95</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3238,10 +3246,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.346</v>
+        <v>3.152</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.355</v>
+        <v>2.672</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3254,39 +3262,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PANTECH</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>0.0299</v>
+        <v>0.22</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1552500</v>
+        <v>1900000</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>5.52</v>
+        <v>3.98</v>
       </c>
       <c r="H62" t="n">
-        <v>68.31</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.5</v>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.663</v>
+        <v>0.224</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.662</v>
+        <v>0.224</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3299,28 +3307,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3.01</v>
+        <v>0.35</v>
       </c>
       <c r="E63" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1533600</v>
+        <v>1890200</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.47</v>
+        <v>2.22</v>
       </c>
       <c r="H63" t="n">
-        <v>51.04</v>
+        <v>70.63</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3328,10 +3336,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>3.009</v>
+        <v>0.335</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>2.88</v>
+        <v>0.319</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3344,28 +3352,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>PANTECH</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1.29</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E64" s="16" t="n">
-        <v>0.0157</v>
+        <v>0.0224</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1533400</v>
+        <v>1888100</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.49</v>
+        <v>6.72</v>
       </c>
       <c r="H64" t="n">
-        <v>56.73</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3373,10 +3381,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1.269</v>
+        <v>0.662</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1.27</v>
+        <v>0.661</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3389,28 +3397,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>0</v>
+        <v>0.78</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1527300</v>
+        <v>1858500</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="H65" t="n">
-        <v>48.02</v>
+        <v>53.12</v>
       </c>
       <c r="I65" s="15" t="inlineStr">
         <is>
@@ -3418,10 +3426,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.335</v>
+        <v>0.771</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.339</v>
+        <v>0.771</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3434,28 +3442,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>-0.0161</v>
+        <v>1.3</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>0.0236</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1486000</v>
+        <v>1817900</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>1.83</v>
+        <v>0.58</v>
       </c>
       <c r="H66" t="n">
-        <v>56.04</v>
+        <v>59.11</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3463,10 +3471,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.294</v>
+        <v>1.27</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.293</v>
+        <v>1.27</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3479,39 +3487,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>0.0242</v>
+        <v>0.4</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1477900</v>
+        <v>1812500</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.18</v>
+        <v>0.91</v>
       </c>
       <c r="H67" t="n">
-        <v>57.22</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.27</v>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>1.635</v>
+        <v>0.434</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1.667</v>
+        <v>0.452</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3524,28 +3532,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>-0.029</v>
+        <v>2.67</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1411700</v>
+        <v>1760600</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.92</v>
+        <v>0.33</v>
       </c>
       <c r="H68" t="n">
-        <v>57.81</v>
+        <v>56.31</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3553,10 +3561,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.32</v>
+        <v>2.61</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.33</v>
+        <v>2.599</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3569,28 +3577,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.63</v>
+        <v>0.305</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>-0.0181</v>
+        <v>-0.0161</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1401700</v>
+        <v>1691200</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.22</v>
+        <v>2.08</v>
       </c>
       <c r="H69" t="n">
-        <v>46.02</v>
+        <v>56.04</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3598,10 +3606,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.648</v>
+        <v>0.294</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.731</v>
+        <v>0.293</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3614,39 +3622,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>-0.0185</v>
+        <v>5.29</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1400000</v>
+        <v>1600000</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1.32</v>
+        <v>0.1</v>
       </c>
       <c r="H70" t="n">
-        <v>34.28</v>
-      </c>
-      <c r="I70" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.65</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.274</v>
+        <v>5.353</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.283</v>
+        <v>5.53</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3659,28 +3667,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>-0.0033</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1372300</v>
+        <v>1582200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.08</v>
+        <v>0.49</v>
       </c>
       <c r="H71" t="n">
-        <v>45.91</v>
+        <v>50.6</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3688,10 +3696,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>5.351</v>
+        <v>3.008</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>5.53</v>
+        <v>2.88</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3704,28 +3712,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>-0.0215</v>
+        <v>0.33</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1350600</v>
+        <v>1552800</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H72" t="n">
-        <v>43.55</v>
+        <v>48.02</v>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
@@ -3733,10 +3741,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.485</v>
+        <v>0.335</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.473</v>
+        <v>0.339</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3749,28 +3757,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>0</v>
+        <v>0.85</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>0.0119</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1342900</v>
+        <v>1550700</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.13</v>
+        <v>0.57</v>
       </c>
       <c r="H73" t="n">
-        <v>44.93</v>
+        <v>42.56</v>
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
@@ -3778,10 +3786,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.726</v>
+        <v>0.861</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.724</v>
+        <v>0.918</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3794,25 +3802,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TDM</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.21</v>
+        <v>1.69</v>
       </c>
       <c r="E74" s="16" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.0242</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1320400</v>
+        <v>1541800</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>3.63</v>
+        <v>0.19</v>
       </c>
       <c r="H74" t="n">
         <v>57.22</v>
@@ -3823,10 +3831,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.201</v>
+        <v>1.635</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.214</v>
+        <v>1.667</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3839,39 +3847,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>0</v>
+        <v>2.09</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1307100</v>
+        <v>1524800</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="H75" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="I75" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.17</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.522</v>
+        <v>2.105</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.554</v>
+        <v>2.115</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3884,39 +3892,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.595</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1250800</v>
+        <v>1519300</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="H76" t="n">
-        <v>68.38</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.18</v>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>1.131</v>
+        <v>0.605</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1.071</v>
+        <v>0.618</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3929,39 +3937,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.31</v>
+        <v>0.46</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>-0.0462</v>
+        <v>-0.0108</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1206800</v>
+        <v>1508300</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.74</v>
+        <v>0.17</v>
       </c>
       <c r="H77" t="n">
-        <v>52.43</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.44</v>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.301</v>
+        <v>0.485</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.324</v>
+        <v>0.473</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3974,39 +3982,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>-0.0165</v>
+        <v>6.91</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>0.0073</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1158700</v>
+        <v>1485200</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H78" t="n">
-        <v>47.18</v>
-      </c>
-      <c r="I78" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.33</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.605</v>
+        <v>6.994</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.618</v>
+        <v>7.436</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4019,39 +4027,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>2.09</v>
+        <v>0.265</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>-0.0048</v>
+        <v>-0.0185</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1148800</v>
+        <v>1477000</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.12</v>
+        <v>1.39</v>
       </c>
       <c r="H79" t="n">
-        <v>47.17</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.28</v>
+      </c>
+      <c r="I79" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>2.105</v>
+        <v>0.274</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>2.115</v>
+        <v>0.283</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4064,39 +4072,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>0.0179</v>
+        <v>1.63</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.0181</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1143400</v>
+        <v>1467400</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="H80" t="n">
-        <v>44.32</v>
-      </c>
-      <c r="I80" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.02</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.861</v>
+        <v>1.648</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.918</v>
+        <v>1.731</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4109,28 +4117,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E81" s="17" t="n">
-        <v>0</v>
+        <v>0.335</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>-0.029</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1106900</v>
+        <v>1436700</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.3</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>69.45</v>
+        <v>57.81</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -4138,10 +4146,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.623</v>
+        <v>0.32</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.613</v>
+        <v>0.33</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4154,39 +4162,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1063400</v>
+        <v>1382900</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.32</v>
+        <v>0.13</v>
       </c>
       <c r="H82" t="n">
-        <v>52.96</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.93</v>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.337</v>
+        <v>0.726</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.343</v>
+        <v>0.724</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4199,39 +4207,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>0.0131</v>
+        <v>0.505</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1062300</v>
+        <v>1359700</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="H83" t="n">
-        <v>44.89</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.5</v>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>6.998</v>
+        <v>0.522</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>7.437</v>
+        <v>0.554</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4244,28 +4252,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>TDM</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>-0.0312</v>
+        <v>0.21</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1054600</v>
+        <v>1326100</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.4</v>
+        <v>3.65</v>
       </c>
       <c r="H84" t="n">
-        <v>54</v>
+        <v>57.22</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -4273,10 +4281,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.457</v>
+        <v>0.201</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.449</v>
+        <v>0.214</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4289,28 +4297,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>3.94</v>
+        <v>0.63</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>-0.0125</v>
+        <v>-0.0156</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1044100</v>
+        <v>1310600</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.16</v>
+        <v>0.6</v>
       </c>
       <c r="H85" t="n">
-        <v>56.72</v>
+        <v>45.12</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4318,10 +4326,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>3.851</v>
+        <v>0.64</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>3.379</v>
+        <v>0.631</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4334,28 +4342,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>-0.0105</v>
+        <v>2.11</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>0.0048</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1024200</v>
+        <v>1253200</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H86" t="n">
-        <v>51.71</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4363,10 +4371,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.944</v>
+        <v>2.004</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.9</v>
+        <v>1.971</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4379,28 +4387,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E87" s="16" t="n">
-        <v>0.0037</v>
+        <v>0.315</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>-0.0308</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1000000</v>
+        <v>1236900</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.19</v>
+        <v>0.75</v>
       </c>
       <c r="H87" t="n">
-        <v>57.1</v>
+        <v>54.6</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4408,10 +4416,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>2.611</v>
+        <v>0.301</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>2.599</v>
+        <v>0.324</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4424,28 +4432,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>-0.0156</v>
+        <v>0.34</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>959000</v>
+        <v>1226900</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="H88" t="n">
-        <v>45.12</v>
+        <v>52.96</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4453,10 +4461,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.64</v>
+        <v>0.337</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.631</v>
+        <v>0.343</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4469,39 +4477,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E89" s="16" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.93</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>956400</v>
+        <v>1217200</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="H89" t="n">
-        <v>25.71</v>
-      </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.68</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.409</v>
+        <v>0.903</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.447</v>
+        <v>0.953</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4514,28 +4522,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.77</v>
+        <v>1.36</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.0286</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>944400</v>
+        <v>1186300</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="H90" t="n">
-        <v>55.85</v>
+        <v>55.24</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4543,10 +4551,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.749</v>
+        <v>1.311</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.699</v>
+        <v>1.257</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4559,33 +4567,40 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>-0.0207</v>
+        <v>1.29</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>911700</v>
+        <v>1184500</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
+      </c>
+      <c r="H91" t="n">
+        <v>25.71</v>
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J91" s="9" t="n"/>
-      <c r="K91" s="9" t="n"/>
+      <c r="J91" s="9" t="n">
+        <v>1.409</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>1.447</v>
+      </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
     </row>
@@ -4597,28 +4612,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>-0.0231</v>
+        <v>7.47</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>0.0122</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>870300</v>
+        <v>1147600</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="H92" t="n">
-        <v>56.11</v>
+        <v>49.94</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4626,10 +4641,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>1.244</v>
+        <v>7.411</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1.214</v>
+        <v>7.755</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4642,28 +4657,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>0.0122</v>
+        <v>3.94</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>864900</v>
+        <v>1144900</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="H93" t="n">
-        <v>49.94</v>
+        <v>56.72</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4671,10 +4686,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>7.411</v>
+        <v>3.851</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>7.755</v>
+        <v>3.379</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4687,28 +4702,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="E94" s="16" t="n">
-        <v>0.0143</v>
+        <v>0.765</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>829700</v>
+        <v>1121100</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="H94" t="n">
-        <v>50</v>
+        <v>54.86</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4716,10 +4731,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>6.338</v>
+        <v>0.749</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>6.588</v>
+        <v>0.699</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4732,28 +4747,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>0.0244</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.0158</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>797100</v>
+        <v>1103300</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="H95" t="n">
-        <v>47.38</v>
+        <v>49.94</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4761,10 +4776,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.27</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.318</v>
+        <v>0.9</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4777,40 +4792,33 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>6.83</v>
+        <v>0.71</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>-0.0101</v>
+        <v>-0.0207</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>791500</v>
+        <v>1100500</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H96" t="n">
-        <v>59.68</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J96" s="9" t="n">
-        <v>6.446</v>
-      </c>
-      <c r="K96" s="9" t="n">
-        <v>6.068</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="I96" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n"/>
+      <c r="K96" s="9" t="n"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
     </row>
@@ -4822,39 +4830,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>-0.0053</v>
+        <v>2.44</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>0.004099999999999999</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>774000</v>
+        <v>1090700</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="H97" t="n">
-        <v>54.68</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.95</v>
+      </c>
+      <c r="I97" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.903</v>
+        <v>2.431</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.953</v>
+        <v>2.429</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4867,28 +4875,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>4.7</v>
+        <v>1.26</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>-0.0042</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>770000</v>
+        <v>1085000</v>
       </c>
       <c r="G98" s="12" t="n">
         <v>0.16</v>
       </c>
       <c r="H98" t="n">
-        <v>59.69</v>
+        <v>61.25</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4896,10 +4904,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>4.492</v>
+        <v>1.2</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>4.452</v>
+        <v>1.16</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4912,28 +4920,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>4.23</v>
+        <v>6.34</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>0.0024</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>699400</v>
+        <v>1080700</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="H99" t="n">
-        <v>60.37</v>
+        <v>47.5</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4941,10 +4949,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>4.043</v>
+        <v>6.335</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>3.707</v>
+        <v>6.587</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4957,28 +4965,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>-0.0308</v>
+        <v>0.36</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>697000</v>
+        <v>1004600</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.21</v>
+        <v>3.22</v>
       </c>
       <c r="H100" t="n">
-        <v>39.32</v>
+        <v>73.72</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4986,10 +4994,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.672</v>
+        <v>0.317</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.728</v>
+        <v>0.299</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5002,28 +5010,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1.36</v>
+        <v>6.87</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>-0.0286</v>
+        <v>-0.0043</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>696800</v>
+        <v>982200</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="H101" t="n">
-        <v>55.24</v>
+        <v>60.57</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5031,10 +5039,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.311</v>
+        <v>6.45</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1.257</v>
+        <v>6.069</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5047,39 +5055,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>0</v>
+        <v>4.68</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>695200</v>
+        <v>963800</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H102" t="n">
-        <v>58.56</v>
-      </c>
-      <c r="I102" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.74</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.289</v>
+        <v>4.49</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1.197</v>
+        <v>4.451</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5092,39 +5100,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E103" s="17" t="n">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>-0.0231</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>659800</v>
+        <v>948500</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.3</v>
+        <v>0.14</v>
       </c>
       <c r="H103" t="n">
-        <v>68.64</v>
-      </c>
-      <c r="I103" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.11</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.751</v>
+        <v>1.244</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.68</v>
+        <v>1.214</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5137,39 +5145,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>0</v>
+        <v>0.745</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.0197</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>658600</v>
+        <v>922300</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="H104" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.49</v>
+      </c>
+      <c r="I104" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.494</v>
+        <v>0.745</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.485</v>
+        <v>0.709</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5182,39 +5190,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>7.85</v>
+        <v>4.23</v>
       </c>
       <c r="E105" s="16" t="n">
-        <v>0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>649700</v>
+        <v>897700</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="H105" t="n">
-        <v>45.92</v>
-      </c>
-      <c r="I105" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.37</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>7.892</v>
+        <v>4.043</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>7.914</v>
+        <v>3.707</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5227,39 +5235,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>-0.0263</v>
+        <v>1.25</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>0.0163</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>635600</v>
+        <v>849000</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="H106" t="n">
-        <v>50.52</v>
-      </c>
-      <c r="I106" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.91</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.745</v>
+        <v>1.269</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.709</v>
+        <v>1.318</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5272,28 +5280,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="E107" s="16" t="n">
-        <v>0.0168</v>
+        <v>0.63</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>-0.0308</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>597900</v>
+        <v>838800</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.54</v>
+        <v>0.25</v>
       </c>
       <c r="H107" t="n">
-        <v>63.38</v>
+        <v>39.32</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5301,10 +5309,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>2.849</v>
+        <v>0.672</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>2.855</v>
+        <v>0.728</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5317,39 +5325,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>4.48</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>565200</v>
+        <v>826200</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.57</v>
+        <v>0.09</v>
       </c>
       <c r="H108" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.34</v>
+      </c>
+      <c r="I108" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.636</v>
+        <v>4.533</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.634</v>
+        <v>4.643</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5362,28 +5370,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>0</v>
+        <v>6.86</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>-0.0029</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>559300</v>
+        <v>808500</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="H109" t="n">
-        <v>57.26</v>
+        <v>51.87</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5391,10 +5399,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>6.839</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.533</v>
+        <v>6.829</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5407,28 +5415,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E110" s="17" t="n">
-        <v>0</v>
+        <v>7.84</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>0.0013</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>552800</v>
+        <v>773200</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="H110" t="n">
-        <v>31.64</v>
+        <v>45.1</v>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
@@ -5436,10 +5444,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.825</v>
+        <v>7.891</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.853</v>
+        <v>7.913</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5452,39 +5460,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="E111" s="16" t="n">
-        <v>0.0157</v>
+        <v>1.35</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>548300</v>
+        <v>753200</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="H111" t="n">
-        <v>48.58</v>
-      </c>
-      <c r="I111" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.56</v>
+      </c>
+      <c r="I111" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>5.814</v>
+        <v>1.289</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>6.046</v>
+        <v>1.197</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5497,39 +5505,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>2.44</v>
+        <v>5.85</v>
       </c>
       <c r="E112" s="16" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.0174</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>541200</v>
+        <v>739800</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H112" t="n">
-        <v>51.95</v>
-      </c>
-      <c r="I112" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.22</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>2.431</v>
+        <v>5.815</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>2.429</v>
+        <v>6.046</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5542,39 +5550,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E113" s="17" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>521600</v>
+        <v>734200</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="H113" t="n">
-        <v>59.38</v>
-      </c>
-      <c r="I113" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>69.41</v>
+      </c>
+      <c r="I113" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>7.872</v>
+        <v>0.752</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>7.867</v>
+        <v>0.68</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5587,28 +5595,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="E114" s="16" t="n">
-        <v>0.0051</v>
+        <v>0.0269</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>520200</v>
+        <v>728000</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.14</v>
+        <v>0.66</v>
       </c>
       <c r="H114" t="n">
-        <v>55.94</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5616,10 +5624,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>3.849</v>
+        <v>2.852</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>3.776</v>
+        <v>2.856</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5632,28 +5640,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.655</v>
+        <v>0.64</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>-0.0076</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>510900</v>
+        <v>695200</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.37</v>
+        <v>0.7</v>
       </c>
       <c r="H115" t="n">
-        <v>68.29000000000001</v>
+        <v>58.16</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5661,16 +5669,1096 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.619</v>
+        <v>0.636</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.552</v>
+        <v>0.634</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>-0.0233</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>689500</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H116" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>CLOUDPT</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>686300</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H117" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>678900</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H118" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>648600</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H119" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>3.776</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>648300</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H120" t="n">
+        <v>58.06</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>13.132</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>13.259</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.0229</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>644000</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H121" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="I121" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.0214</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>637300</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H122" t="n">
+        <v>43</v>
+      </c>
+      <c r="I122" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>2.809</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>606900</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H123" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>600100</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>2.827</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>2.712</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>598300</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H125" t="n">
+        <v>51.02</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>-0.0148</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>593100</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H126" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="I126" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>586600</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H127" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="I127" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>5.572</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>6459</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>MNRB</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>581700</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H128" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>6599</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AEON</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>569900</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H129" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="I129" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E130" s="16" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>566600</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H130" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="I130" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>562300</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H131" t="n">
+        <v>57.26</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>554000</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H132" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="I132" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>4863</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>543600</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H133" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>7.871</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>7.867</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>530900</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H134" t="n">
+        <v>68.29000000000001</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>530500</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H135" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="I135" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E136" s="16" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>525500</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H136" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="I136" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>2.511</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>2.623</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E137" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>517400</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H137" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="I137" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E138" s="16" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>508200</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H138" t="n">
+        <v>44.68</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>1.578</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>505300</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H139" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="I139" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>3.106</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>3.234</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M115"/>
+  <autoFilter ref="A1:M139"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
+++ b/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$163</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,9 +97,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M155"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.64</v>
+        <v>0.645</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0407</v>
+        <v>0.0488</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4356800</v>
+        <v>4399800</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>60.96</v>
+        <v>61.52</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 60.96未超买，现价高于50日均线约28.5%，技术面信号较为可靠。</t>
+          <t>SAR转多信号，RSI 61.52未超买，现价高于50日均线约29.5%，技术面信号可靠性较高。</t>
         </is>
       </c>
     </row>
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.1485</v>
+        <v>0.1386</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>10540600</v>
+        <v>10832200</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.91</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.871</v>
+        <v>0.87</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.668</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 66.91接近超买区，现价1.16远高于50日均线0.668，偏离较大，信号可靠性需谨慎看待。</t>
+          <t>SAR转多信号出现，但RSI 66.6已接近超买区，现价1.15远高于50日均线0.668，偏离较大，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.645</v>
+        <v>0.655</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>-0.0227</v>
+        <v>-0.0076</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1018900</v>
+        <v>1039200</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>63.99</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.618</v>
+        <v>0.619</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.552</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 63.99未超买，现价高于50日均线约16.8%，技术面信号较为可靠。</t>
+          <t>SAR转多信号，但RSI 68.29接近超买区，现价高于50日均线约18.7%，信号可靠性中等。</t>
         </is>
       </c>
     </row>
@@ -732,10 +732,10 @@
         <v>-0.0588</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>107106000</v>
+        <v>113894300</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="H5" t="n">
         <v>36.06</v>
@@ -762,39 +762,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>-0.1111</v>
+        <v>0.055</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>28139700</v>
+        <v>35737600</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>2.39</v>
+        <v>2.79</v>
       </c>
       <c r="H6" t="n">
-        <v>27.36</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
+        <v>56.53</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.056</v>
+        <v>0.051</v>
       </c>
       <c r="K6" s="10" t="n">
-        <v>0.068</v>
+        <v>0.047</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="15" t="inlineStr"/>
@@ -807,39 +807,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0170</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KANGER</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>-0.3333</v>
+        <v>-0.1111</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>27077500</v>
+        <v>33069400</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>35.54</v>
+        <v>2.81</v>
       </c>
       <c r="H7" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
+        <v>27.36</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.019</v>
+        <v>0.056</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>0.023</v>
+        <v>0.068</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="15" t="inlineStr"/>
@@ -852,39 +852,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0170</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>KANGER</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.01</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>-0.3333</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>25502200</v>
+        <v>27286500</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>1.95</v>
+        <v>35.82</v>
       </c>
       <c r="H8" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.25</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.453</v>
+        <v>0.019</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.023</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="15" t="inlineStr"/>
@@ -897,28 +897,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>-0.0141</v>
+        <v>0.42</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>23903600</v>
+        <v>25623200</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.3</v>
+        <v>1.96</v>
       </c>
       <c r="H9" t="n">
-        <v>64.94</v>
+        <v>40.45</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.325</v>
+        <v>0.453</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>0.273</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="15" t="inlineStr"/>
@@ -942,39 +942,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.665</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>-0.0634</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>22945000</v>
+        <v>25380400</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1.79</v>
+        <v>1.1</v>
       </c>
       <c r="H10" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
+        <v>53.55</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.052</v>
+        <v>0.671</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>0.047</v>
+        <v>0.58</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="15" t="inlineStr"/>
@@ -987,39 +987,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>-0.0352</v>
+        <v>-0.0141</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>21332900</v>
+        <v>24932100</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.92</v>
+        <v>0.31</v>
       </c>
       <c r="H11" t="n">
-        <v>59.48</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.94</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.673</v>
+        <v>0.325</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>0.581</v>
+        <v>0.273</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="15" t="inlineStr"/>
@@ -1041,19 +1041,19 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>0</v>
+        <v>0.495</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>17009600</v>
+        <v>20292600</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="H12" t="n">
-        <v>74.67</v>
+        <v>72.61</v>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
@@ -1077,28 +1077,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>0.0435</v>
+        <v>0.96</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>14498400</v>
+        <v>18970000</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>2.88</v>
+        <v>0.24</v>
       </c>
       <c r="H13" t="n">
-        <v>73.66</v>
+        <v>67.83</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.103</v>
+        <v>0.887</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.782</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="15" t="inlineStr"/>
@@ -1131,27 +1131,27 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>6.89</v>
+        <v>6.88</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>-0.0309</v>
+        <v>-0.0323</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>13911600</v>
+        <v>14825300</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="H14" t="n">
-        <v>24.96</v>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
+        <v>24.71</v>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J14" s="10" t="n">
-        <v>7.274</v>
+        <v>7.273</v>
       </c>
       <c r="K14" s="10" t="n">
         <v>7.583</v>
@@ -1167,28 +1167,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>-0.0155</v>
+        <v>0.12</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>12186500</v>
+        <v>14745800</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.16</v>
+        <v>2.93</v>
       </c>
       <c r="H15" t="n">
-        <v>66.68000000000001</v>
+        <v>73.66</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.887</v>
+        <v>0.103</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>0.782</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="15" t="inlineStr"/>
@@ -1212,39 +1212,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0.0185</v>
+        <v>0.82</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>11233400</v>
+        <v>12050400</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>1.77</v>
+        <v>0.76</v>
       </c>
       <c r="H16" t="n">
-        <v>47.51</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.1</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.279</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>0.282</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="15" t="inlineStr"/>
@@ -1257,39 +1257,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.82</v>
+        <v>0.465</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>-0.0061</v>
+        <v>-0.0312</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>11220900</v>
+        <v>12011500</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>0.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.75</v>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.445</v>
       </c>
       <c r="K17" s="10" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.398</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="15" t="inlineStr"/>
@@ -1302,39 +1302,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>-0.0417</v>
+        <v>0.275</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>10071400</v>
+        <v>11233800</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.47</v>
+        <v>1.77</v>
       </c>
       <c r="H18" t="n">
-        <v>57.23</v>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
+        <v>47.51</v>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.444</v>
+        <v>0.279</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>0.397</v>
+        <v>0.282</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="15" t="inlineStr"/>
@@ -1347,39 +1347,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>0.0133</v>
+        <v>0.155</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>9807500</v>
+        <v>10960000</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.95</v>
+        <v>0.29</v>
       </c>
       <c r="H19" t="n">
-        <v>36.71</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.74</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.387</v>
+        <v>0.156</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>0.401</v>
+        <v>0.156</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="15" t="inlineStr"/>
@@ -1403,19 +1403,19 @@
       <c r="D20" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>9667000</v>
+        <v>10471500</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="H20" t="n">
         <v>39.44</v>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1437,36 +1437,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>-0.0217</v>
+        <v>0.38</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>8061700</v>
+        <v>9807500</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>0.42</v>
+        <v>0.95</v>
       </c>
       <c r="H21" t="n">
-        <v>51.02</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
+        <v>36.71</v>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="10" t="n"/>
+      <c r="J21" s="10" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>0.401</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="15" t="inlineStr"/>
     </row>
@@ -1478,39 +1482,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.15</v>
+        <v>0.865</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>0</v>
+        <v>0.0058</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>7727600</v>
+        <v>9645000</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="H22" t="n">
-        <v>37.77</v>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.34</v>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.153</v>
+        <v>0.867</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>0.172</v>
+        <v>0.868</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="15" t="inlineStr"/>
@@ -1523,40 +1527,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>7643900</v>
+        <v>8421700</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="H23" t="n">
-        <v>46</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
+        <v>51.02</v>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J23" s="10" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="K23" s="10" t="n">
-        <v>0.279</v>
-      </c>
+      <c r="J23" s="10" t="n"/>
+      <c r="K23" s="10" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="15" t="inlineStr"/>
     </row>
@@ -1568,39 +1568,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0.0058</v>
+        <v>0.15</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>7462500</v>
+        <v>7941100</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="H24" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.77</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.867</v>
+        <v>0.153</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>0.868</v>
+        <v>0.172</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="15" t="inlineStr"/>
@@ -1613,28 +1613,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.215</v>
+        <v>2.25</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>7055500</v>
+        <v>7758900</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.88</v>
+        <v>0.27</v>
       </c>
       <c r="H25" t="n">
-        <v>85.94</v>
+        <v>66.83</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.145</v>
+        <v>2.035</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>0.122</v>
+        <v>1.838</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="15" t="inlineStr"/>
@@ -1669,14 +1669,14 @@
       <c r="D26" s="10" t="n">
         <v>0.775</v>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>6874800</v>
+        <v>7662800</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="H26" t="n">
         <v>50.93</v>
@@ -1703,39 +1703,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E27" s="18" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E27" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>6571000</v>
+        <v>7643900</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.36</v>
+        <v>0.66</v>
       </c>
       <c r="H27" t="n">
-        <v>53.65</v>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46</v>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.186</v>
+        <v>0.283</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>0.187</v>
+        <v>0.279</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="15" t="inlineStr"/>
@@ -1748,28 +1748,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>2.22</v>
+        <v>0.22</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>0</v>
+        <v>0.0233</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>6527500</v>
+        <v>7059100</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.23</v>
+        <v>0.88</v>
       </c>
       <c r="H28" t="n">
-        <v>65.62</v>
+        <v>86.52</v>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="J28" s="10" t="n">
-        <v>2.032</v>
+        <v>0.146</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>1.837</v>
+        <v>0.122</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="15" t="inlineStr"/>
@@ -1793,28 +1793,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>0.0133</v>
+        <v>0.185</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>6383600</v>
+        <v>6601000</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.92</v>
+        <v>0.36</v>
       </c>
       <c r="H29" t="n">
-        <v>58.8</v>
+        <v>49.13</v>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.374</v>
+        <v>0.185</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0.37</v>
+        <v>0.187</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="15" t="inlineStr"/>
@@ -1838,33 +1838,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>0.025</v>
+        <v>0.38</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>6125300</v>
+        <v>6528600</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="n"/>
-      <c r="K30" s="10" t="n"/>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>0.37</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="15" t="inlineStr"/>
     </row>
@@ -1876,40 +1883,33 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.205</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>0.025</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>5696400</v>
+        <v>6150700</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H31" t="n">
-        <v>53.36</v>
-      </c>
-      <c r="I31" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="n">
-        <v>2.109</v>
-      </c>
-      <c r="K31" s="10" t="n">
-        <v>2.225</v>
-      </c>
+        <v>0.24</v>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="n"/>
+      <c r="K31" s="10" t="n"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="15" t="inlineStr"/>
     </row>
@@ -1921,28 +1921,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.53</v>
+        <v>2.17</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>0</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>5025900</v>
+        <v>5942900</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>1.16</v>
+        <v>0.47</v>
       </c>
       <c r="H32" t="n">
-        <v>79.91</v>
+        <v>54.18</v>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.471</v>
+        <v>2.11</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>0.441</v>
+        <v>2.225</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="15" t="inlineStr"/>
@@ -1966,39 +1966,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>0.008500000000000001</v>
+        <v>10.02</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>0.003</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>4983500</v>
+        <v>5068100</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.23</v>
+        <v>0.44</v>
       </c>
       <c r="H33" t="n">
-        <v>50.86</v>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.37</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="10" t="n">
-        <v>4.731</v>
+        <v>9.996</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>4.795</v>
+        <v>10.095</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="15" t="inlineStr"/>
@@ -2011,39 +2011,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>0.0476</v>
+        <v>0.535</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>4504400</v>
+        <v>5049200</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.27</v>
+        <v>1.16</v>
       </c>
       <c r="H34" t="n">
-        <v>36.82</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.70999999999999</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.125</v>
+        <v>0.472</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>0.144</v>
+        <v>0.441</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="15" t="inlineStr"/>
@@ -2056,39 +2056,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>-0.0337</v>
+        <v>4.75</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>4231500</v>
+        <v>5026300</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="H35" t="n">
-        <v>31.06</v>
-      </c>
-      <c r="I35" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.86</v>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.468</v>
+        <v>4.731</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0.585</v>
+        <v>4.795</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="15" t="inlineStr"/>
@@ -2112,14 +2112,14 @@
       <c r="D36" s="10" t="n">
         <v>0.405</v>
       </c>
-      <c r="E36" s="17" t="n">
+      <c r="E36" s="18" t="n">
         <v>0.0125</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>4225700</v>
+        <v>4659500</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="H36" t="n">
         <v>52.36</v>
@@ -2146,39 +2146,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.295</v>
+        <v>0.11</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>4156500</v>
+        <v>4564400</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>1.17</v>
+        <v>0.27</v>
       </c>
       <c r="H37" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
+        <v>36.82</v>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.295</v>
+        <v>0.125</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.295</v>
+        <v>0.144</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="15" t="inlineStr"/>
@@ -2191,28 +2191,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>0</v>
+        <v>0.43</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>-0.0337</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>3903000</v>
+        <v>4362600</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H38" t="n">
-        <v>66.40000000000001</v>
+        <v>31.06</v>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.629</v>
+        <v>0.468</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0.62</v>
+        <v>0.585</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="15" t="inlineStr"/>
@@ -2236,28 +2236,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FPI</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>0.0261</v>
+        <v>0.645</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>3834900</v>
+        <v>4334200</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>9.109999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="H39" t="n">
-        <v>67.86</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.098</v>
+        <v>0.629</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>1.099</v>
+        <v>0.62</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="15" t="inlineStr"/>
@@ -2281,39 +2281,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>0.003</v>
+        <v>0.295</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>3799600</v>
+        <v>4156500</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.33</v>
+        <v>1.17</v>
       </c>
       <c r="H40" t="n">
-        <v>50.37</v>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="10" t="n">
-        <v>9.996</v>
+        <v>0.295</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>10.095</v>
+        <v>0.295</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="15" t="inlineStr"/>
@@ -2326,28 +2326,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>FPI</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>-0.0208</v>
+        <v>1.18</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>0.0261</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>3537800</v>
+        <v>3872300</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>1.34</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>55.99</v>
+        <v>67.86</v>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.457</v>
+        <v>1.098</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0.449</v>
+        <v>1.099</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="15" t="inlineStr"/>
@@ -2371,39 +2371,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>3373600</v>
+        <v>3685300</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.42</v>
+        <v>0.92</v>
       </c>
       <c r="H42" t="n">
-        <v>37.11</v>
-      </c>
-      <c r="I42" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.2</v>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="10" t="n">
-        <v>1.275</v>
+        <v>1.41</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>1.469</v>
+        <v>1.447</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="15" t="inlineStr"/>
@@ -2416,28 +2416,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>4.98</v>
+        <v>0.47</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>-0.004</v>
+        <v>-0.0208</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>3344300</v>
+        <v>3662800</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.17</v>
+        <v>1.39</v>
       </c>
       <c r="H43" t="n">
-        <v>56.78</v>
+        <v>55.99</v>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="J43" s="10" t="n">
-        <v>4.899</v>
+        <v>0.457</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>4.795</v>
+        <v>0.449</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="15" t="inlineStr"/>
@@ -2461,28 +2461,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>-0.0066</v>
+        <v>2.69</v>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>3280500</v>
+        <v>3549200</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.23</v>
+        <v>0.67</v>
       </c>
       <c r="H44" t="n">
-        <v>38.79</v>
+        <v>57.86</v>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="J44" s="10" t="n">
-        <v>1.555</v>
+        <v>2.612</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>1.822</v>
+        <v>2.599</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="15" t="inlineStr"/>
@@ -2515,19 +2515,19 @@
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>0</v>
+        <v>0.155</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>3255500</v>
+        <v>3520500</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>51.28</v>
+        <v>48.93</v>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
@@ -2551,28 +2551,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E46" s="18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E46" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>3218100</v>
+        <v>3519000</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.61</v>
+        <v>0.24</v>
       </c>
       <c r="H46" t="n">
-        <v>56.31</v>
+        <v>39.52</v>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="J46" s="10" t="n">
-        <v>2.61</v>
+        <v>1.556</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>2.599</v>
+        <v>1.822</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="15" t="inlineStr"/>
@@ -2596,28 +2596,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.22</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>3195800</v>
+        <v>3513700</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.88</v>
+        <v>0.44</v>
       </c>
       <c r="H47" t="n">
-        <v>74.23</v>
+        <v>37.11</v>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="J47" s="10" t="n">
-        <v>0.623</v>
+        <v>1.275</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>0.613</v>
+        <v>1.469</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="15" t="inlineStr"/>
@@ -2641,39 +2641,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>-0.0112</v>
+        <v>-0.0038</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>3118600</v>
+        <v>3421200</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="H48" t="n">
-        <v>42</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
+        <v>50.58</v>
+      </c>
+      <c r="I48" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J48" s="10" t="n">
-        <v>2.713</v>
+        <v>2.595</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>2.749</v>
+        <v>2.571</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="15" t="inlineStr"/>
@@ -2686,39 +2686,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1.15</v>
+        <v>4.98</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>-0.0086</v>
+        <v>-0.004</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>2866000</v>
+        <v>3377100</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.29</v>
+        <v>0.17</v>
       </c>
       <c r="H49" t="n">
-        <v>35.03</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.78</v>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="10" t="n">
-        <v>1.191</v>
+        <v>4.899</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>1.272</v>
+        <v>4.795</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="15" t="inlineStr"/>
@@ -2731,39 +2731,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E50" s="11" t="n">
-        <v>-0.0077</v>
+        <v>2.43</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2854300</v>
+        <v>3370400</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="H50" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.42</v>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="10" t="n">
-        <v>2.594</v>
+        <v>2.43</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>2.57</v>
+        <v>2.429</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="15" t="inlineStr"/>
@@ -2776,39 +2776,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E51" s="18" t="n">
-        <v>0</v>
+        <v>2.65</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>2851400</v>
+        <v>3335800</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.64</v>
+        <v>0.34</v>
       </c>
       <c r="H51" t="n">
-        <v>62.72</v>
-      </c>
-      <c r="I51" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.8</v>
+      </c>
+      <c r="I51" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="10" t="n">
-        <v>0.61</v>
+        <v>2.714</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>0.587</v>
+        <v>2.749</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="15" t="inlineStr"/>
@@ -2821,39 +2821,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E52" s="18" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E52" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>2727900</v>
+        <v>3228700</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.23</v>
+        <v>0.89</v>
       </c>
       <c r="H52" t="n">
-        <v>43.12</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.45</v>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="10" t="n">
-        <v>0.988</v>
+        <v>0.623</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>0.993</v>
+        <v>0.613</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="15" t="inlineStr"/>
@@ -2866,28 +2866,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E53" s="11" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.67</v>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>2662400</v>
+        <v>3122500</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>0.26</v>
+        <v>0.7</v>
       </c>
       <c r="H53" t="n">
-        <v>65.81999999999999</v>
+        <v>63.44</v>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="J53" s="10" t="n">
-        <v>1.129</v>
+        <v>0.61</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>1.071</v>
+        <v>0.587</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="15" t="inlineStr"/>
@@ -2922,14 +2922,14 @@
       <c r="D54" s="10" t="n">
         <v>0.835</v>
       </c>
-      <c r="E54" s="18" t="n">
+      <c r="E54" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>2645400</v>
+        <v>3006900</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="H54" t="n">
         <v>72.51000000000001</v>
@@ -2956,28 +2956,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.595</v>
+        <v>0.215</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>-0.0083</v>
+        <v>-0.0444</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>2592600</v>
+        <v>2981900</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>0.13</v>
+        <v>2.76</v>
       </c>
       <c r="H55" t="n">
-        <v>55.64</v>
+        <v>41.91</v>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.575</v>
+        <v>0.223</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>0.552</v>
+        <v>0.229</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="15" t="inlineStr"/>
@@ -3001,39 +3001,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E56" s="11" t="n">
-        <v>-0.0444</v>
+        <v>0.945</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>2584300</v>
+        <v>2955200</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>2.39</v>
+        <v>0.25</v>
       </c>
       <c r="H56" t="n">
-        <v>41.91</v>
-      </c>
-      <c r="I56" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.12</v>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.223</v>
+        <v>0.988</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>0.229</v>
+        <v>0.993</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="15" t="inlineStr"/>
@@ -3046,28 +3046,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>0.0236</v>
+        <v>1.23</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>2568200</v>
+        <v>2928400</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>0.82</v>
+        <v>0.28</v>
       </c>
       <c r="H57" t="n">
-        <v>59.11</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="J57" s="10" t="n">
-        <v>1.27</v>
+        <v>1.129</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>1.27</v>
+        <v>1.071</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="15" t="inlineStr"/>
@@ -3091,28 +3091,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E58" s="18" t="n">
-        <v>0</v>
+        <v>0.595</v>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>2474100</v>
+        <v>2924500</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>1.28</v>
+        <v>0.15</v>
       </c>
       <c r="H58" t="n">
-        <v>50.78</v>
+        <v>55.64</v>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="J58" s="10" t="n">
-        <v>0.904</v>
+        <v>0.575</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>0.898</v>
+        <v>0.552</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="15" t="inlineStr"/>
@@ -3136,39 +3136,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>0.21</v>
+        <v>1.15</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>-0.0455</v>
+        <v>-0.0086</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>2392100</v>
+        <v>2870200</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="H59" t="n">
-        <v>38.42</v>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
+        <v>35.03</v>
+      </c>
+      <c r="I59" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J59" s="10" t="n">
-        <v>0.22</v>
+        <v>1.191</v>
       </c>
       <c r="K59" s="10" t="n">
-        <v>0.26</v>
+        <v>1.272</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="15" t="inlineStr"/>
@@ -3181,28 +3181,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E60" s="11" t="n">
-        <v>-0.0267</v>
+        <v>0.44</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>2371000</v>
+        <v>2795500</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>1.95</v>
+        <v>0.39</v>
       </c>
       <c r="H60" t="n">
-        <v>60.14</v>
+        <v>53.62</v>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.345</v>
+        <v>0.431</v>
       </c>
       <c r="K60" s="10" t="n">
-        <v>0.355</v>
+        <v>0.416</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="15" t="inlineStr"/>
@@ -3226,39 +3226,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="E61" s="18" t="n">
-        <v>0</v>
+        <v>0.78</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>2367700</v>
+        <v>2788100</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>0.24</v>
+        <v>0.39</v>
       </c>
       <c r="H61" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="I61" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.12</v>
+      </c>
+      <c r="I61" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="10" t="n">
-        <v>2.43</v>
+        <v>0.771</v>
       </c>
       <c r="K61" s="10" t="n">
-        <v>2.429</v>
+        <v>0.771</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="15" t="inlineStr"/>
@@ -3271,28 +3271,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E62" s="11" t="n">
-        <v>-0.0227</v>
+        <v>1.29</v>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>2363300</v>
+        <v>2617100</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="H62" t="n">
-        <v>50.79</v>
+        <v>56.73</v>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="J62" s="10" t="n">
-        <v>0.43</v>
+        <v>1.269</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>0.416</v>
+        <v>1.27</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="15" t="inlineStr"/>
@@ -3316,28 +3316,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>0.445</v>
+        <v>3.41</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>-0.0111</v>
+        <v>-0.0116</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>2362000</v>
+        <v>2564200</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H63" t="n">
-        <v>46.14</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I63" s="14" t="inlineStr">
         <is>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="J63" s="10" t="n">
-        <v>0.453</v>
+        <v>3.146</v>
       </c>
       <c r="K63" s="10" t="n">
-        <v>0.471</v>
+        <v>2.671</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="15" t="inlineStr"/>
@@ -3361,28 +3361,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="E64" s="11" t="n">
-        <v>-0.0133</v>
+        <v>5.3</v>
+      </c>
+      <c r="E64" s="18" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>2306500</v>
+        <v>2501400</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>0.71</v>
+        <v>0.15</v>
       </c>
       <c r="H64" t="n">
-        <v>49.33</v>
+        <v>47.02</v>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="J64" s="10" t="n">
-        <v>3.005</v>
+        <v>5.354</v>
       </c>
       <c r="K64" s="10" t="n">
-        <v>2.88</v>
+        <v>5.53</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="15" t="inlineStr"/>
@@ -3406,39 +3406,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E65" s="11" t="n">
-        <v>-0.0064</v>
+        <v>0.905</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>2297600</v>
+        <v>2474100</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>0.32</v>
+        <v>1.28</v>
       </c>
       <c r="H65" t="n">
-        <v>53.12</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.78</v>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="10" t="n">
-        <v>0.771</v>
+        <v>0.904</v>
       </c>
       <c r="K65" s="10" t="n">
-        <v>0.771</v>
+        <v>0.898</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="15" t="inlineStr"/>
@@ -3451,28 +3451,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>3.44</v>
+        <v>1.39</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>-0.0029</v>
+        <v>-0.0071</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>2297200</v>
+        <v>2452600</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="H66" t="n">
-        <v>88.01000000000001</v>
+        <v>57.97</v>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="J66" s="10" t="n">
-        <v>3.149</v>
+        <v>1.314</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>2.672</v>
+        <v>1.258</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="15" t="inlineStr"/>
@@ -3496,39 +3496,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>0.0076</v>
+        <v>0.21</v>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>2275100</v>
+        <v>2444600</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="H67" t="n">
-        <v>47.38</v>
-      </c>
-      <c r="I67" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.42</v>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="10" t="n">
-        <v>5.355</v>
+        <v>0.22</v>
       </c>
       <c r="K67" s="10" t="n">
-        <v>5.53</v>
+        <v>0.26</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="15" t="inlineStr"/>
@@ -3541,28 +3541,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>1.27</v>
+        <v>0.445</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>-0.0155</v>
+        <v>-0.0111</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>2192700</v>
+        <v>2384600</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.64</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>53.45</v>
+        <v>46.14</v>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
@@ -3570,10 +3570,10 @@
         </is>
       </c>
       <c r="J68" s="10" t="n">
-        <v>1.258</v>
+        <v>0.453</v>
       </c>
       <c r="K68" s="10" t="n">
-        <v>1.137</v>
+        <v>0.471</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="15" t="inlineStr"/>
@@ -3586,28 +3586,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>0.0357</v>
+        <v>0.365</v>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>2116400</v>
+        <v>2371000</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>0.29</v>
+        <v>1.95</v>
       </c>
       <c r="H69" t="n">
-        <v>38.02</v>
+        <v>60.14</v>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="J69" s="10" t="n">
-        <v>0.308</v>
+        <v>0.345</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>0.352</v>
+        <v>0.355</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="15" t="inlineStr"/>
@@ -3631,28 +3631,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D70" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E70" s="18" t="n">
-        <v>0</v>
+        <v>2.99</v>
+      </c>
+      <c r="E70" s="11" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>2094200</v>
+        <v>2366700</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="H70" t="n">
-        <v>58.94</v>
+        <v>50.17</v>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="J70" s="10" t="n">
-        <v>1.315</v>
+        <v>3.007</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>1.258</v>
+        <v>2.88</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="15" t="inlineStr"/>
@@ -3676,28 +3676,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PANTECH</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>0.0299</v>
+        <v>1.28</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>2003100</v>
+        <v>2238800</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>7.13</v>
+        <v>0.66</v>
       </c>
       <c r="H71" t="n">
-        <v>68.31</v>
+        <v>54.43</v>
       </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="J71" s="10" t="n">
-        <v>0.663</v>
+        <v>1.258</v>
       </c>
       <c r="K71" s="10" t="n">
-        <v>0.662</v>
+        <v>1.137</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="15" t="inlineStr"/>
@@ -3721,39 +3721,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.35</v>
+        <v>4.48</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>0</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>1927200</v>
+        <v>2228300</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>2.26</v>
+        <v>0.25</v>
       </c>
       <c r="H72" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="I72" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.34</v>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="10" t="n">
-        <v>0.335</v>
+        <v>4.533</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>0.319</v>
+        <v>4.643</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="15" t="inlineStr"/>
@@ -3766,39 +3766,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E73" s="11" t="n">
-        <v>-0.0222</v>
+        <v>1.26</v>
+      </c>
+      <c r="E73" s="18" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>1900000</v>
+        <v>2165600</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>3.98</v>
+        <v>0.33</v>
       </c>
       <c r="H73" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.38</v>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="10" t="n">
-        <v>0.224</v>
+        <v>1.27</v>
       </c>
       <c r="K73" s="10" t="n">
-        <v>0.224</v>
+        <v>1.318</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="15" t="inlineStr"/>
@@ -3811,39 +3811,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E74" s="11" t="n">
-        <v>-0.0244</v>
+        <v>0.7</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>1838600</v>
+        <v>2159100</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.92</v>
+        <v>0.21</v>
       </c>
       <c r="H74" t="n">
-        <v>34.27</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
+        <v>44.93</v>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J74" s="10" t="n">
-        <v>0.434</v>
+        <v>0.726</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>0.452</v>
+        <v>0.724</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="15" t="inlineStr"/>
@@ -3856,28 +3856,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>0.0242</v>
+        <v>0.29</v>
+      </c>
+      <c r="E75" s="18" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>1798300</v>
+        <v>2119900</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="H75" t="n">
-        <v>57.22</v>
+        <v>38.02</v>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="J75" s="10" t="n">
-        <v>1.635</v>
+        <v>0.308</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>1.667</v>
+        <v>0.352</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="15" t="inlineStr"/>
@@ -3901,39 +3901,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D76" s="10" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>0.0073</v>
+        <v>3.03</v>
+      </c>
+      <c r="E76" s="18" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1773100</v>
+        <v>2115800</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0.17</v>
+        <v>0.77</v>
       </c>
       <c r="H76" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="I76" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.15</v>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="10" t="n">
-        <v>6.994</v>
+        <v>3.107</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>7.436</v>
+        <v>3.234</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="15" t="inlineStr"/>
@@ -3946,28 +3946,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>PANTECH</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>0</v>
+        <v>0.0224</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>1727800</v>
+        <v>2104600</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>0.4</v>
+        <v>7.49</v>
       </c>
       <c r="H77" t="n">
-        <v>56.13</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="J77" s="10" t="n">
-        <v>0.904</v>
+        <v>0.662</v>
       </c>
       <c r="K77" s="10" t="n">
-        <v>0.953</v>
+        <v>0.661</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="15" t="inlineStr"/>
@@ -3991,39 +3991,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E78" s="11" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>1700100</v>
+        <v>2038000</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.18</v>
+        <v>1.92</v>
       </c>
       <c r="H78" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
+        <v>34.28</v>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J78" s="10" t="n">
-        <v>0.335</v>
+        <v>0.274</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>0.339</v>
+        <v>0.283</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="15" t="inlineStr"/>
@@ -4036,28 +4036,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E79" s="11" t="n">
-        <v>-0.0161</v>
+        <v>6.9</v>
+      </c>
+      <c r="E79" s="18" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>1691200</v>
+        <v>2009100</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>2.08</v>
+        <v>0.19</v>
       </c>
       <c r="H79" t="n">
-        <v>56.04</v>
+        <v>42.93</v>
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="J79" s="10" t="n">
-        <v>0.294</v>
+        <v>6.993</v>
       </c>
       <c r="K79" s="10" t="n">
-        <v>0.293</v>
+        <v>7.436</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="15" t="inlineStr"/>
@@ -4081,39 +4081,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>0</v>
+        <v>1.64</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>1688100</v>
+        <v>2007800</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.95</v>
+        <v>0.31</v>
       </c>
       <c r="H80" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="I80" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.96</v>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="10" t="n">
-        <v>0.746</v>
+        <v>1.649</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>0.725</v>
+        <v>1.731</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="15" t="inlineStr"/>
@@ -4126,28 +4126,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E81" s="11" t="n">
-        <v>-0.0181</v>
+        <v>2.1</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>1686100</v>
+        <v>1991400</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="H81" t="n">
-        <v>46.02</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
@@ -4155,10 +4155,10 @@
         </is>
       </c>
       <c r="J81" s="10" t="n">
-        <v>1.648</v>
+        <v>2.003</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>1.731</v>
+        <v>1.971</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="15" t="inlineStr"/>
@@ -4182,14 +4182,14 @@
       <c r="D82" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="E82" s="18" t="n">
+      <c r="E82" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1680400</v>
+        <v>1987300</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H82" t="n">
         <v>49.09</v>
@@ -4216,39 +4216,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0098</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>AUMAS</t>
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="E83" s="17" t="n">
-        <v>0.0068</v>
+        <v>0.36</v>
+      </c>
+      <c r="E83" s="18" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>1663600</v>
+        <v>1974200</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>0.19</v>
+        <v>1.56</v>
       </c>
       <c r="H83" t="n">
-        <v>40.04</v>
-      </c>
-      <c r="I83" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.2</v>
+      </c>
+      <c r="I83" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="10" t="n">
-        <v>4.532</v>
+        <v>0.348</v>
       </c>
       <c r="K83" s="10" t="n">
-        <v>4.643</v>
+        <v>0.357</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="15" t="inlineStr"/>
@@ -4270,21 +4270,21 @@
         </is>
       </c>
       <c r="D84" s="10" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E84" s="11" t="n">
-        <v>-0.0108</v>
+        <v>0.465</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>1646800</v>
+        <v>1948500</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="H84" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="I84" s="16" t="inlineStr">
+        <v>45.37</v>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -4306,39 +4306,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D85" s="10" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E85" s="18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E85" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>1637400</v>
+        <v>1941200</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>0.43</v>
+        <v>0.29</v>
       </c>
       <c r="H85" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="I85" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.12</v>
+      </c>
+      <c r="I85" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="10" t="n">
-        <v>0.522</v>
+        <v>1.201</v>
       </c>
       <c r="K85" s="10" t="n">
-        <v>0.554</v>
+        <v>1.16</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="15" t="inlineStr"/>
@@ -4351,39 +4351,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>0.0119</v>
+        <v>0.35</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>1623900</v>
+        <v>1927200</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.59</v>
+        <v>2.26</v>
       </c>
       <c r="H86" t="n">
-        <v>42.56</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.63</v>
+      </c>
+      <c r="I86" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="10" t="n">
-        <v>0.861</v>
+        <v>0.335</v>
       </c>
       <c r="K86" s="10" t="n">
-        <v>0.918</v>
+        <v>0.319</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="15" t="inlineStr"/>
@@ -4396,39 +4396,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>0.59</v>
+        <v>3.87</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>-0.0248</v>
+        <v>-0.0301</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>1609800</v>
+        <v>1903300</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>0.18</v>
+        <v>0.29</v>
       </c>
       <c r="H87" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="I87" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.21</v>
+      </c>
+      <c r="I87" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="10" t="n">
-        <v>0.604</v>
+        <v>3.844</v>
       </c>
       <c r="K87" s="10" t="n">
-        <v>0.618</v>
+        <v>3.378</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="15" t="inlineStr"/>
@@ -4441,39 +4441,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E88" s="18" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>1577400</v>
+        <v>1900000</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.25</v>
+        <v>3.98</v>
       </c>
       <c r="H88" t="n">
-        <v>66.23999999999999</v>
-      </c>
-      <c r="I88" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.5</v>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="10" t="n">
-        <v>2.003</v>
+        <v>0.224</v>
       </c>
       <c r="K88" s="10" t="n">
-        <v>1.971</v>
+        <v>0.224</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="15" t="inlineStr"/>
@@ -4497,19 +4497,19 @@
       <c r="D89" s="10" t="n">
         <v>0.55</v>
       </c>
-      <c r="E89" s="18" t="n">
+      <c r="E89" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>1560400</v>
+        <v>1889900</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="H89" t="n">
         <v>41.67</v>
       </c>
-      <c r="I89" s="16" t="inlineStr">
+      <c r="I89" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -4531,28 +4531,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>0.0163</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>1484900</v>
+        <v>1855100</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.23</v>
+        <v>0.43</v>
       </c>
       <c r="H90" t="n">
-        <v>45.91</v>
+        <v>56.13</v>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="J90" s="10" t="n">
-        <v>1.269</v>
+        <v>0.904</v>
       </c>
       <c r="K90" s="10" t="n">
-        <v>1.318</v>
+        <v>0.953</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="15" t="inlineStr"/>
@@ -4576,39 +4576,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D91" s="10" t="n">
-        <v>6.85</v>
+        <v>0.4</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>-0.0044</v>
+        <v>-0.0244</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>1481700</v>
+        <v>1842600</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>0.25</v>
+        <v>0.92</v>
       </c>
       <c r="H91" t="n">
-        <v>51.37</v>
-      </c>
-      <c r="I91" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.27</v>
+      </c>
+      <c r="I91" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="10" t="n">
-        <v>6.838</v>
+        <v>0.434</v>
       </c>
       <c r="K91" s="10" t="n">
-        <v>6.829</v>
+        <v>0.452</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="15" t="inlineStr"/>
@@ -4621,39 +4621,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E92" s="11" t="n">
-        <v>-0.0185</v>
+        <v>1.69</v>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>0.0242</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>1477000</v>
+        <v>1830700</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>1.39</v>
+        <v>0.22</v>
       </c>
       <c r="H92" t="n">
-        <v>34.28</v>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.22</v>
+      </c>
+      <c r="I92" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="10" t="n">
-        <v>0.274</v>
+        <v>1.635</v>
       </c>
       <c r="K92" s="10" t="n">
-        <v>0.283</v>
+        <v>1.667</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="15" t="inlineStr"/>
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D93" s="10" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>0.0095</v>
+        <v>0.845</v>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>0.006</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>1473500</v>
+        <v>1776700</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>0.19</v>
+        <v>0.65</v>
       </c>
       <c r="H93" t="n">
-        <v>48.15</v>
-      </c>
-      <c r="I93" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.69</v>
+      </c>
+      <c r="I93" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="10" t="n">
-        <v>6.335</v>
+        <v>0.86</v>
       </c>
       <c r="K93" s="10" t="n">
-        <v>6.587</v>
+        <v>0.918</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="15" t="inlineStr"/>
@@ -4711,39 +4711,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D94" s="10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>1750100</v>
+      </c>
+      <c r="G94" s="13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H94" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="10" t="n">
         <v>0.335</v>
       </c>
-      <c r="E94" s="11" t="n">
-        <v>-0.029</v>
-      </c>
-      <c r="F94" s="12" t="n">
-        <v>1446700</v>
-      </c>
-      <c r="G94" s="13" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H94" t="n">
-        <v>57.81</v>
-      </c>
-      <c r="I94" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J94" s="10" t="n">
-        <v>0.32</v>
-      </c>
       <c r="K94" s="10" t="n">
-        <v>0.33</v>
+        <v>0.339</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="15" t="inlineStr"/>
@@ -4756,39 +4756,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D95" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E95" s="18" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E95" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>1409900</v>
+        <v>1715700</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>0.13</v>
+        <v>0.97</v>
       </c>
       <c r="H95" t="n">
-        <v>44.93</v>
-      </c>
-      <c r="I95" s="16" t="inlineStr">
+        <v>44.88</v>
+      </c>
+      <c r="I95" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J95" s="10" t="n">
-        <v>0.726</v>
+        <v>0.746</v>
       </c>
       <c r="K95" s="10" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="15" t="inlineStr"/>
@@ -4801,39 +4801,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>0.007800000000000001</v>
+        <v>4.27</v>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>1397100</v>
+        <v>1704800</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="H96" t="n">
-        <v>25.71</v>
-      </c>
-      <c r="I96" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.58</v>
+      </c>
+      <c r="I96" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="10" t="n">
-        <v>1.409</v>
+        <v>4.047</v>
       </c>
       <c r="K96" s="10" t="n">
-        <v>1.447</v>
+        <v>3.708</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="15" t="inlineStr"/>
@@ -4846,39 +4846,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D97" s="10" t="n">
-        <v>1.26</v>
+        <v>0.59</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0248</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>1394800</v>
+        <v>1703900</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="H97" t="n">
-        <v>61.25</v>
-      </c>
-      <c r="I97" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.38</v>
+      </c>
+      <c r="I97" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="10" t="n">
-        <v>1.2</v>
+        <v>0.604</v>
       </c>
       <c r="K97" s="10" t="n">
-        <v>1.16</v>
+        <v>0.618</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="15" t="inlineStr"/>
@@ -4891,28 +4891,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TDM</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D98" s="10" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>0.0513</v>
+        <v>6.85</v>
+      </c>
+      <c r="E98" s="11" t="n">
+        <v>-0.0044</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>1385700</v>
+        <v>1703900</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>3.81</v>
+        <v>0.29</v>
       </c>
       <c r="H98" t="n">
-        <v>52.51</v>
+        <v>51.37</v>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="J98" s="10" t="n">
-        <v>0.201</v>
+        <v>6.838</v>
       </c>
       <c r="K98" s="10" t="n">
-        <v>0.214</v>
+        <v>6.829</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="15" t="inlineStr"/>
@@ -4936,39 +4936,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ESCERAM</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D99" s="10" t="n">
-        <v>0.2</v>
+        <v>0.305</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.0161</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>1361500</v>
+        <v>1691200</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>0.6</v>
+        <v>2.08</v>
       </c>
       <c r="H99" t="n">
-        <v>46.74</v>
-      </c>
-      <c r="I99" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.04</v>
+      </c>
+      <c r="I99" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="10" t="n">
-        <v>0.209</v>
+        <v>0.294</v>
       </c>
       <c r="K99" s="10" t="n">
-        <v>0.194</v>
+        <v>0.293</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="15" t="inlineStr"/>
@@ -4981,39 +4981,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E100" s="17" t="n">
-        <v>0.0071</v>
+        <v>0.51</v>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1317500</v>
+        <v>1660800</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.16</v>
+        <v>0.44</v>
       </c>
       <c r="H100" t="n">
-        <v>60.98</v>
-      </c>
-      <c r="I100" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.17</v>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="10" t="n">
-        <v>4.045</v>
+        <v>0.522</v>
       </c>
       <c r="K100" s="10" t="n">
-        <v>3.708</v>
+        <v>0.554</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="15" t="inlineStr"/>
@@ -5026,28 +5026,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D101" s="10" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>-0.0156</v>
+        <v>-0.0435</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>1311100</v>
+        <v>1532800</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>45.12</v>
+        <v>54.89</v>
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="J101" s="10" t="n">
-        <v>0.64</v>
+        <v>0.32</v>
       </c>
       <c r="K101" s="10" t="n">
-        <v>0.631</v>
+        <v>0.33</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="15" t="inlineStr"/>
@@ -5071,28 +5071,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>TDM</t>
         </is>
       </c>
       <c r="D102" s="10" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>0.0122</v>
+        <v>0.205</v>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>0.0513</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>1288400</v>
+        <v>1525100</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>0.12</v>
+        <v>4.19</v>
       </c>
       <c r="H102" t="n">
-        <v>49.94</v>
+        <v>52.51</v>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="J102" s="10" t="n">
-        <v>7.411</v>
+        <v>0.201</v>
       </c>
       <c r="K102" s="10" t="n">
-        <v>7.755</v>
+        <v>0.214</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="15" t="inlineStr"/>
@@ -5116,39 +5116,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D103" s="10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="E103" s="17" t="n">
-        <v>0.0033</v>
+        <v>6.35</v>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>1278200</v>
+        <v>1499800</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>0.46</v>
+        <v>0.2</v>
       </c>
       <c r="H103" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="I103" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.15</v>
+      </c>
+      <c r="I103" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="10" t="n">
-        <v>3.106</v>
+        <v>6.335</v>
       </c>
       <c r="K103" s="10" t="n">
-        <v>3.234</v>
+        <v>6.587</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="15" t="inlineStr"/>
@@ -5161,28 +5161,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0098</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AUMAS</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D104" s="10" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>0.0145</v>
+        <v>7.47</v>
+      </c>
+      <c r="E104" s="18" t="n">
+        <v>0.0122</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1253400</v>
+        <v>1458000</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>0.99</v>
+        <v>0.13</v>
       </c>
       <c r="H104" t="n">
-        <v>51.42</v>
+        <v>49.94</v>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
@@ -5190,10 +5190,10 @@
         </is>
       </c>
       <c r="J104" s="10" t="n">
-        <v>0.347</v>
+        <v>7.411</v>
       </c>
       <c r="K104" s="10" t="n">
-        <v>0.356</v>
+        <v>7.755</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="15" t="inlineStr"/>
@@ -5206,39 +5206,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D105" s="10" t="n">
-        <v>0.315</v>
+        <v>0.2</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>-0.0308</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>1236900</v>
+        <v>1382500</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>0.75</v>
+        <v>0.61</v>
       </c>
       <c r="H105" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="I105" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.74</v>
+      </c>
+      <c r="I105" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="10" t="n">
-        <v>0.301</v>
+        <v>0.209</v>
       </c>
       <c r="K105" s="10" t="n">
-        <v>0.324</v>
+        <v>0.194</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="15" t="inlineStr"/>
@@ -5251,28 +5251,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="E106" s="11" t="n">
-        <v>-0.0125</v>
+        <v>0.345</v>
+      </c>
+      <c r="E106" s="18" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1232200</v>
+        <v>1352500</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
       <c r="H106" t="n">
-        <v>56.72</v>
+        <v>58.74</v>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="J106" s="10" t="n">
-        <v>3.851</v>
+        <v>0.338</v>
       </c>
       <c r="K106" s="10" t="n">
-        <v>3.379</v>
+        <v>0.343</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="15" t="inlineStr"/>
@@ -5296,28 +5296,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D107" s="10" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E107" s="18" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>1226900</v>
+        <v>1311100</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>0.37</v>
+        <v>0.6</v>
       </c>
       <c r="H107" t="n">
-        <v>52.96</v>
+        <v>45.12</v>
       </c>
       <c r="I107" s="14" t="inlineStr">
         <is>
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="J107" s="10" t="n">
-        <v>0.337</v>
+        <v>0.64</v>
       </c>
       <c r="K107" s="10" t="n">
-        <v>0.343</v>
+        <v>0.631</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="15" t="inlineStr"/>
@@ -5350,19 +5350,19 @@
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>6.83</v>
+        <v>6.86</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>-0.0101</v>
+        <v>-0.0058</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>1222300</v>
+        <v>1286800</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H108" t="n">
-        <v>59.68</v>
+        <v>60.35</v>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="J108" s="10" t="n">
-        <v>6.446</v>
+        <v>6.449</v>
       </c>
       <c r="K108" s="10" t="n">
         <v>6.068</v>
@@ -5386,33 +5386,40 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D109" s="10" t="n">
-        <v>0.715</v>
+        <v>4.67</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>-0.0138</v>
+        <v>-0.0106</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>1146000</v>
+        <v>1237700</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I109" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J109" s="10" t="n"/>
-      <c r="K109" s="10" t="n"/>
+        <v>0.26</v>
+      </c>
+      <c r="H109" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="I109" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J109" s="10" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="K109" s="10" t="n">
+        <v>4.451</v>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="15" t="inlineStr"/>
     </row>
@@ -5424,28 +5431,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>0.76</v>
+        <v>0.315</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>-0.0194</v>
+        <v>-0.0308</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1129500</v>
+        <v>1236900</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>0.21</v>
+        <v>0.75</v>
       </c>
       <c r="H110" t="n">
-        <v>53.9</v>
+        <v>54.6</v>
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
@@ -5453,10 +5460,10 @@
         </is>
       </c>
       <c r="J110" s="10" t="n">
-        <v>0.748</v>
+        <v>0.301</v>
       </c>
       <c r="K110" s="10" t="n">
-        <v>0.699</v>
+        <v>0.324</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="15" t="inlineStr"/>
@@ -5469,28 +5476,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D111" s="10" t="n">
-        <v>4.68</v>
+        <v>0.765</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0129</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>1122800</v>
+        <v>1221600</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="H111" t="n">
-        <v>58.74</v>
+        <v>54.86</v>
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
@@ -5498,10 +5505,10 @@
         </is>
       </c>
       <c r="J111" s="10" t="n">
-        <v>4.49</v>
+        <v>0.749</v>
       </c>
       <c r="K111" s="10" t="n">
-        <v>4.451</v>
+        <v>0.699</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="15" t="inlineStr"/>
@@ -5514,28 +5521,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.635</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>-0.0158</v>
+        <v>-0.0231</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>1108800</v>
+        <v>1215900</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H112" t="n">
-        <v>49.94</v>
+        <v>40.04</v>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
@@ -5543,10 +5550,10 @@
         </is>
       </c>
       <c r="J112" s="10" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="K112" s="10" t="n">
-        <v>0.9</v>
+        <v>0.729</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="15" t="inlineStr"/>
@@ -5559,28 +5566,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D113" s="10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E113" s="11" t="n">
-        <v>-0.0231</v>
+        <v>5.86</v>
+      </c>
+      <c r="E113" s="18" t="n">
+        <v>0.0191</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>1047400</v>
+        <v>1149300</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="H113" t="n">
-        <v>40.04</v>
+        <v>49.85</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
@@ -5588,10 +5595,10 @@
         </is>
       </c>
       <c r="J113" s="10" t="n">
-        <v>0.673</v>
+        <v>5.816</v>
       </c>
       <c r="K113" s="10" t="n">
-        <v>0.729</v>
+        <v>6.046</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="15" t="inlineStr"/>
@@ -5604,40 +5611,33 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D114" s="10" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>0.0435</v>
+        <v>0.715</v>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>-0.0138</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>1030600</v>
+        <v>1146000</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H114" t="n">
-        <v>73.72</v>
-      </c>
-      <c r="I114" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J114" s="10" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="K114" s="10" t="n">
-        <v>0.299</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="I114" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="10" t="n"/>
+      <c r="K114" s="10" t="n"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="15" t="inlineStr"/>
     </row>
@@ -5649,28 +5649,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D115" s="10" t="n">
-        <v>1.28</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>-0.0154</v>
+        <v>-0.0158</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>979700</v>
+        <v>1134800</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>0.15</v>
+        <v>0.28</v>
       </c>
       <c r="H115" t="n">
-        <v>57.77</v>
+        <v>49.94</v>
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="J115" s="10" t="n">
-        <v>1.245</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K115" s="10" t="n">
-        <v>1.214</v>
+        <v>0.9</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="15" t="inlineStr"/>
@@ -5694,39 +5694,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E116" s="11" t="n">
-        <v>-0.0197</v>
+        <v>0.36</v>
+      </c>
+      <c r="E116" s="18" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>976300</v>
+        <v>1041400</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.3</v>
+        <v>3.34</v>
       </c>
       <c r="H116" t="n">
-        <v>51.49</v>
-      </c>
-      <c r="I116" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.72</v>
+      </c>
+      <c r="I116" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="10" t="n">
-        <v>0.745</v>
+        <v>0.317</v>
       </c>
       <c r="K116" s="10" t="n">
-        <v>0.709</v>
+        <v>0.299</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="15" t="inlineStr"/>
@@ -5739,39 +5739,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D117" s="10" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>0.0174</v>
+        <v>0.865</v>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>865800</v>
+        <v>1040000</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>0.11</v>
+        <v>0.36</v>
       </c>
       <c r="H117" t="n">
-        <v>49.22</v>
-      </c>
-      <c r="I117" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.58</v>
+      </c>
+      <c r="I117" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="10" t="n">
-        <v>5.815</v>
+        <v>0.866</v>
       </c>
       <c r="K117" s="10" t="n">
-        <v>6.046</v>
+        <v>0.861</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="15" t="inlineStr"/>
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D118" s="10" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="E118" s="17" t="n">
-        <v>0.0026</v>
+        <v>1.28</v>
+      </c>
+      <c r="E118" s="11" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>854700</v>
+        <v>1034200</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H118" t="n">
-        <v>45.92</v>
-      </c>
-      <c r="I118" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.77</v>
+      </c>
+      <c r="I118" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="10" t="n">
-        <v>7.892</v>
+        <v>1.245</v>
       </c>
       <c r="K118" s="10" t="n">
-        <v>7.914</v>
+        <v>1.214</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="15" t="inlineStr"/>
@@ -5829,39 +5829,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D119" s="10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E119" s="17" t="n">
-        <v>0.0269</v>
+        <v>2.28</v>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>799200</v>
+        <v>1022800</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>0.72</v>
+        <v>0.28</v>
       </c>
       <c r="H119" t="n">
-        <v>64.81999999999999</v>
-      </c>
-      <c r="I119" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.29</v>
+      </c>
+      <c r="I119" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="10" t="n">
-        <v>2.852</v>
+        <v>2.296</v>
       </c>
       <c r="K119" s="10" t="n">
-        <v>2.856</v>
+        <v>2.225</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="15" t="inlineStr"/>
@@ -5874,39 +5874,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D120" s="10" t="n">
-        <v>1.34</v>
+        <v>2.9</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>-0.0074</v>
+        <v>-0.0068</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>781000</v>
+        <v>995100</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="H120" t="n">
-        <v>57.42</v>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.62</v>
+      </c>
+      <c r="I120" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="10" t="n">
-        <v>1.288</v>
+        <v>2.826</v>
       </c>
       <c r="K120" s="10" t="n">
-        <v>1.196</v>
+        <v>2.712</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="15" t="inlineStr"/>
@@ -5919,39 +5919,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D121" s="10" t="n">
-        <v>0.845</v>
+        <v>0.745</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>-0.0174</v>
+        <v>-0.0197</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>771200</v>
+        <v>990500</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="H121" t="n">
-        <v>44.54</v>
-      </c>
-      <c r="I121" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.49</v>
+      </c>
+      <c r="I121" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="10" t="n">
-        <v>0.878</v>
+        <v>0.745</v>
       </c>
       <c r="K121" s="10" t="n">
-        <v>0.867</v>
+        <v>0.709</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="15" t="inlineStr"/>
@@ -5964,39 +5964,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D122" s="10" t="n">
-        <v>1.27</v>
+        <v>0.855</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>-0.0155</v>
+        <v>-0.0229</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>753000</v>
+        <v>949700</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H122" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="I122" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.98</v>
+      </c>
+      <c r="I122" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="10" t="n">
-        <v>1.139</v>
+        <v>0.84</v>
       </c>
       <c r="K122" s="10" t="n">
-        <v>0.999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="15" t="inlineStr"/>
@@ -6009,39 +6009,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D123" s="10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E123" s="11" t="n">
-        <v>-0.0179</v>
+        <v>1.35</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>752100</v>
+        <v>932800</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="H123" t="n">
-        <v>43.58</v>
-      </c>
-      <c r="I123" s="16" t="inlineStr">
+        <v>58.56</v>
+      </c>
+      <c r="I123" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J123" s="10" t="n">
-        <v>2.81</v>
+        <v>1.289</v>
       </c>
       <c r="K123" s="10" t="n">
-        <v>2.94</v>
+        <v>1.197</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="15" t="inlineStr"/>
@@ -6054,39 +6054,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D124" s="10" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="E124" s="11" t="n">
-        <v>-0.0229</v>
+        <v>7.85</v>
+      </c>
+      <c r="E124" s="18" t="n">
+        <v>0.0026</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>748400</v>
+        <v>925000</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="H124" t="n">
-        <v>54.98</v>
-      </c>
-      <c r="I124" s="16" t="inlineStr">
+        <v>45.92</v>
+      </c>
+      <c r="I124" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J124" s="10" t="n">
-        <v>0.84</v>
+        <v>7.892</v>
       </c>
       <c r="K124" s="10" t="n">
-        <v>0.8070000000000001</v>
+        <v>7.914</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="15" t="inlineStr"/>
@@ -6099,39 +6099,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D125" s="10" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E125" s="17" t="n">
-        <v>0.0062</v>
+        <v>1.29</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>747300</v>
+        <v>890000</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="H125" t="n">
-        <v>69.41</v>
-      </c>
-      <c r="I125" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.06999999999999</v>
+      </c>
+      <c r="I125" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="10" t="n">
-        <v>0.752</v>
+        <v>1.141</v>
       </c>
       <c r="K125" s="10" t="n">
-        <v>0.68</v>
+        <v>0.999</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="15" t="inlineStr"/>
@@ -6144,28 +6144,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="D126" s="10" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>0.0102</v>
+        <v>3.06</v>
+      </c>
+      <c r="E126" s="18" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>722200</v>
+        <v>855300</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>0.19</v>
+        <v>0.77</v>
       </c>
       <c r="H126" t="n">
-        <v>56.72</v>
+        <v>65.27</v>
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="J126" s="10" t="n">
-        <v>3.85</v>
+        <v>2.853</v>
       </c>
       <c r="K126" s="10" t="n">
-        <v>3.776</v>
+        <v>2.856</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="15" t="inlineStr"/>
@@ -6189,39 +6189,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D127" s="10" t="n">
-        <v>0.51</v>
+        <v>1.03</v>
       </c>
       <c r="E127" s="18" t="n">
-        <v>0</v>
+        <v>0.0198</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>712600</v>
+        <v>845800</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="H127" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="I127" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.18</v>
+      </c>
+      <c r="I127" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="10" t="n">
-        <v>0.494</v>
+        <v>1.052</v>
       </c>
       <c r="K127" s="10" t="n">
-        <v>0.485</v>
+        <v>1.11</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="15" t="inlineStr"/>
@@ -6234,28 +6234,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D128" s="10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E128" s="17" t="n">
-        <v>0.0061</v>
+        <v>0.855</v>
+      </c>
+      <c r="E128" s="11" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>709000</v>
+        <v>842800</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H128" t="n">
-        <v>58.06</v>
+        <v>45.84</v>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="J128" s="10" t="n">
-        <v>13.132</v>
+        <v>0.879</v>
       </c>
       <c r="K128" s="10" t="n">
-        <v>13.259</v>
+        <v>0.868</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="15" t="inlineStr"/>
@@ -6279,39 +6279,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D129" s="10" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E129" s="17" t="n">
-        <v>0.0205</v>
+        <v>0.605</v>
+      </c>
+      <c r="E129" s="11" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F129" s="12" t="n">
-        <v>701900</v>
+        <v>827600</v>
       </c>
       <c r="G129" s="13" t="n">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="H129" t="n">
-        <v>44.49</v>
-      </c>
-      <c r="I129" s="16" t="inlineStr">
+        <v>40.64</v>
+      </c>
+      <c r="I129" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J129" s="10" t="n">
-        <v>2.51</v>
+        <v>0.636</v>
       </c>
       <c r="K129" s="10" t="n">
-        <v>2.623</v>
+        <v>0.676</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="15" t="inlineStr"/>
@@ -6333,21 +6333,21 @@
         </is>
       </c>
       <c r="D130" s="10" t="n">
-        <v>0.66</v>
+        <v>0.665</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>-0.0222</v>
+        <v>-0.0148</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>699400</v>
+        <v>796500</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H130" t="n">
-        <v>43.11</v>
-      </c>
-      <c r="I130" s="16" t="inlineStr">
+        <v>43.74</v>
+      </c>
+      <c r="I130" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6369,28 +6369,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D131" s="10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E131" s="11" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.47</v>
+      </c>
+      <c r="E131" s="18" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F131" s="12" t="n">
-        <v>695200</v>
+        <v>794500</v>
       </c>
       <c r="G131" s="13" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="H131" t="n">
-        <v>58.16</v>
+        <v>47.14</v>
       </c>
       <c r="I131" s="14" t="inlineStr">
         <is>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="J131" s="10" t="n">
-        <v>0.636</v>
+        <v>1.467</v>
       </c>
       <c r="K131" s="10" t="n">
-        <v>0.634</v>
+        <v>1.578</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="15" t="inlineStr"/>
@@ -6414,28 +6414,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D132" s="10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E132" s="11" t="n">
-        <v>-0.0068</v>
+        <v>2.52</v>
+      </c>
+      <c r="E132" s="18" t="n">
+        <v>0.0328</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>694500</v>
+        <v>789300</v>
       </c>
       <c r="G132" s="13" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="H132" t="n">
-        <v>56.62</v>
+        <v>51.36</v>
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
@@ -6443,10 +6443,10 @@
         </is>
       </c>
       <c r="J132" s="10" t="n">
-        <v>2.826</v>
+        <v>2.475</v>
       </c>
       <c r="K132" s="10" t="n">
-        <v>2.712</v>
+        <v>2.611</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="15" t="inlineStr"/>
@@ -6459,39 +6459,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D133" s="10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E133" s="17" t="n">
-        <v>0.0198</v>
+        <v>3.98</v>
+      </c>
+      <c r="E133" s="18" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F133" s="12" t="n">
-        <v>690600</v>
+        <v>778200</v>
       </c>
       <c r="G133" s="13" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="H133" t="n">
-        <v>43.18</v>
-      </c>
-      <c r="I133" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.09</v>
+      </c>
+      <c r="I133" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="10" t="n">
-        <v>1.052</v>
+        <v>3.851</v>
       </c>
       <c r="K133" s="10" t="n">
-        <v>1.11</v>
+        <v>3.776</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="15" t="inlineStr"/>
@@ -6504,39 +6504,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>2.29</v>
+        <v>2.74</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0214</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>671200</v>
+        <v>762900</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H134" t="n">
-        <v>51.02</v>
-      </c>
-      <c r="I134" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43</v>
+      </c>
+      <c r="I134" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="10" t="n">
-        <v>2.297</v>
+        <v>2.809</v>
       </c>
       <c r="K134" s="10" t="n">
-        <v>2.225</v>
+        <v>2.94</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="15" t="inlineStr"/>
@@ -6549,39 +6549,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D135" s="10" t="n">
-        <v>0.775</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E135" s="18" t="n">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="F135" s="12" t="n">
-        <v>667100</v>
+        <v>759200</v>
       </c>
       <c r="G135" s="13" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="H135" t="n">
-        <v>22.02</v>
-      </c>
-      <c r="I135" s="16" t="inlineStr">
+        <v>69.41</v>
+      </c>
+      <c r="I135" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J135" s="10" t="n">
-        <v>0.855</v>
+        <v>0.752</v>
       </c>
       <c r="K135" s="10" t="n">
-        <v>1.017</v>
+        <v>0.68</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="15" t="inlineStr"/>
@@ -6594,39 +6594,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D136" s="10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E136" s="11" t="n">
-        <v>-0.011</v>
+        <v>13.28</v>
+      </c>
+      <c r="E136" s="18" t="n">
+        <v>0.004500000000000001</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>653400</v>
+        <v>758900</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>0.8</v>
+        <v>0.14</v>
       </c>
       <c r="H136" t="n">
-        <v>34.68</v>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.23</v>
+      </c>
+      <c r="I136" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>13.13</v>
       </c>
       <c r="K136" s="10" t="n">
-        <v>0.966</v>
+        <v>13.259</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="15" t="inlineStr"/>
@@ -6639,28 +6639,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MNRB</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D137" s="10" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E137" s="18" t="n">
-        <v>0</v>
+        <v>10.98</v>
+      </c>
+      <c r="E137" s="11" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F137" s="12" t="n">
-        <v>640100</v>
+        <v>748900</v>
       </c>
       <c r="G137" s="13" t="n">
-        <v>1.22</v>
+        <v>0.2</v>
       </c>
       <c r="H137" t="n">
-        <v>39.16</v>
+        <v>60.61</v>
       </c>
       <c r="I137" s="14" t="inlineStr">
         <is>
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="J137" s="10" t="n">
-        <v>2.56</v>
+        <v>10.598</v>
       </c>
       <c r="K137" s="10" t="n">
-        <v>2.667</v>
+        <v>9.971</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="15" t="inlineStr"/>
@@ -6684,39 +6684,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="E138" s="11" t="n">
-        <v>-0.0127</v>
+        <v>2.5</v>
+      </c>
+      <c r="E138" s="18" t="n">
+        <v>0.0246</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>636700</v>
+        <v>732300</v>
       </c>
       <c r="G138" s="13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="H138" t="n">
-        <v>59.25</v>
-      </c>
-      <c r="I138" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.78</v>
+      </c>
+      <c r="I138" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="10" t="n">
-        <v>10.592</v>
+        <v>2.511</v>
       </c>
       <c r="K138" s="10" t="n">
-        <v>9.970000000000001</v>
+        <v>2.623</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
@@ -6729,39 +6729,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>KEEMING</t>
         </is>
       </c>
       <c r="D139" s="10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E139" s="11" t="n">
-        <v>-0.0017</v>
+        <v>2.87</v>
+      </c>
+      <c r="E139" s="18" t="n">
+        <v>0.0361</v>
       </c>
       <c r="F139" s="12" t="n">
-        <v>634500</v>
+        <v>725800</v>
       </c>
       <c r="G139" s="13" t="n">
-        <v>0.15</v>
+        <v>0.95</v>
       </c>
       <c r="H139" t="n">
-        <v>58.39</v>
-      </c>
-      <c r="I139" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.73</v>
+      </c>
+      <c r="I139" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="10" t="n">
-        <v>5.573</v>
+        <v>2.611</v>
       </c>
       <c r="K139" s="10" t="n">
-        <v>5.4</v>
+        <v>2.54</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="15" t="inlineStr"/>
@@ -6774,39 +6774,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D140" s="10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E140" s="11" t="n">
-        <v>-0.0053</v>
+        <v>0.78</v>
+      </c>
+      <c r="E140" s="18" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F140" s="12" t="n">
-        <v>628800</v>
+        <v>721700</v>
       </c>
       <c r="G140" s="13" t="n">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
       <c r="H140" t="n">
-        <v>40.07</v>
-      </c>
-      <c r="I140" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.74</v>
+      </c>
+      <c r="I140" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="10" t="n">
-        <v>0.95</v>
+        <v>0.856</v>
       </c>
       <c r="K140" s="10" t="n">
-        <v>1.023</v>
+        <v>1.017</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="15" t="inlineStr"/>
@@ -6819,28 +6819,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D141" s="10" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="E141" s="11" t="n">
-        <v>-0.0019</v>
+        <v>0.51</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="12" t="n">
-        <v>625900</v>
+        <v>713300</v>
       </c>
       <c r="G141" s="13" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="H141" t="n">
-        <v>55.01</v>
+        <v>58.07</v>
       </c>
       <c r="I141" s="14" t="inlineStr">
         <is>
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="J141" s="10" t="n">
-        <v>5.079</v>
+        <v>0.494</v>
       </c>
       <c r="K141" s="10" t="n">
-        <v>5.033</v>
+        <v>0.485</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="15" t="inlineStr"/>
@@ -6864,39 +6864,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>MNRB</t>
         </is>
       </c>
       <c r="D142" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E142" s="11" t="n">
-        <v>-0.0164</v>
+        <v>2.53</v>
+      </c>
+      <c r="E142" s="18" t="n">
+        <v>0.004</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>623500</v>
+        <v>702800</v>
       </c>
       <c r="G142" s="13" t="n">
-        <v>0.13</v>
+        <v>1.34</v>
       </c>
       <c r="H142" t="n">
-        <v>62.84</v>
-      </c>
-      <c r="I142" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.16</v>
+      </c>
+      <c r="I142" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>2.561</v>
       </c>
       <c r="K142" s="10" t="n">
-        <v>0.494</v>
+        <v>2.667</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="15" t="inlineStr"/>
@@ -6909,28 +6909,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>KEEMING</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D143" s="10" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E143" s="17" t="n">
-        <v>0.0361</v>
+        <v>0.64</v>
+      </c>
+      <c r="E143" s="11" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F143" s="12" t="n">
-        <v>618300</v>
+        <v>695200</v>
       </c>
       <c r="G143" s="13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H143" t="n">
-        <v>65.73</v>
+        <v>58.16</v>
       </c>
       <c r="I143" s="14" t="inlineStr">
         <is>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="J143" s="10" t="n">
-        <v>2.611</v>
+        <v>0.636</v>
       </c>
       <c r="K143" s="10" t="n">
-        <v>2.54</v>
+        <v>0.634</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="15" t="inlineStr"/>
@@ -6954,39 +6954,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D144" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E144" s="11" t="n">
-        <v>-0.0164</v>
+        <v>5.17</v>
+      </c>
+      <c r="E144" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>617200</v>
+        <v>689700</v>
       </c>
       <c r="G144" s="13" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="H144" t="n">
-        <v>39.77</v>
-      </c>
-      <c r="I144" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.59</v>
+      </c>
+      <c r="I144" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J144" s="10" t="n">
-        <v>0.636</v>
+        <v>5.08</v>
       </c>
       <c r="K144" s="10" t="n">
-        <v>0.676</v>
+        <v>5.033</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -6999,28 +6999,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D145" s="10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E145" s="17" t="n">
-        <v>0.0069</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E145" s="11" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F145" s="12" t="n">
-        <v>616900</v>
+        <v>668700</v>
       </c>
       <c r="G145" s="13" t="n">
-        <v>0.88</v>
+        <v>0.14</v>
       </c>
       <c r="H145" t="n">
-        <v>44.68</v>
+        <v>40.07</v>
       </c>
       <c r="I145" s="14" t="inlineStr">
         <is>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="J145" s="10" t="n">
-        <v>1.465</v>
+        <v>0.95</v>
       </c>
       <c r="K145" s="10" t="n">
-        <v>1.578</v>
+        <v>1.023</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="15" t="inlineStr"/>
@@ -7044,39 +7044,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D146" s="10" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E146" s="17" t="n">
-        <v>0.0287</v>
+        <v>0.605</v>
+      </c>
+      <c r="E146" s="11" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>603100</v>
+        <v>663700</v>
       </c>
       <c r="G146" s="13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H146" t="n">
-        <v>50.38</v>
-      </c>
-      <c r="I146" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.16</v>
+      </c>
+      <c r="I146" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J146" s="10" t="n">
-        <v>2.474</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K146" s="10" t="n">
-        <v>2.611</v>
+        <v>0.494</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="15" t="inlineStr"/>
@@ -7089,39 +7089,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D147" s="10" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E147" s="17" t="n">
-        <v>0.0091</v>
+        <v>0.905</v>
+      </c>
+      <c r="E147" s="11" t="n">
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F147" s="12" t="n">
-        <v>600600</v>
+        <v>662600</v>
       </c>
       <c r="G147" s="13" t="n">
-        <v>0.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H147" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="I147" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.8</v>
+      </c>
+      <c r="I147" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="10" t="n">
-        <v>0.553</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K147" s="10" t="n">
-        <v>0.587</v>
+        <v>0.966</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="15" t="inlineStr"/>
@@ -7134,39 +7134,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D148" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E148" s="18" t="n">
-        <v>0</v>
+        <v>5.8</v>
+      </c>
+      <c r="E148" s="11" t="n">
+        <v>-0.0017</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>587900</v>
+        <v>648000</v>
       </c>
       <c r="G148" s="13" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H148" t="n">
-        <v>59.38</v>
-      </c>
-      <c r="I148" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.39</v>
+      </c>
+      <c r="I148" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="10" t="n">
-        <v>7.872</v>
+        <v>5.573</v>
       </c>
       <c r="K148" s="10" t="n">
-        <v>7.867</v>
+        <v>5.4</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -7179,28 +7179,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D149" s="10" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E149" s="11" t="n">
-        <v>-0.008500000000000001</v>
+        <v>4.36</v>
+      </c>
+      <c r="E149" s="18" t="n">
+        <v>0.0023</v>
       </c>
       <c r="F149" s="12" t="n">
-        <v>566300</v>
+        <v>633300</v>
       </c>
       <c r="G149" s="13" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="H149" t="n">
-        <v>56.05</v>
+        <v>48.44</v>
       </c>
       <c r="I149" s="14" t="inlineStr">
         <is>
@@ -7208,10 +7208,10 @@
         </is>
       </c>
       <c r="J149" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>4.333</v>
       </c>
       <c r="K149" s="10" t="n">
-        <v>0.532</v>
+        <v>4.578</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="15" t="inlineStr"/>
@@ -7224,39 +7224,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D150" s="10" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E150" s="18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E150" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>564100</v>
+        <v>629500</v>
       </c>
       <c r="G150" s="13" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="H150" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="I150" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.53</v>
+      </c>
+      <c r="I150" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="10" t="n">
-        <v>0.825</v>
+        <v>1.383</v>
       </c>
       <c r="K150" s="10" t="n">
-        <v>0.853</v>
+        <v>1.354</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -7284,15 +7284,15 @@
         <v>-0.0073</v>
       </c>
       <c r="F151" s="12" t="n">
-        <v>531400</v>
+        <v>613900</v>
       </c>
       <c r="G151" s="13" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="H151" t="n">
         <v>58.43</v>
       </c>
-      <c r="I151" s="16" t="inlineStr">
+      <c r="I151" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -7314,28 +7314,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D152" s="10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E152" s="17" t="n">
-        <v>0.0132</v>
+        <v>8</v>
+      </c>
+      <c r="E152" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>524800</v>
+        <v>600700</v>
       </c>
       <c r="G152" s="13" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="H152" t="n">
-        <v>61.4</v>
+        <v>59.38</v>
       </c>
       <c r="I152" s="14" t="inlineStr">
         <is>
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="J152" s="10" t="n">
-        <v>2.153</v>
+        <v>7.872</v>
       </c>
       <c r="K152" s="10" t="n">
-        <v>2.218</v>
+        <v>7.867</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="15" t="inlineStr"/>
@@ -7359,39 +7359,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D153" s="10" t="n">
-        <v>0.635</v>
+        <v>0.555</v>
       </c>
       <c r="E153" s="18" t="n">
-        <v>0</v>
+        <v>0.0091</v>
       </c>
       <c r="F153" s="12" t="n">
-        <v>517400</v>
+        <v>600600</v>
       </c>
       <c r="G153" s="13" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H153" t="n">
-        <v>51.45</v>
-      </c>
-      <c r="I153" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.31</v>
+      </c>
+      <c r="I153" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="10" t="n">
-        <v>0.634</v>
+        <v>0.553</v>
       </c>
       <c r="K153" s="10" t="n">
-        <v>0.625</v>
+        <v>0.587</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="15" t="inlineStr"/>
@@ -7404,28 +7404,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D154" s="10" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="E154" s="11" t="n">
-        <v>-0.0023</v>
+        <v>0.585</v>
+      </c>
+      <c r="E154" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>514500</v>
+        <v>580000</v>
       </c>
       <c r="G154" s="13" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="H154" t="n">
-        <v>46.99</v>
+        <v>57.26</v>
       </c>
       <c r="I154" s="14" t="inlineStr">
         <is>
@@ -7433,10 +7433,10 @@
         </is>
       </c>
       <c r="J154" s="10" t="n">
-        <v>4.331</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K154" s="10" t="n">
-        <v>4.578</v>
+        <v>0.533</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="15" t="inlineStr"/>
@@ -7449,28 +7449,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D155" s="10" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="E155" s="11" t="n">
-        <v>-0.0105</v>
+        <v>2.28</v>
+      </c>
+      <c r="E155" s="18" t="n">
+        <v>0.0044</v>
       </c>
       <c r="F155" s="12" t="n">
-        <v>500600</v>
+        <v>573400</v>
       </c>
       <c r="G155" s="13" t="n">
-        <v>0.11</v>
+        <v>0.41</v>
       </c>
       <c r="H155" t="n">
-        <v>55.67</v>
+        <v>60.17</v>
       </c>
       <c r="I155" s="14" t="inlineStr">
         <is>
@@ -7478,16 +7478,376 @@
         </is>
       </c>
       <c r="J155" s="10" t="n">
-        <v>7.348</v>
+        <v>2.151</v>
       </c>
       <c r="K155" s="10" t="n">
-        <v>6.997</v>
+        <v>2.218</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="15" t="inlineStr"/>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="E156" s="18" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="F156" s="12" t="n">
+        <v>566300</v>
+      </c>
+      <c r="G156" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H156" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="I156" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="10" t="n">
+        <v>3.274</v>
+      </c>
+      <c r="K156" s="10" t="n">
+        <v>3.506</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="15" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E157" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="12" t="n">
+        <v>564100</v>
+      </c>
+      <c r="G157" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H157" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="I157" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="10" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="K157" s="10" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="15" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>MAXIS</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E158" s="18" t="n">
+        <v>0.0199</v>
+      </c>
+      <c r="F158" s="12" t="n">
+        <v>532600</v>
+      </c>
+      <c r="G158" s="13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H158" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="I158" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="10" t="n">
+        <v>3.545</v>
+      </c>
+      <c r="K158" s="10" t="n">
+        <v>3.572</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="15" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D159" s="10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E159" s="18" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="F159" s="12" t="n">
+        <v>530200</v>
+      </c>
+      <c r="G159" s="13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H159" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="I159" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J159" s="10" t="n">
+        <v>1.817</v>
+      </c>
+      <c r="K159" s="10" t="n">
+        <v>1.696</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="15" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E160" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="12" t="n">
+        <v>529100</v>
+      </c>
+      <c r="G160" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H160" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="I160" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="10" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K160" s="10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="15" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="E161" s="11" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F161" s="12" t="n">
+        <v>525400</v>
+      </c>
+      <c r="G161" s="13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H161" t="n">
+        <v>56.19</v>
+      </c>
+      <c r="I161" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J161" s="10" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="K161" s="10" t="n">
+        <v>6.998</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="15" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E162" s="11" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="F162" s="12" t="n">
+        <v>519200</v>
+      </c>
+      <c r="G162" s="13" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H162" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="I162" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="10" t="n">
+        <v>1.628</v>
+      </c>
+      <c r="K162" s="10" t="n">
+        <v>1.693</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="15" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>9075</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>THETA</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E163" s="18" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="F163" s="12" t="n">
+        <v>513000</v>
+      </c>
+      <c r="G163" s="13" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H163" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="I163" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="10" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K163" s="10" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M155"/>
+  <autoFilter ref="A1:M163"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
+++ b/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
   </fonts>
   <fills count="4">
@@ -97,8 +97,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.645</v>
+        <v>0.665</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0488</v>
+        <v>0.08130000000000001</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4399800</v>
+        <v>5785100</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>61.52</v>
+        <v>63.61</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.588</v>
+        <v>0.59</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.498</v>
@@ -599,7 +599,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 61.52未超买，现价高于50日均线约29.5%，技术面信号可靠性较高。</t>
+          <t>SAR转多信号，RSI 63.61未超买，现价高于50日均线约33.5%，技术面信号偏可靠。</t>
         </is>
       </c>
     </row>
@@ -626,10 +626,10 @@
         <v>0.1386</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>10832200</v>
+        <v>11259800</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>66.59999999999999</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号出现，但RSI 66.6已接近超买区，现价1.15远高于50日均线0.668，偏离较大，信号可靠性需谨慎看待。</t>
+          <t>SAR转多信号，RSI 66.6接近超买区，现价1.15远高于50日均线0.668，偏离较大，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.655</v>
+        <v>0.66</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>-0.0076</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1039200</v>
+        <v>1204200</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>68.29000000000001</v>
+        <v>70.66</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.619</v>
+        <v>0.62</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.552</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，但RSI 68.29接近超买区，现价高于50日均线约18.7%，信号可靠性中等。</t>
+          <t>SAR转多信号出现，但RSI 70.66已接近超买区，现价高于50日均线约19.6%，短期涨幅偏大，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -726,19 +726,19 @@
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0.08</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>-0.0588</v>
+        <v>0</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>113894300</v>
+        <v>121678400</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="H5" t="n">
-        <v>36.06</v>
+        <v>37.22</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -773,19 +773,19 @@
       <c r="D6" s="10" t="n">
         <v>0.055</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>35737600</v>
+        <v>37379100</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="H6" t="n">
         <v>56.53</v>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -818,19 +818,19 @@
       <c r="D7" s="10" t="n">
         <v>0.04</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="17" t="n">
         <v>-0.1111</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>33069400</v>
+        <v>35119400</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>2.81</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
         <v>27.36</v>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -852,39 +852,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0170</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KANGER</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>-0.3333</v>
+        <v>0.495</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>27286500</v>
+        <v>34597400</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>35.82</v>
+        <v>0.91</v>
       </c>
       <c r="H8" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.61</v>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.019</v>
+        <v>0.441</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>0.023</v>
+        <v>0.343</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="15" t="inlineStr"/>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.0513</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>25623200</v>
+        <v>29387100</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="H9" t="n">
-        <v>40.45</v>
+        <v>38.58</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="15" t="inlineStr"/>
@@ -951,30 +951,30 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>-0.0634</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>-0.0352</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>25380400</v>
+        <v>28320900</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="H10" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
+        <v>59.48</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.671</v>
+        <v>0.673</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>0.58</v>
+        <v>0.581</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="15" t="inlineStr"/>
@@ -998,14 +998,14 @@
       <c r="D11" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="17" t="n">
         <v>-0.0141</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>24932100</v>
+        <v>27568500</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="H11" t="n">
         <v>64.94</v>
@@ -1032,39 +1032,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0170</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>KANGER</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>-0.3333</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>20292600</v>
+        <v>27296500</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.53</v>
+        <v>35.83</v>
       </c>
       <c r="H12" t="n">
-        <v>72.61</v>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.25</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.441</v>
+        <v>0.019</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>0.343</v>
+        <v>0.023</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="15" t="inlineStr"/>
@@ -1086,19 +1086,19 @@
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>-0.0103</v>
+        <v>0.965</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>18970000</v>
+        <v>25162000</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="H13" t="n">
-        <v>67.83</v>
+        <v>69.03</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.887</v>
+        <v>0.888</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>0.782</v>
@@ -1122,39 +1122,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>-0.0323</v>
+        <v>0.12</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>14825300</v>
+        <v>16325300</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.91</v>
+        <v>3.24</v>
       </c>
       <c r="H14" t="n">
-        <v>24.71</v>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.66</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="10" t="n">
-        <v>7.273</v>
+        <v>0.103</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>7.583</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="15" t="inlineStr"/>
@@ -1167,39 +1167,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>0.0435</v>
+        <v>6.89</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>-0.0309</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>14745800</v>
+        <v>15852200</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>2.93</v>
+        <v>0.97</v>
       </c>
       <c r="H15" t="n">
-        <v>73.66</v>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.96</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.103</v>
+        <v>7.274</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>0.08699999999999999</v>
+        <v>7.583</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="15" t="inlineStr"/>
@@ -1212,39 +1212,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.82</v>
+        <v>0.3</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>-0.0061</v>
+        <v>0</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>12050400</v>
+        <v>13385900</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="H16" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.44</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.306</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.304</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="15" t="inlineStr"/>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>-0.0312</v>
+        <v>0.47</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>12011500</v>
+        <v>13215900</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H17" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
+        <v>60.36</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1302,39 +1302,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>0.0185</v>
+        <v>0.82</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>11233800</v>
+        <v>12846500</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>1.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>47.51</v>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.1</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.279</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>0.282</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="15" t="inlineStr"/>
@@ -1347,28 +1347,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>0.0267</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>10960000</v>
+        <v>12131300</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.29</v>
+        <v>1.17</v>
       </c>
       <c r="H19" t="n">
-        <v>47.74</v>
+        <v>43.88</v>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.156</v>
+        <v>0.387</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>0.156</v>
+        <v>0.401</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="15" t="inlineStr"/>
@@ -1392,39 +1392,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>10471500</v>
+        <v>11620100</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="H20" t="n">
-        <v>39.44</v>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
+        <v>47.34</v>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.306</v>
+        <v>0.867</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>0.304</v>
+        <v>0.868</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="15" t="inlineStr"/>
@@ -1437,39 +1437,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.38</v>
+        <v>0.275</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>0.0133</v>
+        <v>0.0185</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>9807500</v>
+        <v>11493000</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>0.95</v>
+        <v>1.81</v>
       </c>
       <c r="H21" t="n">
-        <v>36.71</v>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
+        <v>47.51</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.387</v>
+        <v>0.279</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>0.401</v>
+        <v>0.282</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="15" t="inlineStr"/>
@@ -1482,39 +1482,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E22" s="18" t="n">
-        <v>0.0058</v>
+        <v>0.155</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>9645000</v>
+        <v>11060000</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.46</v>
+        <v>0.29</v>
       </c>
       <c r="H22" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.74</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.867</v>
+        <v>0.156</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>0.868</v>
+        <v>0.156</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="15" t="inlineStr"/>
@@ -1536,21 +1536,21 @@
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>-0.0217</v>
+        <v>0.22</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>8421700</v>
+        <v>10278600</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="H23" t="n">
-        <v>51.02</v>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
+        <v>47.99</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1568,28 +1568,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E24" s="16" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E24" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>7941100</v>
+        <v>9132500</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H24" t="n">
-        <v>37.77</v>
+        <v>50.93</v>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.153</v>
+        <v>0.774</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>0.172</v>
+        <v>0.775</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="15" t="inlineStr"/>
@@ -1613,28 +1613,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>0.0135</v>
+        <v>0.215</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>7758900</v>
+        <v>8826400</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.27</v>
+        <v>1.11</v>
       </c>
       <c r="H25" t="n">
-        <v>66.83</v>
+        <v>85.94</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="J25" s="10" t="n">
-        <v>2.035</v>
+        <v>0.145</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>1.838</v>
+        <v>0.122</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="15" t="inlineStr"/>
@@ -1658,28 +1658,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E26" s="16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E26" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>7662800</v>
+        <v>8253800</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.49</v>
+        <v>0.65</v>
       </c>
       <c r="H26" t="n">
-        <v>50.93</v>
+        <v>37.77</v>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.774</v>
+        <v>0.153</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>0.775</v>
+        <v>0.172</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="15" t="inlineStr"/>
@@ -1703,39 +1703,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>0</v>
+        <v>2.25</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>0.0135</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>7643900</v>
+        <v>8099500</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.66</v>
+        <v>0.28</v>
       </c>
       <c r="H27" t="n">
-        <v>46</v>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.83</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.283</v>
+        <v>2.035</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>0.279</v>
+        <v>1.838</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="15" t="inlineStr"/>
@@ -1748,39 +1748,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>0.0233</v>
+        <v>0.275</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>7059100</v>
+        <v>7648900</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="H28" t="n">
-        <v>86.52</v>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46</v>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.146</v>
+        <v>0.283</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>0.122</v>
+        <v>0.279</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="15" t="inlineStr"/>
@@ -1793,28 +1793,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>-0.0263</v>
+        <v>2.16</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>6601000</v>
+        <v>7046900</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.36</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>49.13</v>
+        <v>53.36</v>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.185</v>
+        <v>2.109</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0.187</v>
+        <v>2.225</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="15" t="inlineStr"/>
@@ -1838,28 +1838,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>0.0133</v>
+        <v>0.185</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>6528600</v>
+        <v>6655200</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="H30" t="n">
-        <v>58.8</v>
+        <v>49.13</v>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.374</v>
+        <v>0.185</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>0.37</v>
+        <v>0.187</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="15" t="inlineStr"/>
@@ -1883,33 +1883,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.205</v>
+        <v>0.38</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>0.025</v>
+        <v>0.0133</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>6150700</v>
+        <v>6618600</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="n"/>
-      <c r="K31" s="10" t="n"/>
+        <v>0.96</v>
+      </c>
+      <c r="H31" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="K31" s="10" t="n">
+        <v>0.37</v>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="15" t="inlineStr"/>
     </row>
@@ -1921,40 +1928,33 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2.17</v>
+        <v>0.205</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.025</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>5942900</v>
+        <v>6218700</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H32" t="n">
-        <v>54.18</v>
-      </c>
-      <c r="I32" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="K32" s="10" t="n">
-        <v>2.225</v>
-      </c>
+        <v>0.24</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="15" t="inlineStr"/>
     </row>
@@ -1966,28 +1966,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>10.02</v>
+        <v>0.405</v>
       </c>
       <c r="E33" s="18" t="n">
-        <v>0.003</v>
+        <v>0.0125</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>5068100</v>
+        <v>5553500</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="H33" t="n">
-        <v>50.37</v>
+        <v>52.36</v>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="J33" s="10" t="n">
-        <v>9.996</v>
+        <v>0.402</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>10.095</v>
+        <v>0.385</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="15" t="inlineStr"/>
@@ -2011,28 +2011,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>0.009399999999999999</v>
+        <v>9.99</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>5049200</v>
+        <v>5385700</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>1.16</v>
+        <v>0.46</v>
       </c>
       <c r="H34" t="n">
-        <v>80.70999999999999</v>
+        <v>48.09</v>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.472</v>
+        <v>9.994</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>0.441</v>
+        <v>10.094</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="15" t="inlineStr"/>
@@ -2056,39 +2056,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>4.75</v>
+        <v>0.535</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>5026300</v>
+        <v>5310300</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.23</v>
+        <v>1.22</v>
       </c>
       <c r="H35" t="n">
-        <v>50.86</v>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.70999999999999</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="10" t="n">
-        <v>4.731</v>
+        <v>0.472</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>4.795</v>
+        <v>0.441</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="15" t="inlineStr"/>
@@ -2101,39 +2101,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.405</v>
+        <v>4.75</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>0.0125</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>4659500</v>
+        <v>5291700</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.39</v>
+        <v>0.25</v>
       </c>
       <c r="H36" t="n">
-        <v>52.36</v>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.86</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.402</v>
+        <v>4.731</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0.385</v>
+        <v>4.795</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="15" t="inlineStr"/>
@@ -2146,39 +2146,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>0.0476</v>
+        <v>0.645</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>4564400</v>
+        <v>5266100</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="H37" t="n">
-        <v>36.82</v>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.40000000000001</v>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.125</v>
+        <v>0.629</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.144</v>
+        <v>0.62</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="15" t="inlineStr"/>
@@ -2191,39 +2191,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E38" s="11" t="n">
-        <v>-0.0337</v>
+        <v>1.3</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>4362600</v>
+        <v>5073400</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.3</v>
+        <v>1.27</v>
       </c>
       <c r="H38" t="n">
-        <v>31.06</v>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.2</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.468</v>
+        <v>1.41</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0.585</v>
+        <v>1.447</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="15" t="inlineStr"/>
@@ -2236,28 +2236,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>0</v>
+        <v>0.43</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>-0.0337</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>4334200</v>
+        <v>4756800</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.41</v>
+        <v>0.33</v>
       </c>
       <c r="H39" t="n">
-        <v>66.40000000000001</v>
+        <v>31.06</v>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.629</v>
+        <v>0.468</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>0.62</v>
+        <v>0.585</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="15" t="inlineStr"/>
@@ -2281,39 +2281,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>0</v>
+        <v>0.11</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>4156500</v>
+        <v>4634400</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>1.17</v>
+        <v>0.27</v>
       </c>
       <c r="H40" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I40" s="17" t="inlineStr">
+        <v>36.82</v>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.295</v>
+        <v>0.125</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0.295</v>
+        <v>0.144</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="15" t="inlineStr"/>
@@ -2326,39 +2326,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FPI</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>0.0261</v>
+        <v>0.295</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>3872300</v>
+        <v>4156500</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="H41" t="n">
-        <v>67.86</v>
-      </c>
-      <c r="I41" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="10" t="n">
-        <v>1.098</v>
+        <v>0.295</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>1.099</v>
+        <v>0.295</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="15" t="inlineStr"/>
@@ -2371,39 +2371,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>0.0156</v>
+        <v>2.6</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>-0.0038</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>3685300</v>
+        <v>4074500</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.92</v>
+        <v>0.24</v>
       </c>
       <c r="H42" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="I42" s="17" t="inlineStr">
+        <v>50.58</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J42" s="10" t="n">
-        <v>1.41</v>
+        <v>2.595</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>1.447</v>
+        <v>2.571</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="15" t="inlineStr"/>
@@ -2416,39 +2416,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <v>-0.0208</v>
+        <v>1.14</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>3662800</v>
+        <v>3946500</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>1.39</v>
+        <v>0.4</v>
       </c>
       <c r="H43" t="n">
-        <v>55.99</v>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.47</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.457</v>
+        <v>1.19</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0.449</v>
+        <v>1.271</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="15" t="inlineStr"/>
@@ -2461,28 +2461,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>FPI</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>2.69</v>
+        <v>1.19</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>0.0075</v>
+        <v>0.0348</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>3549200</v>
+        <v>3910600</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>57.86</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="J44" s="10" t="n">
-        <v>2.612</v>
+        <v>1.099</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>2.599</v>
+        <v>1.1</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="15" t="inlineStr"/>
@@ -2506,28 +2506,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>-0.0313</v>
+        <v>2.7</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>3520500</v>
+        <v>3820800</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="H45" t="n">
-        <v>48.93</v>
+        <v>58.59</v>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="J45" s="10" t="n">
-        <v>0.159</v>
+        <v>2.613</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>0.15</v>
+        <v>2.6</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="15" t="inlineStr"/>
@@ -2551,28 +2551,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>3519000</v>
+        <v>3792000</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.24</v>
+        <v>1.44</v>
       </c>
       <c r="H46" t="n">
-        <v>39.52</v>
+        <v>55.99</v>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="J46" s="10" t="n">
-        <v>1.556</v>
+        <v>0.457</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>1.822</v>
+        <v>0.449</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="15" t="inlineStr"/>
@@ -2596,28 +2596,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E47" s="16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E47" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>3513700</v>
+        <v>3740000</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="H47" t="n">
-        <v>37.11</v>
+        <v>39.52</v>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="J47" s="10" t="n">
-        <v>1.275</v>
+        <v>1.556</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>1.469</v>
+        <v>1.822</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="15" t="inlineStr"/>
@@ -2641,39 +2641,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>-0.0038</v>
+        <v>0</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>3421200</v>
+        <v>3712300</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="H48" t="n">
-        <v>50.58</v>
-      </c>
-      <c r="I48" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.42</v>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="10" t="n">
-        <v>2.595</v>
+        <v>2.43</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>2.571</v>
+        <v>2.429</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="15" t="inlineStr"/>
@@ -2686,28 +2686,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>4.98</v>
+        <v>1.22</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>3377100</v>
+        <v>3693300</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.17</v>
+        <v>0.46</v>
       </c>
       <c r="H49" t="n">
-        <v>56.78</v>
+        <v>37.11</v>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="J49" s="10" t="n">
-        <v>4.899</v>
+        <v>1.275</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>4.795</v>
+        <v>1.469</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="15" t="inlineStr"/>
@@ -2731,28 +2731,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>0</v>
+        <v>0.83</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>3370400</v>
+        <v>3648300</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.34</v>
+        <v>0.74</v>
       </c>
       <c r="H50" t="n">
-        <v>50.42</v>
+        <v>67.58</v>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="J50" s="10" t="n">
-        <v>2.43</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>2.429</v>
+        <v>0.783</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="15" t="inlineStr"/>
@@ -2776,39 +2776,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E51" s="11" t="n">
-        <v>-0.0075</v>
+        <v>4.98</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>-0.004</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>3335800</v>
+        <v>3635000</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.34</v>
+        <v>0.18</v>
       </c>
       <c r="H51" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="I51" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.78</v>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="10" t="n">
-        <v>2.714</v>
+        <v>4.899</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>2.749</v>
+        <v>4.795</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="15" t="inlineStr"/>
@@ -2821,28 +2821,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0</v>
+        <v>0.155</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>3228700</v>
+        <v>3520500</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.89</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>69.45</v>
+        <v>48.93</v>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="J52" s="10" t="n">
-        <v>0.623</v>
+        <v>0.159</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>0.613</v>
+        <v>0.15</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="15" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         <v>0.0075</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>3122500</v>
+        <v>3458200</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="H53" t="n">
         <v>63.44</v>
@@ -2911,39 +2911,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>0</v>
+        <v>2.65</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>3006900</v>
+        <v>3450400</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0.61</v>
+        <v>0.35</v>
       </c>
       <c r="H54" t="n">
-        <v>72.51000000000001</v>
-      </c>
-      <c r="I54" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.8</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="10" t="n">
-        <v>0.8129999999999999</v>
+        <v>2.714</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>0.783</v>
+        <v>2.749</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="15" t="inlineStr"/>
@@ -2956,28 +2956,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E55" s="11" t="n">
-        <v>-0.0444</v>
+        <v>1.29</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>2981900</v>
+        <v>3329900</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>2.76</v>
+        <v>1.07</v>
       </c>
       <c r="H55" t="n">
-        <v>41.91</v>
+        <v>56.73</v>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.223</v>
+        <v>1.269</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>0.229</v>
+        <v>1.27</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="15" t="inlineStr"/>
@@ -3001,39 +3001,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>2955200</v>
+        <v>3254600</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="H56" t="n">
-        <v>43.12</v>
-      </c>
-      <c r="I56" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.07</v>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.988</v>
+        <v>0.432</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>0.993</v>
+        <v>0.417</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="15" t="inlineStr"/>
@@ -3046,28 +3046,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>1.23</v>
+        <v>0.63</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>2928400</v>
+        <v>3228700</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>0.28</v>
+        <v>0.89</v>
       </c>
       <c r="H57" t="n">
-        <v>65.81999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="J57" s="10" t="n">
-        <v>1.129</v>
+        <v>0.623</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>1.071</v>
+        <v>0.613</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="15" t="inlineStr"/>
@@ -3091,28 +3091,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E58" s="11" t="n">
-        <v>-0.0083</v>
+        <v>1.42</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>0.0143</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>2924500</v>
+        <v>3140700</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>0.15</v>
+        <v>1.01</v>
       </c>
       <c r="H58" t="n">
-        <v>55.64</v>
+        <v>60.27</v>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="J58" s="10" t="n">
-        <v>0.575</v>
+        <v>1.317</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>0.552</v>
+        <v>1.258</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="15" t="inlineStr"/>
@@ -3136,39 +3136,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>1.15</v>
+        <v>0.945</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>-0.0086</v>
+        <v>0</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>2870200</v>
+        <v>3111400</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="H59" t="n">
-        <v>35.03</v>
-      </c>
-      <c r="I59" s="17" t="inlineStr">
+        <v>43.12</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J59" s="10" t="n">
-        <v>1.191</v>
+        <v>0.988</v>
       </c>
       <c r="K59" s="10" t="n">
-        <v>1.272</v>
+        <v>0.993</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="15" t="inlineStr"/>
@@ -3181,28 +3181,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>0</v>
+        <v>1.23</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>2795500</v>
+        <v>3053600</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="H60" t="n">
-        <v>53.62</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.431</v>
+        <v>1.129</v>
       </c>
       <c r="K60" s="10" t="n">
-        <v>0.416</v>
+        <v>1.071</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="15" t="inlineStr"/>
@@ -3226,39 +3226,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E61" s="11" t="n">
-        <v>-0.0064</v>
+        <v>0.445</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>2788100</v>
+        <v>3047400</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
       <c r="H61" t="n">
-        <v>53.12</v>
-      </c>
-      <c r="I61" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.14</v>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="10" t="n">
-        <v>0.771</v>
+        <v>0.453</v>
       </c>
       <c r="K61" s="10" t="n">
-        <v>0.771</v>
+        <v>0.471</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="15" t="inlineStr"/>
@@ -3271,28 +3271,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>1.29</v>
+        <v>5.32</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>0.0157</v>
+        <v>0.0095</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>2617100</v>
+        <v>3035300</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.84</v>
+        <v>0.19</v>
       </c>
       <c r="H62" t="n">
-        <v>56.73</v>
+        <v>47.74</v>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="J62" s="10" t="n">
-        <v>1.269</v>
+        <v>5.356</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>1.27</v>
+        <v>5.531</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="15" t="inlineStr"/>
@@ -3316,28 +3316,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="E63" s="11" t="n">
-        <v>-0.0116</v>
+        <v>0.595</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>2564200</v>
+        <v>3005000</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="H63" t="n">
-        <v>83.59999999999999</v>
+        <v>55.64</v>
       </c>
       <c r="I63" s="14" t="inlineStr">
         <is>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="J63" s="10" t="n">
-        <v>3.146</v>
+        <v>0.575</v>
       </c>
       <c r="K63" s="10" t="n">
-        <v>2.671</v>
+        <v>0.552</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="15" t="inlineStr"/>
@@ -3361,28 +3361,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E64" s="18" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.215</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>-0.0444</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>2501400</v>
+        <v>2981900</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>0.15</v>
+        <v>2.76</v>
       </c>
       <c r="H64" t="n">
-        <v>47.02</v>
+        <v>41.91</v>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="J64" s="10" t="n">
-        <v>5.354</v>
+        <v>0.223</v>
       </c>
       <c r="K64" s="10" t="n">
-        <v>5.53</v>
+        <v>0.229</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="15" t="inlineStr"/>
@@ -3406,39 +3406,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E65" s="16" t="n">
-        <v>0</v>
+        <v>0.78</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>2474100</v>
+        <v>2788100</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>1.28</v>
+        <v>0.39</v>
       </c>
       <c r="H65" t="n">
-        <v>50.78</v>
-      </c>
-      <c r="I65" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.12</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="10" t="n">
-        <v>0.904</v>
+        <v>0.771</v>
       </c>
       <c r="K65" s="10" t="n">
-        <v>0.898</v>
+        <v>0.771</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="15" t="inlineStr"/>
@@ -3451,39 +3451,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E66" s="11" t="n">
-        <v>-0.0071</v>
+        <v>0.705</v>
+      </c>
+      <c r="E66" s="18" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>2452600</v>
+        <v>2783900</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.79</v>
+        <v>0.27</v>
       </c>
       <c r="H66" t="n">
-        <v>57.97</v>
-      </c>
-      <c r="I66" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.86</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="10" t="n">
-        <v>1.314</v>
+        <v>0.726</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>1.258</v>
+        <v>0.724</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="15" t="inlineStr"/>
@@ -3496,39 +3496,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E67" s="11" t="n">
-        <v>-0.0455</v>
+        <v>3.4</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>2444600</v>
+        <v>2719700</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>0.25</v>
+        <v>0.85</v>
       </c>
       <c r="H67" t="n">
-        <v>38.42</v>
-      </c>
-      <c r="I67" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.22</v>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="10" t="n">
-        <v>0.22</v>
+        <v>3.145</v>
       </c>
       <c r="K67" s="10" t="n">
-        <v>0.26</v>
+        <v>2.671</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="15" t="inlineStr"/>
@@ -3541,39 +3541,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E68" s="11" t="n">
-        <v>-0.0111</v>
+        <v>4.46</v>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>0.004500000000000001</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>2384600</v>
+        <v>2712300</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="H68" t="n">
-        <v>46.14</v>
-      </c>
-      <c r="I68" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.69</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="10" t="n">
-        <v>0.453</v>
+        <v>4.531</v>
       </c>
       <c r="K68" s="10" t="n">
-        <v>0.471</v>
+        <v>4.642</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="15" t="inlineStr"/>
@@ -3586,28 +3586,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E69" s="11" t="n">
-        <v>-0.0267</v>
+        <v>1.25</v>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>0.0163</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>2371000</v>
+        <v>2683400</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>1.95</v>
+        <v>0.41</v>
       </c>
       <c r="H69" t="n">
-        <v>60.14</v>
+        <v>45.91</v>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="J69" s="10" t="n">
-        <v>0.345</v>
+        <v>1.269</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>0.355</v>
+        <v>1.318</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="15" t="inlineStr"/>
@@ -3631,39 +3631,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D70" s="10" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E70" s="11" t="n">
-        <v>-0.0066</v>
+        <v>0.215</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>2366700</v>
+        <v>2646200</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.73</v>
+        <v>0.27</v>
       </c>
       <c r="H70" t="n">
-        <v>50.17</v>
-      </c>
-      <c r="I70" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.78</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="10" t="n">
-        <v>3.007</v>
+        <v>0.221</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>2.88</v>
+        <v>0.26</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="15" t="inlineStr"/>
@@ -3685,19 +3685,19 @@
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E71" s="11" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.27</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>2238800</v>
+        <v>2582200</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>0.66</v>
+        <v>0.76</v>
       </c>
       <c r="H71" t="n">
-        <v>54.43</v>
+        <v>53.45</v>
       </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
@@ -3721,39 +3721,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="E72" s="18" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.905</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>2228300</v>
+        <v>2474100</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>0.25</v>
+        <v>1.28</v>
       </c>
       <c r="H72" t="n">
-        <v>41.34</v>
-      </c>
-      <c r="I72" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.78</v>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="10" t="n">
-        <v>4.533</v>
+        <v>0.904</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>4.643</v>
+        <v>0.898</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="15" t="inlineStr"/>
@@ -3766,28 +3766,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E73" s="18" t="n">
-        <v>0.0244</v>
+        <v>3.01</v>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>2165600</v>
+        <v>2455300</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="H73" t="n">
-        <v>47.38</v>
+        <v>51.04</v>
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="J73" s="10" t="n">
-        <v>1.27</v>
+        <v>3.009</v>
       </c>
       <c r="K73" s="10" t="n">
-        <v>1.318</v>
+        <v>2.88</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="15" t="inlineStr"/>
@@ -3811,39 +3811,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>0</v>
+        <v>3.02</v>
+      </c>
+      <c r="E74" s="18" t="n">
+        <v>0.0033</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>2159100</v>
+        <v>2400900</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.21</v>
+        <v>0.87</v>
       </c>
       <c r="H74" t="n">
-        <v>44.93</v>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
+        <v>37.95</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J74" s="10" t="n">
-        <v>0.726</v>
+        <v>3.106</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>0.724</v>
+        <v>3.234</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="15" t="inlineStr"/>
@@ -3856,39 +3856,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E75" s="18" t="n">
-        <v>0.0357</v>
+        <v>0.405</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>2119900</v>
+        <v>2386400</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>0.29</v>
+        <v>1.19</v>
       </c>
       <c r="H75" t="n">
-        <v>38.02</v>
-      </c>
-      <c r="I75" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.62</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="10" t="n">
-        <v>0.308</v>
+        <v>0.435</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>0.352</v>
+        <v>0.452</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="15" t="inlineStr"/>
@@ -3901,39 +3901,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D76" s="10" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="E76" s="18" t="n">
-        <v>0.0066</v>
+        <v>0.365</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>2115800</v>
+        <v>2371000</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0.77</v>
+        <v>1.95</v>
       </c>
       <c r="H76" t="n">
-        <v>39.15</v>
-      </c>
-      <c r="I76" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.14</v>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="10" t="n">
-        <v>3.107</v>
+        <v>0.345</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>3.234</v>
+        <v>0.355</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="15" t="inlineStr"/>
@@ -3955,19 +3955,19 @@
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>0.0224</v>
+        <v>0.0299</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>2104600</v>
+        <v>2331700</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>7.49</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>66.26000000000001</v>
+        <v>68.31</v>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="J77" s="10" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="K77" s="10" t="n">
         <v>0.662</v>
-      </c>
-      <c r="K77" s="10" t="n">
-        <v>0.661</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="15" t="inlineStr"/>
@@ -3991,39 +3991,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>0.265</v>
+        <v>2.1</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>-0.0185</v>
+        <v>0</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2038000</v>
+        <v>2312700</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>1.92</v>
+        <v>0.24</v>
       </c>
       <c r="H78" t="n">
-        <v>34.28</v>
-      </c>
-      <c r="I78" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.09</v>
+      </c>
+      <c r="I78" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="10" t="n">
-        <v>0.274</v>
+        <v>2.105</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>0.283</v>
+        <v>2.115</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="15" t="inlineStr"/>
@@ -4036,39 +4036,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>0.0058</v>
+        <v>0.735</v>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>2009100</v>
+        <v>2300800</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>0.19</v>
+        <v>1.29</v>
       </c>
       <c r="H79" t="n">
-        <v>42.93</v>
-      </c>
-      <c r="I79" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.88</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="10" t="n">
-        <v>6.993</v>
+        <v>0.746</v>
       </c>
       <c r="K79" s="10" t="n">
-        <v>7.436</v>
+        <v>0.725</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="15" t="inlineStr"/>
@@ -4081,39 +4081,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>1.64</v>
+        <v>0.55</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>-0.012</v>
+        <v>0</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>2007800</v>
+        <v>2243900</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.31</v>
+        <v>0.98</v>
       </c>
       <c r="H80" t="n">
-        <v>46.96</v>
-      </c>
-      <c r="I80" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.67</v>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="10" t="n">
-        <v>1.649</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>1.731</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="15" t="inlineStr"/>
@@ -4126,28 +4126,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E81" s="16" t="n">
-        <v>0</v>
+        <v>6.91</v>
+      </c>
+      <c r="E81" s="18" t="n">
+        <v>0.0073</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>1991400</v>
+        <v>2243600</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="H81" t="n">
-        <v>66.23999999999999</v>
+        <v>43.33</v>
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
@@ -4155,10 +4155,10 @@
         </is>
       </c>
       <c r="J81" s="10" t="n">
-        <v>2.003</v>
+        <v>6.994</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>1.971</v>
+        <v>7.436</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="15" t="inlineStr"/>
@@ -4171,28 +4171,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>0</v>
+        <v>0.29</v>
+      </c>
+      <c r="E82" s="18" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1987300</v>
+        <v>2210500</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="H82" t="n">
-        <v>49.09</v>
+        <v>38.02</v>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="J82" s="10" t="n">
-        <v>2.105</v>
+        <v>0.308</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>2.115</v>
+        <v>0.352</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="15" t="inlineStr"/>
@@ -4216,28 +4216,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0098</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AUMAS</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>0.0435</v>
+        <v>3.9</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>-0.0226</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>1974200</v>
+        <v>2202000</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>1.56</v>
+        <v>0.33</v>
       </c>
       <c r="H83" t="n">
-        <v>56.2</v>
+        <v>55.26</v>
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="J83" s="10" t="n">
-        <v>0.348</v>
+        <v>3.847</v>
       </c>
       <c r="K83" s="10" t="n">
-        <v>0.357</v>
+        <v>3.379</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="15" t="inlineStr"/>
@@ -4261,39 +4261,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D84" s="10" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>0</v>
+        <v>6.85</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>-0.0044</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>1948500</v>
+        <v>2189200</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="H84" t="n">
-        <v>45.37</v>
-      </c>
-      <c r="I84" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.37</v>
+      </c>
+      <c r="I84" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="10" t="n">
-        <v>0.485</v>
+        <v>6.838</v>
       </c>
       <c r="K84" s="10" t="n">
-        <v>0.473</v>
+        <v>6.829</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="15" t="inlineStr"/>
@@ -4306,28 +4306,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D85" s="10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E85" s="16" t="n">
-        <v>0</v>
+        <v>4.3</v>
+      </c>
+      <c r="E85" s="18" t="n">
+        <v>0.019</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>1941200</v>
+        <v>2187000</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="H85" t="n">
-        <v>63.12</v>
+        <v>62.43</v>
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="J85" s="10" t="n">
-        <v>1.201</v>
+        <v>4.05</v>
       </c>
       <c r="K85" s="10" t="n">
-        <v>1.16</v>
+        <v>3.709</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="15" t="inlineStr"/>
@@ -4351,28 +4351,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>-0.0308</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>1927200</v>
+        <v>2186100</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>2.26</v>
+        <v>0.65</v>
       </c>
       <c r="H86" t="n">
-        <v>70.63</v>
+        <v>39.32</v>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="J86" s="10" t="n">
-        <v>0.335</v>
+        <v>0.672</v>
       </c>
       <c r="K86" s="10" t="n">
-        <v>0.319</v>
+        <v>0.728</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="15" t="inlineStr"/>
@@ -4396,28 +4396,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>3.87</v>
+        <v>2.1</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>-0.0301</v>
+        <v>0</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>1903300</v>
+        <v>2164100</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="H87" t="n">
-        <v>54.21</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="J87" s="10" t="n">
-        <v>3.844</v>
+        <v>2.003</v>
       </c>
       <c r="K87" s="10" t="n">
-        <v>3.378</v>
+        <v>1.971</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="15" t="inlineStr"/>
@@ -4441,39 +4441,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>0.22</v>
+        <v>1.27</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>-0.0222</v>
+        <v>0</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>1900000</v>
+        <v>2159600</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>3.98</v>
+        <v>0.33</v>
       </c>
       <c r="H88" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="I88" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.12</v>
+      </c>
+      <c r="I88" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="10" t="n">
-        <v>0.224</v>
+        <v>1.201</v>
       </c>
       <c r="K88" s="10" t="n">
-        <v>0.224</v>
+        <v>1.16</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="15" t="inlineStr"/>
@@ -4486,39 +4486,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D89" s="10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E89" s="16" t="n">
-        <v>0</v>
+        <v>1.63</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>-0.0181</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>1889900</v>
+        <v>2065500</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>0.82</v>
+        <v>0.32</v>
       </c>
       <c r="H89" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="I89" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.02</v>
+      </c>
+      <c r="I89" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="10" t="n">
-        <v>0.5570000000000001</v>
+        <v>1.648</v>
       </c>
       <c r="K89" s="10" t="n">
-        <v>0.5610000000000001</v>
+        <v>1.731</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="15" t="inlineStr"/>
@@ -4531,28 +4531,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E90" s="16" t="n">
-        <v>0</v>
+        <v>6.35</v>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>1855100</v>
+        <v>2058500</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.43</v>
+        <v>0.27</v>
       </c>
       <c r="H90" t="n">
-        <v>56.13</v>
+        <v>48.15</v>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="J90" s="10" t="n">
-        <v>0.904</v>
+        <v>6.335</v>
       </c>
       <c r="K90" s="10" t="n">
-        <v>0.953</v>
+        <v>6.587</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="15" t="inlineStr"/>
@@ -4576,39 +4576,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D91" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E91" s="11" t="n">
-        <v>-0.0244</v>
+        <v>0.265</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>1842600</v>
+        <v>2038000</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>0.92</v>
+        <v>1.92</v>
       </c>
       <c r="H91" t="n">
-        <v>34.27</v>
-      </c>
-      <c r="I91" s="17" t="inlineStr">
+        <v>34.28</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J91" s="10" t="n">
-        <v>0.434</v>
+        <v>0.274</v>
       </c>
       <c r="K91" s="10" t="n">
-        <v>0.452</v>
+        <v>0.283</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="15" t="inlineStr"/>
@@ -4621,28 +4621,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0098</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>AUMAS</t>
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>1.69</v>
+        <v>0.355</v>
       </c>
       <c r="E92" s="18" t="n">
-        <v>0.0242</v>
+        <v>0.029</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>1830700</v>
+        <v>2028900</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>0.22</v>
+        <v>1.6</v>
       </c>
       <c r="H92" t="n">
-        <v>57.22</v>
+        <v>53.94</v>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="J92" s="10" t="n">
-        <v>1.635</v>
+        <v>0.347</v>
       </c>
       <c r="K92" s="10" t="n">
-        <v>1.667</v>
+        <v>0.357</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="15" t="inlineStr"/>
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D93" s="10" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>0.006</v>
+        <v>0.465</v>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>1776700</v>
+        <v>2005600</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>0.65</v>
+        <v>0.23</v>
       </c>
       <c r="H93" t="n">
-        <v>40.69</v>
-      </c>
-      <c r="I93" s="17" t="inlineStr">
+        <v>45.37</v>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J93" s="10" t="n">
-        <v>0.86</v>
+        <v>0.485</v>
       </c>
       <c r="K93" s="10" t="n">
-        <v>0.918</v>
+        <v>0.473</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="15" t="inlineStr"/>
@@ -4711,39 +4711,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D94" s="10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E94" s="16" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E94" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>1750100</v>
+        <v>1950600</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="H94" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I94" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.13</v>
+      </c>
+      <c r="I94" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="10" t="n">
-        <v>0.335</v>
+        <v>0.904</v>
       </c>
       <c r="K94" s="10" t="n">
-        <v>0.339</v>
+        <v>0.953</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="15" t="inlineStr"/>
@@ -4756,39 +4756,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D95" s="10" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E95" s="16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E95" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>1715700</v>
+        <v>1927200</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>0.97</v>
+        <v>2.26</v>
       </c>
       <c r="H95" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="I95" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.63</v>
+      </c>
+      <c r="I95" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="10" t="n">
-        <v>0.746</v>
+        <v>0.335</v>
       </c>
       <c r="K95" s="10" t="n">
-        <v>0.725</v>
+        <v>0.319</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="15" t="inlineStr"/>
@@ -4801,39 +4801,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>4.27</v>
+        <v>0.845</v>
       </c>
       <c r="E96" s="18" t="n">
-        <v>0.0118</v>
+        <v>0.006</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>1704800</v>
+        <v>1920000</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="H96" t="n">
-        <v>61.58</v>
-      </c>
-      <c r="I96" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.69</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="10" t="n">
-        <v>4.047</v>
+        <v>0.86</v>
       </c>
       <c r="K96" s="10" t="n">
-        <v>3.708</v>
+        <v>0.918</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="15" t="inlineStr"/>
@@ -4846,39 +4846,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D97" s="10" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E97" s="11" t="n">
-        <v>-0.0248</v>
+        <v>0.22</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>1703900</v>
+        <v>1900000</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>0.19</v>
+        <v>3.98</v>
       </c>
       <c r="H97" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="I97" s="17" t="inlineStr">
+        <v>38.5</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J97" s="10" t="n">
-        <v>0.604</v>
+        <v>0.224</v>
       </c>
       <c r="K97" s="10" t="n">
-        <v>0.618</v>
+        <v>0.224</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="15" t="inlineStr"/>
@@ -4891,28 +4891,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D98" s="10" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="E98" s="11" t="n">
-        <v>-0.0044</v>
+        <v>1.69</v>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>0.0242</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>1703900</v>
+        <v>1878400</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="H98" t="n">
-        <v>51.37</v>
+        <v>57.22</v>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="J98" s="10" t="n">
-        <v>6.838</v>
+        <v>1.635</v>
       </c>
       <c r="K98" s="10" t="n">
-        <v>6.829</v>
+        <v>1.667</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="15" t="inlineStr"/>
@@ -4936,39 +4936,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D99" s="10" t="n">
-        <v>0.305</v>
+        <v>0.33</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>-0.0161</v>
+        <v>0</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>1691200</v>
+        <v>1754100</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>2.08</v>
+        <v>0.19</v>
       </c>
       <c r="H99" t="n">
-        <v>56.04</v>
-      </c>
-      <c r="I99" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.02</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="10" t="n">
-        <v>0.294</v>
+        <v>0.335</v>
       </c>
       <c r="K99" s="10" t="n">
-        <v>0.293</v>
+        <v>0.339</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="15" t="inlineStr"/>
@@ -4981,39 +4981,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E100" s="18" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.59</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>-0.0248</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1660800</v>
+        <v>1731900</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.44</v>
+        <v>0.19</v>
       </c>
       <c r="H100" t="n">
-        <v>38.17</v>
-      </c>
-      <c r="I100" s="17" t="inlineStr">
+        <v>46.38</v>
+      </c>
+      <c r="I100" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J100" s="10" t="n">
-        <v>0.522</v>
+        <v>0.604</v>
       </c>
       <c r="K100" s="10" t="n">
-        <v>0.554</v>
+        <v>0.618</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="15" t="inlineStr"/>
@@ -5026,28 +5026,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D101" s="10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E101" s="11" t="n">
-        <v>-0.0435</v>
+        <v>5.88</v>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>0.0226</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>1532800</v>
+        <v>1693900</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>1</v>
+        <v>0.21</v>
       </c>
       <c r="H101" t="n">
-        <v>54.89</v>
+        <v>51.06</v>
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="J101" s="10" t="n">
-        <v>0.32</v>
+        <v>5.818</v>
       </c>
       <c r="K101" s="10" t="n">
-        <v>0.33</v>
+        <v>6.046</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="15" t="inlineStr"/>
@@ -5071,28 +5071,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TDM</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D102" s="10" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E102" s="18" t="n">
-        <v>0.0513</v>
+        <v>0.305</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>1525100</v>
+        <v>1691200</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>4.19</v>
+        <v>2.08</v>
       </c>
       <c r="H102" t="n">
-        <v>52.51</v>
+        <v>56.04</v>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="J102" s="10" t="n">
-        <v>0.201</v>
+        <v>0.294</v>
       </c>
       <c r="K102" s="10" t="n">
-        <v>0.214</v>
+        <v>0.293</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="15" t="inlineStr"/>
@@ -5116,39 +5116,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D103" s="10" t="n">
-        <v>6.35</v>
+        <v>0.51</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>0.0095</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>1499800</v>
+        <v>1669900</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="H103" t="n">
-        <v>48.15</v>
-      </c>
-      <c r="I103" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.17</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="10" t="n">
-        <v>6.335</v>
+        <v>0.522</v>
       </c>
       <c r="K103" s="10" t="n">
-        <v>6.587</v>
+        <v>0.554</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="15" t="inlineStr"/>
@@ -5161,39 +5161,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D104" s="10" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="E104" s="18" t="n">
-        <v>0.0122</v>
+        <v>0.865</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1458000</v>
+        <v>1618000</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>0.13</v>
+        <v>0.55</v>
       </c>
       <c r="H104" t="n">
-        <v>49.94</v>
-      </c>
-      <c r="I104" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.58</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="10" t="n">
-        <v>7.411</v>
+        <v>0.866</v>
       </c>
       <c r="K104" s="10" t="n">
-        <v>7.755</v>
+        <v>0.861</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="15" t="inlineStr"/>
@@ -5206,39 +5206,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ESCERAM</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D105" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E105" s="11" t="n">
-        <v>-0.09089999999999999</v>
+        <v>7.48</v>
+      </c>
+      <c r="E105" s="18" t="n">
+        <v>0.0136</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>1382500</v>
+        <v>1603400</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>0.61</v>
+        <v>0.15</v>
       </c>
       <c r="H105" t="n">
-        <v>46.74</v>
-      </c>
-      <c r="I105" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.52</v>
+      </c>
+      <c r="I105" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="10" t="n">
-        <v>0.209</v>
+        <v>7.411</v>
       </c>
       <c r="K105" s="10" t="n">
-        <v>0.194</v>
+        <v>7.755</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="15" t="inlineStr"/>
@@ -5266,10 +5266,10 @@
         <v>0.0147</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1352500</v>
+        <v>1601300</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="H106" t="n">
         <v>58.74</v>
@@ -5296,28 +5296,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D107" s="10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E107" s="11" t="n">
-        <v>-0.0156</v>
+        <v>0.335</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>-0.029</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>1311100</v>
+        <v>1547800</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>0.6</v>
+        <v>1.01</v>
       </c>
       <c r="H107" t="n">
-        <v>45.12</v>
+        <v>57.81</v>
       </c>
       <c r="I107" s="14" t="inlineStr">
         <is>
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="J107" s="10" t="n">
-        <v>0.64</v>
+        <v>0.32</v>
       </c>
       <c r="K107" s="10" t="n">
-        <v>0.631</v>
+        <v>0.33</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="15" t="inlineStr"/>
@@ -5341,39 +5341,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="E108" s="11" t="n">
-        <v>-0.0058</v>
+        <v>0.205</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>-0.0682</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>1286800</v>
+        <v>1538800</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.22</v>
+        <v>0.68</v>
       </c>
       <c r="H108" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="I108" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.66</v>
+      </c>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="10" t="n">
-        <v>6.449</v>
+        <v>0.209</v>
       </c>
       <c r="K108" s="10" t="n">
-        <v>6.068</v>
+        <v>0.194</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="15" t="inlineStr"/>
@@ -5386,28 +5386,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>TDM</t>
         </is>
       </c>
       <c r="D109" s="10" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="E109" s="11" t="n">
-        <v>-0.0106</v>
+        <v>0.205</v>
+      </c>
+      <c r="E109" s="18" t="n">
+        <v>0.0513</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>1237700</v>
+        <v>1525100</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>0.26</v>
+        <v>4.19</v>
       </c>
       <c r="H109" t="n">
-        <v>58.28</v>
+        <v>52.51</v>
       </c>
       <c r="I109" s="14" t="inlineStr">
         <is>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="J109" s="10" t="n">
-        <v>4.489</v>
+        <v>0.201</v>
       </c>
       <c r="K109" s="10" t="n">
-        <v>4.451</v>
+        <v>0.214</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="15" t="inlineStr"/>
@@ -5431,40 +5431,33 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>0.315</v>
+        <v>0.725</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>-0.0308</v>
+        <v>0</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1236900</v>
+        <v>1518700</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H110" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="I110" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J110" s="10" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="K110" s="10" t="n">
-        <v>0.324</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="I110" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="10" t="n"/>
+      <c r="K110" s="10" t="n"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="15" t="inlineStr"/>
     </row>
@@ -5476,28 +5469,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D111" s="10" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E111" s="11" t="n">
-        <v>-0.0129</v>
+        <v>4.65</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>-0.0148</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>1221600</v>
+        <v>1485400</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="H111" t="n">
-        <v>54.86</v>
+        <v>57.38</v>
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
@@ -5505,10 +5498,10 @@
         </is>
       </c>
       <c r="J111" s="10" t="n">
-        <v>0.749</v>
+        <v>4.487</v>
       </c>
       <c r="K111" s="10" t="n">
-        <v>0.699</v>
+        <v>4.451</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="15" t="inlineStr"/>
@@ -5521,28 +5514,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E112" s="11" t="n">
-        <v>-0.0231</v>
+        <v>6.86</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>1215900</v>
+        <v>1451800</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="H112" t="n">
-        <v>40.04</v>
+        <v>60.35</v>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
@@ -5550,10 +5543,10 @@
         </is>
       </c>
       <c r="J112" s="10" t="n">
-        <v>0.673</v>
+        <v>6.449</v>
       </c>
       <c r="K112" s="10" t="n">
-        <v>0.729</v>
+        <v>6.068</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="15" t="inlineStr"/>
@@ -5566,28 +5559,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D113" s="10" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="E113" s="18" t="n">
-        <v>0.0191</v>
+        <v>0.765</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>1149300</v>
+        <v>1413700</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H113" t="n">
-        <v>49.85</v>
+        <v>54.86</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
@@ -5595,10 +5588,10 @@
         </is>
       </c>
       <c r="J113" s="10" t="n">
-        <v>5.816</v>
+        <v>0.749</v>
       </c>
       <c r="K113" s="10" t="n">
-        <v>6.046</v>
+        <v>0.699</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="15" t="inlineStr"/>
@@ -5611,33 +5604,40 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>COMFORT</t>
         </is>
       </c>
       <c r="D114" s="10" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E114" s="11" t="n">
-        <v>-0.0138</v>
+        <v>0.2</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>-0.0476</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>1146000</v>
+        <v>1325600</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I114" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J114" s="10" t="n"/>
-      <c r="K114" s="10" t="n"/>
+        <v>0.65</v>
+      </c>
+      <c r="H114" t="n">
+        <v>63.86</v>
+      </c>
+      <c r="I114" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="10" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="K114" s="10" t="n">
+        <v>0.166</v>
+      </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="15" t="inlineStr"/>
     </row>
@@ -5649,28 +5649,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D115" s="10" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E115" s="11" t="n">
-        <v>-0.0158</v>
+        <v>0.63</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>1134800</v>
+        <v>1312100</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>0.28</v>
+        <v>0.6</v>
       </c>
       <c r="H115" t="n">
-        <v>49.94</v>
+        <v>45.12</v>
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="J115" s="10" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="K115" s="10" t="n">
-        <v>0.9</v>
+        <v>0.631</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="15" t="inlineStr"/>
@@ -5694,39 +5694,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>0.36</v>
+        <v>7.84</v>
       </c>
       <c r="E116" s="18" t="n">
-        <v>0.0435</v>
+        <v>0.0013</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>1041400</v>
+        <v>1306800</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>3.34</v>
+        <v>0.44</v>
       </c>
       <c r="H116" t="n">
-        <v>73.72</v>
-      </c>
-      <c r="I116" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.1</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="10" t="n">
-        <v>0.317</v>
+        <v>7.891</v>
       </c>
       <c r="K116" s="10" t="n">
-        <v>0.299</v>
+        <v>7.913</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="15" t="inlineStr"/>
@@ -5739,39 +5739,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D117" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E117" s="11" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.315</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>-0.0308</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>1040000</v>
+        <v>1256900</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>0.36</v>
+        <v>0.77</v>
       </c>
       <c r="H117" t="n">
-        <v>49.58</v>
-      </c>
-      <c r="I117" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.6</v>
+      </c>
+      <c r="I117" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="10" t="n">
-        <v>0.866</v>
+        <v>0.301</v>
       </c>
       <c r="K117" s="10" t="n">
-        <v>0.861</v>
+        <v>0.324</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="15" t="inlineStr"/>
@@ -5793,19 +5793,19 @@
         </is>
       </c>
       <c r="D118" s="10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E118" s="11" t="n">
-        <v>-0.0154</v>
+        <v>1.26</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>-0.0308</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>1034200</v>
+        <v>1230300</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="H118" t="n">
-        <v>57.77</v>
+        <v>54.54</v>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="J118" s="10" t="n">
-        <v>1.245</v>
+        <v>1.243</v>
       </c>
       <c r="K118" s="10" t="n">
         <v>1.214</v>
@@ -5840,19 +5840,19 @@
       <c r="D119" s="10" t="n">
         <v>2.28</v>
       </c>
-      <c r="E119" s="11" t="n">
+      <c r="E119" s="17" t="n">
         <v>-0.013</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>1022800</v>
+        <v>1192000</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="H119" t="n">
         <v>50.29</v>
       </c>
-      <c r="I119" s="17" t="inlineStr">
+      <c r="I119" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5874,28 +5874,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D120" s="10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E120" s="11" t="n">
-        <v>-0.0068</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>-0.0158</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>995100</v>
+        <v>1134900</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="H120" t="n">
-        <v>56.62</v>
+        <v>49.94</v>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="J120" s="10" t="n">
-        <v>2.826</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K120" s="10" t="n">
-        <v>2.712</v>
+        <v>0.9</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="15" t="inlineStr"/>
@@ -5919,39 +5919,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D121" s="10" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E121" s="11" t="n">
-        <v>-0.0197</v>
+        <v>0.865</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>-0.0114</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>990500</v>
+        <v>1101900</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="H121" t="n">
-        <v>51.49</v>
-      </c>
-      <c r="I121" s="17" t="inlineStr">
+        <v>57.24</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J121" s="10" t="n">
-        <v>0.745</v>
+        <v>0.841</v>
       </c>
       <c r="K121" s="10" t="n">
-        <v>0.709</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="15" t="inlineStr"/>
@@ -5964,39 +5964,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D122" s="10" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="E122" s="11" t="n">
-        <v>-0.0229</v>
+        <v>2.91</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>949700</v>
+        <v>1097800</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="H122" t="n">
-        <v>54.98</v>
-      </c>
-      <c r="I122" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.34</v>
+      </c>
+      <c r="I122" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="10" t="n">
-        <v>0.84</v>
+        <v>2.827</v>
       </c>
       <c r="K122" s="10" t="n">
-        <v>0.8070000000000001</v>
+        <v>2.712</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="15" t="inlineStr"/>
@@ -6009,39 +6009,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D123" s="10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E123" s="16" t="n">
-        <v>0</v>
+        <v>13.3</v>
+      </c>
+      <c r="E123" s="18" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>932800</v>
+        <v>1079100</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="H123" t="n">
-        <v>58.56</v>
-      </c>
-      <c r="I123" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.06</v>
+      </c>
+      <c r="I123" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="10" t="n">
-        <v>1.289</v>
+        <v>13.132</v>
       </c>
       <c r="K123" s="10" t="n">
-        <v>1.197</v>
+        <v>13.259</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="15" t="inlineStr"/>
@@ -6054,39 +6054,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D124" s="10" t="n">
-        <v>7.85</v>
+        <v>0.36</v>
       </c>
       <c r="E124" s="18" t="n">
-        <v>0.0026</v>
+        <v>0.0435</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>925000</v>
+        <v>1077100</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.31</v>
+        <v>3.45</v>
       </c>
       <c r="H124" t="n">
-        <v>45.92</v>
-      </c>
-      <c r="I124" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.72</v>
+      </c>
+      <c r="I124" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="10" t="n">
-        <v>7.892</v>
+        <v>0.317</v>
       </c>
       <c r="K124" s="10" t="n">
-        <v>7.914</v>
+        <v>0.299</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="15" t="inlineStr"/>
@@ -6099,39 +6099,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D125" s="10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E125" s="16" t="n">
-        <v>0</v>
+        <v>0.75</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>890000</v>
+        <v>1018800</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="H125" t="n">
-        <v>69.06999999999999</v>
-      </c>
-      <c r="I125" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.49</v>
+      </c>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="10" t="n">
-        <v>1.141</v>
+        <v>0.746</v>
       </c>
       <c r="K125" s="10" t="n">
-        <v>0.999</v>
+        <v>0.709</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="15" t="inlineStr"/>
@@ -6144,39 +6144,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D126" s="10" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="E126" s="18" t="n">
-        <v>0.0303</v>
+        <v>1.35</v>
+      </c>
+      <c r="E126" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>855300</v>
+        <v>939400</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>0.77</v>
+        <v>0.34</v>
       </c>
       <c r="H126" t="n">
-        <v>65.27</v>
-      </c>
-      <c r="I126" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.56</v>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="10" t="n">
-        <v>2.853</v>
+        <v>1.289</v>
       </c>
       <c r="K126" s="10" t="n">
-        <v>2.856</v>
+        <v>1.197</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="15" t="inlineStr"/>
@@ -6189,39 +6189,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D127" s="10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E127" s="18" t="n">
-        <v>0.0198</v>
+        <v>0.855</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>845800</v>
+        <v>927500</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="H127" t="n">
-        <v>43.18</v>
-      </c>
-      <c r="I127" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.84</v>
+      </c>
+      <c r="I127" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="10" t="n">
-        <v>1.052</v>
+        <v>0.879</v>
       </c>
       <c r="K127" s="10" t="n">
-        <v>1.11</v>
+        <v>0.868</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="15" t="inlineStr"/>
@@ -6234,28 +6234,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D128" s="10" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="E128" s="11" t="n">
-        <v>-0.0058</v>
+        <v>1.28</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>842800</v>
+        <v>926400</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="H128" t="n">
-        <v>45.84</v>
+        <v>67.77</v>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="J128" s="10" t="n">
-        <v>0.879</v>
+        <v>1.14</v>
       </c>
       <c r="K128" s="10" t="n">
-        <v>0.868</v>
+        <v>0.999</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="15" t="inlineStr"/>
@@ -6279,39 +6279,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="D129" s="10" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E129" s="11" t="n">
-        <v>-0.008199999999999999</v>
+        <v>3.06</v>
+      </c>
+      <c r="E129" s="18" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F129" s="12" t="n">
-        <v>827600</v>
+        <v>902700</v>
       </c>
       <c r="G129" s="13" t="n">
-        <v>0.11</v>
+        <v>0.82</v>
       </c>
       <c r="H129" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="I129" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.27</v>
+      </c>
+      <c r="I129" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="10" t="n">
-        <v>0.636</v>
+        <v>2.853</v>
       </c>
       <c r="K129" s="10" t="n">
-        <v>0.676</v>
+        <v>2.856</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="15" t="inlineStr"/>
@@ -6324,39 +6324,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D130" s="10" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E130" s="11" t="n">
-        <v>-0.0148</v>
+        <v>1.47</v>
+      </c>
+      <c r="E130" s="18" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>796500</v>
+        <v>902300</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>0.17</v>
+        <v>1.29</v>
       </c>
       <c r="H130" t="n">
-        <v>43.74</v>
-      </c>
-      <c r="I130" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.14</v>
+      </c>
+      <c r="I130" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="10" t="n">
-        <v>0.703</v>
+        <v>1.467</v>
       </c>
       <c r="K130" s="10" t="n">
-        <v>0.6919999999999999</v>
+        <v>1.578</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="15" t="inlineStr"/>
@@ -6369,28 +6369,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D131" s="10" t="n">
-        <v>1.47</v>
+        <v>2.5</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>0.0208</v>
+        <v>0.0246</v>
       </c>
       <c r="F131" s="12" t="n">
-        <v>794500</v>
+        <v>896000</v>
       </c>
       <c r="G131" s="13" t="n">
-        <v>1.14</v>
+        <v>0.22</v>
       </c>
       <c r="H131" t="n">
-        <v>47.14</v>
+        <v>49.36</v>
       </c>
       <c r="I131" s="14" t="inlineStr">
         <is>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="J131" s="10" t="n">
-        <v>1.467</v>
+        <v>2.474</v>
       </c>
       <c r="K131" s="10" t="n">
-        <v>1.578</v>
+        <v>2.61</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="15" t="inlineStr"/>
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D132" s="10" t="n">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>0.0328</v>
+        <v>0.0198</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>789300</v>
+        <v>890500</v>
       </c>
       <c r="G132" s="13" t="n">
-        <v>0.19</v>
+        <v>0.36</v>
       </c>
       <c r="H132" t="n">
-        <v>51.36</v>
-      </c>
-      <c r="I132" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.18</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="10" t="n">
-        <v>2.475</v>
+        <v>1.052</v>
       </c>
       <c r="K132" s="10" t="n">
-        <v>2.611</v>
+        <v>1.11</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="15" t="inlineStr"/>
@@ -6459,28 +6459,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D133" s="10" t="n">
-        <v>3.98</v>
+        <v>5.18</v>
       </c>
       <c r="E133" s="18" t="n">
-        <v>0.0127</v>
+        <v>0.0019</v>
       </c>
       <c r="F133" s="12" t="n">
-        <v>778200</v>
+        <v>874200</v>
       </c>
       <c r="G133" s="13" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H133" t="n">
-        <v>57.09</v>
+        <v>56.04</v>
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="J133" s="10" t="n">
-        <v>3.851</v>
+        <v>5.081</v>
       </c>
       <c r="K133" s="10" t="n">
-        <v>3.776</v>
+        <v>5.034</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="15" t="inlineStr"/>
@@ -6504,39 +6504,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E134" s="11" t="n">
-        <v>-0.0214</v>
+        <v>5.8</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>-0.0017</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>762900</v>
+        <v>872500</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="H134" t="n">
-        <v>43</v>
-      </c>
-      <c r="I134" s="17" t="inlineStr">
+        <v>58.39</v>
+      </c>
+      <c r="I134" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J134" s="10" t="n">
-        <v>2.809</v>
+        <v>5.573</v>
       </c>
       <c r="K134" s="10" t="n">
-        <v>2.94</v>
+        <v>5.4</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="15" t="inlineStr"/>
@@ -6549,39 +6549,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D135" s="10" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E135" s="18" t="n">
-        <v>0.0062</v>
+        <v>0.67</v>
+      </c>
+      <c r="E135" s="17" t="n">
+        <v>-0.0074</v>
       </c>
       <c r="F135" s="12" t="n">
-        <v>759200</v>
+        <v>869700</v>
       </c>
       <c r="G135" s="13" t="n">
-        <v>0.34</v>
+        <v>0.19</v>
       </c>
       <c r="H135" t="n">
-        <v>69.41</v>
-      </c>
-      <c r="I135" s="17" t="inlineStr">
+        <v>44.38</v>
+      </c>
+      <c r="I135" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J135" s="10" t="n">
-        <v>0.752</v>
+        <v>0.704</v>
       </c>
       <c r="K135" s="10" t="n">
-        <v>0.68</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="15" t="inlineStr"/>
@@ -6594,28 +6594,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D136" s="10" t="n">
-        <v>13.28</v>
+        <v>3.95</v>
       </c>
       <c r="E136" s="18" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>758900</v>
+        <v>864800</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="H136" t="n">
-        <v>57.23</v>
+        <v>55.94</v>
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="J136" s="10" t="n">
-        <v>13.13</v>
+        <v>3.849</v>
       </c>
       <c r="K136" s="10" t="n">
-        <v>13.259</v>
+        <v>3.776</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="15" t="inlineStr"/>
@@ -6648,19 +6648,19 @@
         </is>
       </c>
       <c r="D137" s="10" t="n">
-        <v>10.98</v>
-      </c>
-      <c r="E137" s="11" t="n">
-        <v>-0.0072</v>
+        <v>11.02</v>
+      </c>
+      <c r="E137" s="17" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F137" s="12" t="n">
-        <v>748900</v>
+        <v>858200</v>
       </c>
       <c r="G137" s="13" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="H137" t="n">
-        <v>60.61</v>
+        <v>61.56</v>
       </c>
       <c r="I137" s="14" t="inlineStr">
         <is>
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="J137" s="10" t="n">
-        <v>10.598</v>
+        <v>10.602</v>
       </c>
       <c r="K137" s="10" t="n">
-        <v>9.971</v>
+        <v>9.972</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="15" t="inlineStr"/>
@@ -6684,39 +6684,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E138" s="18" t="n">
-        <v>0.0246</v>
+        <v>0.605</v>
+      </c>
+      <c r="E138" s="17" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>732300</v>
+        <v>845100</v>
       </c>
       <c r="G138" s="13" t="n">
-        <v>0.29</v>
+        <v>0.11</v>
       </c>
       <c r="H138" t="n">
-        <v>45.78</v>
-      </c>
-      <c r="I138" s="17" t="inlineStr">
+        <v>40.64</v>
+      </c>
+      <c r="I138" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J138" s="10" t="n">
-        <v>2.511</v>
+        <v>0.636</v>
       </c>
       <c r="K138" s="10" t="n">
-        <v>2.623</v>
+        <v>0.676</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
@@ -6729,39 +6729,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>KEEMING</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D139" s="10" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="E139" s="18" t="n">
-        <v>0.0361</v>
+        <v>0.0246</v>
       </c>
       <c r="F139" s="12" t="n">
-        <v>725800</v>
+        <v>836500</v>
       </c>
       <c r="G139" s="13" t="n">
-        <v>0.95</v>
+        <v>0.33</v>
       </c>
       <c r="H139" t="n">
-        <v>65.73</v>
-      </c>
-      <c r="I139" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.78</v>
+      </c>
+      <c r="I139" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="10" t="n">
-        <v>2.611</v>
+        <v>2.511</v>
       </c>
       <c r="K139" s="10" t="n">
-        <v>2.54</v>
+        <v>2.623</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="15" t="inlineStr"/>
@@ -6774,39 +6774,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D140" s="10" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E140" s="18" t="n">
-        <v>0.006500000000000001</v>
+        <v>2.74</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>-0.0214</v>
       </c>
       <c r="F140" s="12" t="n">
-        <v>721700</v>
+        <v>822300</v>
       </c>
       <c r="G140" s="13" t="n">
-        <v>0.34</v>
+        <v>0.23</v>
       </c>
       <c r="H140" t="n">
-        <v>23.74</v>
-      </c>
-      <c r="I140" s="17" t="inlineStr">
+        <v>43</v>
+      </c>
+      <c r="I140" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J140" s="10" t="n">
-        <v>0.856</v>
+        <v>2.809</v>
       </c>
       <c r="K140" s="10" t="n">
-        <v>1.017</v>
+        <v>2.94</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="15" t="inlineStr"/>
@@ -6819,28 +6819,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>KEEMING</t>
         </is>
       </c>
       <c r="D141" s="10" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E141" s="16" t="n">
-        <v>0</v>
+        <v>2.88</v>
+      </c>
+      <c r="E141" s="18" t="n">
+        <v>0.0397</v>
       </c>
       <c r="F141" s="12" t="n">
-        <v>713300</v>
+        <v>782000</v>
       </c>
       <c r="G141" s="13" t="n">
-        <v>0.26</v>
+        <v>1.02</v>
       </c>
       <c r="H141" t="n">
-        <v>58.07</v>
+        <v>66.08</v>
       </c>
       <c r="I141" s="14" t="inlineStr">
         <is>
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="J141" s="10" t="n">
-        <v>0.494</v>
+        <v>2.612</v>
       </c>
       <c r="K141" s="10" t="n">
-        <v>0.485</v>
+        <v>2.54</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="15" t="inlineStr"/>
@@ -6864,39 +6864,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MNRB</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D142" s="10" t="n">
-        <v>2.53</v>
+        <v>0.785</v>
       </c>
       <c r="E142" s="18" t="n">
-        <v>0.004</v>
+        <v>0.0129</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>702800</v>
+        <v>761500</v>
       </c>
       <c r="G142" s="13" t="n">
-        <v>1.34</v>
+        <v>0.35</v>
       </c>
       <c r="H142" t="n">
-        <v>41.16</v>
-      </c>
-      <c r="I142" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.39</v>
+      </c>
+      <c r="I142" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="10" t="n">
-        <v>2.561</v>
+        <v>0.856</v>
       </c>
       <c r="K142" s="10" t="n">
-        <v>2.667</v>
+        <v>1.017</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="15" t="inlineStr"/>
@@ -6909,39 +6909,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D143" s="10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E143" s="11" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E143" s="18" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F143" s="12" t="n">
-        <v>695200</v>
+        <v>760400</v>
       </c>
       <c r="G143" s="13" t="n">
-        <v>0.7</v>
+        <v>0.34</v>
       </c>
       <c r="H143" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="I143" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>69.41</v>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="10" t="n">
-        <v>0.636</v>
+        <v>0.752</v>
       </c>
       <c r="K143" s="10" t="n">
-        <v>0.634</v>
+        <v>0.68</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="15" t="inlineStr"/>
@@ -6954,39 +6954,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D144" s="10" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="E144" s="16" t="n">
-        <v>0</v>
+        <v>0.675</v>
+      </c>
+      <c r="E144" s="17" t="n">
+        <v>-0.0146</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>689700</v>
+        <v>744700</v>
       </c>
       <c r="G144" s="13" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="H144" t="n">
-        <v>55.59</v>
-      </c>
-      <c r="I144" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.05</v>
+      </c>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="10" t="n">
-        <v>5.08</v>
+        <v>0.659</v>
       </c>
       <c r="K144" s="10" t="n">
-        <v>5.033</v>
+        <v>0.592</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -6999,28 +6999,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>MNRB</t>
         </is>
       </c>
       <c r="D145" s="10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E145" s="11" t="n">
-        <v>-0.0053</v>
+        <v>2.53</v>
+      </c>
+      <c r="E145" s="18" t="n">
+        <v>0.004</v>
       </c>
       <c r="F145" s="12" t="n">
-        <v>668700</v>
+        <v>729800</v>
       </c>
       <c r="G145" s="13" t="n">
-        <v>0.14</v>
+        <v>1.39</v>
       </c>
       <c r="H145" t="n">
-        <v>40.07</v>
+        <v>41.16</v>
       </c>
       <c r="I145" s="14" t="inlineStr">
         <is>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="J145" s="10" t="n">
-        <v>0.95</v>
+        <v>2.561</v>
       </c>
       <c r="K145" s="10" t="n">
-        <v>1.023</v>
+        <v>2.667</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="15" t="inlineStr"/>
@@ -7044,39 +7044,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D146" s="10" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E146" s="11" t="n">
-        <v>-0.008199999999999999</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E146" s="17" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>663700</v>
+        <v>727900</v>
       </c>
       <c r="G146" s="13" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H146" t="n">
-        <v>64.16</v>
-      </c>
-      <c r="I146" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.07</v>
+      </c>
+      <c r="I146" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J146" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="K146" s="10" t="n">
-        <v>0.494</v>
+        <v>1.023</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="15" t="inlineStr"/>
@@ -7089,39 +7089,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D147" s="10" t="n">
-        <v>0.905</v>
+        <v>0.51</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>-0.005500000000000001</v>
+        <v>0</v>
       </c>
       <c r="F147" s="12" t="n">
-        <v>662600</v>
+        <v>724100</v>
       </c>
       <c r="G147" s="13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H147" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="I147" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.07</v>
+      </c>
+      <c r="I147" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J147" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.494</v>
       </c>
       <c r="K147" s="10" t="n">
-        <v>0.966</v>
+        <v>0.485</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="15" t="inlineStr"/>
@@ -7134,39 +7134,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D148" s="10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E148" s="11" t="n">
-        <v>-0.0017</v>
+        <v>0.64</v>
+      </c>
+      <c r="E148" s="17" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>648000</v>
+        <v>695200</v>
       </c>
       <c r="G148" s="13" t="n">
-        <v>0.15</v>
+        <v>0.7</v>
       </c>
       <c r="H148" t="n">
-        <v>58.39</v>
-      </c>
-      <c r="I148" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.16</v>
+      </c>
+      <c r="I148" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J148" s="10" t="n">
-        <v>5.573</v>
+        <v>0.636</v>
       </c>
       <c r="K148" s="10" t="n">
-        <v>5.4</v>
+        <v>0.634</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -7188,19 +7188,19 @@
         </is>
       </c>
       <c r="D149" s="10" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="E149" s="18" t="n">
-        <v>0.0023</v>
+        <v>4.33</v>
+      </c>
+      <c r="E149" s="17" t="n">
+        <v>-0.0046</v>
       </c>
       <c r="F149" s="12" t="n">
-        <v>633300</v>
+        <v>682300</v>
       </c>
       <c r="G149" s="13" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H149" t="n">
-        <v>48.44</v>
+        <v>46.32</v>
       </c>
       <c r="I149" s="14" t="inlineStr">
         <is>
@@ -7208,10 +7208,10 @@
         </is>
       </c>
       <c r="J149" s="10" t="n">
-        <v>4.333</v>
+        <v>4.33</v>
       </c>
       <c r="K149" s="10" t="n">
-        <v>4.578</v>
+        <v>4.577</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="15" t="inlineStr"/>
@@ -7224,39 +7224,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D150" s="10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E150" s="16" t="n">
-        <v>0</v>
+        <v>0.9</v>
+      </c>
+      <c r="E150" s="17" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>629500</v>
+        <v>681900</v>
       </c>
       <c r="G150" s="13" t="n">
-        <v>0.29</v>
+        <v>0.83</v>
       </c>
       <c r="H150" t="n">
-        <v>68.53</v>
-      </c>
-      <c r="I150" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.68</v>
+      </c>
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="10" t="n">
-        <v>1.383</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K150" s="10" t="n">
-        <v>1.354</v>
+        <v>0.966</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -7269,39 +7269,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D151" s="10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E151" s="11" t="n">
-        <v>-0.0073</v>
+        <v>1.15</v>
+      </c>
+      <c r="E151" s="17" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F151" s="12" t="n">
-        <v>613900</v>
+        <v>674500</v>
       </c>
       <c r="G151" s="13" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="H151" t="n">
-        <v>58.43</v>
-      </c>
-      <c r="I151" s="17" t="inlineStr">
+        <v>57.15</v>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J151" s="10" t="n">
-        <v>0.66</v>
+        <v>1.11</v>
       </c>
       <c r="K151" s="10" t="n">
-        <v>0.592</v>
+        <v>0.954</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="15" t="inlineStr"/>
@@ -7325,14 +7325,14 @@
       <c r="D152" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="E152" s="16" t="n">
+      <c r="E152" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>600700</v>
+        <v>672200</v>
       </c>
       <c r="G152" s="13" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H152" t="n">
         <v>59.38</v>
@@ -7359,39 +7359,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D153" s="10" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E153" s="18" t="n">
-        <v>0.0091</v>
+        <v>0.605</v>
+      </c>
+      <c r="E153" s="17" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F153" s="12" t="n">
-        <v>600600</v>
+        <v>671800</v>
       </c>
       <c r="G153" s="13" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="H153" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="I153" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.16</v>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="10" t="n">
-        <v>0.553</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K153" s="10" t="n">
-        <v>0.587</v>
+        <v>0.494</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="15" t="inlineStr"/>
@@ -7404,39 +7404,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D154" s="10" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E154" s="16" t="n">
-        <v>0</v>
+        <v>3.15</v>
+      </c>
+      <c r="E154" s="18" t="n">
+        <v>0.0032</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>580000</v>
+        <v>644600</v>
       </c>
       <c r="G154" s="13" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="H154" t="n">
-        <v>57.26</v>
-      </c>
-      <c r="I154" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.45</v>
+      </c>
+      <c r="I154" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.273</v>
       </c>
       <c r="K154" s="10" t="n">
-        <v>0.533</v>
+        <v>3.506</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="15" t="inlineStr"/>
@@ -7449,39 +7449,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D155" s="10" t="n">
-        <v>2.28</v>
+        <v>3.57</v>
       </c>
       <c r="E155" s="18" t="n">
-        <v>0.0044</v>
+        <v>0.0171</v>
       </c>
       <c r="F155" s="12" t="n">
-        <v>573400</v>
+        <v>630400</v>
       </c>
       <c r="G155" s="13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="H155" t="n">
-        <v>60.17</v>
-      </c>
-      <c r="I155" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.28</v>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="10" t="n">
-        <v>2.151</v>
+        <v>3.544</v>
       </c>
       <c r="K155" s="10" t="n">
-        <v>2.218</v>
+        <v>3.571</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="15" t="inlineStr"/>
@@ -7494,39 +7494,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D156" s="10" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="E156" s="18" t="n">
-        <v>0.0064</v>
+        <v>1.43</v>
+      </c>
+      <c r="E156" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>566300</v>
+        <v>629500</v>
       </c>
       <c r="G156" s="13" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="H156" t="n">
-        <v>35.56</v>
-      </c>
-      <c r="I156" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.53</v>
+      </c>
+      <c r="I156" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J156" s="10" t="n">
-        <v>3.274</v>
+        <v>1.383</v>
       </c>
       <c r="K156" s="10" t="n">
-        <v>3.506</v>
+        <v>1.354</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -7539,39 +7539,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D157" s="10" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E157" s="16" t="n">
-        <v>0</v>
+        <v>1.56</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F157" s="12" t="n">
-        <v>564100</v>
+        <v>618400</v>
       </c>
       <c r="G157" s="13" t="n">
-        <v>0.22</v>
+        <v>0.62</v>
       </c>
       <c r="H157" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="I157" s="17" t="inlineStr">
+        <v>38.73</v>
+      </c>
+      <c r="I157" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J157" s="10" t="n">
-        <v>0.825</v>
+        <v>1.628</v>
       </c>
       <c r="K157" s="10" t="n">
-        <v>0.853</v>
+        <v>1.693</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="15" t="inlineStr"/>
@@ -7584,39 +7584,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D158" s="10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="E158" s="18" t="n">
-        <v>0.0199</v>
+        <v>1.88</v>
+      </c>
+      <c r="E158" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>532600</v>
+        <v>617200</v>
       </c>
       <c r="G158" s="13" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="H158" t="n">
-        <v>53.08</v>
-      </c>
-      <c r="I158" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.32</v>
+      </c>
+      <c r="I158" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J158" s="10" t="n">
-        <v>3.545</v>
+        <v>1.816</v>
       </c>
       <c r="K158" s="10" t="n">
-        <v>3.572</v>
+        <v>1.696</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="15" t="inlineStr"/>
@@ -7629,28 +7629,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D159" s="10" t="n">
-        <v>1.89</v>
+        <v>0.555</v>
       </c>
       <c r="E159" s="18" t="n">
-        <v>0.0053</v>
+        <v>0.0091</v>
       </c>
       <c r="F159" s="12" t="n">
-        <v>530200</v>
+        <v>600600</v>
       </c>
       <c r="G159" s="13" t="n">
-        <v>0.65</v>
+        <v>0.21</v>
       </c>
       <c r="H159" t="n">
-        <v>64.3</v>
+        <v>48.31</v>
       </c>
       <c r="I159" s="14" t="inlineStr">
         <is>
@@ -7658,10 +7658,10 @@
         </is>
       </c>
       <c r="J159" s="10" t="n">
-        <v>1.817</v>
+        <v>0.553</v>
       </c>
       <c r="K159" s="10" t="n">
-        <v>1.696</v>
+        <v>0.587</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="15" t="inlineStr"/>
@@ -7674,39 +7674,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>PJBUMI</t>
         </is>
       </c>
       <c r="D160" s="10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E160" s="16" t="n">
-        <v>0</v>
+        <v>4.14</v>
+      </c>
+      <c r="E160" s="17" t="n">
+        <v>-0.0119</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>529100</v>
+        <v>599700</v>
       </c>
       <c r="G160" s="13" t="n">
-        <v>0.2</v>
+        <v>1.02</v>
       </c>
       <c r="H160" t="n">
-        <v>51.45</v>
-      </c>
-      <c r="I160" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.33</v>
+      </c>
+      <c r="I160" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J160" s="10" t="n">
-        <v>0.634</v>
+        <v>4.175</v>
       </c>
       <c r="K160" s="10" t="n">
-        <v>0.625</v>
+        <v>4.059</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="15" t="inlineStr"/>
@@ -7719,28 +7719,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D161" s="10" t="n">
-        <v>7.53</v>
+        <v>0.585</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="F161" s="12" t="n">
-        <v>525400</v>
+        <v>588800</v>
       </c>
       <c r="G161" s="13" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H161" t="n">
-        <v>56.19</v>
+        <v>57.26</v>
       </c>
       <c r="I161" s="14" t="inlineStr">
         <is>
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="J161" s="10" t="n">
-        <v>7.35</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K161" s="10" t="n">
-        <v>6.998</v>
+        <v>0.533</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="15" t="inlineStr"/>
@@ -7764,39 +7764,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D162" s="10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E162" s="11" t="n">
-        <v>-0.0189</v>
+        <v>2.3</v>
+      </c>
+      <c r="E162" s="18" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>519200</v>
+        <v>585600</v>
       </c>
       <c r="G162" s="13" t="n">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="H162" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="I162" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.4</v>
+      </c>
+      <c r="I162" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="10" t="n">
-        <v>1.628</v>
+        <v>2.153</v>
       </c>
       <c r="K162" s="10" t="n">
-        <v>1.693</v>
+        <v>2.218</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -7809,45 +7809,405 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D163" s="10" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E163" s="18" t="n">
-        <v>0.1038</v>
+        <v>0.805</v>
+      </c>
+      <c r="E163" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F163" s="12" t="n">
-        <v>513000</v>
+        <v>584100</v>
       </c>
       <c r="G163" s="13" t="n">
-        <v>0.97</v>
+        <v>0.22</v>
       </c>
       <c r="H163" t="n">
-        <v>53.89</v>
-      </c>
-      <c r="I163" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.64</v>
+      </c>
+      <c r="I163" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.825</v>
       </c>
       <c r="K163" s="10" t="n">
-        <v>0.622</v>
+        <v>0.853</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="15" t="inlineStr"/>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="E164" s="17" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F164" s="12" t="n">
+        <v>576900</v>
+      </c>
+      <c r="G164" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H164" t="n">
+        <v>56.19</v>
+      </c>
+      <c r="I164" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="10" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="K164" s="10" t="n">
+        <v>6.998</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="15" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>9075</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>THETA</t>
+        </is>
+      </c>
+      <c r="D165" s="10" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E165" s="18" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="F165" s="12" t="n">
+        <v>558100</v>
+      </c>
+      <c r="G165" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H165" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="I165" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J165" s="10" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="K165" s="10" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="15" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E166" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="12" t="n">
+        <v>540700</v>
+      </c>
+      <c r="G166" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H166" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="I166" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J166" s="10" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K166" s="10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="15" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D167" s="10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E167" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="12" t="n">
+        <v>532400</v>
+      </c>
+      <c r="G167" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H167" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="I167" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J167" s="10" t="n">
+        <v>1.362</v>
+      </c>
+      <c r="K167" s="10" t="n">
+        <v>1.428</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="15" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E168" s="18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F168" s="12" t="n">
+        <v>514500</v>
+      </c>
+      <c r="G168" s="13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H168" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="I168" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="10" t="n">
+        <v>2.036</v>
+      </c>
+      <c r="K168" s="10" t="n">
+        <v>2.059</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="15" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>HI</t>
+        </is>
+      </c>
+      <c r="D169" s="10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E169" s="17" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F169" s="12" t="n">
+        <v>513900</v>
+      </c>
+      <c r="G169" s="13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H169" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="I169" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J169" s="10" t="n">
+        <v>1.683</v>
+      </c>
+      <c r="K169" s="10" t="n">
+        <v>1.756</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="15" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E170" s="17" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="F170" s="12" t="n">
+        <v>509400</v>
+      </c>
+      <c r="G170" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H170" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="I170" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J170" s="10" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="K170" s="10" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="15" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E171" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="12" t="n">
+        <v>508800</v>
+      </c>
+      <c r="G171" s="13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H171" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="10" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="K171" s="10" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M163"/>
+  <autoFilter ref="A1:M171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
+++ b/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$176</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,7 @@
         <v>0.08130000000000001</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5785100</v>
+        <v>5792900</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>1.11</v>
@@ -599,7 +599,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 63.61未超买，现价高于50日均线约33.5%，技术面信号偏可靠。</t>
+          <t>SAR转多信号，RSI 63.61未超买，现价高于50日均线约33.5%，技术面信号可靠性较高。</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
         <v>0.1386</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>11259800</v>
+        <v>11288800</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>1.74</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 66.6接近超买区，现价1.15远高于50日均线0.668，偏离较大，信号可靠性需谨慎看待。</t>
+          <t>SAR转多信号出现，但RSI 66.6已接近超买区，现价1.15远高于50日均线0.668，偏离幅度较大，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号出现，但RSI 70.66已接近超买区，现价高于50日均线约19.6%，短期涨幅偏大，信号可靠性需谨慎看待。</t>
+          <t>SAR转多信号出现，但RSI达70.66已近超买区，现价高于50日均线约19.6%，短期涨幅偏大，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>121678400</v>
+        <v>122504600</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>0.33</v>
@@ -777,10 +777,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>37379100</v>
+        <v>37518900</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="H6" t="n">
         <v>56.53</v>
@@ -807,39 +807,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.04</v>
+        <v>0.49</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>-0.1111</v>
+        <v>-0.02</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>35119400</v>
+        <v>35454700</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>2.98</v>
+        <v>0.93</v>
       </c>
       <c r="H7" t="n">
-        <v>27.36</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.67</v>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.056</v>
+        <v>0.44</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>0.068</v>
+        <v>0.343</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="15" t="inlineStr"/>
@@ -852,39 +852,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.495</v>
+        <v>0.04</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>-0.01</v>
+        <v>-0.1111</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>34597400</v>
+        <v>35119400</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.91</v>
+        <v>2.98</v>
       </c>
       <c r="H8" t="n">
-        <v>72.61</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.36</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.441</v>
+        <v>0.056</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>0.343</v>
+        <v>0.068</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="15" t="inlineStr"/>
@@ -912,10 +912,10 @@
         <v>0.0513</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>29387100</v>
+        <v>29492200</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="H9" t="n">
         <v>38.58</v>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>-0.0352</v>
+        <v>-0.0563</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>28320900</v>
+        <v>28624100</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="H10" t="n">
-        <v>59.48</v>
+        <v>54.92</v>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.673</v>
+        <v>0.671</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>0.581</v>
+        <v>0.58</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="15" t="inlineStr"/>
@@ -987,39 +987,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0170</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>KANGER</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>-0.0141</v>
+        <v>-0.3333</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>27568500</v>
+        <v>28074300</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.35</v>
+        <v>36.85</v>
       </c>
       <c r="H11" t="n">
-        <v>64.94</v>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.25</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.325</v>
+        <v>0.019</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>0.273</v>
+        <v>0.023</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="15" t="inlineStr"/>
@@ -1032,39 +1032,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0170</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KANGER</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.01</v>
+        <v>0.35</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>-0.3333</v>
+        <v>-0.0141</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>27296500</v>
+        <v>27570400</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>35.83</v>
+        <v>0.35</v>
       </c>
       <c r="H12" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.94</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.019</v>
+        <v>0.325</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>0.023</v>
+        <v>0.273</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="15" t="inlineStr"/>
@@ -1086,19 +1086,19 @@
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>-0.0052</v>
+        <v>0.97</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>25162000</v>
+        <v>25474100</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H13" t="n">
-        <v>69.03</v>
+        <v>70.27</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>0.0435</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>16325300</v>
+        <v>16327400</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>3.24</v>
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>-0.0309</v>
+        <v>-0.0295</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>15852200</v>
+        <v>16229800</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="H15" t="n">
-        <v>24.96</v>
+        <v>25.22</v>
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="J15" s="10" t="n">
-        <v>7.274</v>
+        <v>7.275</v>
       </c>
       <c r="K15" s="10" t="n">
         <v>7.583</v>
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>13385900</v>
+        <v>13387700</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>0.68</v>
@@ -1356,19 +1356,19 @@
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.385</v>
+        <v>0.38</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>0.0267</v>
+        <v>0.0133</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>12131300</v>
+        <v>12375600</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="H19" t="n">
-        <v>43.88</v>
+        <v>36.71</v>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
@@ -1392,28 +1392,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>0.0058</v>
+        <v>0.27</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>11620100</v>
+        <v>11819100</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.55</v>
+        <v>1.86</v>
       </c>
       <c r="H20" t="n">
-        <v>47.34</v>
+        <v>44.95</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.867</v>
+        <v>0.278</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>0.868</v>
+        <v>0.282</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="15" t="inlineStr"/>
@@ -1437,28 +1437,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.275</v>
+        <v>0.865</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>0.0185</v>
+        <v>0.0058</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>11493000</v>
+        <v>11790100</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1.81</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>47.51</v>
+        <v>47.34</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.279</v>
+        <v>0.867</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>0.282</v>
+        <v>0.868</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="15" t="inlineStr"/>
@@ -1536,19 +1536,19 @@
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.22</v>
+        <v>0.215</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>-0.0435</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>10278600</v>
+        <v>10328500</v>
       </c>
       <c r="G23" s="13" t="n">
         <v>0.54</v>
       </c>
       <c r="H23" t="n">
-        <v>47.99</v>
+        <v>45.3</v>
       </c>
       <c r="I23" s="16" t="inlineStr">
         <is>
@@ -1568,28 +1568,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.775</v>
+        <v>0.15</v>
       </c>
       <c r="E24" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>9132500</v>
+        <v>9938200</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.59</v>
+        <v>0.78</v>
       </c>
       <c r="H24" t="n">
-        <v>50.93</v>
+        <v>37.77</v>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.774</v>
+        <v>0.153</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>0.775</v>
+        <v>0.172</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="15" t="inlineStr"/>
@@ -1613,28 +1613,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.215</v>
+        <v>0.775</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>8826400</v>
+        <v>9132800</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>1.11</v>
+        <v>0.59</v>
       </c>
       <c r="H25" t="n">
-        <v>85.94</v>
+        <v>50.93</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.145</v>
+        <v>0.774</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>0.122</v>
+        <v>0.775</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="15" t="inlineStr"/>
@@ -1658,28 +1658,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="E26" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>8253800</v>
+        <v>9006900</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.65</v>
+        <v>1.13</v>
       </c>
       <c r="H26" t="n">
-        <v>37.77</v>
+        <v>85.94</v>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.153</v>
+        <v>0.145</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>0.172</v>
+        <v>0.122</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="15" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         <v>0.0135</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>8099500</v>
+        <v>8380500</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="H27" t="n">
         <v>66.83</v>
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>7648900</v>
+        <v>7649400</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>0.66</v>
@@ -1808,10 +1808,10 @@
         <v>0.004699999999999999</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>7046900</v>
+        <v>7134300</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H29" t="n">
         <v>53.36</v>
@@ -1853,7 +1853,7 @@
         <v>-0.0263</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>6655200</v>
+        <v>6665200</v>
       </c>
       <c r="G30" s="13" t="n">
         <v>0.37</v>
@@ -1943,7 +1943,7 @@
         <v>0.025</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>6218700</v>
+        <v>6218900</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>0.24</v>
@@ -1966,39 +1966,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>0.0125</v>
+        <v>0.02</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>5553500</v>
+        <v>5693100</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.47</v>
+        <v>0.72</v>
       </c>
       <c r="H33" t="n">
-        <v>52.36</v>
-      </c>
-      <c r="I33" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.21</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.402</v>
+        <v>0.023</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>0.385</v>
+        <v>0.024</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="15" t="inlineStr"/>
@@ -2020,19 +2020,19 @@
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E34" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>0.001</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>5385700</v>
+        <v>5599100</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="H34" t="n">
-        <v>48.09</v>
+        <v>48.87</v>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="J34" s="10" t="n">
-        <v>9.994</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>10.094</v>
@@ -2056,28 +2056,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.535</v>
+        <v>0.41</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.025</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>5310300</v>
+        <v>5578500</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>1.22</v>
+        <v>0.47</v>
       </c>
       <c r="H35" t="n">
-        <v>80.70999999999999</v>
+        <v>53.97</v>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.472</v>
+        <v>0.403</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0.441</v>
+        <v>0.385</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="15" t="inlineStr"/>
@@ -2110,19 +2110,19 @@
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0064</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>5291700</v>
+        <v>5351000</v>
       </c>
       <c r="G36" s="13" t="n">
         <v>0.25</v>
       </c>
       <c r="H36" t="n">
-        <v>50.86</v>
+        <v>49.91</v>
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="J36" s="10" t="n">
-        <v>4.731</v>
+        <v>4.73</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>4.795</v>
+        <v>4.794</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="15" t="inlineStr"/>
@@ -2146,28 +2146,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.645</v>
+        <v>0.53</v>
       </c>
       <c r="E37" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>5266100</v>
+        <v>5349900</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.5</v>
+        <v>1.23</v>
       </c>
       <c r="H37" t="n">
-        <v>66.40000000000001</v>
+        <v>79.91</v>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.629</v>
+        <v>0.471</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.62</v>
+        <v>0.441</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="15" t="inlineStr"/>
@@ -2191,39 +2191,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>0.0156</v>
+        <v>0.645</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>5073400</v>
+        <v>5266100</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>1.27</v>
+        <v>0.5</v>
       </c>
       <c r="H38" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.40000000000001</v>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1.41</v>
+        <v>0.629</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>1.447</v>
+        <v>0.62</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="15" t="inlineStr"/>
@@ -2236,39 +2236,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>-0.0337</v>
+        <v>1.3</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>4756800</v>
+        <v>5243000</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.33</v>
+        <v>1.31</v>
       </c>
       <c r="H39" t="n">
-        <v>31.06</v>
-      </c>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.2</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.468</v>
+        <v>1.41</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>0.585</v>
+        <v>1.447</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="15" t="inlineStr"/>
@@ -2281,39 +2281,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>0.0476</v>
+        <v>0.43</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>-0.0337</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>4634400</v>
+        <v>4803500</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="H40" t="n">
-        <v>36.82</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.06</v>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.125</v>
+        <v>0.468</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0.144</v>
+        <v>0.585</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="15" t="inlineStr"/>
@@ -2326,28 +2326,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>0</v>
+        <v>0.11</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>4156500</v>
+        <v>4634400</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>1.17</v>
+        <v>0.27</v>
       </c>
       <c r="H41" t="n">
-        <v>49.15</v>
+        <v>36.82</v>
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.295</v>
+        <v>0.125</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0.295</v>
+        <v>0.144</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="15" t="inlineStr"/>
@@ -2371,28 +2371,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>-0.0038</v>
+        <v>-0.0112</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>4074500</v>
+        <v>4203500</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.24</v>
+        <v>0.43</v>
       </c>
       <c r="H42" t="n">
-        <v>50.58</v>
+        <v>42</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="J42" s="10" t="n">
-        <v>2.595</v>
+        <v>2.713</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>2.571</v>
+        <v>2.749</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="15" t="inlineStr"/>
@@ -2416,28 +2416,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>-0.0172</v>
+        <v>0.295</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>3946500</v>
+        <v>4156500</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.4</v>
+        <v>1.17</v>
       </c>
       <c r="H43" t="n">
-        <v>33.47</v>
+        <v>49.15</v>
       </c>
       <c r="I43" s="16" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="J43" s="10" t="n">
-        <v>1.19</v>
+        <v>0.295</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>1.271</v>
+        <v>0.295</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="15" t="inlineStr"/>
@@ -2461,39 +2461,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FPI</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>0.0348</v>
+        <v>2.61</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>3910600</v>
+        <v>4102800</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>9.289999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="H44" t="n">
-        <v>69.06999999999999</v>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.27</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="10" t="n">
-        <v>1.099</v>
+        <v>2.596</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>1.1</v>
+        <v>2.571</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="15" t="inlineStr"/>
@@ -2506,39 +2506,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>0.0112</v>
+        <v>1.15</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>3820800</v>
+        <v>4082500</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="H45" t="n">
-        <v>58.59</v>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.03</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="10" t="n">
-        <v>2.613</v>
+        <v>1.191</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>2.6</v>
+        <v>1.272</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="15" t="inlineStr"/>
@@ -2551,28 +2551,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>FPI</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>-0.0208</v>
+        <v>1.19</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>0.0348</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>3792000</v>
+        <v>3923900</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>1.44</v>
+        <v>9.32</v>
       </c>
       <c r="H46" t="n">
-        <v>55.99</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.457</v>
+        <v>1.099</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>0.449</v>
+        <v>1.1</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="15" t="inlineStr"/>
@@ -2596,28 +2596,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1.51</v>
+        <v>2.43</v>
       </c>
       <c r="E47" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>3740000</v>
+        <v>3904400</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
       <c r="H47" t="n">
-        <v>39.52</v>
+        <v>50.42</v>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="J47" s="10" t="n">
-        <v>1.556</v>
+        <v>2.43</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>1.822</v>
+        <v>2.429</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="15" t="inlineStr"/>
@@ -2641,28 +2641,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="E48" s="11" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>3712300</v>
+        <v>3849800</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.38</v>
+        <v>1.46</v>
       </c>
       <c r="H48" t="n">
-        <v>50.42</v>
+        <v>55.99</v>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="J48" s="10" t="n">
-        <v>2.43</v>
+        <v>0.457</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>2.429</v>
+        <v>0.449</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="15" t="inlineStr"/>
@@ -2686,28 +2686,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v>0</v>
+        <v>2.7</v>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>3693300</v>
+        <v>3825300</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.46</v>
+        <v>0.72</v>
       </c>
       <c r="H49" t="n">
-        <v>37.11</v>
+        <v>58.59</v>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="J49" s="10" t="n">
-        <v>1.275</v>
+        <v>2.613</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>1.469</v>
+        <v>2.6</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="15" t="inlineStr"/>
@@ -2731,28 +2731,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>-0.006</v>
+        <v>1.51</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>3648300</v>
+        <v>3815600</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="H50" t="n">
-        <v>67.58</v>
+        <v>39.52</v>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="J50" s="10" t="n">
-        <v>0.8129999999999999</v>
+        <v>1.556</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>0.783</v>
+        <v>1.822</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="15" t="inlineStr"/>
@@ -2776,28 +2776,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>4.98</v>
+        <v>0.155</v>
       </c>
       <c r="E51" s="17" t="n">
-        <v>-0.004</v>
+        <v>-0.0313</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>3635000</v>
+        <v>3740000</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>56.78</v>
+        <v>48.93</v>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="J51" s="10" t="n">
-        <v>4.899</v>
+        <v>0.159</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>4.795</v>
+        <v>0.15</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="15" t="inlineStr"/>
@@ -2821,28 +2821,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>-0.0313</v>
+        <v>1.22</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>3520500</v>
+        <v>3711600</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="H52" t="n">
-        <v>48.93</v>
+        <v>37.11</v>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="J52" s="10" t="n">
-        <v>0.159</v>
+        <v>1.275</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>0.15</v>
+        <v>1.469</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="15" t="inlineStr"/>
@@ -2866,28 +2866,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E53" s="18" t="n">
-        <v>0.0075</v>
+        <v>4.99</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>-0.002</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>3458200</v>
+        <v>3664800</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>0.78</v>
+        <v>0.18</v>
       </c>
       <c r="H53" t="n">
-        <v>63.44</v>
+        <v>57.51</v>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.61</v>
+        <v>4.9</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>0.587</v>
+        <v>4.795</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="15" t="inlineStr"/>
@@ -2911,39 +2911,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>2.65</v>
+        <v>0.83</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>-0.0075</v>
+        <v>-0.006</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>3450400</v>
+        <v>3648300</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0.35</v>
+        <v>0.74</v>
       </c>
       <c r="H54" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.58</v>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="10" t="n">
-        <v>2.714</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>2.749</v>
+        <v>0.783</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="15" t="inlineStr"/>
@@ -2956,28 +2956,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>0.0157</v>
+        <v>0.0075</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>3329900</v>
+        <v>3636600</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>1.07</v>
+        <v>0.82</v>
       </c>
       <c r="H55" t="n">
-        <v>56.73</v>
+        <v>63.44</v>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="J55" s="10" t="n">
-        <v>1.269</v>
+        <v>0.61</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>1.27</v>
+        <v>0.587</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="15" t="inlineStr"/>
@@ -3001,28 +3001,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E56" s="18" t="n">
-        <v>0.0227</v>
+        <v>1.24</v>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>3254600</v>
+        <v>3482000</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="H56" t="n">
-        <v>56.07</v>
+        <v>67.55</v>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.432</v>
+        <v>1.13</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>0.417</v>
+        <v>1.071</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="15" t="inlineStr"/>
@@ -3046,28 +3046,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E57" s="11" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E57" s="18" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>3228700</v>
+        <v>3335000</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>0.89</v>
+        <v>1.07</v>
       </c>
       <c r="H57" t="n">
-        <v>69.45</v>
+        <v>56.73</v>
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="J57" s="10" t="n">
-        <v>0.623</v>
+        <v>1.269</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>0.613</v>
+        <v>1.27</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="15" t="inlineStr"/>
@@ -3091,28 +3091,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E58" s="18" t="n">
-        <v>0.0143</v>
+        <v>0.595</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>3140700</v>
+        <v>3294300</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>1.01</v>
+        <v>0.17</v>
       </c>
       <c r="H58" t="n">
-        <v>60.27</v>
+        <v>55.64</v>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="J58" s="10" t="n">
-        <v>1.317</v>
+        <v>0.575</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>1.258</v>
+        <v>0.552</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="15" t="inlineStr"/>
@@ -3136,39 +3136,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E59" s="11" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>3111400</v>
+        <v>3258900</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>0.26</v>
+        <v>0.46</v>
       </c>
       <c r="H59" t="n">
-        <v>43.12</v>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.07</v>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="10" t="n">
-        <v>0.988</v>
+        <v>0.432</v>
       </c>
       <c r="K59" s="10" t="n">
-        <v>0.993</v>
+        <v>0.417</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="15" t="inlineStr"/>
@@ -3181,39 +3181,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.945</v>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>3053600</v>
+        <v>3234800</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="H60" t="n">
-        <v>65.81999999999999</v>
-      </c>
-      <c r="I60" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.12</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="10" t="n">
-        <v>1.129</v>
+        <v>0.988</v>
       </c>
       <c r="K60" s="10" t="n">
-        <v>1.071</v>
+        <v>0.993</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="15" t="inlineStr"/>
@@ -3226,28 +3226,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>-0.0111</v>
+        <v>0.63</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>3047400</v>
+        <v>3228800</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>0.08</v>
+        <v>0.89</v>
       </c>
       <c r="H61" t="n">
-        <v>46.14</v>
+        <v>69.45</v>
       </c>
       <c r="I61" s="14" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="J61" s="10" t="n">
-        <v>0.453</v>
+        <v>0.623</v>
       </c>
       <c r="K61" s="10" t="n">
-        <v>0.471</v>
+        <v>0.613</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="15" t="inlineStr"/>
@@ -3271,28 +3271,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>5.32</v>
+        <v>1.43</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>0.0095</v>
+        <v>0.0214</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>3035300</v>
+        <v>3168400</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="H62" t="n">
-        <v>47.74</v>
+        <v>60.9</v>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="J62" s="10" t="n">
-        <v>5.356</v>
+        <v>1.318</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>5.531</v>
+        <v>1.259</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="15" t="inlineStr"/>
@@ -3316,28 +3316,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>0.595</v>
+        <v>0.18</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>-0.0083</v>
+        <v>-0.0526</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>3005000</v>
+        <v>3157100</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>0.15</v>
+        <v>0.84</v>
       </c>
       <c r="H63" t="n">
-        <v>55.64</v>
+        <v>40.28</v>
       </c>
       <c r="I63" s="14" t="inlineStr">
         <is>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="J63" s="10" t="n">
-        <v>0.575</v>
+        <v>0.188</v>
       </c>
       <c r="K63" s="10" t="n">
-        <v>0.552</v>
+        <v>0.204</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="15" t="inlineStr"/>
@@ -3361,28 +3361,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>0.215</v>
+        <v>0.44</v>
       </c>
       <c r="E64" s="17" t="n">
-        <v>-0.0444</v>
+        <v>-0.0222</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>2981900</v>
+        <v>3119400</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>2.76</v>
+        <v>0.09</v>
       </c>
       <c r="H64" t="n">
-        <v>41.91</v>
+        <v>44.81</v>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="J64" s="10" t="n">
-        <v>0.223</v>
+        <v>0.452</v>
       </c>
       <c r="K64" s="10" t="n">
-        <v>0.229</v>
+        <v>0.471</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="15" t="inlineStr"/>
@@ -3406,39 +3406,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>-0.0064</v>
+        <v>5.31</v>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>0.0076</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>2788100</v>
+        <v>3071200</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
       <c r="H65" t="n">
-        <v>53.12</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.38</v>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="10" t="n">
-        <v>0.771</v>
+        <v>5.355</v>
       </c>
       <c r="K65" s="10" t="n">
-        <v>0.771</v>
+        <v>5.53</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="15" t="inlineStr"/>
@@ -3451,39 +3451,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E66" s="18" t="n">
-        <v>0.0071</v>
+        <v>0.215</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>-0.0444</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>2783900</v>
+        <v>2981900</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.27</v>
+        <v>2.76</v>
       </c>
       <c r="H66" t="n">
-        <v>45.86</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.91</v>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="10" t="n">
-        <v>0.726</v>
+        <v>0.223</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>0.724</v>
+        <v>0.229</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="15" t="inlineStr"/>
@@ -3505,19 +3505,19 @@
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="E67" s="17" t="n">
-        <v>-0.0145</v>
+        <v>-0.0174</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>2719700</v>
+        <v>2887700</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H67" t="n">
-        <v>82.22</v>
+        <v>80.89</v>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
@@ -3550,19 +3550,19 @@
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>4.46</v>
+        <v>4.47</v>
       </c>
       <c r="E68" s="18" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0068</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>2712300</v>
+        <v>2802400</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H68" t="n">
-        <v>38.69</v>
+        <v>40.04</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -3570,10 +3570,10 @@
         </is>
       </c>
       <c r="J68" s="10" t="n">
-        <v>4.531</v>
+        <v>4.532</v>
       </c>
       <c r="K68" s="10" t="n">
-        <v>4.642</v>
+        <v>4.643</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="15" t="inlineStr"/>
@@ -3586,39 +3586,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E69" s="18" t="n">
-        <v>0.0163</v>
+        <v>0.78</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>2683400</v>
+        <v>2788200</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="H69" t="n">
-        <v>45.91</v>
-      </c>
-      <c r="I69" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.12</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="10" t="n">
-        <v>1.269</v>
+        <v>0.771</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>1.318</v>
+        <v>0.771</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="15" t="inlineStr"/>
@@ -3631,28 +3631,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>-0.0227</v>
+        <v>0.705</v>
+      </c>
+      <c r="E70" s="18" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>2646200</v>
+        <v>2784900</v>
       </c>
       <c r="G70" s="13" t="n">
         <v>0.27</v>
       </c>
       <c r="H70" t="n">
-        <v>40.78</v>
+        <v>45.86</v>
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="J70" s="10" t="n">
-        <v>0.221</v>
+        <v>0.726</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>0.26</v>
+        <v>0.724</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="15" t="inlineStr"/>
@@ -3676,28 +3676,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>-0.0155</v>
+        <v>1.25</v>
+      </c>
+      <c r="E71" s="18" t="n">
+        <v>0.0163</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>2582200</v>
+        <v>2734200</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="H71" t="n">
-        <v>53.45</v>
+        <v>45.91</v>
       </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="J71" s="10" t="n">
-        <v>1.258</v>
+        <v>1.269</v>
       </c>
       <c r="K71" s="10" t="n">
-        <v>1.137</v>
+        <v>1.318</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="15" t="inlineStr"/>
@@ -3721,28 +3721,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E72" s="11" t="n">
-        <v>0</v>
+        <v>2.12</v>
+      </c>
+      <c r="E72" s="18" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>2474100</v>
+        <v>2669900</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>1.28</v>
+        <v>0.42</v>
       </c>
       <c r="H72" t="n">
-        <v>50.78</v>
+        <v>68</v>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="J72" s="10" t="n">
-        <v>0.904</v>
+        <v>2.005</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>0.898</v>
+        <v>1.972</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="15" t="inlineStr"/>
@@ -3766,39 +3766,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="E73" s="11" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>2455300</v>
+        <v>2657400</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>0.76</v>
+        <v>0.27</v>
       </c>
       <c r="H73" t="n">
-        <v>51.04</v>
-      </c>
-      <c r="I73" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.78</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="10" t="n">
-        <v>3.009</v>
+        <v>0.221</v>
       </c>
       <c r="K73" s="10" t="n">
-        <v>2.88</v>
+        <v>0.26</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="15" t="inlineStr"/>
@@ -3811,39 +3811,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="E74" s="18" t="n">
-        <v>0.0033</v>
+        <v>1.27</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>2400900</v>
+        <v>2589600</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="H74" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.45</v>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="10" t="n">
-        <v>3.106</v>
+        <v>1.258</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>3.234</v>
+        <v>1.137</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="15" t="inlineStr"/>
@@ -3856,39 +3856,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>-0.0122</v>
+        <v>0.905</v>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>2386400</v>
+        <v>2474100</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="H75" t="n">
-        <v>35.62</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.78</v>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="10" t="n">
-        <v>0.435</v>
+        <v>0.904</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>0.452</v>
+        <v>0.898</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="15" t="inlineStr"/>
@@ -3901,28 +3901,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D76" s="10" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>-0.0267</v>
+        <v>3.01</v>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>2371000</v>
+        <v>2460400</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>1.95</v>
+        <v>0.76</v>
       </c>
       <c r="H76" t="n">
-        <v>60.14</v>
+        <v>51.04</v>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="J76" s="10" t="n">
-        <v>0.345</v>
+        <v>3.009</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>0.355</v>
+        <v>2.88</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="15" t="inlineStr"/>
@@ -3946,39 +3946,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PANTECH</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>0.6899999999999999</v>
+        <v>3.02</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>0.0299</v>
+        <v>0.0033</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>2331700</v>
+        <v>2444800</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>8.300000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H77" t="n">
-        <v>68.31</v>
-      </c>
-      <c r="I77" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.95</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="10" t="n">
-        <v>0.663</v>
+        <v>3.106</v>
       </c>
       <c r="K77" s="10" t="n">
-        <v>0.662</v>
+        <v>3.234</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="15" t="inlineStr"/>
@@ -3991,39 +3991,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E78" s="11" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2312700</v>
+        <v>2398200</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.24</v>
+        <v>1.2</v>
       </c>
       <c r="H78" t="n">
-        <v>49.09</v>
-      </c>
-      <c r="I78" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.62</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="10" t="n">
-        <v>2.105</v>
+        <v>0.435</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>2.115</v>
+        <v>0.452</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="15" t="inlineStr"/>
@@ -4036,39 +4036,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>PANTECH</t>
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E79" s="11" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E79" s="18" t="n">
+        <v>0.0299</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>2300800</v>
+        <v>2392300</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>1.29</v>
+        <v>8.51</v>
       </c>
       <c r="H79" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="I79" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.31</v>
+      </c>
+      <c r="I79" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="10" t="n">
-        <v>0.746</v>
+        <v>0.663</v>
       </c>
       <c r="K79" s="10" t="n">
-        <v>0.725</v>
+        <v>0.662</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="15" t="inlineStr"/>
@@ -4081,39 +4081,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E80" s="11" t="n">
-        <v>0</v>
+        <v>0.365</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>2243900</v>
+        <v>2371000</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.98</v>
+        <v>1.95</v>
       </c>
       <c r="H80" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="I80" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.14</v>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="10" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.345</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.355</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="15" t="inlineStr"/>
@@ -4126,28 +4126,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>0.0073</v>
+        <v>2.1</v>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>2243600</v>
+        <v>2346100</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="H81" t="n">
-        <v>43.33</v>
+        <v>49.09</v>
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
@@ -4155,10 +4155,10 @@
         </is>
       </c>
       <c r="J81" s="10" t="n">
-        <v>6.994</v>
+        <v>2.105</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>7.436</v>
+        <v>2.115</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="15" t="inlineStr"/>
@@ -4171,39 +4171,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>0.0357</v>
+        <v>0.735</v>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>2210500</v>
+        <v>2306900</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="H82" t="n">
-        <v>38.02</v>
-      </c>
-      <c r="I82" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.88</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="10" t="n">
-        <v>0.308</v>
+        <v>0.746</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>0.352</v>
+        <v>0.725</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="15" t="inlineStr"/>
@@ -4216,28 +4216,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E83" s="17" t="n">
-        <v>-0.0226</v>
+        <v>6.9</v>
+      </c>
+      <c r="E83" s="18" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>2202000</v>
+        <v>2272000</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="H83" t="n">
-        <v>55.26</v>
+        <v>42.93</v>
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="J83" s="10" t="n">
-        <v>3.847</v>
+        <v>6.993</v>
       </c>
       <c r="K83" s="10" t="n">
-        <v>3.379</v>
+        <v>7.436</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="15" t="inlineStr"/>
@@ -4276,10 +4276,10 @@
         <v>-0.0044</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>2189200</v>
+        <v>2259300</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="H84" t="n">
         <v>51.37</v>
@@ -4306,28 +4306,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D85" s="10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E85" s="18" t="n">
-        <v>0.019</v>
+        <v>3.87</v>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>-0.0301</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>2187000</v>
+        <v>2250200</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="H85" t="n">
-        <v>62.43</v>
+        <v>54.21</v>
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="J85" s="10" t="n">
-        <v>4.05</v>
+        <v>3.844</v>
       </c>
       <c r="K85" s="10" t="n">
-        <v>3.709</v>
+        <v>3.378</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="15" t="inlineStr"/>
@@ -4351,39 +4351,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>-0.0308</v>
+        <v>0.55</v>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>2186100</v>
+        <v>2243900</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.65</v>
+        <v>0.98</v>
       </c>
       <c r="H86" t="n">
-        <v>39.32</v>
-      </c>
-      <c r="I86" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.67</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="10" t="n">
-        <v>0.672</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K86" s="10" t="n">
-        <v>0.728</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="15" t="inlineStr"/>
@@ -4396,28 +4396,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E87" s="11" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>-0.0231</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>2164100</v>
+        <v>2238600</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>0.34</v>
+        <v>0.66</v>
       </c>
       <c r="H87" t="n">
-        <v>66.23999999999999</v>
+        <v>40.04</v>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="J87" s="10" t="n">
-        <v>2.003</v>
+        <v>0.673</v>
       </c>
       <c r="K87" s="10" t="n">
-        <v>1.971</v>
+        <v>0.729</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="15" t="inlineStr"/>
@@ -4441,28 +4441,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E88" s="11" t="n">
-        <v>0</v>
+        <v>0.29</v>
+      </c>
+      <c r="E88" s="18" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>2159600</v>
+        <v>2224500</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="H88" t="n">
-        <v>63.12</v>
+        <v>38.02</v>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="J88" s="10" t="n">
-        <v>1.201</v>
+        <v>0.308</v>
       </c>
       <c r="K88" s="10" t="n">
-        <v>1.16</v>
+        <v>0.352</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="15" t="inlineStr"/>
@@ -4486,28 +4486,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D89" s="10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>-0.0181</v>
+        <v>4.3</v>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>0.019</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>2065500</v>
+        <v>2199800</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="H89" t="n">
-        <v>46.02</v>
+        <v>62.43</v>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="J89" s="10" t="n">
-        <v>1.648</v>
+        <v>4.05</v>
       </c>
       <c r="K89" s="10" t="n">
-        <v>1.731</v>
+        <v>3.709</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="15" t="inlineStr"/>
@@ -4531,28 +4531,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="E90" s="18" t="n">
-        <v>0.0095</v>
+        <v>1.26</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>2058500</v>
+        <v>2163900</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="H90" t="n">
-        <v>48.15</v>
+        <v>61.25</v>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="J90" s="10" t="n">
-        <v>6.335</v>
+        <v>1.2</v>
       </c>
       <c r="K90" s="10" t="n">
-        <v>6.587</v>
+        <v>1.16</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="15" t="inlineStr"/>
@@ -4576,39 +4576,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D91" s="10" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>-0.0185</v>
+        <v>6.35</v>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>2038000</v>
+        <v>2093100</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>1.92</v>
+        <v>0.27</v>
       </c>
       <c r="H91" t="n">
-        <v>34.28</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.15</v>
+      </c>
+      <c r="I91" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="10" t="n">
-        <v>0.274</v>
+        <v>6.335</v>
       </c>
       <c r="K91" s="10" t="n">
-        <v>0.283</v>
+        <v>6.587</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="15" t="inlineStr"/>
@@ -4621,28 +4621,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0098</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AUMAS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E92" s="18" t="n">
-        <v>0.029</v>
+        <v>1.63</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>-0.0181</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>2028900</v>
+        <v>2065500</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>1.6</v>
+        <v>0.32</v>
       </c>
       <c r="H92" t="n">
-        <v>53.94</v>
+        <v>46.02</v>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="J92" s="10" t="n">
-        <v>0.347</v>
+        <v>1.648</v>
       </c>
       <c r="K92" s="10" t="n">
-        <v>0.357</v>
+        <v>1.731</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="15" t="inlineStr"/>
@@ -4666,28 +4666,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D93" s="10" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E93" s="11" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>2005600</v>
+        <v>2038000</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>0.23</v>
+        <v>1.92</v>
       </c>
       <c r="H93" t="n">
-        <v>45.37</v>
+        <v>34.28</v>
       </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="J93" s="10" t="n">
-        <v>0.485</v>
+        <v>0.274</v>
       </c>
       <c r="K93" s="10" t="n">
-        <v>0.473</v>
+        <v>0.283</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="15" t="inlineStr"/>
@@ -4711,28 +4711,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0098</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>AUMAS</t>
         </is>
       </c>
       <c r="D94" s="10" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E94" s="11" t="n">
-        <v>0</v>
+        <v>0.355</v>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>0.029</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>1950600</v>
+        <v>2028900</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>0.45</v>
+        <v>1.6</v>
       </c>
       <c r="H94" t="n">
-        <v>56.13</v>
+        <v>53.94</v>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="J94" s="10" t="n">
-        <v>0.904</v>
+        <v>0.347</v>
       </c>
       <c r="K94" s="10" t="n">
-        <v>0.953</v>
+        <v>0.357</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="15" t="inlineStr"/>
@@ -4756,39 +4756,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D95" s="10" t="n">
-        <v>0.35</v>
+        <v>0.465</v>
       </c>
       <c r="E95" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>1927200</v>
+        <v>2018200</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>2.26</v>
+        <v>0.23</v>
       </c>
       <c r="H95" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="I95" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.37</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="10" t="n">
-        <v>0.335</v>
+        <v>0.485</v>
       </c>
       <c r="K95" s="10" t="n">
-        <v>0.319</v>
+        <v>0.473</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="15" t="inlineStr"/>
@@ -4801,39 +4801,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E96" s="18" t="n">
-        <v>0.006</v>
+        <v>0.93</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>1920000</v>
+        <v>1963100</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="H96" t="n">
-        <v>40.69</v>
-      </c>
-      <c r="I96" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.68</v>
+      </c>
+      <c r="I96" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="10" t="n">
-        <v>0.86</v>
+        <v>0.903</v>
       </c>
       <c r="K96" s="10" t="n">
-        <v>0.918</v>
+        <v>0.953</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="15" t="inlineStr"/>
@@ -4846,28 +4846,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D97" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E97" s="17" t="n">
-        <v>-0.0222</v>
+        <v>0.845</v>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>0.006</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>1900000</v>
+        <v>1941000</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>3.98</v>
+        <v>0.71</v>
       </c>
       <c r="H97" t="n">
-        <v>38.5</v>
+        <v>40.69</v>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="J97" s="10" t="n">
-        <v>0.224</v>
+        <v>0.86</v>
       </c>
       <c r="K97" s="10" t="n">
-        <v>0.224</v>
+        <v>0.918</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="15" t="inlineStr"/>
@@ -4891,28 +4891,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D98" s="10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E98" s="18" t="n">
-        <v>0.0242</v>
+        <v>0.35</v>
+      </c>
+      <c r="E98" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>1878400</v>
+        <v>1927200</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>0.23</v>
+        <v>2.26</v>
       </c>
       <c r="H98" t="n">
-        <v>57.22</v>
+        <v>70.63</v>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="J98" s="10" t="n">
-        <v>1.635</v>
+        <v>0.335</v>
       </c>
       <c r="K98" s="10" t="n">
-        <v>1.667</v>
+        <v>0.319</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="15" t="inlineStr"/>
@@ -4936,28 +4936,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D99" s="10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E99" s="11" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>1754100</v>
+        <v>1900000</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>0.19</v>
+        <v>3.98</v>
       </c>
       <c r="H99" t="n">
-        <v>48.02</v>
+        <v>38.5</v>
       </c>
       <c r="I99" s="16" t="inlineStr">
         <is>
@@ -4965,10 +4965,10 @@
         </is>
       </c>
       <c r="J99" s="10" t="n">
-        <v>0.335</v>
+        <v>0.224</v>
       </c>
       <c r="K99" s="10" t="n">
-        <v>0.339</v>
+        <v>0.224</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="15" t="inlineStr"/>
@@ -4981,39 +4981,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E100" s="17" t="n">
-        <v>-0.0248</v>
+        <v>1.68</v>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1731900</v>
+        <v>1896300</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="H100" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="I100" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.05</v>
+      </c>
+      <c r="I100" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="10" t="n">
-        <v>0.604</v>
+        <v>1.634</v>
       </c>
       <c r="K100" s="10" t="n">
-        <v>0.618</v>
+        <v>1.667</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="15" t="inlineStr"/>
@@ -5035,19 +5035,19 @@
         </is>
       </c>
       <c r="D101" s="10" t="n">
-        <v>5.88</v>
+        <v>5.85</v>
       </c>
       <c r="E101" s="18" t="n">
-        <v>0.0226</v>
+        <v>0.0174</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>1693900</v>
+        <v>1836800</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="H101" t="n">
-        <v>51.06</v>
+        <v>49.22</v>
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="J101" s="10" t="n">
-        <v>5.818</v>
+        <v>5.815</v>
       </c>
       <c r="K101" s="10" t="n">
         <v>6.046</v>
@@ -5071,39 +5071,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D102" s="10" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>-0.0161</v>
+        <v>0.33</v>
+      </c>
+      <c r="E102" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>1691200</v>
+        <v>1754200</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>2.08</v>
+        <v>0.19</v>
       </c>
       <c r="H102" t="n">
-        <v>56.04</v>
-      </c>
-      <c r="I102" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.02</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="10" t="n">
-        <v>0.294</v>
+        <v>0.335</v>
       </c>
       <c r="K102" s="10" t="n">
-        <v>0.293</v>
+        <v>0.339</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="15" t="inlineStr"/>
@@ -5131,10 +5131,10 @@
         <v>0.009899999999999999</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>1669900</v>
+        <v>1733700</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H103" t="n">
         <v>38.17</v>
@@ -5161,28 +5161,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D104" s="10" t="n">
-        <v>0.865</v>
+        <v>0.59</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0248</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1618000</v>
+        <v>1731900</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>0.55</v>
+        <v>0.19</v>
       </c>
       <c r="H104" t="n">
-        <v>49.58</v>
+        <v>46.38</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5190,10 +5190,10 @@
         </is>
       </c>
       <c r="J104" s="10" t="n">
-        <v>0.866</v>
+        <v>0.604</v>
       </c>
       <c r="K104" s="10" t="n">
-        <v>0.861</v>
+        <v>0.618</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="15" t="inlineStr"/>
@@ -5206,40 +5206,33 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D105" s="10" t="n">
-        <v>7.48</v>
+        <v>0.73</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>0.0136</v>
+        <v>0.0069</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>1603400</v>
+        <v>1724600</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H105" t="n">
-        <v>50.52</v>
-      </c>
-      <c r="I105" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J105" s="10" t="n">
-        <v>7.411</v>
-      </c>
-      <c r="K105" s="10" t="n">
-        <v>7.755</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="10" t="n"/>
+      <c r="K105" s="10" t="n"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="15" t="inlineStr"/>
     </row>
@@ -5251,28 +5244,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E106" s="18" t="n">
-        <v>0.0147</v>
+        <v>0.305</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1601300</v>
+        <v>1691200</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.48</v>
+        <v>2.08</v>
       </c>
       <c r="H106" t="n">
-        <v>58.74</v>
+        <v>56.04</v>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
@@ -5280,10 +5273,10 @@
         </is>
       </c>
       <c r="J106" s="10" t="n">
-        <v>0.338</v>
+        <v>0.294</v>
       </c>
       <c r="K106" s="10" t="n">
-        <v>0.343</v>
+        <v>0.293</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="15" t="inlineStr"/>
@@ -5296,39 +5289,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D107" s="10" t="n">
-        <v>0.335</v>
+        <v>0.2</v>
       </c>
       <c r="E107" s="17" t="n">
-        <v>-0.029</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>1547800</v>
+        <v>1638800</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>1.01</v>
+        <v>0.73</v>
       </c>
       <c r="H107" t="n">
-        <v>57.81</v>
-      </c>
-      <c r="I107" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.74</v>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="10" t="n">
-        <v>0.32</v>
+        <v>0.209</v>
       </c>
       <c r="K107" s="10" t="n">
-        <v>0.33</v>
+        <v>0.194</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="15" t="inlineStr"/>
@@ -5341,39 +5334,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ESCERAM</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E108" s="17" t="n">
-        <v>-0.0682</v>
+        <v>7.49</v>
+      </c>
+      <c r="E108" s="18" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>1538800</v>
+        <v>1622200</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.68</v>
+        <v>0.15</v>
       </c>
       <c r="H108" t="n">
-        <v>49.66</v>
-      </c>
-      <c r="I108" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.08</v>
+      </c>
+      <c r="I108" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="10" t="n">
-        <v>0.209</v>
+        <v>7.412</v>
       </c>
       <c r="K108" s="10" t="n">
-        <v>0.194</v>
+        <v>7.755</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="15" t="inlineStr"/>
@@ -5386,39 +5379,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TDM</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D109" s="10" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E109" s="18" t="n">
-        <v>0.0513</v>
+        <v>0.865</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>1525100</v>
+        <v>1618000</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>4.19</v>
+        <v>0.55</v>
       </c>
       <c r="H109" t="n">
-        <v>52.51</v>
-      </c>
-      <c r="I109" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.58</v>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="10" t="n">
-        <v>0.201</v>
+        <v>0.866</v>
       </c>
       <c r="K109" s="10" t="n">
-        <v>0.214</v>
+        <v>0.861</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="15" t="inlineStr"/>
@@ -5431,33 +5424,40 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E110" s="11" t="n">
-        <v>0</v>
+        <v>0.345</v>
+      </c>
+      <c r="E110" s="18" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1518700</v>
+        <v>1616300</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I110" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J110" s="10" t="n"/>
-      <c r="K110" s="10" t="n"/>
+        <v>0.49</v>
+      </c>
+      <c r="H110" t="n">
+        <v>58.74</v>
+      </c>
+      <c r="I110" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="K110" s="10" t="n">
+        <v>0.343</v>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="15" t="inlineStr"/>
     </row>
@@ -5469,28 +5469,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D111" s="10" t="n">
-        <v>4.65</v>
+        <v>0.335</v>
       </c>
       <c r="E111" s="17" t="n">
-        <v>-0.0148</v>
+        <v>-0.029</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>1485400</v>
+        <v>1547800</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>0.31</v>
+        <v>1.01</v>
       </c>
       <c r="H111" t="n">
-        <v>57.38</v>
+        <v>57.81</v>
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="J111" s="10" t="n">
-        <v>4.487</v>
+        <v>0.32</v>
       </c>
       <c r="K111" s="10" t="n">
-        <v>4.451</v>
+        <v>0.33</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="15" t="inlineStr"/>
@@ -5514,28 +5514,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TDM</t>
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="E112" s="17" t="n">
-        <v>-0.0058</v>
+        <v>0.205</v>
+      </c>
+      <c r="E112" s="18" t="n">
+        <v>0.0513</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>1451800</v>
+        <v>1525100</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>0.25</v>
+        <v>4.19</v>
       </c>
       <c r="H112" t="n">
-        <v>60.35</v>
+        <v>52.51</v>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
@@ -5543,10 +5543,10 @@
         </is>
       </c>
       <c r="J112" s="10" t="n">
-        <v>6.449</v>
+        <v>0.201</v>
       </c>
       <c r="K112" s="10" t="n">
-        <v>6.068</v>
+        <v>0.214</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="15" t="inlineStr"/>
@@ -5559,28 +5559,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D113" s="10" t="n">
-        <v>0.765</v>
+        <v>4.65</v>
       </c>
       <c r="E113" s="17" t="n">
-        <v>-0.0129</v>
+        <v>-0.0148</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>1413700</v>
+        <v>1487200</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="H113" t="n">
-        <v>54.86</v>
+        <v>57.38</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="J113" s="10" t="n">
-        <v>0.749</v>
+        <v>4.487</v>
       </c>
       <c r="K113" s="10" t="n">
-        <v>0.699</v>
+        <v>4.451</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="15" t="inlineStr"/>
@@ -5604,28 +5604,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>COMFORT</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D114" s="10" t="n">
-        <v>0.2</v>
+        <v>6.87</v>
       </c>
       <c r="E114" s="17" t="n">
-        <v>-0.0476</v>
+        <v>-0.0043</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>1325600</v>
+        <v>1454800</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.65</v>
+        <v>0.25</v>
       </c>
       <c r="H114" t="n">
-        <v>63.86</v>
+        <v>60.57</v>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="J114" s="10" t="n">
-        <v>0.181</v>
+        <v>6.45</v>
       </c>
       <c r="K114" s="10" t="n">
-        <v>0.166</v>
+        <v>6.069</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="15" t="inlineStr"/>
@@ -5649,28 +5649,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D115" s="10" t="n">
-        <v>0.63</v>
+        <v>0.765</v>
       </c>
       <c r="E115" s="17" t="n">
-        <v>-0.0156</v>
+        <v>-0.0129</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>1312100</v>
+        <v>1417000</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="H115" t="n">
-        <v>45.12</v>
+        <v>54.86</v>
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="J115" s="10" t="n">
-        <v>0.64</v>
+        <v>0.749</v>
       </c>
       <c r="K115" s="10" t="n">
-        <v>0.631</v>
+        <v>0.699</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="15" t="inlineStr"/>
@@ -5694,39 +5694,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>COMFORT</t>
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="E116" s="18" t="n">
-        <v>0.0013</v>
+        <v>0.2</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>-0.0476</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>1306800</v>
+        <v>1355600</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="H116" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="I116" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.86</v>
+      </c>
+      <c r="I116" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="10" t="n">
-        <v>7.891</v>
+        <v>0.181</v>
       </c>
       <c r="K116" s="10" t="n">
-        <v>7.913</v>
+        <v>0.166</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="15" t="inlineStr"/>
@@ -5754,10 +5754,10 @@
         <v>-0.0308</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>1256900</v>
+        <v>1349500</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="H117" t="n">
         <v>54.6</v>
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D118" s="10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E118" s="17" t="n">
-        <v>-0.0308</v>
+        <v>7.85</v>
+      </c>
+      <c r="E118" s="18" t="n">
+        <v>0.0026</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>1230300</v>
+        <v>1319300</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>0.19</v>
+        <v>0.44</v>
       </c>
       <c r="H118" t="n">
-        <v>54.54</v>
-      </c>
-      <c r="I118" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.92</v>
+      </c>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="10" t="n">
-        <v>1.243</v>
+        <v>7.892</v>
       </c>
       <c r="K118" s="10" t="n">
-        <v>1.214</v>
+        <v>7.914</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="15" t="inlineStr"/>
@@ -5829,39 +5829,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D119" s="10" t="n">
-        <v>2.28</v>
+        <v>0.63</v>
       </c>
       <c r="E119" s="17" t="n">
-        <v>-0.013</v>
+        <v>-0.0156</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>1192000</v>
+        <v>1312100</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="H119" t="n">
-        <v>50.29</v>
-      </c>
-      <c r="I119" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.12</v>
+      </c>
+      <c r="I119" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="10" t="n">
-        <v>2.296</v>
+        <v>0.64</v>
       </c>
       <c r="K119" s="10" t="n">
-        <v>2.225</v>
+        <v>0.631</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="15" t="inlineStr"/>
@@ -5874,28 +5874,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D120" s="10" t="n">
-        <v>0.9350000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="E120" s="17" t="n">
-        <v>-0.0158</v>
+        <v>-0.0308</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>1134900</v>
+        <v>1261400</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="H120" t="n">
-        <v>49.94</v>
+        <v>54.54</v>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="J120" s="10" t="n">
-        <v>0.9429999999999999</v>
+        <v>1.243</v>
       </c>
       <c r="K120" s="10" t="n">
-        <v>0.9</v>
+        <v>1.214</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="15" t="inlineStr"/>
@@ -5919,28 +5919,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D121" s="10" t="n">
-        <v>0.865</v>
+        <v>2.28</v>
       </c>
       <c r="E121" s="17" t="n">
-        <v>-0.0114</v>
+        <v>-0.013</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>1101900</v>
+        <v>1217300</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="H121" t="n">
-        <v>57.24</v>
+        <v>50.29</v>
       </c>
       <c r="I121" s="16" t="inlineStr">
         <is>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="J121" s="10" t="n">
-        <v>0.841</v>
+        <v>2.296</v>
       </c>
       <c r="K121" s="10" t="n">
-        <v>0.8080000000000001</v>
+        <v>2.225</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="15" t="inlineStr"/>
@@ -5964,28 +5964,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D122" s="10" t="n">
-        <v>2.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E122" s="17" t="n">
-        <v>-0.0034</v>
+        <v>-0.0105</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>1097800</v>
+        <v>1154700</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="H122" t="n">
-        <v>57.34</v>
+        <v>51.71</v>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
@@ -5993,10 +5993,10 @@
         </is>
       </c>
       <c r="J122" s="10" t="n">
-        <v>2.827</v>
+        <v>0.944</v>
       </c>
       <c r="K122" s="10" t="n">
-        <v>2.712</v>
+        <v>0.9</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="15" t="inlineStr"/>
@@ -6009,39 +6009,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D123" s="10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E123" s="18" t="n">
-        <v>0.0061</v>
+        <v>0.865</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>-0.0114</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>1079100</v>
+        <v>1124000</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="H123" t="n">
-        <v>58.06</v>
-      </c>
-      <c r="I123" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.24</v>
+      </c>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="10" t="n">
-        <v>13.132</v>
+        <v>0.841</v>
       </c>
       <c r="K123" s="10" t="n">
-        <v>13.259</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="15" t="inlineStr"/>
@@ -6054,28 +6054,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D124" s="10" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E124" s="18" t="n">
-        <v>0.0435</v>
+        <v>2.89</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1077100</v>
+        <v>1100400</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>3.45</v>
+        <v>0.18</v>
       </c>
       <c r="H124" t="n">
-        <v>73.72</v>
+        <v>55.92</v>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="J124" s="10" t="n">
-        <v>0.317</v>
+        <v>2.825</v>
       </c>
       <c r="K124" s="10" t="n">
-        <v>0.299</v>
+        <v>2.712</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="15" t="inlineStr"/>
@@ -6099,39 +6099,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D125" s="10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E125" s="17" t="n">
-        <v>-0.0132</v>
+        <v>13.3</v>
+      </c>
+      <c r="E125" s="18" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>1018800</v>
+        <v>1096000</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="H125" t="n">
-        <v>52.49</v>
-      </c>
-      <c r="I125" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.06</v>
+      </c>
+      <c r="I125" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="10" t="n">
-        <v>0.746</v>
+        <v>13.132</v>
       </c>
       <c r="K125" s="10" t="n">
-        <v>0.709</v>
+        <v>13.259</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="15" t="inlineStr"/>
@@ -6144,39 +6144,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D126" s="10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E126" s="11" t="n">
-        <v>0</v>
+        <v>0.36</v>
+      </c>
+      <c r="E126" s="18" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>939400</v>
+        <v>1078100</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>0.34</v>
+        <v>3.45</v>
       </c>
       <c r="H126" t="n">
-        <v>58.56</v>
-      </c>
-      <c r="I126" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.72</v>
+      </c>
+      <c r="I126" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="10" t="n">
-        <v>1.289</v>
+        <v>0.317</v>
       </c>
       <c r="K126" s="10" t="n">
-        <v>1.197</v>
+        <v>0.299</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="15" t="inlineStr"/>
@@ -6189,39 +6189,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D127" s="10" t="n">
-        <v>0.855</v>
+        <v>0.425</v>
       </c>
       <c r="E127" s="17" t="n">
-        <v>-0.0058</v>
+        <v>-0.0116</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>927500</v>
+        <v>1049600</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H127" t="n">
-        <v>45.84</v>
-      </c>
-      <c r="I127" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.63</v>
+      </c>
+      <c r="I127" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="10" t="n">
-        <v>0.879</v>
+        <v>0.405</v>
       </c>
       <c r="K127" s="10" t="n">
-        <v>0.868</v>
+        <v>0.369</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="15" t="inlineStr"/>
@@ -6234,39 +6234,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D128" s="10" t="n">
-        <v>1.28</v>
+        <v>0.74</v>
       </c>
       <c r="E128" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0263</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>926400</v>
+        <v>1040400</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="H128" t="n">
-        <v>67.77</v>
-      </c>
-      <c r="I128" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.52</v>
+      </c>
+      <c r="I128" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="10" t="n">
-        <v>1.14</v>
+        <v>0.745</v>
       </c>
       <c r="K128" s="10" t="n">
-        <v>0.999</v>
+        <v>0.709</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="15" t="inlineStr"/>
@@ -6288,19 +6288,19 @@
         </is>
       </c>
       <c r="D129" s="10" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="E129" s="18" t="n">
-        <v>0.0303</v>
+        <v>0.0337</v>
       </c>
       <c r="F129" s="12" t="n">
-        <v>902700</v>
+        <v>943700</v>
       </c>
       <c r="G129" s="13" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="H129" t="n">
-        <v>65.27</v>
+        <v>65.72</v>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="J129" s="10" t="n">
-        <v>2.853</v>
+        <v>2.854</v>
       </c>
       <c r="K129" s="10" t="n">
         <v>2.856</v>
@@ -6324,39 +6324,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D130" s="10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E130" s="18" t="n">
-        <v>0.0208</v>
+        <v>1.35</v>
+      </c>
+      <c r="E130" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>902300</v>
+        <v>940700</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>1.29</v>
+        <v>0.34</v>
       </c>
       <c r="H130" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="I130" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.56</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="10" t="n">
-        <v>1.467</v>
+        <v>1.289</v>
       </c>
       <c r="K130" s="10" t="n">
-        <v>1.578</v>
+        <v>1.197</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="15" t="inlineStr"/>
@@ -6369,28 +6369,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D131" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E131" s="18" t="n">
-        <v>0.0246</v>
+        <v>0.855</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F131" s="12" t="n">
-        <v>896000</v>
+        <v>931800</v>
       </c>
       <c r="G131" s="13" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="H131" t="n">
-        <v>49.36</v>
+        <v>45.84</v>
       </c>
       <c r="I131" s="14" t="inlineStr">
         <is>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="J131" s="10" t="n">
-        <v>2.474</v>
+        <v>0.879</v>
       </c>
       <c r="K131" s="10" t="n">
-        <v>2.61</v>
+        <v>0.868</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="15" t="inlineStr"/>
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D132" s="10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E132" s="18" t="n">
-        <v>0.0198</v>
+        <v>1.28</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>890500</v>
+        <v>927100</v>
       </c>
       <c r="G132" s="13" t="n">
-        <v>0.36</v>
+        <v>0.18</v>
       </c>
       <c r="H132" t="n">
-        <v>43.18</v>
-      </c>
-      <c r="I132" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.77</v>
+      </c>
+      <c r="I132" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="10" t="n">
-        <v>1.052</v>
+        <v>1.14</v>
       </c>
       <c r="K132" s="10" t="n">
-        <v>1.11</v>
+        <v>0.999</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="15" t="inlineStr"/>
@@ -6459,28 +6459,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D133" s="10" t="n">
-        <v>5.18</v>
+        <v>1.47</v>
       </c>
       <c r="E133" s="18" t="n">
-        <v>0.0019</v>
+        <v>0.0208</v>
       </c>
       <c r="F133" s="12" t="n">
-        <v>874200</v>
+        <v>908700</v>
       </c>
       <c r="G133" s="13" t="n">
-        <v>0.21</v>
+        <v>1.3</v>
       </c>
       <c r="H133" t="n">
-        <v>56.04</v>
+        <v>47.14</v>
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="J133" s="10" t="n">
-        <v>5.081</v>
+        <v>1.467</v>
       </c>
       <c r="K133" s="10" t="n">
-        <v>5.034</v>
+        <v>1.578</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="15" t="inlineStr"/>
@@ -6504,39 +6504,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E134" s="17" t="n">
-        <v>-0.0017</v>
+        <v>2.5</v>
+      </c>
+      <c r="E134" s="18" t="n">
+        <v>0.0246</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>872500</v>
+        <v>904600</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H134" t="n">
-        <v>58.39</v>
-      </c>
-      <c r="I134" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.36</v>
+      </c>
+      <c r="I134" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="10" t="n">
-        <v>5.573</v>
+        <v>2.474</v>
       </c>
       <c r="K134" s="10" t="n">
-        <v>5.4</v>
+        <v>2.61</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="15" t="inlineStr"/>
@@ -6549,39 +6549,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D135" s="10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E135" s="17" t="n">
-        <v>-0.0074</v>
+        <v>5.19</v>
+      </c>
+      <c r="E135" s="18" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F135" s="12" t="n">
-        <v>869700</v>
+        <v>903600</v>
       </c>
       <c r="G135" s="13" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="H135" t="n">
-        <v>44.38</v>
-      </c>
-      <c r="I135" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.49</v>
+      </c>
+      <c r="I135" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="10" t="n">
-        <v>0.704</v>
+        <v>5.082</v>
       </c>
       <c r="K135" s="10" t="n">
-        <v>0.6919999999999999</v>
+        <v>5.034</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="15" t="inlineStr"/>
@@ -6594,39 +6594,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D136" s="10" t="n">
-        <v>3.95</v>
+        <v>1.02</v>
       </c>
       <c r="E136" s="18" t="n">
-        <v>0.0051</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>864800</v>
+        <v>899900</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="H136" t="n">
-        <v>55.94</v>
-      </c>
-      <c r="I136" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.02</v>
+      </c>
+      <c r="I136" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="10" t="n">
-        <v>3.849</v>
+        <v>1.051</v>
       </c>
       <c r="K136" s="10" t="n">
-        <v>3.776</v>
+        <v>1.11</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="15" t="inlineStr"/>
@@ -6639,39 +6639,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D137" s="10" t="n">
-        <v>11.02</v>
+        <v>0.67</v>
       </c>
       <c r="E137" s="17" t="n">
-        <v>-0.0036</v>
+        <v>-0.0074</v>
       </c>
       <c r="F137" s="12" t="n">
-        <v>858200</v>
+        <v>890400</v>
       </c>
       <c r="G137" s="13" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="H137" t="n">
-        <v>61.56</v>
-      </c>
-      <c r="I137" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.38</v>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="10" t="n">
-        <v>10.602</v>
+        <v>0.704</v>
       </c>
       <c r="K137" s="10" t="n">
-        <v>9.972</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="15" t="inlineStr"/>
@@ -6684,28 +6684,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>0.605</v>
+        <v>5.8</v>
       </c>
       <c r="E138" s="17" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0017</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>845100</v>
+        <v>883700</v>
       </c>
       <c r="G138" s="13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="H138" t="n">
-        <v>40.64</v>
+        <v>58.39</v>
       </c>
       <c r="I138" s="16" t="inlineStr">
         <is>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="J138" s="10" t="n">
-        <v>0.636</v>
+        <v>5.573</v>
       </c>
       <c r="K138" s="10" t="n">
-        <v>0.676</v>
+        <v>5.4</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
@@ -6729,39 +6729,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D139" s="10" t="n">
-        <v>2.5</v>
+        <v>3.96</v>
       </c>
       <c r="E139" s="18" t="n">
-        <v>0.0246</v>
+        <v>0.0076</v>
       </c>
       <c r="F139" s="12" t="n">
-        <v>836500</v>
+        <v>867500</v>
       </c>
       <c r="G139" s="13" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="H139" t="n">
-        <v>45.78</v>
-      </c>
-      <c r="I139" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.33</v>
+      </c>
+      <c r="I139" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="10" t="n">
-        <v>2.511</v>
+        <v>3.85</v>
       </c>
       <c r="K139" s="10" t="n">
-        <v>2.623</v>
+        <v>3.776</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="15" t="inlineStr"/>
@@ -6774,39 +6774,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D140" s="10" t="n">
-        <v>2.74</v>
+        <v>11</v>
       </c>
       <c r="E140" s="17" t="n">
-        <v>-0.0214</v>
+        <v>-0.0054</v>
       </c>
       <c r="F140" s="12" t="n">
-        <v>822300</v>
+        <v>861500</v>
       </c>
       <c r="G140" s="13" t="n">
         <v>0.23</v>
       </c>
       <c r="H140" t="n">
-        <v>43</v>
-      </c>
-      <c r="I140" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.08</v>
+      </c>
+      <c r="I140" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="10" t="n">
-        <v>2.809</v>
+        <v>10.6</v>
       </c>
       <c r="K140" s="10" t="n">
-        <v>2.94</v>
+        <v>9.972</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="15" t="inlineStr"/>
@@ -6819,39 +6819,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>KEEMING</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D141" s="10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E141" s="18" t="n">
-        <v>0.0397</v>
+        <v>0.605</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F141" s="12" t="n">
-        <v>782000</v>
+        <v>845200</v>
       </c>
       <c r="G141" s="13" t="n">
-        <v>1.02</v>
+        <v>0.11</v>
       </c>
       <c r="H141" t="n">
-        <v>66.08</v>
-      </c>
-      <c r="I141" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.64</v>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="10" t="n">
-        <v>2.612</v>
+        <v>0.636</v>
       </c>
       <c r="K141" s="10" t="n">
-        <v>2.54</v>
+        <v>0.676</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="15" t="inlineStr"/>
@@ -6864,28 +6864,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D142" s="10" t="n">
-        <v>0.785</v>
+        <v>2.5</v>
       </c>
       <c r="E142" s="18" t="n">
-        <v>0.0129</v>
+        <v>0.0246</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>761500</v>
+        <v>836500</v>
       </c>
       <c r="G142" s="13" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="H142" t="n">
-        <v>25.39</v>
+        <v>45.78</v>
       </c>
       <c r="I142" s="16" t="inlineStr">
         <is>
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="J142" s="10" t="n">
-        <v>0.856</v>
+        <v>2.511</v>
       </c>
       <c r="K142" s="10" t="n">
-        <v>1.017</v>
+        <v>2.623</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="15" t="inlineStr"/>
@@ -6909,28 +6909,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D143" s="10" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E143" s="18" t="n">
-        <v>0.0062</v>
+        <v>2.74</v>
+      </c>
+      <c r="E143" s="17" t="n">
+        <v>-0.0214</v>
       </c>
       <c r="F143" s="12" t="n">
-        <v>760400</v>
+        <v>824800</v>
       </c>
       <c r="G143" s="13" t="n">
-        <v>0.34</v>
+        <v>0.23</v>
       </c>
       <c r="H143" t="n">
-        <v>69.41</v>
+        <v>43</v>
       </c>
       <c r="I143" s="16" t="inlineStr">
         <is>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="J143" s="10" t="n">
-        <v>0.752</v>
+        <v>2.809</v>
       </c>
       <c r="K143" s="10" t="n">
-        <v>0.68</v>
+        <v>2.94</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="15" t="inlineStr"/>
@@ -6954,28 +6954,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D144" s="10" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E144" s="17" t="n">
-        <v>-0.0146</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E144" s="18" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>744700</v>
+        <v>791500</v>
       </c>
       <c r="G144" s="13" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H144" t="n">
-        <v>57.05</v>
+        <v>69.41</v>
       </c>
       <c r="I144" s="16" t="inlineStr">
         <is>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="J144" s="10" t="n">
-        <v>0.659</v>
+        <v>0.752</v>
       </c>
       <c r="K144" s="10" t="n">
-        <v>0.592</v>
+        <v>0.68</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -6999,28 +6999,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MNRB</t>
+          <t>KEEMING</t>
         </is>
       </c>
       <c r="D145" s="10" t="n">
-        <v>2.53</v>
+        <v>2.87</v>
       </c>
       <c r="E145" s="18" t="n">
-        <v>0.004</v>
+        <v>0.0361</v>
       </c>
       <c r="F145" s="12" t="n">
-        <v>729800</v>
+        <v>785500</v>
       </c>
       <c r="G145" s="13" t="n">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="H145" t="n">
-        <v>41.16</v>
+        <v>65.73</v>
       </c>
       <c r="I145" s="14" t="inlineStr">
         <is>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="J145" s="10" t="n">
-        <v>2.561</v>
+        <v>2.611</v>
       </c>
       <c r="K145" s="10" t="n">
-        <v>2.667</v>
+        <v>2.54</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="15" t="inlineStr"/>
@@ -7044,39 +7044,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D146" s="10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E146" s="17" t="n">
-        <v>-0.0053</v>
+        <v>0.78</v>
+      </c>
+      <c r="E146" s="18" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>727900</v>
+        <v>768500</v>
       </c>
       <c r="G146" s="13" t="n">
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="H146" t="n">
-        <v>40.07</v>
-      </c>
-      <c r="I146" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.74</v>
+      </c>
+      <c r="I146" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J146" s="10" t="n">
-        <v>0.95</v>
+        <v>0.856</v>
       </c>
       <c r="K146" s="10" t="n">
-        <v>1.023</v>
+        <v>1.017</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="15" t="inlineStr"/>
@@ -7089,39 +7089,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D147" s="10" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E147" s="11" t="n">
-        <v>0</v>
+        <v>0.675</v>
+      </c>
+      <c r="E147" s="17" t="n">
+        <v>-0.0146</v>
       </c>
       <c r="F147" s="12" t="n">
-        <v>724100</v>
+        <v>754700</v>
       </c>
       <c r="G147" s="13" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="H147" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="I147" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.05</v>
+      </c>
+      <c r="I147" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="10" t="n">
-        <v>0.494</v>
+        <v>0.659</v>
       </c>
       <c r="K147" s="10" t="n">
-        <v>0.485</v>
+        <v>0.592</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="15" t="inlineStr"/>
@@ -7134,28 +7134,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D148" s="10" t="n">
-        <v>0.64</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E148" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0053</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>695200</v>
+        <v>737900</v>
       </c>
       <c r="G148" s="13" t="n">
-        <v>0.7</v>
+        <v>0.16</v>
       </c>
       <c r="H148" t="n">
-        <v>58.16</v>
+        <v>40.07</v>
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="J148" s="10" t="n">
-        <v>0.636</v>
+        <v>0.95</v>
       </c>
       <c r="K148" s="10" t="n">
-        <v>0.634</v>
+        <v>1.023</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -7179,28 +7179,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D149" s="10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E149" s="17" t="n">
-        <v>-0.0046</v>
+        <v>0.51</v>
+      </c>
+      <c r="E149" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F149" s="12" t="n">
-        <v>682300</v>
+        <v>733900</v>
       </c>
       <c r="G149" s="13" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="H149" t="n">
-        <v>46.32</v>
+        <v>58.07</v>
       </c>
       <c r="I149" s="14" t="inlineStr">
         <is>
@@ -7208,10 +7208,10 @@
         </is>
       </c>
       <c r="J149" s="10" t="n">
-        <v>4.33</v>
+        <v>0.494</v>
       </c>
       <c r="K149" s="10" t="n">
-        <v>4.577</v>
+        <v>0.485</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="15" t="inlineStr"/>
@@ -7224,39 +7224,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>MNRB</t>
         </is>
       </c>
       <c r="D150" s="10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E150" s="17" t="n">
-        <v>-0.011</v>
+        <v>2.53</v>
+      </c>
+      <c r="E150" s="18" t="n">
+        <v>0.004</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>681900</v>
+        <v>730300</v>
       </c>
       <c r="G150" s="13" t="n">
-        <v>0.83</v>
+        <v>1.39</v>
       </c>
       <c r="H150" t="n">
-        <v>34.68</v>
-      </c>
-      <c r="I150" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.16</v>
+      </c>
+      <c r="I150" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.561</v>
       </c>
       <c r="K150" s="10" t="n">
-        <v>0.966</v>
+        <v>2.667</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -7269,39 +7269,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D151" s="10" t="n">
-        <v>1.15</v>
+        <v>4.31</v>
       </c>
       <c r="E151" s="17" t="n">
-        <v>-0.0171</v>
+        <v>-0.0092</v>
       </c>
       <c r="F151" s="12" t="n">
-        <v>674500</v>
+        <v>725200</v>
       </c>
       <c r="G151" s="13" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="H151" t="n">
-        <v>57.15</v>
-      </c>
-      <c r="I151" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.03</v>
+      </c>
+      <c r="I151" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="10" t="n">
-        <v>1.11</v>
+        <v>4.328</v>
       </c>
       <c r="K151" s="10" t="n">
-        <v>0.954</v>
+        <v>4.577</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="15" t="inlineStr"/>
@@ -7314,39 +7314,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D152" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E152" s="11" t="n">
-        <v>0</v>
+        <v>1.16</v>
+      </c>
+      <c r="E152" s="17" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>672200</v>
+        <v>717300</v>
       </c>
       <c r="G152" s="13" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H152" t="n">
-        <v>59.38</v>
-      </c>
-      <c r="I152" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.36</v>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="10" t="n">
-        <v>7.872</v>
+        <v>1.111</v>
       </c>
       <c r="K152" s="10" t="n">
-        <v>7.867</v>
+        <v>0.955</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="15" t="inlineStr"/>
@@ -7359,39 +7359,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D153" s="10" t="n">
-        <v>0.605</v>
+        <v>0.64</v>
       </c>
       <c r="E153" s="17" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F153" s="12" t="n">
-        <v>671800</v>
+        <v>695200</v>
       </c>
       <c r="G153" s="13" t="n">
-        <v>0.14</v>
+        <v>0.7</v>
       </c>
       <c r="H153" t="n">
-        <v>64.16</v>
-      </c>
-      <c r="I153" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.16</v>
+      </c>
+      <c r="I153" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.636</v>
       </c>
       <c r="K153" s="10" t="n">
-        <v>0.494</v>
+        <v>0.634</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="15" t="inlineStr"/>
@@ -7404,39 +7404,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D154" s="10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E154" s="18" t="n">
-        <v>0.0032</v>
+        <v>7.98</v>
+      </c>
+      <c r="E154" s="17" t="n">
+        <v>-0.0025</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>644600</v>
+        <v>689000</v>
       </c>
       <c r="G154" s="13" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H154" t="n">
-        <v>34.45</v>
-      </c>
-      <c r="I154" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.88</v>
+      </c>
+      <c r="I154" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="10" t="n">
-        <v>3.273</v>
+        <v>7.87</v>
       </c>
       <c r="K154" s="10" t="n">
-        <v>3.506</v>
+        <v>7.867</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="15" t="inlineStr"/>
@@ -7449,28 +7449,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D155" s="10" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="E155" s="18" t="n">
-        <v>0.0171</v>
+        <v>0.9</v>
+      </c>
+      <c r="E155" s="17" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F155" s="12" t="n">
-        <v>630400</v>
+        <v>682100</v>
       </c>
       <c r="G155" s="13" t="n">
-        <v>0.39</v>
+        <v>0.83</v>
       </c>
       <c r="H155" t="n">
-        <v>52.28</v>
+        <v>34.68</v>
       </c>
       <c r="I155" s="16" t="inlineStr">
         <is>
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="J155" s="10" t="n">
-        <v>3.544</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K155" s="10" t="n">
-        <v>3.571</v>
+        <v>0.966</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="15" t="inlineStr"/>
@@ -7494,39 +7494,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D156" s="10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E156" s="11" t="n">
-        <v>0</v>
+        <v>0.605</v>
+      </c>
+      <c r="E156" s="17" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>629500</v>
+        <v>677600</v>
       </c>
       <c r="G156" s="13" t="n">
-        <v>0.29</v>
+        <v>0.15</v>
       </c>
       <c r="H156" t="n">
-        <v>68.53</v>
-      </c>
-      <c r="I156" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.16</v>
+      </c>
+      <c r="I156" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J156" s="10" t="n">
-        <v>1.383</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K156" s="10" t="n">
-        <v>1.354</v>
+        <v>0.494</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -7539,28 +7539,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D157" s="10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E157" s="17" t="n">
-        <v>-0.0189</v>
+        <v>3.15</v>
+      </c>
+      <c r="E157" s="18" t="n">
+        <v>0.0032</v>
       </c>
       <c r="F157" s="12" t="n">
-        <v>618400</v>
+        <v>646300</v>
       </c>
       <c r="G157" s="13" t="n">
-        <v>0.62</v>
+        <v>0.17</v>
       </c>
       <c r="H157" t="n">
-        <v>38.73</v>
+        <v>34.45</v>
       </c>
       <c r="I157" s="16" t="inlineStr">
         <is>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="J157" s="10" t="n">
-        <v>1.628</v>
+        <v>3.273</v>
       </c>
       <c r="K157" s="10" t="n">
-        <v>1.693</v>
+        <v>3.506</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="15" t="inlineStr"/>
@@ -7584,28 +7584,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D158" s="10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="E158" s="11" t="n">
-        <v>0</v>
+        <v>1.57</v>
+      </c>
+      <c r="E158" s="17" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>617200</v>
+        <v>637800</v>
       </c>
       <c r="G158" s="13" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="H158" t="n">
-        <v>63.32</v>
+        <v>32.35</v>
       </c>
       <c r="I158" s="14" t="inlineStr">
         <is>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="J158" s="10" t="n">
-        <v>1.816</v>
+        <v>1.683</v>
       </c>
       <c r="K158" s="10" t="n">
-        <v>1.696</v>
+        <v>1.756</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="15" t="inlineStr"/>
@@ -7629,39 +7629,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D159" s="10" t="n">
-        <v>0.555</v>
+        <v>3.58</v>
       </c>
       <c r="E159" s="18" t="n">
-        <v>0.0091</v>
+        <v>0.0199</v>
       </c>
       <c r="F159" s="12" t="n">
-        <v>600600</v>
+        <v>632200</v>
       </c>
       <c r="G159" s="13" t="n">
-        <v>0.21</v>
+        <v>0.39</v>
       </c>
       <c r="H159" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="I159" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.08</v>
+      </c>
+      <c r="I159" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J159" s="10" t="n">
-        <v>0.553</v>
+        <v>3.545</v>
       </c>
       <c r="K159" s="10" t="n">
-        <v>0.587</v>
+        <v>3.572</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="15" t="inlineStr"/>
@@ -7674,28 +7674,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PJBUMI</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D160" s="10" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="E160" s="17" t="n">
-        <v>-0.0119</v>
+        <v>1.43</v>
+      </c>
+      <c r="E160" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>599700</v>
+        <v>629500</v>
       </c>
       <c r="G160" s="13" t="n">
-        <v>1.02</v>
+        <v>0.29</v>
       </c>
       <c r="H160" t="n">
-        <v>48.33</v>
+        <v>68.53</v>
       </c>
       <c r="I160" s="14" t="inlineStr">
         <is>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="J160" s="10" t="n">
-        <v>4.175</v>
+        <v>1.383</v>
       </c>
       <c r="K160" s="10" t="n">
-        <v>4.059</v>
+        <v>1.354</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="15" t="inlineStr"/>
@@ -7719,28 +7719,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D161" s="10" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E161" s="11" t="n">
-        <v>0</v>
+        <v>1.9</v>
+      </c>
+      <c r="E161" s="18" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F161" s="12" t="n">
-        <v>588800</v>
+        <v>619200</v>
       </c>
       <c r="G161" s="13" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="H161" t="n">
-        <v>57.26</v>
+        <v>65.23</v>
       </c>
       <c r="I161" s="14" t="inlineStr">
         <is>
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="J161" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.818</v>
       </c>
       <c r="K161" s="10" t="n">
-        <v>0.533</v>
+        <v>1.696</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="15" t="inlineStr"/>
@@ -7764,39 +7764,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D162" s="10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E162" s="18" t="n">
-        <v>0.0132</v>
+        <v>1.56</v>
+      </c>
+      <c r="E162" s="17" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>585600</v>
+        <v>618400</v>
       </c>
       <c r="G162" s="13" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="H162" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="I162" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.73</v>
+      </c>
+      <c r="I162" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J162" s="10" t="n">
-        <v>2.153</v>
+        <v>1.628</v>
       </c>
       <c r="K162" s="10" t="n">
-        <v>2.218</v>
+        <v>1.693</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -7809,39 +7809,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D163" s="10" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E163" s="11" t="n">
-        <v>0</v>
+        <v>0.555</v>
+      </c>
+      <c r="E163" s="18" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F163" s="12" t="n">
-        <v>584100</v>
+        <v>600600</v>
       </c>
       <c r="G163" s="13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="H163" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="I163" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.31</v>
+      </c>
+      <c r="I163" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J163" s="10" t="n">
-        <v>0.825</v>
+        <v>0.553</v>
       </c>
       <c r="K163" s="10" t="n">
-        <v>0.853</v>
+        <v>0.587</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="15" t="inlineStr"/>
@@ -7854,28 +7854,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>PJBUMI</t>
         </is>
       </c>
       <c r="D164" s="10" t="n">
-        <v>7.53</v>
+        <v>4.14</v>
       </c>
       <c r="E164" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>576900</v>
+        <v>599700</v>
       </c>
       <c r="G164" s="13" t="n">
-        <v>0.12</v>
+        <v>1.02</v>
       </c>
       <c r="H164" t="n">
-        <v>56.19</v>
+        <v>48.33</v>
       </c>
       <c r="I164" s="14" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         </is>
       </c>
       <c r="J164" s="10" t="n">
-        <v>7.35</v>
+        <v>4.175</v>
       </c>
       <c r="K164" s="10" t="n">
-        <v>6.998</v>
+        <v>4.059</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="15" t="inlineStr"/>
@@ -7899,28 +7899,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D165" s="10" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E165" s="18" t="n">
-        <v>0.1132</v>
+        <v>0.585</v>
+      </c>
+      <c r="E165" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F165" s="12" t="n">
-        <v>558100</v>
+        <v>588800</v>
       </c>
       <c r="G165" s="13" t="n">
-        <v>1.05</v>
+        <v>0.12</v>
       </c>
       <c r="H165" t="n">
-        <v>55.11</v>
+        <v>57.26</v>
       </c>
       <c r="I165" s="14" t="inlineStr">
         <is>
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="J165" s="10" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K165" s="10" t="n">
-        <v>0.622</v>
+        <v>0.533</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="15" t="inlineStr"/>
@@ -7944,39 +7944,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D166" s="10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E166" s="11" t="n">
-        <v>0</v>
+        <v>2.3</v>
+      </c>
+      <c r="E166" s="18" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>540700</v>
+        <v>587700</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="H166" t="n">
-        <v>51.45</v>
-      </c>
-      <c r="I166" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.4</v>
+      </c>
+      <c r="I166" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J166" s="10" t="n">
-        <v>0.634</v>
+        <v>2.153</v>
       </c>
       <c r="K166" s="10" t="n">
-        <v>0.625</v>
+        <v>2.218</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -7989,28 +7989,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>THETA</t>
         </is>
       </c>
       <c r="D167" s="10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E167" s="11" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E167" s="18" t="n">
+        <v>0.1132</v>
       </c>
       <c r="F167" s="12" t="n">
-        <v>532400</v>
+        <v>587600</v>
       </c>
       <c r="G167" s="13" t="n">
-        <v>0.21</v>
+        <v>1.11</v>
       </c>
       <c r="H167" t="n">
-        <v>47.14</v>
+        <v>55.11</v>
       </c>
       <c r="I167" s="14" t="inlineStr">
         <is>
@@ -8018,10 +8018,10 @@
         </is>
       </c>
       <c r="J167" s="10" t="n">
-        <v>1.362</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K167" s="10" t="n">
-        <v>1.428</v>
+        <v>0.622</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="15" t="inlineStr"/>
@@ -8034,28 +8034,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D168" s="10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E168" s="18" t="n">
-        <v>0.005</v>
+        <v>0.805</v>
+      </c>
+      <c r="E168" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>514500</v>
+        <v>584100</v>
       </c>
       <c r="G168" s="13" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="H168" t="n">
-        <v>47.15</v>
+        <v>31.64</v>
       </c>
       <c r="I168" s="16" t="inlineStr">
         <is>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="J168" s="10" t="n">
-        <v>2.036</v>
+        <v>0.825</v>
       </c>
       <c r="K168" s="10" t="n">
-        <v>2.059</v>
+        <v>0.853</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="15" t="inlineStr"/>
@@ -8079,28 +8079,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D169" s="10" t="n">
-        <v>1.57</v>
+        <v>7.53</v>
       </c>
       <c r="E169" s="17" t="n">
-        <v>-0.0063</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F169" s="12" t="n">
-        <v>513900</v>
+        <v>577000</v>
       </c>
       <c r="G169" s="13" t="n">
-        <v>0.67</v>
+        <v>0.12</v>
       </c>
       <c r="H169" t="n">
-        <v>32.35</v>
+        <v>56.19</v>
       </c>
       <c r="I169" s="14" t="inlineStr">
         <is>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="J169" s="10" t="n">
-        <v>1.683</v>
+        <v>7.35</v>
       </c>
       <c r="K169" s="10" t="n">
-        <v>1.756</v>
+        <v>6.998</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="15" t="inlineStr"/>
@@ -8124,39 +8124,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>SENTRAL</t>
         </is>
       </c>
       <c r="D170" s="10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="E170" s="17" t="n">
-        <v>-0.0133</v>
+        <v>0.61</v>
+      </c>
+      <c r="E170" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>509400</v>
+        <v>547300</v>
       </c>
       <c r="G170" s="13" t="n">
-        <v>0.18</v>
+        <v>1.26</v>
       </c>
       <c r="H170" t="n">
-        <v>62.68</v>
-      </c>
-      <c r="I170" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.13</v>
+      </c>
+      <c r="I170" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J170" s="10" t="n">
-        <v>2.785</v>
+        <v>0.627</v>
       </c>
       <c r="K170" s="10" t="n">
-        <v>2.429</v>
+        <v>0.65</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="15" t="inlineStr"/>
@@ -8169,28 +8169,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D171" s="10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E171" s="11" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E171" s="17" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F171" s="12" t="n">
-        <v>508800</v>
+        <v>546000</v>
       </c>
       <c r="G171" s="13" t="n">
-        <v>0.86</v>
+        <v>0.2</v>
       </c>
       <c r="H171" t="n">
-        <v>49.92</v>
+        <v>49.35</v>
       </c>
       <c r="I171" s="16" t="inlineStr">
         <is>
@@ -8198,16 +8198,241 @@
         </is>
       </c>
       <c r="J171" s="10" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="K171" s="10" t="n">
-        <v>0.665</v>
+        <v>0.625</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="15" t="inlineStr"/>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D172" s="10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E172" s="17" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="F172" s="12" t="n">
+        <v>532500</v>
+      </c>
+      <c r="G172" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H172" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="I172" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J172" s="10" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="K172" s="10" t="n">
+        <v>1.427</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="15" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D173" s="10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E173" s="18" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F173" s="12" t="n">
+        <v>528200</v>
+      </c>
+      <c r="G173" s="13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H173" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="I173" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="10" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="K173" s="10" t="n">
+        <v>2.059</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="15" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D174" s="10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E174" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="12" t="n">
+        <v>517500</v>
+      </c>
+      <c r="G174" s="13" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H174" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="I174" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="K174" s="10" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="15" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D175" s="10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E175" s="17" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="F175" s="12" t="n">
+        <v>511300</v>
+      </c>
+      <c r="G175" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H175" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="I175" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="10" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="K175" s="10" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="15" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E176" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="12" t="n">
+        <v>508800</v>
+      </c>
+      <c r="G176" s="13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H176" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="I176" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="10" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="K176" s="10" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M171"/>
+  <autoFilter ref="A1:M176"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
+++ b/docs/downloads/2026-10-29/bursa-report-2026-10-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-29'!$A$1:$M$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,8 +97,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M176"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.665</v>
+        <v>0.655</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.08130000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5792900</v>
+        <v>6359500</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.61</v>
+        <v>62.6</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.59</v>
+        <v>0.589</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.498</v>
@@ -599,7 +599,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 63.61未超买，现价高于50日均线约33.5%，技术面信号可靠性较高。</t>
+          <t>SAR转多信号，现价0.655高于50日均线0.498约31%，RSI 62.6偏强但未超买，信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.1386</v>
+        <v>0.1485</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>11288800</v>
+        <v>12746900</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>66.91</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.87</v>
+        <v>0.871</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.668</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号出现，但RSI 66.6已接近超买区，现价1.15远高于50日均线0.668，偏离幅度较大，信号可靠性需谨慎看待。</t>
+          <t>SAR转多信号，RSI 66.91接近超买区，现价1.16远高于50日均线0.668，偏离较大，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -679,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1204200</v>
+        <v>1227200</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>70.66</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号出现，但RSI达70.66已近超买区，现价高于50日均线约19.6%，短期涨幅偏大，信号可靠性需谨慎看待。</t>
+          <t>SAR转多信号出现，但RSI达70.66已近超买区，现价高于50日均线约19.6%，短线偏热。</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>122504600</v>
+        <v>122861700</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>0.33</v>
@@ -762,39 +762,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>0</v>
+        <v>0.49</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>37518900</v>
+        <v>42070100</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>2.93</v>
+        <v>1.1</v>
       </c>
       <c r="H6" t="n">
-        <v>56.53</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.67</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.051</v>
+        <v>0.44</v>
       </c>
       <c r="K6" s="10" t="n">
-        <v>0.047</v>
+        <v>0.343</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="15" t="inlineStr"/>
@@ -807,39 +807,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>-0.1111</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>35454700</v>
+        <v>38580600</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>0.93</v>
+        <v>3.28</v>
       </c>
       <c r="H7" t="n">
-        <v>70.67</v>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.36</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.44</v>
+        <v>0.056</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>0.343</v>
+        <v>0.068</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="15" t="inlineStr"/>
@@ -852,39 +852,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>-0.1111</v>
+        <v>0.055</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>35119400</v>
+        <v>38318600</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="H8" t="n">
-        <v>27.36</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
+        <v>56.53</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.056</v>
+        <v>0.051</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>0.068</v>
+        <v>0.047</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="15" t="inlineStr"/>
@@ -897,28 +897,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>0.0513</v>
+        <v>0.97</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>29492200</v>
+        <v>34262100</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>2.25</v>
+        <v>0.44</v>
       </c>
       <c r="H9" t="n">
-        <v>38.58</v>
+        <v>70.27</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.452</v>
+        <v>0.888</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.782</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="15" t="inlineStr"/>
@@ -942,39 +942,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>-0.0563</v>
+        <v>0.41</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>0.0513</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>28624100</v>
+        <v>31112700</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1.24</v>
+        <v>2.37</v>
       </c>
       <c r="H10" t="n">
-        <v>54.92</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.58</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.671</v>
+        <v>0.452</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>0.58</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="15" t="inlineStr"/>
@@ -987,39 +987,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0170</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KANGER</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>-0.3333</v>
+        <v>0.665</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.0634</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>28074300</v>
+        <v>30480500</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>36.85</v>
+        <v>1.32</v>
       </c>
       <c r="H11" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
+        <v>53.55</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.019</v>
+        <v>0.671</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>0.023</v>
+        <v>0.58</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="15" t="inlineStr"/>
@@ -1032,39 +1032,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0170</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>KANGER</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>-0.0141</v>
+        <v>0.01</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>-0.3333</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>27570400</v>
+        <v>28215000</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.35</v>
+        <v>37.04</v>
       </c>
       <c r="H12" t="n">
-        <v>64.94</v>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.25</v>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.325</v>
+        <v>0.019</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>0.273</v>
+        <v>0.023</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="15" t="inlineStr"/>
@@ -1077,28 +1077,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>-0.0141</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>25474100</v>
+        <v>27876800</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="H13" t="n">
-        <v>70.27</v>
+        <v>64.94</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.888</v>
+        <v>0.325</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>0.782</v>
+        <v>0.273</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="15" t="inlineStr"/>
@@ -1122,39 +1122,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>0.0435</v>
+        <v>6.9</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>-0.0295</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>16327400</v>
+        <v>19583100</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>3.24</v>
+        <v>1.2</v>
       </c>
       <c r="H14" t="n">
-        <v>73.66</v>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.22</v>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.103</v>
+        <v>7.275</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>0.08699999999999999</v>
+        <v>7.583</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="15" t="inlineStr"/>
@@ -1167,39 +1167,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>-0.0295</v>
+        <v>0.155</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>16229800</v>
+        <v>18137000</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.99</v>
+        <v>0.48</v>
       </c>
       <c r="H15" t="n">
-        <v>25.22</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.74</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="10" t="n">
-        <v>7.275</v>
+        <v>0.156</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>7.583</v>
+        <v>0.156</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="15" t="inlineStr"/>
@@ -1212,39 +1212,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>0</v>
+        <v>0.12</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>13387700</v>
+        <v>16827400</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.68</v>
+        <v>3.34</v>
       </c>
       <c r="H16" t="n">
-        <v>39.44</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.66</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.306</v>
+        <v>0.103</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>0.304</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="15" t="inlineStr"/>
@@ -1257,39 +1257,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>-0.0208</v>
+        <v>0.3</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>13215900</v>
+        <v>16012700</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>0.62</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>60.36</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
+        <v>39.44</v>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.445</v>
+        <v>0.306</v>
       </c>
       <c r="K17" s="10" t="n">
-        <v>0.398</v>
+        <v>0.304</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="15" t="inlineStr"/>
@@ -1302,28 +1302,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0126</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>MICROLN</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>-0.0061</v>
+        <v>0.06</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>12846500</v>
+        <v>15763100</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.8100000000000001</v>
+        <v>12.32</v>
       </c>
       <c r="H18" t="n">
-        <v>53.1</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.047</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.047</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="15" t="inlineStr"/>
@@ -1347,39 +1347,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>0.0133</v>
+        <v>0.47</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>12375600</v>
+        <v>15091300</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>1.19</v>
+        <v>0.71</v>
       </c>
       <c r="H19" t="n">
-        <v>36.71</v>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.36</v>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.387</v>
+        <v>0.445</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>0.401</v>
+        <v>0.398</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="15" t="inlineStr"/>
@@ -1392,39 +1392,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>0</v>
+        <v>0.82</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>11819100</v>
+        <v>14821200</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>1.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>44.95</v>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.1</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.278</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>0.282</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="15" t="inlineStr"/>
@@ -1452,15 +1452,15 @@
         <v>0.0058</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>11790100</v>
+        <v>14177900</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="H21" t="n">
         <v>47.34</v>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1482,40 +1482,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>11060000</v>
+        <v>13700600</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.29</v>
+        <v>0.72</v>
       </c>
       <c r="H22" t="n">
-        <v>47.74</v>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="K22" s="10" t="n">
-        <v>0.156</v>
-      </c>
+        <v>47.99</v>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="10" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="15" t="inlineStr"/>
     </row>
@@ -1527,36 +1523,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.38</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>10328500</v>
+        <v>12684400</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.54</v>
+        <v>1.22</v>
       </c>
       <c r="H23" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="n"/>
-      <c r="K23" s="10" t="n"/>
+        <v>36.71</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>0.401</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="15" t="inlineStr"/>
     </row>
@@ -1568,39 +1568,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>0</v>
+        <v>0.275</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>9938200</v>
+        <v>11944800</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.78</v>
+        <v>1.88</v>
       </c>
       <c r="H24" t="n">
-        <v>37.77</v>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.51</v>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.153</v>
+        <v>0.279</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>0.172</v>
+        <v>0.282</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="15" t="inlineStr"/>
@@ -1613,28 +1613,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.775</v>
+        <v>0.15</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>9132800</v>
+        <v>10934900</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.59</v>
+        <v>0.86</v>
       </c>
       <c r="H25" t="n">
-        <v>50.93</v>
+        <v>37.77</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.774</v>
+        <v>0.153</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>0.775</v>
+        <v>0.172</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="15" t="inlineStr"/>
@@ -1658,28 +1658,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.215</v>
+        <v>0.775</v>
       </c>
       <c r="E26" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>9006900</v>
+        <v>10688300</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>1.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>85.94</v>
+        <v>50.93</v>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.145</v>
+        <v>0.774</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>0.122</v>
+        <v>0.775</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="15" t="inlineStr"/>
@@ -1703,28 +1703,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>0.0135</v>
+        <v>0.215</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>8380500</v>
+        <v>10161400</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.29</v>
+        <v>1.27</v>
       </c>
       <c r="H27" t="n">
-        <v>66.83</v>
+        <v>85.94</v>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="J27" s="10" t="n">
-        <v>2.035</v>
+        <v>0.145</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>1.838</v>
+        <v>0.122</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="15" t="inlineStr"/>
@@ -1748,39 +1748,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>0</v>
+        <v>2.24</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>7649400</v>
+        <v>9663900</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.66</v>
+        <v>0.34</v>
       </c>
       <c r="H28" t="n">
-        <v>46</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.44</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.283</v>
+        <v>2.034</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>0.279</v>
+        <v>1.837</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="15" t="inlineStr"/>
@@ -1793,39 +1793,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>2.16</v>
+        <v>4.72</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0021</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>7134300</v>
+        <v>8410800</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.57</v>
+        <v>0.39</v>
       </c>
       <c r="H29" t="n">
-        <v>53.36</v>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.88</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="10" t="n">
-        <v>2.109</v>
+        <v>4.728</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>2.225</v>
+        <v>4.794</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="15" t="inlineStr"/>
@@ -1838,39 +1838,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>-0.0263</v>
+        <v>0.275</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>6665200</v>
+        <v>7649400</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.37</v>
+        <v>0.66</v>
       </c>
       <c r="H30" t="n">
-        <v>49.13</v>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46</v>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.185</v>
+        <v>0.283</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>0.187</v>
+        <v>0.279</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="15" t="inlineStr"/>
@@ -1883,28 +1883,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>0.0133</v>
+        <v>2.15</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>6618600</v>
+        <v>7606400</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.96</v>
+        <v>0.61</v>
       </c>
       <c r="H31" t="n">
-        <v>58.8</v>
+        <v>52.51</v>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.374</v>
+        <v>2.108</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>0.37</v>
+        <v>2.225</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="15" t="inlineStr"/>
@@ -1928,33 +1928,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.205</v>
+        <v>1.29</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>0.025</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>6218900</v>
+        <v>7545300</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
+        <v>1.88</v>
+      </c>
+      <c r="H32" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J32" s="10" t="n"/>
-      <c r="K32" s="10" t="n"/>
+      <c r="J32" s="10" t="n">
+        <v>1.409</v>
+      </c>
+      <c r="K32" s="10" t="n">
+        <v>1.447</v>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="15" t="inlineStr"/>
     </row>
@@ -1966,40 +1973,33 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="E33" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>5693100</v>
+        <v>7362300</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="H33" t="n">
-        <v>43.21</v>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
+        <v>0.29</v>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J33" s="10" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="K33" s="10" t="n">
-        <v>0.024</v>
-      </c>
+      <c r="J33" s="10" t="n"/>
+      <c r="K33" s="10" t="n"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="15" t="inlineStr"/>
     </row>
@@ -2020,19 +2020,19 @@
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>0.001</v>
+        <v>9.99</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>5599100</v>
+        <v>7148000</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="H34" t="n">
-        <v>48.87</v>
+        <v>48.09</v>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="J34" s="10" t="n">
-        <v>9.994999999999999</v>
+        <v>9.994</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>10.094</v>
@@ -2056,28 +2056,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>0.025</v>
+        <v>0.645</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>5578500</v>
+        <v>6942100</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.47</v>
+        <v>0.66</v>
       </c>
       <c r="H35" t="n">
-        <v>53.97</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.403</v>
+        <v>0.629</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0.385</v>
+        <v>0.62</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="15" t="inlineStr"/>
@@ -2101,39 +2101,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>4.74</v>
+        <v>0.405</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>0.0064</v>
+        <v>0.0125</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>5351000</v>
+        <v>6881900</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.25</v>
+        <v>0.58</v>
       </c>
       <c r="H36" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.36</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="10" t="n">
-        <v>4.73</v>
+        <v>0.402</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>4.794</v>
+        <v>0.385</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="15" t="inlineStr"/>
@@ -2146,28 +2146,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>5349900</v>
+        <v>6875200</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>1.23</v>
+        <v>0.38</v>
       </c>
       <c r="H37" t="n">
-        <v>79.91</v>
+        <v>49.13</v>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.471</v>
+        <v>0.185</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.441</v>
+        <v>0.187</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="15" t="inlineStr"/>
@@ -2191,28 +2191,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.645</v>
+        <v>0.375</v>
       </c>
       <c r="E38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>5266100</v>
+        <v>6667200</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.5</v>
+        <v>0.96</v>
       </c>
       <c r="H38" t="n">
-        <v>66.40000000000001</v>
+        <v>53.68</v>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.629</v>
+        <v>0.373</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0.62</v>
+        <v>0.37</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="15" t="inlineStr"/>
@@ -2236,39 +2236,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>0.0156</v>
+        <v>0.435</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>-0.0225</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>5243000</v>
+        <v>6165500</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>1.31</v>
+        <v>0.42</v>
       </c>
       <c r="H39" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.93</v>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.41</v>
+        <v>0.469</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>1.447</v>
+        <v>0.585</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="15" t="inlineStr"/>
@@ -2281,39 +2281,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>-0.0337</v>
+        <v>2.61</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>4803500</v>
+        <v>5860200</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="H40" t="n">
-        <v>31.06</v>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.27</v>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.468</v>
+        <v>2.596</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0.585</v>
+        <v>2.571</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="15" t="inlineStr"/>
@@ -2326,39 +2326,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>0.0476</v>
+        <v>2.43</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>4634400</v>
+        <v>5770800</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.27</v>
+        <v>0.59</v>
       </c>
       <c r="H41" t="n">
-        <v>36.82</v>
-      </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.42</v>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.125</v>
+        <v>2.43</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0.144</v>
+        <v>2.429</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="15" t="inlineStr"/>
@@ -2371,39 +2371,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>-0.0112</v>
+        <v>0.02</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>4203500</v>
+        <v>5693100</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.43</v>
+        <v>0.72</v>
       </c>
       <c r="H42" t="n">
-        <v>42</v>
-      </c>
-      <c r="I42" s="16" t="inlineStr">
+        <v>43.21</v>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J42" s="10" t="n">
-        <v>2.713</v>
+        <v>0.023</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>2.749</v>
+        <v>0.024</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="15" t="inlineStr"/>
@@ -2416,39 +2416,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>4156500</v>
+        <v>5473400</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="H43" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.70999999999999</v>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.295</v>
+        <v>0.472</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0.295</v>
+        <v>0.441</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="15" t="inlineStr"/>
@@ -2461,39 +2461,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>2.61</v>
+        <v>0.105</v>
       </c>
       <c r="E44" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>4102800</v>
+        <v>4690500</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="H44" t="n">
-        <v>51.27</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
+        <v>32.61</v>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J44" s="10" t="n">
-        <v>2.596</v>
+        <v>0.124</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>2.571</v>
+        <v>0.144</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="15" t="inlineStr"/>
@@ -2506,39 +2506,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>-0.0086</v>
+        <v>1.5</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>4082500</v>
+        <v>4433000</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="H45" t="n">
-        <v>35.03</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.79</v>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="10" t="n">
-        <v>1.191</v>
+        <v>1.555</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>1.272</v>
+        <v>1.822</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="15" t="inlineStr"/>
@@ -2551,39 +2551,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FPI</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E46" s="18" t="n">
-        <v>0.0348</v>
+        <v>1.15</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>3923900</v>
+        <v>4412100</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>9.32</v>
+        <v>0.45</v>
       </c>
       <c r="H46" t="n">
-        <v>69.06999999999999</v>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.03</v>
+      </c>
+      <c r="I46" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="10" t="n">
-        <v>1.099</v>
+        <v>1.191</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>1.1</v>
+        <v>1.272</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="15" t="inlineStr"/>
@@ -2596,39 +2596,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="E47" s="11" t="n">
-        <v>0</v>
+        <v>2.64</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>3904400</v>
+        <v>4339500</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="H47" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42</v>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="10" t="n">
-        <v>2.43</v>
+        <v>2.713</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>2.429</v>
+        <v>2.749</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="15" t="inlineStr"/>
@@ -2641,28 +2641,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>-0.0208</v>
+        <v>0.155</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>3849800</v>
+        <v>4337600</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>1.46</v>
+        <v>0.08</v>
       </c>
       <c r="H48" t="n">
-        <v>55.99</v>
+        <v>48.93</v>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="J48" s="10" t="n">
-        <v>0.457</v>
+        <v>0.159</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>0.449</v>
+        <v>0.15</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="15" t="inlineStr"/>
@@ -2686,28 +2686,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E49" s="18" t="n">
-        <v>0.0112</v>
+        <v>1.23</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>3825300</v>
+        <v>4333600</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="H49" t="n">
-        <v>58.59</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="J49" s="10" t="n">
-        <v>2.613</v>
+        <v>1.129</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>2.6</v>
+        <v>1.071</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="15" t="inlineStr"/>
@@ -2731,39 +2731,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1.51</v>
+        <v>0.295</v>
       </c>
       <c r="E50" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>3815600</v>
+        <v>4156500</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.26</v>
+        <v>1.17</v>
       </c>
       <c r="H50" t="n">
-        <v>39.52</v>
-      </c>
-      <c r="I50" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I50" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="10" t="n">
-        <v>1.556</v>
+        <v>0.295</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>1.822</v>
+        <v>0.295</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="15" t="inlineStr"/>
@@ -2776,39 +2776,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>-0.0313</v>
+        <v>4.47</v>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>3740000</v>
+        <v>4107200</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="H51" t="n">
-        <v>48.93</v>
-      </c>
-      <c r="I51" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.04</v>
+      </c>
+      <c r="I51" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="10" t="n">
-        <v>0.159</v>
+        <v>4.532</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>0.15</v>
+        <v>4.643</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="15" t="inlineStr"/>
@@ -2821,28 +2821,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E52" s="11" t="n">
-        <v>0</v>
+        <v>2.7</v>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>3711600</v>
+        <v>4096400</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.46</v>
+        <v>0.77</v>
       </c>
       <c r="H52" t="n">
-        <v>37.11</v>
+        <v>58.59</v>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="J52" s="10" t="n">
-        <v>1.275</v>
+        <v>2.613</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>1.469</v>
+        <v>2.6</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="15" t="inlineStr"/>
@@ -2866,28 +2866,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>-0.002</v>
+        <v>0.67</v>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>3664800</v>
+        <v>4035000</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>0.18</v>
+        <v>0.91</v>
       </c>
       <c r="H53" t="n">
-        <v>57.51</v>
+        <v>63.44</v>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="J53" s="10" t="n">
-        <v>4.9</v>
+        <v>0.61</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>4.795</v>
+        <v>0.587</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="15" t="inlineStr"/>
@@ -2911,28 +2911,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>-0.006</v>
+        <v>1.45</v>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>3648300</v>
+        <v>4033400</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0.74</v>
+        <v>1.3</v>
       </c>
       <c r="H54" t="n">
-        <v>67.58</v>
+        <v>62.11</v>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="J54" s="10" t="n">
-        <v>0.8129999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>0.783</v>
+        <v>1.259</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="15" t="inlineStr"/>
@@ -2956,28 +2956,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E55" s="18" t="n">
-        <v>0.0075</v>
+        <v>0.835</v>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>3636600</v>
+        <v>4021200</v>
       </c>
       <c r="G55" s="13" t="n">
         <v>0.82</v>
       </c>
       <c r="H55" t="n">
-        <v>63.44</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.61</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>0.587</v>
+        <v>0.783</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="15" t="inlineStr"/>
@@ -3001,28 +3001,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E56" s="11" t="n">
-        <v>0</v>
+        <v>4.96</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>3482000</v>
+        <v>4004500</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H56" t="n">
-        <v>67.55</v>
+        <v>55.39</v>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="J56" s="10" t="n">
-        <v>1.13</v>
+        <v>4.897</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>1.071</v>
+        <v>4.794</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="15" t="inlineStr"/>
@@ -3046,28 +3046,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E57" s="18" t="n">
-        <v>0.0157</v>
+        <v>0.64</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>3335000</v>
+        <v>3978100</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>1.07</v>
+        <v>1.83</v>
       </c>
       <c r="H57" t="n">
-        <v>56.73</v>
+        <v>51.42</v>
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="J57" s="10" t="n">
-        <v>1.269</v>
+        <v>0.641</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>1.27</v>
+        <v>0.631</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="15" t="inlineStr"/>
@@ -3091,39 +3091,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>-0.0083</v>
+        <v>0.945</v>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>3294300</v>
+        <v>3974900</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="H58" t="n">
-        <v>55.64</v>
-      </c>
-      <c r="I58" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.12</v>
+      </c>
+      <c r="I58" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="10" t="n">
-        <v>0.575</v>
+        <v>0.988</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>0.552</v>
+        <v>0.993</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="15" t="inlineStr"/>
@@ -3136,28 +3136,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E59" s="18" t="n">
-        <v>0.0227</v>
+        <v>0.47</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>3258900</v>
+        <v>3962000</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>0.46</v>
+        <v>1.5</v>
       </c>
       <c r="H59" t="n">
-        <v>56.07</v>
+        <v>55.99</v>
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="J59" s="10" t="n">
-        <v>0.432</v>
+        <v>0.457</v>
       </c>
       <c r="K59" s="10" t="n">
-        <v>0.417</v>
+        <v>0.449</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="15" t="inlineStr"/>
@@ -3181,39 +3181,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.945</v>
+        <v>1.22</v>
       </c>
       <c r="E60" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>3234800</v>
+        <v>3944800</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0.28</v>
+        <v>0.49</v>
       </c>
       <c r="H60" t="n">
-        <v>43.12</v>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.11</v>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.988</v>
+        <v>1.275</v>
       </c>
       <c r="K60" s="10" t="n">
-        <v>0.993</v>
+        <v>1.469</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="15" t="inlineStr"/>
@@ -3226,28 +3226,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>FPI</t>
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E61" s="11" t="n">
-        <v>0</v>
+        <v>1.18</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>0.0261</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>3228800</v>
+        <v>3938800</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>0.89</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>69.45</v>
+        <v>67.86</v>
       </c>
       <c r="I61" s="14" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="J61" s="10" t="n">
-        <v>0.623</v>
+        <v>1.098</v>
       </c>
       <c r="K61" s="10" t="n">
-        <v>0.613</v>
+        <v>1.099</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="15" t="inlineStr"/>
@@ -3271,28 +3271,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>1.43</v>
+        <v>5.31</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>0.0214</v>
+        <v>0.0076</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>3168400</v>
+        <v>3901000</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>1.02</v>
+        <v>0.24</v>
       </c>
       <c r="H62" t="n">
-        <v>60.9</v>
+        <v>47.38</v>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="J62" s="10" t="n">
-        <v>1.318</v>
+        <v>5.355</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>1.259</v>
+        <v>5.53</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="15" t="inlineStr"/>
@@ -3316,28 +3316,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E63" s="17" t="n">
-        <v>-0.0526</v>
+        <v>6.89</v>
+      </c>
+      <c r="E63" s="18" t="n">
+        <v>0.0044</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>3157100</v>
+        <v>3767500</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>0.84</v>
+        <v>0.36</v>
       </c>
       <c r="H63" t="n">
-        <v>40.28</v>
+        <v>42.52</v>
       </c>
       <c r="I63" s="14" t="inlineStr">
         <is>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="J63" s="10" t="n">
-        <v>0.188</v>
+        <v>6.992</v>
       </c>
       <c r="K63" s="10" t="n">
-        <v>0.204</v>
+        <v>7.435</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="15" t="inlineStr"/>
@@ -3361,28 +3361,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>-0.0222</v>
+        <v>1.29</v>
+      </c>
+      <c r="E64" s="18" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>3119400</v>
+        <v>3746100</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>0.09</v>
+        <v>1.2</v>
       </c>
       <c r="H64" t="n">
-        <v>44.81</v>
+        <v>56.73</v>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="J64" s="10" t="n">
-        <v>0.452</v>
+        <v>1.269</v>
       </c>
       <c r="K64" s="10" t="n">
-        <v>0.471</v>
+        <v>1.27</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="15" t="inlineStr"/>
@@ -3406,28 +3406,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>5.31</v>
+        <v>0.45</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>0.0076</v>
+        <v>0.0227</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>3071200</v>
+        <v>3681100</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>0.19</v>
+        <v>0.52</v>
       </c>
       <c r="H65" t="n">
-        <v>47.38</v>
+        <v>56.07</v>
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="J65" s="10" t="n">
-        <v>5.355</v>
+        <v>0.432</v>
       </c>
       <c r="K65" s="10" t="n">
-        <v>5.53</v>
+        <v>0.417</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="15" t="inlineStr"/>
@@ -3451,39 +3451,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0379</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>PMW</t>
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>-0.0444</v>
+        <v>0.265</v>
+      </c>
+      <c r="E66" s="18" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>2981900</v>
+        <v>3541400</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>2.76</v>
+        <v>6.88</v>
       </c>
       <c r="H66" t="n">
-        <v>41.91</v>
-      </c>
-      <c r="I66" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.41</v>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="10" t="n">
-        <v>0.223</v>
+        <v>0.273</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>0.229</v>
+        <v>0.268</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="15" t="inlineStr"/>
@@ -3505,30 +3505,30 @@
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>-0.0174</v>
+        <v>3.28</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>-0.0493</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>2887700</v>
+        <v>3527900</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H67" t="n">
-        <v>80.89</v>
-      </c>
-      <c r="I67" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>68.66</v>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="10" t="n">
-        <v>3.145</v>
+        <v>3.134</v>
       </c>
       <c r="K67" s="10" t="n">
-        <v>2.671</v>
+        <v>2.668</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="15" t="inlineStr"/>
@@ -3541,39 +3541,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="E68" s="18" t="n">
-        <v>0.0068</v>
+        <v>0.59</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>2802400</v>
+        <v>3494300</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="H68" t="n">
-        <v>40.04</v>
-      </c>
-      <c r="I68" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.49</v>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="10" t="n">
-        <v>4.532</v>
+        <v>0.575</v>
       </c>
       <c r="K68" s="10" t="n">
-        <v>4.643</v>
+        <v>0.552</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="15" t="inlineStr"/>
@@ -3586,39 +3586,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>-0.0064</v>
+        <v>3.02</v>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>0.0033</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>2788200</v>
+        <v>3445400</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>0.39</v>
+        <v>1.25</v>
       </c>
       <c r="H69" t="n">
-        <v>53.12</v>
-      </c>
-      <c r="I69" s="16" t="inlineStr">
+        <v>37.95</v>
+      </c>
+      <c r="I69" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J69" s="10" t="n">
-        <v>0.771</v>
+        <v>3.106</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>0.771</v>
+        <v>3.234</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="15" t="inlineStr"/>
@@ -3631,39 +3631,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E70" s="18" t="n">
-        <v>0.0071</v>
+        <v>0.215</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>2784900</v>
+        <v>3433200</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="H70" t="n">
-        <v>45.86</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
+        <v>40.78</v>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J70" s="10" t="n">
-        <v>0.726</v>
+        <v>0.221</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>0.724</v>
+        <v>0.26</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="15" t="inlineStr"/>
@@ -3676,28 +3676,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E71" s="18" t="n">
-        <v>0.0163</v>
+        <v>0.44</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>2734200</v>
+        <v>3375600</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>0.42</v>
+        <v>0.09</v>
       </c>
       <c r="H71" t="n">
-        <v>45.91</v>
+        <v>44.81</v>
       </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="J71" s="10" t="n">
-        <v>1.269</v>
+        <v>0.452</v>
       </c>
       <c r="K71" s="10" t="n">
-        <v>1.318</v>
+        <v>0.471</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="15" t="inlineStr"/>
@@ -3721,28 +3721,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>2.12</v>
+        <v>6.34</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>0.0095</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>2669900</v>
+        <v>3364000</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="H72" t="n">
-        <v>68</v>
+        <v>47.5</v>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="J72" s="10" t="n">
-        <v>2.005</v>
+        <v>6.335</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>1.972</v>
+        <v>6.587</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="15" t="inlineStr"/>
@@ -3766,39 +3766,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>-0.0227</v>
+        <v>0.63</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>-0.0308</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>2657400</v>
+        <v>3360700</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>0.27</v>
+        <v>0.99</v>
       </c>
       <c r="H73" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.32</v>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="10" t="n">
-        <v>0.221</v>
+        <v>0.672</v>
       </c>
       <c r="K73" s="10" t="n">
-        <v>0.26</v>
+        <v>0.728</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="15" t="inlineStr"/>
@@ -3811,28 +3811,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>-0.0155</v>
+        <v>5.83</v>
+      </c>
+      <c r="E74" s="18" t="n">
+        <v>0.0139</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>2589600</v>
+        <v>3357900</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="H74" t="n">
-        <v>53.45</v>
+        <v>47.92</v>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="J74" s="10" t="n">
-        <v>1.258</v>
+        <v>5.813</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>1.137</v>
+        <v>6.045</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="15" t="inlineStr"/>
@@ -3856,28 +3856,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E75" s="11" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>2474100</v>
+        <v>3268200</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>1.28</v>
+        <v>0.87</v>
       </c>
       <c r="H75" t="n">
-        <v>50.78</v>
+        <v>43.88</v>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="J75" s="10" t="n">
-        <v>0.904</v>
+        <v>0.189</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>0.898</v>
+        <v>0.204</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="15" t="inlineStr"/>
@@ -3901,39 +3901,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D76" s="10" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="E76" s="11" t="n">
-        <v>0</v>
+        <v>0.73</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>2460400</v>
+        <v>3257600</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0.76</v>
+        <v>1.83</v>
       </c>
       <c r="H76" t="n">
-        <v>51.04</v>
-      </c>
-      <c r="I76" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.49</v>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="10" t="n">
-        <v>3.009</v>
+        <v>0.746</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>2.88</v>
+        <v>0.725</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="15" t="inlineStr"/>
@@ -3946,39 +3946,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="E77" s="18" t="n">
-        <v>0.0033</v>
+        <v>0.63</v>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>2444800</v>
+        <v>3228900</v>
       </c>
       <c r="G77" s="13" t="n">
         <v>0.89</v>
       </c>
       <c r="H77" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.45</v>
+      </c>
+      <c r="I77" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="10" t="n">
-        <v>3.106</v>
+        <v>0.623</v>
       </c>
       <c r="K77" s="10" t="n">
-        <v>3.234</v>
+        <v>0.613</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="15" t="inlineStr"/>
@@ -3991,39 +3991,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E78" s="17" t="n">
-        <v>-0.0122</v>
+        <v>1.25</v>
+      </c>
+      <c r="E78" s="18" t="n">
+        <v>0.0163</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2398200</v>
+        <v>3130200</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>1.2</v>
+        <v>0.48</v>
       </c>
       <c r="H78" t="n">
-        <v>35.62</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.91</v>
+      </c>
+      <c r="I78" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="10" t="n">
-        <v>0.435</v>
+        <v>1.269</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>0.452</v>
+        <v>1.318</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="15" t="inlineStr"/>
@@ -4036,28 +4036,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PANTECH</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.12</v>
       </c>
       <c r="E79" s="18" t="n">
-        <v>0.0299</v>
+        <v>0.0095</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>2392300</v>
+        <v>3125500</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>8.51</v>
+        <v>0.49</v>
       </c>
       <c r="H79" t="n">
-        <v>68.31</v>
+        <v>68</v>
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="J79" s="10" t="n">
-        <v>0.663</v>
+        <v>2.005</v>
       </c>
       <c r="K79" s="10" t="n">
-        <v>0.662</v>
+        <v>1.972</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="15" t="inlineStr"/>
@@ -4081,39 +4081,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <v>-0.0267</v>
+        <v>0.79</v>
+      </c>
+      <c r="E80" s="18" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>2371000</v>
+        <v>3064100</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>1.95</v>
+        <v>0.43</v>
       </c>
       <c r="H80" t="n">
-        <v>60.14</v>
-      </c>
-      <c r="I80" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.28</v>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="10" t="n">
-        <v>0.345</v>
+        <v>0.772</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>0.355</v>
+        <v>0.772</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="15" t="inlineStr"/>
@@ -4126,39 +4126,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E81" s="11" t="n">
-        <v>0</v>
+        <v>0.705</v>
+      </c>
+      <c r="E81" s="18" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>2346100</v>
+        <v>3046700</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="H81" t="n">
-        <v>49.09</v>
-      </c>
-      <c r="I81" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.86</v>
+      </c>
+      <c r="I81" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="10" t="n">
-        <v>2.105</v>
+        <v>0.726</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>2.115</v>
+        <v>0.724</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="15" t="inlineStr"/>
@@ -4171,39 +4171,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E82" s="11" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>-0.0444</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>2306900</v>
+        <v>2981900</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>1.3</v>
+        <v>2.76</v>
       </c>
       <c r="H82" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.91</v>
+      </c>
+      <c r="I82" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="10" t="n">
-        <v>0.746</v>
+        <v>0.223</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>0.725</v>
+        <v>0.229</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="15" t="inlineStr"/>
@@ -4216,28 +4216,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>6.9</v>
+        <v>1.28</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>0.0058</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>2272000</v>
+        <v>2874200</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="H83" t="n">
-        <v>42.93</v>
+        <v>64.22</v>
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="J83" s="10" t="n">
-        <v>6.993</v>
+        <v>1.202</v>
       </c>
       <c r="K83" s="10" t="n">
-        <v>7.436</v>
+        <v>1.16</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="15" t="inlineStr"/>
@@ -4261,28 +4261,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D84" s="10" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>-0.0044</v>
+        <v>2.1</v>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>2259300</v>
+        <v>2846400</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="H84" t="n">
-        <v>51.37</v>
+        <v>49.09</v>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="J84" s="10" t="n">
-        <v>6.838</v>
+        <v>2.105</v>
       </c>
       <c r="K84" s="10" t="n">
-        <v>6.829</v>
+        <v>2.115</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="15" t="inlineStr"/>
@@ -4306,39 +4306,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D85" s="10" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>-0.0301</v>
+        <v>0.555</v>
+      </c>
+      <c r="E85" s="18" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>2250200</v>
+        <v>2844500</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>0.34</v>
+        <v>1.24</v>
       </c>
       <c r="H85" t="n">
-        <v>54.21</v>
-      </c>
-      <c r="I85" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.53</v>
+      </c>
+      <c r="I85" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="10" t="n">
-        <v>3.844</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="K85" s="10" t="n">
-        <v>3.378</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="15" t="inlineStr"/>
@@ -4351,39 +4351,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E86" s="11" t="n">
-        <v>0</v>
+        <v>2.93</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>-0.0266</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>2243900</v>
+        <v>2839000</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="H86" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.72</v>
+      </c>
+      <c r="I86" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="10" t="n">
-        <v>0.5570000000000001</v>
+        <v>3.001</v>
       </c>
       <c r="K86" s="10" t="n">
-        <v>0.5610000000000001</v>
+        <v>2.879</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="15" t="inlineStr"/>
@@ -4396,28 +4396,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E87" s="17" t="n">
-        <v>-0.0231</v>
+        <v>1.26</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>2238600</v>
+        <v>2811800</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>0.66</v>
+        <v>0.83</v>
       </c>
       <c r="H87" t="n">
-        <v>40.04</v>
+        <v>52.5</v>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="J87" s="10" t="n">
-        <v>0.673</v>
+        <v>1.257</v>
       </c>
       <c r="K87" s="10" t="n">
-        <v>0.729</v>
+        <v>1.137</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="15" t="inlineStr"/>
@@ -4441,39 +4441,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E88" s="18" t="n">
-        <v>0.0357</v>
+        <v>0.27</v>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>2224500</v>
+        <v>2705200</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.3</v>
+        <v>2.55</v>
       </c>
       <c r="H88" t="n">
-        <v>38.02</v>
-      </c>
-      <c r="I88" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.45</v>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="10" t="n">
-        <v>0.308</v>
+        <v>0.275</v>
       </c>
       <c r="K88" s="10" t="n">
-        <v>0.352</v>
+        <v>0.283</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="15" t="inlineStr"/>
@@ -4495,19 +4495,19 @@
         </is>
       </c>
       <c r="D89" s="10" t="n">
-        <v>4.3</v>
+        <v>4.23</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0.019</v>
+        <v>0.0024</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>2199800</v>
+        <v>2695300</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="H89" t="n">
-        <v>62.43</v>
+        <v>60.37</v>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="J89" s="10" t="n">
-        <v>4.05</v>
+        <v>4.043</v>
       </c>
       <c r="K89" s="10" t="n">
-        <v>3.709</v>
+        <v>3.707</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="15" t="inlineStr"/>
@@ -4531,39 +4531,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.4</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>2163900</v>
+        <v>2588400</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.33</v>
+        <v>1.29</v>
       </c>
       <c r="H90" t="n">
-        <v>61.25</v>
-      </c>
-      <c r="I90" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.27</v>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="10" t="n">
-        <v>1.2</v>
+        <v>0.434</v>
       </c>
       <c r="K90" s="10" t="n">
-        <v>1.16</v>
+        <v>0.452</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="15" t="inlineStr"/>
@@ -4576,28 +4576,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D91" s="10" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="E91" s="18" t="n">
-        <v>0.0095</v>
+        <v>6.85</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>-0.0044</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>2093100</v>
+        <v>2558900</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="H91" t="n">
-        <v>48.15</v>
+        <v>51.37</v>
       </c>
       <c r="I91" s="14" t="inlineStr">
         <is>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="J91" s="10" t="n">
-        <v>6.335</v>
+        <v>6.838</v>
       </c>
       <c r="K91" s="10" t="n">
-        <v>6.587</v>
+        <v>6.829</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="15" t="inlineStr"/>
@@ -4621,28 +4621,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>PANTECH</t>
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>-0.0181</v>
+        <v>0.695</v>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>0.0373</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>2065500</v>
+        <v>2502500</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>0.32</v>
+        <v>8.9</v>
       </c>
       <c r="H92" t="n">
-        <v>46.02</v>
+        <v>70.13</v>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="J92" s="10" t="n">
-        <v>1.648</v>
+        <v>0.663</v>
       </c>
       <c r="K92" s="10" t="n">
-        <v>1.731</v>
+        <v>0.662</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="15" t="inlineStr"/>
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D93" s="10" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>-0.0185</v>
+        <v>3.89</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>-0.0251</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>2038000</v>
+        <v>2499700</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>1.92</v>
+        <v>0.37</v>
       </c>
       <c r="H93" t="n">
-        <v>34.28</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.91</v>
+      </c>
+      <c r="I93" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="10" t="n">
-        <v>0.274</v>
+        <v>3.846</v>
       </c>
       <c r="K93" s="10" t="n">
-        <v>0.283</v>
+        <v>3.378</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="15" t="inlineStr"/>
@@ -4711,28 +4711,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0098</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AUMAS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D94" s="10" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E94" s="18" t="n">
-        <v>0.029</v>
+        <v>1.62</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>-0.0241</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>2028900</v>
+        <v>2490200</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>1.6</v>
+        <v>0.39</v>
       </c>
       <c r="H94" t="n">
-        <v>53.94</v>
+        <v>45.12</v>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="J94" s="10" t="n">
-        <v>0.347</v>
+        <v>1.647</v>
       </c>
       <c r="K94" s="10" t="n">
-        <v>0.357</v>
+        <v>1.731</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="15" t="inlineStr"/>
@@ -4756,39 +4756,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D95" s="10" t="n">
-        <v>0.465</v>
+        <v>0.905</v>
       </c>
       <c r="E95" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>2018200</v>
+        <v>2474100</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>0.23</v>
+        <v>1.28</v>
       </c>
       <c r="H95" t="n">
-        <v>45.37</v>
-      </c>
-      <c r="I95" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.78</v>
+      </c>
+      <c r="I95" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="10" t="n">
-        <v>0.485</v>
+        <v>0.904</v>
       </c>
       <c r="K95" s="10" t="n">
-        <v>0.473</v>
+        <v>0.898</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="15" t="inlineStr"/>
@@ -4801,39 +4801,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>-0.0053</v>
+        <v>0.51</v>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>1963100</v>
+        <v>2441900</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0.45</v>
+        <v>0.64</v>
       </c>
       <c r="H96" t="n">
-        <v>54.68</v>
-      </c>
-      <c r="I96" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.17</v>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="10" t="n">
-        <v>0.903</v>
+        <v>0.522</v>
       </c>
       <c r="K96" s="10" t="n">
-        <v>0.953</v>
+        <v>0.554</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="15" t="inlineStr"/>
@@ -4846,39 +4846,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D97" s="10" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E97" s="18" t="n">
-        <v>0.006</v>
+        <v>0.37</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>1941000</v>
+        <v>2417000</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>0.71</v>
+        <v>1.99</v>
       </c>
       <c r="H97" t="n">
-        <v>40.69</v>
-      </c>
-      <c r="I97" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.38</v>
+      </c>
+      <c r="I97" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="10" t="n">
-        <v>0.86</v>
+        <v>0.345</v>
       </c>
       <c r="K97" s="10" t="n">
-        <v>0.918</v>
+        <v>0.355</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="15" t="inlineStr"/>
@@ -4891,28 +4891,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D98" s="10" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E98" s="11" t="n">
-        <v>0</v>
+        <v>0.285</v>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>1927200</v>
+        <v>2397900</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>2.26</v>
+        <v>0.33</v>
       </c>
       <c r="H98" t="n">
-        <v>70.63</v>
+        <v>35.46</v>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="J98" s="10" t="n">
-        <v>0.335</v>
+        <v>0.308</v>
       </c>
       <c r="K98" s="10" t="n">
-        <v>0.319</v>
+        <v>0.352</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="15" t="inlineStr"/>
@@ -4936,39 +4936,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D99" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E99" s="17" t="n">
-        <v>-0.0222</v>
+        <v>7.45</v>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>1900000</v>
+        <v>2295300</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>3.98</v>
+        <v>0.21</v>
       </c>
       <c r="H99" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="I99" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.75</v>
+      </c>
+      <c r="I99" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="10" t="n">
-        <v>0.224</v>
+        <v>7.409</v>
       </c>
       <c r="K99" s="10" t="n">
-        <v>0.224</v>
+        <v>7.754</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="15" t="inlineStr"/>
@@ -4981,40 +4981,33 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="E100" s="18" t="n">
-        <v>0.0182</v>
+        <v>0.72</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1896300</v>
+        <v>2165400</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="H100" t="n">
-        <v>56.05</v>
-      </c>
-      <c r="I100" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J100" s="10" t="n">
-        <v>1.634</v>
-      </c>
-      <c r="K100" s="10" t="n">
-        <v>1.667</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="10" t="n"/>
+      <c r="K100" s="10" t="n"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="15" t="inlineStr"/>
     </row>
@@ -5026,39 +5019,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D101" s="10" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="E101" s="18" t="n">
-        <v>0.0174</v>
+        <v>0.84</v>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>1836800</v>
+        <v>2154400</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>0.23</v>
+        <v>0.79</v>
       </c>
       <c r="H101" t="n">
-        <v>49.22</v>
-      </c>
-      <c r="I101" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.69</v>
+      </c>
+      <c r="I101" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="10" t="n">
-        <v>5.815</v>
+        <v>0.86</v>
       </c>
       <c r="K101" s="10" t="n">
-        <v>6.046</v>
+        <v>0.918</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="15" t="inlineStr"/>
@@ -5071,39 +5064,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0098</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>AUMAS</t>
         </is>
       </c>
       <c r="D102" s="10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E102" s="11" t="n">
-        <v>0</v>
+        <v>0.36</v>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>1754200</v>
+        <v>2154300</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>0.19</v>
+        <v>1.7</v>
       </c>
       <c r="H102" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I102" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.2</v>
+      </c>
+      <c r="I102" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="10" t="n">
-        <v>0.335</v>
+        <v>0.348</v>
       </c>
       <c r="K102" s="10" t="n">
-        <v>0.339</v>
+        <v>0.357</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="15" t="inlineStr"/>
@@ -5116,39 +5109,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D103" s="10" t="n">
-        <v>0.51</v>
+        <v>1.68</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0182</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>1733700</v>
+        <v>2131400</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="H103" t="n">
-        <v>38.17</v>
-      </c>
-      <c r="I103" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.05</v>
+      </c>
+      <c r="I103" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="10" t="n">
-        <v>0.522</v>
+        <v>1.634</v>
       </c>
       <c r="K103" s="10" t="n">
-        <v>0.554</v>
+        <v>1.667</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="15" t="inlineStr"/>
@@ -5161,39 +5154,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D104" s="10" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>-0.0248</v>
+        <v>0.865</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1731900</v>
+        <v>2080500</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>0.19</v>
+        <v>0.71</v>
       </c>
       <c r="H104" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="I104" s="16" t="inlineStr">
+        <v>49.58</v>
+      </c>
+      <c r="I104" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J104" s="10" t="n">
-        <v>0.604</v>
+        <v>0.866</v>
       </c>
       <c r="K104" s="10" t="n">
-        <v>0.618</v>
+        <v>0.861</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="15" t="inlineStr"/>
@@ -5206,33 +5199,40 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D105" s="10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E105" s="18" t="n">
-        <v>0.0069</v>
+        <v>0.595</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>1724600</v>
+        <v>2045800</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I105" s="16" t="inlineStr">
+        <v>0.22</v>
+      </c>
+      <c r="H105" t="n">
+        <v>47.18</v>
+      </c>
+      <c r="I105" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J105" s="10" t="n"/>
-      <c r="K105" s="10" t="n"/>
+      <c r="J105" s="10" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="K105" s="10" t="n">
+        <v>0.618</v>
+      </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="15" t="inlineStr"/>
     </row>
@@ -5244,39 +5244,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>-0.0161</v>
+        <v>0.465</v>
+      </c>
+      <c r="E106" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1691200</v>
+        <v>2018200</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>2.08</v>
+        <v>0.23</v>
       </c>
       <c r="H106" t="n">
-        <v>56.04</v>
-      </c>
-      <c r="I106" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.37</v>
+      </c>
+      <c r="I106" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="10" t="n">
-        <v>0.294</v>
+        <v>0.485</v>
       </c>
       <c r="K106" s="10" t="n">
-        <v>0.293</v>
+        <v>0.473</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="15" t="inlineStr"/>
@@ -5300,19 +5300,19 @@
       <c r="D107" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E107" s="17" t="n">
+      <c r="E107" s="16" t="n">
         <v>-0.09089999999999999</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>1638800</v>
+        <v>1986400</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="H107" t="n">
         <v>46.74</v>
       </c>
-      <c r="I107" s="16" t="inlineStr">
+      <c r="I107" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5334,28 +5334,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="E108" s="18" t="n">
-        <v>0.0149</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E108" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>1622200</v>
+        <v>1963300</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="H108" t="n">
-        <v>51.08</v>
+        <v>56.13</v>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
@@ -5363,10 +5363,10 @@
         </is>
       </c>
       <c r="J108" s="10" t="n">
-        <v>7.412</v>
+        <v>0.904</v>
       </c>
       <c r="K108" s="10" t="n">
-        <v>7.755</v>
+        <v>0.953</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="15" t="inlineStr"/>
@@ -5379,39 +5379,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D109" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.35</v>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>1618000</v>
+        <v>1927200</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>0.55</v>
+        <v>2.26</v>
       </c>
       <c r="H109" t="n">
-        <v>49.58</v>
-      </c>
-      <c r="I109" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.63</v>
+      </c>
+      <c r="I109" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="10" t="n">
-        <v>0.866</v>
+        <v>0.335</v>
       </c>
       <c r="K109" s="10" t="n">
-        <v>0.861</v>
+        <v>0.319</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="15" t="inlineStr"/>
@@ -5424,39 +5424,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>0.345</v>
+        <v>7.84</v>
       </c>
       <c r="E110" s="18" t="n">
-        <v>0.0147</v>
+        <v>0.0013</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1616300</v>
+        <v>1903500</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>0.49</v>
+        <v>0.64</v>
       </c>
       <c r="H110" t="n">
-        <v>58.74</v>
-      </c>
-      <c r="I110" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.1</v>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="10" t="n">
-        <v>0.338</v>
+        <v>7.891</v>
       </c>
       <c r="K110" s="10" t="n">
-        <v>0.343</v>
+        <v>7.913</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="15" t="inlineStr"/>
@@ -5469,39 +5469,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D111" s="10" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>-0.029</v>
+        <v>0.22</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>1547800</v>
+        <v>1900000</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>1.01</v>
+        <v>3.98</v>
       </c>
       <c r="H111" t="n">
-        <v>57.81</v>
-      </c>
-      <c r="I111" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.5</v>
+      </c>
+      <c r="I111" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="10" t="n">
-        <v>0.32</v>
+        <v>0.224</v>
       </c>
       <c r="K111" s="10" t="n">
-        <v>0.33</v>
+        <v>0.224</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="15" t="inlineStr"/>
@@ -5514,28 +5514,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TDM</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E112" s="18" t="n">
-        <v>0.0513</v>
+        <v>0.775</v>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>1525100</v>
+        <v>1895500</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>4.19</v>
+        <v>0.35</v>
       </c>
       <c r="H112" t="n">
-        <v>52.51</v>
+        <v>56.87</v>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
@@ -5543,10 +5543,10 @@
         </is>
       </c>
       <c r="J112" s="10" t="n">
-        <v>0.201</v>
+        <v>0.75</v>
       </c>
       <c r="K112" s="10" t="n">
-        <v>0.214</v>
+        <v>0.699</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="15" t="inlineStr"/>
@@ -5559,28 +5559,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D113" s="10" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E113" s="17" t="n">
-        <v>-0.0148</v>
+        <v>0.23</v>
+      </c>
+      <c r="E113" s="18" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>1487200</v>
+        <v>1845100</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>0.31</v>
+        <v>1.16</v>
       </c>
       <c r="H113" t="n">
-        <v>57.38</v>
+        <v>49.26</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="J113" s="10" t="n">
-        <v>4.487</v>
+        <v>0.229</v>
       </c>
       <c r="K113" s="10" t="n">
-        <v>4.451</v>
+        <v>0.237</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="15" t="inlineStr"/>
@@ -5604,39 +5604,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D114" s="10" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>-0.0043</v>
+        <v>0.33</v>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>1454800</v>
+        <v>1807300</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="H114" t="n">
-        <v>60.57</v>
-      </c>
-      <c r="I114" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.02</v>
+      </c>
+      <c r="I114" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="10" t="n">
-        <v>6.45</v>
+        <v>0.335</v>
       </c>
       <c r="K114" s="10" t="n">
-        <v>6.069</v>
+        <v>0.339</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="15" t="inlineStr"/>
@@ -5649,28 +5649,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D115" s="10" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>-0.0129</v>
+        <v>0.345</v>
+      </c>
+      <c r="E115" s="18" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>1417000</v>
+        <v>1790300</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>0.26</v>
+        <v>0.54</v>
       </c>
       <c r="H115" t="n">
-        <v>54.86</v>
+        <v>58.74</v>
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="J115" s="10" t="n">
-        <v>0.749</v>
+        <v>0.338</v>
       </c>
       <c r="K115" s="10" t="n">
-        <v>0.699</v>
+        <v>0.343</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="15" t="inlineStr"/>
@@ -5694,28 +5694,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>COMFORT</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E116" s="17" t="n">
-        <v>-0.0476</v>
+        <v>4.66</v>
+      </c>
+      <c r="E116" s="16" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>1355600</v>
+        <v>1752400</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.66</v>
+        <v>0.36</v>
       </c>
       <c r="H116" t="n">
-        <v>63.86</v>
+        <v>57.83</v>
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="J116" s="10" t="n">
-        <v>0.181</v>
+        <v>4.488</v>
       </c>
       <c r="K116" s="10" t="n">
-        <v>0.166</v>
+        <v>4.451</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="15" t="inlineStr"/>
@@ -5739,28 +5739,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D117" s="10" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>-0.0308</v>
+        <v>0.305</v>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>1349500</v>
+        <v>1691200</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>0.82</v>
+        <v>2.08</v>
       </c>
       <c r="H117" t="n">
-        <v>54.6</v>
+        <v>56.04</v>
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
@@ -5768,10 +5768,10 @@
         </is>
       </c>
       <c r="J117" s="10" t="n">
-        <v>0.301</v>
+        <v>0.294</v>
       </c>
       <c r="K117" s="10" t="n">
-        <v>0.324</v>
+        <v>0.293</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="15" t="inlineStr"/>
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D118" s="10" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="E118" s="18" t="n">
-        <v>0.0026</v>
+        <v>6.87</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>-0.0043</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>1319300</v>
+        <v>1642300</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="H118" t="n">
-        <v>45.92</v>
-      </c>
-      <c r="I118" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.57</v>
+      </c>
+      <c r="I118" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="10" t="n">
-        <v>7.892</v>
+        <v>6.45</v>
       </c>
       <c r="K118" s="10" t="n">
-        <v>7.914</v>
+        <v>6.069</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="15" t="inlineStr"/>
@@ -5829,28 +5829,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>TDM</t>
         </is>
       </c>
       <c r="D119" s="10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E119" s="17" t="n">
-        <v>-0.0156</v>
+        <v>0.205</v>
+      </c>
+      <c r="E119" s="18" t="n">
+        <v>0.0513</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>1312100</v>
+        <v>1635100</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>0.6</v>
+        <v>4.49</v>
       </c>
       <c r="H119" t="n">
-        <v>45.12</v>
+        <v>52.51</v>
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="J119" s="10" t="n">
-        <v>0.64</v>
+        <v>0.201</v>
       </c>
       <c r="K119" s="10" t="n">
-        <v>0.631</v>
+        <v>0.214</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="15" t="inlineStr"/>
@@ -5874,28 +5874,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D120" s="10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E120" s="17" t="n">
-        <v>-0.0308</v>
+        <v>0.335</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>-0.029</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>1261400</v>
+        <v>1547800</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.19</v>
+        <v>1.01</v>
       </c>
       <c r="H120" t="n">
-        <v>54.54</v>
+        <v>57.81</v>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="J120" s="10" t="n">
-        <v>1.243</v>
+        <v>0.32</v>
       </c>
       <c r="K120" s="10" t="n">
-        <v>1.214</v>
+        <v>0.33</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="15" t="inlineStr"/>
@@ -5919,39 +5919,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D121" s="10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>-0.013</v>
+        <v>0.475</v>
+      </c>
+      <c r="E121" s="18" t="n">
+        <v>0.0215</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>1217300</v>
+        <v>1463900</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="H121" t="n">
-        <v>50.29</v>
-      </c>
-      <c r="I121" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.72</v>
+      </c>
+      <c r="I121" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="10" t="n">
-        <v>2.296</v>
+        <v>0.479</v>
       </c>
       <c r="K121" s="10" t="n">
-        <v>2.225</v>
+        <v>0.53</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="15" t="inlineStr"/>
@@ -5964,28 +5964,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>YNHPROP</t>
         </is>
       </c>
       <c r="D122" s="10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E122" s="17" t="n">
-        <v>-0.0105</v>
+        <v>0.33</v>
+      </c>
+      <c r="E122" s="18" t="n">
+        <v>0.08199999999999999</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>1154700</v>
+        <v>1454200</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>0.28</v>
+        <v>2.35</v>
       </c>
       <c r="H122" t="n">
-        <v>51.71</v>
+        <v>67.09</v>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
@@ -5993,10 +5993,10 @@
         </is>
       </c>
       <c r="J122" s="10" t="n">
-        <v>0.944</v>
+        <v>0.3</v>
       </c>
       <c r="K122" s="10" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="15" t="inlineStr"/>
@@ -6009,39 +6009,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D123" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E123" s="17" t="n">
-        <v>-0.0114</v>
+        <v>0.315</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>-0.0308</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>1124000</v>
+        <v>1445500</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>0.29</v>
+        <v>0.88</v>
       </c>
       <c r="H123" t="n">
-        <v>57.24</v>
-      </c>
-      <c r="I123" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.6</v>
+      </c>
+      <c r="I123" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="10" t="n">
-        <v>0.841</v>
+        <v>0.301</v>
       </c>
       <c r="K123" s="10" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.324</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="15" t="inlineStr"/>
@@ -6054,28 +6054,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D124" s="10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E124" s="17" t="n">
-        <v>-0.0103</v>
+        <v>1.27</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>-0.0231</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1100400</v>
+        <v>1377000</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="H124" t="n">
-        <v>55.92</v>
+        <v>56.11</v>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="J124" s="10" t="n">
-        <v>2.825</v>
+        <v>1.244</v>
       </c>
       <c r="K124" s="10" t="n">
-        <v>2.712</v>
+        <v>1.214</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="15" t="inlineStr"/>
@@ -6099,28 +6099,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D125" s="10" t="n">
-        <v>13.3</v>
+        <v>5.19</v>
       </c>
       <c r="E125" s="18" t="n">
-        <v>0.0061</v>
+        <v>0.0039</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>1096000</v>
+        <v>1370700</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="H125" t="n">
-        <v>58.06</v>
+        <v>56.49</v>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="J125" s="10" t="n">
-        <v>13.132</v>
+        <v>5.082</v>
       </c>
       <c r="K125" s="10" t="n">
-        <v>13.259</v>
+        <v>5.034</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="15" t="inlineStr"/>
@@ -6144,28 +6144,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D126" s="10" t="n">
-        <v>0.36</v>
+        <v>2.51</v>
       </c>
       <c r="E126" s="18" t="n">
-        <v>0.0435</v>
+        <v>0.0287</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>1078100</v>
+        <v>1359600</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>3.45</v>
+        <v>0.33</v>
       </c>
       <c r="H126" t="n">
-        <v>73.72</v>
+        <v>50.38</v>
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="J126" s="10" t="n">
-        <v>0.317</v>
+        <v>2.474</v>
       </c>
       <c r="K126" s="10" t="n">
-        <v>0.299</v>
+        <v>2.611</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="15" t="inlineStr"/>
@@ -6189,39 +6189,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D127" s="10" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E127" s="17" t="n">
-        <v>-0.0116</v>
+        <v>2.27</v>
+      </c>
+      <c r="E127" s="16" t="n">
+        <v>-0.0173</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>1049600</v>
+        <v>1347200</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="H127" t="n">
-        <v>56.63</v>
-      </c>
-      <c r="I127" s="16" t="inlineStr">
+        <v>49.58</v>
+      </c>
+      <c r="I127" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J127" s="10" t="n">
-        <v>0.405</v>
+        <v>2.295</v>
       </c>
       <c r="K127" s="10" t="n">
-        <v>0.369</v>
+        <v>2.225</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="15" t="inlineStr"/>
@@ -6234,39 +6234,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D128" s="10" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E128" s="17" t="n">
-        <v>-0.0263</v>
+        <v>0.855</v>
+      </c>
+      <c r="E128" s="16" t="n">
+        <v>-0.0229</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>1040400</v>
+        <v>1337300</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="H128" t="n">
-        <v>50.52</v>
-      </c>
-      <c r="I128" s="16" t="inlineStr">
+        <v>54.98</v>
+      </c>
+      <c r="I128" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J128" s="10" t="n">
-        <v>0.745</v>
+        <v>0.84</v>
       </c>
       <c r="K128" s="10" t="n">
-        <v>0.709</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="15" t="inlineStr"/>
@@ -6279,39 +6279,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D129" s="10" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E129" s="18" t="n">
-        <v>0.0337</v>
+        <v>0.425</v>
+      </c>
+      <c r="E129" s="16" t="n">
+        <v>-0.0116</v>
       </c>
       <c r="F129" s="12" t="n">
-        <v>943700</v>
+        <v>1308200</v>
       </c>
       <c r="G129" s="13" t="n">
-        <v>0.85</v>
+        <v>0.2</v>
       </c>
       <c r="H129" t="n">
-        <v>65.72</v>
-      </c>
-      <c r="I129" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.63</v>
+      </c>
+      <c r="I129" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="10" t="n">
-        <v>2.854</v>
+        <v>0.405</v>
       </c>
       <c r="K129" s="10" t="n">
-        <v>2.856</v>
+        <v>0.369</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="15" t="inlineStr"/>
@@ -6324,39 +6324,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>THETA</t>
         </is>
       </c>
       <c r="D130" s="10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E130" s="11" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E130" s="18" t="n">
+        <v>0.1604</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>940700</v>
+        <v>1257900</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>0.34</v>
+        <v>2.37</v>
       </c>
       <c r="H130" t="n">
-        <v>58.56</v>
-      </c>
-      <c r="I130" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.35</v>
+      </c>
+      <c r="I130" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="10" t="n">
-        <v>1.289</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K130" s="10" t="n">
-        <v>1.197</v>
+        <v>0.623</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="15" t="inlineStr"/>
@@ -6369,28 +6369,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D131" s="10" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="E131" s="17" t="n">
-        <v>-0.0058</v>
+        <v>13.3</v>
+      </c>
+      <c r="E131" s="18" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F131" s="12" t="n">
-        <v>931800</v>
+        <v>1215400</v>
       </c>
       <c r="G131" s="13" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="H131" t="n">
-        <v>45.84</v>
+        <v>58.06</v>
       </c>
       <c r="I131" s="14" t="inlineStr">
         <is>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="J131" s="10" t="n">
-        <v>0.879</v>
+        <v>13.132</v>
       </c>
       <c r="K131" s="10" t="n">
-        <v>0.868</v>
+        <v>13.259</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="15" t="inlineStr"/>
@@ -6414,28 +6414,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D132" s="10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E132" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>-0.0158</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>927100</v>
+        <v>1212500</v>
       </c>
       <c r="G132" s="13" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="H132" t="n">
-        <v>67.77</v>
+        <v>49.94</v>
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
@@ -6443,10 +6443,10 @@
         </is>
       </c>
       <c r="J132" s="10" t="n">
-        <v>1.14</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K132" s="10" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="15" t="inlineStr"/>
@@ -6459,28 +6459,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D133" s="10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E133" s="18" t="n">
-        <v>0.0208</v>
+        <v>2.9</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F133" s="12" t="n">
-        <v>908700</v>
+        <v>1177100</v>
       </c>
       <c r="G133" s="13" t="n">
-        <v>1.3</v>
+        <v>0.19</v>
       </c>
       <c r="H133" t="n">
-        <v>47.14</v>
+        <v>56.62</v>
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="J133" s="10" t="n">
-        <v>1.467</v>
+        <v>2.826</v>
       </c>
       <c r="K133" s="10" t="n">
-        <v>1.578</v>
+        <v>2.712</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="15" t="inlineStr"/>
@@ -6504,39 +6504,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E134" s="18" t="n">
-        <v>0.0246</v>
+        <v>0.745</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>-0.0197</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>904600</v>
+        <v>1176000</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>0.22</v>
+        <v>0.36</v>
       </c>
       <c r="H134" t="n">
-        <v>49.36</v>
-      </c>
-      <c r="I134" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.49</v>
+      </c>
+      <c r="I134" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="10" t="n">
-        <v>2.474</v>
+        <v>0.745</v>
       </c>
       <c r="K134" s="10" t="n">
-        <v>2.61</v>
+        <v>0.709</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="15" t="inlineStr"/>
@@ -6549,39 +6549,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D135" s="10" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="E135" s="18" t="n">
-        <v>0.0039</v>
+        <v>0.275</v>
+      </c>
+      <c r="E135" s="16" t="n">
+        <v>-0.0351</v>
       </c>
       <c r="F135" s="12" t="n">
-        <v>903600</v>
+        <v>1155700</v>
       </c>
       <c r="G135" s="13" t="n">
-        <v>0.22</v>
+        <v>0.52</v>
       </c>
       <c r="H135" t="n">
-        <v>56.49</v>
-      </c>
-      <c r="I135" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.89</v>
+      </c>
+      <c r="I135" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="10" t="n">
-        <v>5.082</v>
+        <v>0.273</v>
       </c>
       <c r="K135" s="10" t="n">
-        <v>5.034</v>
+        <v>0.259</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="15" t="inlineStr"/>
@@ -6609,15 +6609,15 @@
         <v>0.009899999999999999</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>899900</v>
+        <v>1154500</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="H136" t="n">
         <v>41.02</v>
       </c>
-      <c r="I136" s="16" t="inlineStr">
+      <c r="I136" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6639,39 +6639,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="D137" s="10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E137" s="17" t="n">
-        <v>-0.0074</v>
+        <v>3.1</v>
+      </c>
+      <c r="E137" s="18" t="n">
+        <v>0.0438</v>
       </c>
       <c r="F137" s="12" t="n">
-        <v>890400</v>
+        <v>1098600</v>
       </c>
       <c r="G137" s="13" t="n">
-        <v>0.19</v>
+        <v>0.99</v>
       </c>
       <c r="H137" t="n">
-        <v>44.38</v>
-      </c>
-      <c r="I137" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.98999999999999</v>
+      </c>
+      <c r="I137" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="10" t="n">
-        <v>0.704</v>
+        <v>2.857</v>
       </c>
       <c r="K137" s="10" t="n">
-        <v>0.6919999999999999</v>
+        <v>2.857</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="15" t="inlineStr"/>
@@ -6684,39 +6684,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E138" s="17" t="n">
-        <v>-0.0017</v>
+        <v>0.355</v>
+      </c>
+      <c r="E138" s="18" t="n">
+        <v>0.029</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>883700</v>
+        <v>1090100</v>
       </c>
       <c r="G138" s="13" t="n">
-        <v>0.2</v>
+        <v>3.49</v>
       </c>
       <c r="H138" t="n">
-        <v>58.39</v>
-      </c>
-      <c r="I138" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.42</v>
+      </c>
+      <c r="I138" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="10" t="n">
-        <v>5.573</v>
+        <v>0.317</v>
       </c>
       <c r="K138" s="10" t="n">
-        <v>5.4</v>
+        <v>0.299</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
@@ -6729,39 +6729,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D139" s="10" t="n">
-        <v>3.96</v>
+        <v>5.86</v>
       </c>
       <c r="E139" s="18" t="n">
-        <v>0.0076</v>
+        <v>0.0086</v>
       </c>
       <c r="F139" s="12" t="n">
-        <v>867500</v>
+        <v>1088800</v>
       </c>
       <c r="G139" s="13" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H139" t="n">
-        <v>56.33</v>
-      </c>
-      <c r="I139" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.92</v>
+      </c>
+      <c r="I139" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="10" t="n">
-        <v>3.85</v>
+        <v>5.578</v>
       </c>
       <c r="K139" s="10" t="n">
-        <v>3.776</v>
+        <v>5.402</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="15" t="inlineStr"/>
@@ -6774,28 +6774,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D140" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="E140" s="17" t="n">
-        <v>-0.0054</v>
+        <v>0.855</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F140" s="12" t="n">
-        <v>861500</v>
+        <v>1061800</v>
       </c>
       <c r="G140" s="13" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="H140" t="n">
-        <v>61.08</v>
+        <v>45.84</v>
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="J140" s="10" t="n">
-        <v>10.6</v>
+        <v>0.879</v>
       </c>
       <c r="K140" s="10" t="n">
-        <v>9.972</v>
+        <v>0.868</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="15" t="inlineStr"/>
@@ -6819,39 +6819,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0287</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SSF</t>
         </is>
       </c>
       <c r="D141" s="10" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E141" s="17" t="n">
-        <v>-0.008199999999999999</v>
+        <v>0.37</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F141" s="12" t="n">
-        <v>845200</v>
+        <v>1056800</v>
       </c>
       <c r="G141" s="13" t="n">
-        <v>0.11</v>
+        <v>4.19</v>
       </c>
       <c r="H141" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="I141" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.05</v>
+      </c>
+      <c r="I141" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="10" t="n">
-        <v>0.636</v>
+        <v>0.367</v>
       </c>
       <c r="K141" s="10" t="n">
-        <v>0.676</v>
+        <v>0.36</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="15" t="inlineStr"/>
@@ -6864,39 +6864,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D142" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E142" s="18" t="n">
-        <v>0.0246</v>
+        <v>0.665</v>
+      </c>
+      <c r="E142" s="16" t="n">
+        <v>-0.0148</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>836500</v>
+        <v>1054400</v>
       </c>
       <c r="G142" s="13" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="H142" t="n">
-        <v>45.78</v>
-      </c>
-      <c r="I142" s="16" t="inlineStr">
+        <v>43.74</v>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J142" s="10" t="n">
-        <v>2.511</v>
+        <v>0.703</v>
       </c>
       <c r="K142" s="10" t="n">
-        <v>2.623</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="15" t="inlineStr"/>
@@ -6909,39 +6909,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D143" s="10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E143" s="17" t="n">
-        <v>-0.0214</v>
+        <v>1.28</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F143" s="12" t="n">
-        <v>824800</v>
+        <v>1026300</v>
       </c>
       <c r="G143" s="13" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="H143" t="n">
-        <v>43</v>
-      </c>
-      <c r="I143" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.77</v>
+      </c>
+      <c r="I143" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="10" t="n">
-        <v>2.809</v>
+        <v>1.14</v>
       </c>
       <c r="K143" s="10" t="n">
-        <v>2.94</v>
+        <v>0.999</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="15" t="inlineStr"/>
@@ -6954,39 +6954,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>SENDAI</t>
         </is>
       </c>
       <c r="D144" s="10" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E144" s="18" t="n">
-        <v>0.0062</v>
+        <v>0.225</v>
+      </c>
+      <c r="E144" s="16" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>791500</v>
+        <v>1016700</v>
       </c>
       <c r="G144" s="13" t="n">
-        <v>0.36</v>
+        <v>1.12</v>
       </c>
       <c r="H144" t="n">
-        <v>69.41</v>
-      </c>
-      <c r="I144" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.72</v>
+      </c>
+      <c r="I144" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J144" s="10" t="n">
-        <v>0.752</v>
+        <v>0.232</v>
       </c>
       <c r="K144" s="10" t="n">
-        <v>0.68</v>
+        <v>0.245</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -6999,28 +6999,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>KEEMING</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D145" s="10" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E145" s="18" t="n">
-        <v>0.0361</v>
+        <v>11.02</v>
+      </c>
+      <c r="E145" s="16" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F145" s="12" t="n">
-        <v>785500</v>
+        <v>1015400</v>
       </c>
       <c r="G145" s="13" t="n">
-        <v>1.03</v>
+        <v>0.27</v>
       </c>
       <c r="H145" t="n">
-        <v>65.73</v>
+        <v>61.56</v>
       </c>
       <c r="I145" s="14" t="inlineStr">
         <is>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="J145" s="10" t="n">
-        <v>2.611</v>
+        <v>10.602</v>
       </c>
       <c r="K145" s="10" t="n">
-        <v>2.54</v>
+        <v>9.972</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="15" t="inlineStr"/>
@@ -7044,39 +7044,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D146" s="10" t="n">
-        <v>0.78</v>
+        <v>1.36</v>
       </c>
       <c r="E146" s="18" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0074</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>768500</v>
+        <v>988100</v>
       </c>
       <c r="G146" s="13" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="H146" t="n">
-        <v>23.74</v>
-      </c>
-      <c r="I146" s="16" t="inlineStr">
+        <v>59.37</v>
+      </c>
+      <c r="I146" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J146" s="10" t="n">
-        <v>0.856</v>
+        <v>1.29</v>
       </c>
       <c r="K146" s="10" t="n">
-        <v>1.017</v>
+        <v>1.197</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="15" t="inlineStr"/>
@@ -7089,39 +7089,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D147" s="10" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E147" s="17" t="n">
-        <v>-0.0146</v>
+        <v>0.64</v>
+      </c>
+      <c r="E147" s="16" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F147" s="12" t="n">
-        <v>754700</v>
+        <v>985200</v>
       </c>
       <c r="G147" s="13" t="n">
-        <v>0.34</v>
+        <v>0.99</v>
       </c>
       <c r="H147" t="n">
-        <v>57.05</v>
-      </c>
-      <c r="I147" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.16</v>
+      </c>
+      <c r="I147" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J147" s="10" t="n">
-        <v>0.659</v>
+        <v>0.636</v>
       </c>
       <c r="K147" s="10" t="n">
-        <v>0.592</v>
+        <v>0.634</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="15" t="inlineStr"/>
@@ -7134,28 +7134,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D148" s="10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E148" s="17" t="n">
-        <v>-0.0053</v>
+        <v>1.46</v>
+      </c>
+      <c r="E148" s="18" t="n">
+        <v>0.0139</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>737900</v>
+        <v>958900</v>
       </c>
       <c r="G148" s="13" t="n">
-        <v>0.16</v>
+        <v>1.37</v>
       </c>
       <c r="H148" t="n">
-        <v>40.07</v>
+        <v>45.94</v>
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="J148" s="10" t="n">
-        <v>0.95</v>
+        <v>1.466</v>
       </c>
       <c r="K148" s="10" t="n">
-        <v>1.023</v>
+        <v>1.578</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -7179,39 +7179,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D149" s="10" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E149" s="11" t="n">
-        <v>0</v>
+        <v>0.605</v>
+      </c>
+      <c r="E149" s="16" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F149" s="12" t="n">
-        <v>733900</v>
+        <v>903900</v>
       </c>
       <c r="G149" s="13" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="H149" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="I149" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.64</v>
+      </c>
+      <c r="I149" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J149" s="10" t="n">
-        <v>0.494</v>
+        <v>0.636</v>
       </c>
       <c r="K149" s="10" t="n">
-        <v>0.485</v>
+        <v>0.676</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="15" t="inlineStr"/>
@@ -7224,39 +7224,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MNRB</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D150" s="10" t="n">
-        <v>2.53</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E150" s="18" t="n">
-        <v>0.004</v>
+        <v>0.0062</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>730300</v>
+        <v>887700</v>
       </c>
       <c r="G150" s="13" t="n">
-        <v>1.39</v>
+        <v>0.4</v>
       </c>
       <c r="H150" t="n">
-        <v>41.16</v>
-      </c>
-      <c r="I150" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>69.41</v>
+      </c>
+      <c r="I150" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="10" t="n">
-        <v>2.561</v>
+        <v>0.752</v>
       </c>
       <c r="K150" s="10" t="n">
-        <v>2.667</v>
+        <v>0.68</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -7269,28 +7269,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>KEEMING</t>
         </is>
       </c>
       <c r="D151" s="10" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="E151" s="17" t="n">
-        <v>-0.0092</v>
+        <v>2.9</v>
+      </c>
+      <c r="E151" s="18" t="n">
+        <v>0.0469</v>
       </c>
       <c r="F151" s="12" t="n">
-        <v>725200</v>
+        <v>887400</v>
       </c>
       <c r="G151" s="13" t="n">
-        <v>0.19</v>
+        <v>1.16</v>
       </c>
       <c r="H151" t="n">
-        <v>45.03</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="I151" s="14" t="inlineStr">
         <is>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="J151" s="10" t="n">
-        <v>4.328</v>
+        <v>2.614</v>
       </c>
       <c r="K151" s="10" t="n">
-        <v>4.577</v>
+        <v>2.541</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="15" t="inlineStr"/>
@@ -7314,39 +7314,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D152" s="10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E152" s="17" t="n">
-        <v>-0.008500000000000001</v>
+        <v>3.95</v>
+      </c>
+      <c r="E152" s="18" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>717300</v>
+        <v>884700</v>
       </c>
       <c r="G152" s="13" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H152" t="n">
-        <v>58.36</v>
-      </c>
-      <c r="I152" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.94</v>
+      </c>
+      <c r="I152" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="10" t="n">
-        <v>1.111</v>
+        <v>3.849</v>
       </c>
       <c r="K152" s="10" t="n">
-        <v>0.955</v>
+        <v>3.776</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="15" t="inlineStr"/>
@@ -7359,39 +7359,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D153" s="10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E153" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>2.73</v>
+      </c>
+      <c r="E153" s="16" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F153" s="12" t="n">
-        <v>695200</v>
+        <v>868800</v>
       </c>
       <c r="G153" s="13" t="n">
-        <v>0.7</v>
+        <v>0.24</v>
       </c>
       <c r="H153" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="I153" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.43</v>
+      </c>
+      <c r="I153" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="10" t="n">
-        <v>0.636</v>
+        <v>2.808</v>
       </c>
       <c r="K153" s="10" t="n">
-        <v>0.634</v>
+        <v>2.94</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="15" t="inlineStr"/>
@@ -7404,28 +7404,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D154" s="10" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="E154" s="17" t="n">
-        <v>-0.0025</v>
+        <v>4.3</v>
+      </c>
+      <c r="E154" s="16" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>689000</v>
+        <v>854500</v>
       </c>
       <c r="G154" s="13" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="H154" t="n">
-        <v>57.88</v>
+        <v>44.41</v>
       </c>
       <c r="I154" s="14" t="inlineStr">
         <is>
@@ -7433,10 +7433,10 @@
         </is>
       </c>
       <c r="J154" s="10" t="n">
-        <v>7.87</v>
+        <v>4.327</v>
       </c>
       <c r="K154" s="10" t="n">
-        <v>7.867</v>
+        <v>4.577</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="15" t="inlineStr"/>
@@ -7449,39 +7449,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D155" s="10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E155" s="17" t="n">
-        <v>-0.011</v>
+        <v>2.5</v>
+      </c>
+      <c r="E155" s="18" t="n">
+        <v>0.0246</v>
       </c>
       <c r="F155" s="12" t="n">
-        <v>682100</v>
+        <v>852200</v>
       </c>
       <c r="G155" s="13" t="n">
-        <v>0.83</v>
+        <v>0.34</v>
       </c>
       <c r="H155" t="n">
-        <v>34.68</v>
-      </c>
-      <c r="I155" s="16" t="inlineStr">
+        <v>45.78</v>
+      </c>
+      <c r="I155" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J155" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.511</v>
       </c>
       <c r="K155" s="10" t="n">
-        <v>0.966</v>
+        <v>2.623</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="15" t="inlineStr"/>
@@ -7494,39 +7494,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D156" s="10" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E156" s="17" t="n">
-        <v>-0.008199999999999999</v>
+        <v>0.595</v>
+      </c>
+      <c r="E156" s="18" t="n">
+        <v>0.0171</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>677600</v>
+        <v>833700</v>
       </c>
       <c r="G156" s="13" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H156" t="n">
-        <v>64.16</v>
-      </c>
-      <c r="I156" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.05</v>
+      </c>
+      <c r="I156" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J156" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K156" s="10" t="n">
-        <v>0.494</v>
+        <v>0.533</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -7539,39 +7539,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D157" s="10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E157" s="18" t="n">
-        <v>0.0032</v>
+        <v>7.97</v>
+      </c>
+      <c r="E157" s="16" t="n">
+        <v>-0.0038</v>
       </c>
       <c r="F157" s="12" t="n">
-        <v>646300</v>
+        <v>824300</v>
       </c>
       <c r="G157" s="13" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H157" t="n">
-        <v>34.45</v>
-      </c>
-      <c r="I157" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.16</v>
+      </c>
+      <c r="I157" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J157" s="10" t="n">
-        <v>3.273</v>
+        <v>7.869</v>
       </c>
       <c r="K157" s="10" t="n">
-        <v>3.506</v>
+        <v>7.866</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="15" t="inlineStr"/>
@@ -7584,39 +7584,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D158" s="10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="E158" s="17" t="n">
-        <v>-0.0063</v>
+        <v>1.56</v>
+      </c>
+      <c r="E158" s="16" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>637800</v>
+        <v>797700</v>
       </c>
       <c r="G158" s="13" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="H158" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="I158" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.73</v>
+      </c>
+      <c r="I158" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J158" s="10" t="n">
-        <v>1.683</v>
+        <v>1.628</v>
       </c>
       <c r="K158" s="10" t="n">
-        <v>1.756</v>
+        <v>1.693</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="15" t="inlineStr"/>
@@ -7629,39 +7629,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D159" s="10" t="n">
-        <v>3.58</v>
+        <v>2.05</v>
       </c>
       <c r="E159" s="18" t="n">
-        <v>0.0199</v>
+        <v>0.0149</v>
       </c>
       <c r="F159" s="12" t="n">
-        <v>632200</v>
+        <v>793100</v>
       </c>
       <c r="G159" s="13" t="n">
-        <v>0.39</v>
+        <v>0.21</v>
       </c>
       <c r="H159" t="n">
-        <v>53.08</v>
-      </c>
-      <c r="I159" s="16" t="inlineStr">
+        <v>51.84</v>
+      </c>
+      <c r="I159" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J159" s="10" t="n">
-        <v>3.545</v>
+        <v>2.038</v>
       </c>
       <c r="K159" s="10" t="n">
-        <v>3.572</v>
+        <v>2.059</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="15" t="inlineStr"/>
@@ -7674,39 +7674,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D160" s="10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E160" s="11" t="n">
-        <v>0</v>
+        <v>0.785</v>
+      </c>
+      <c r="E160" s="18" t="n">
+        <v>0.0129</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>629500</v>
+        <v>784000</v>
       </c>
       <c r="G160" s="13" t="n">
-        <v>0.29</v>
+        <v>0.37</v>
       </c>
       <c r="H160" t="n">
-        <v>68.53</v>
-      </c>
-      <c r="I160" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.39</v>
+      </c>
+      <c r="I160" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J160" s="10" t="n">
-        <v>1.383</v>
+        <v>0.856</v>
       </c>
       <c r="K160" s="10" t="n">
-        <v>1.354</v>
+        <v>1.017</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="15" t="inlineStr"/>
@@ -7719,28 +7719,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D161" s="10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E161" s="18" t="n">
-        <v>0.0106</v>
+        <v>2.92</v>
+      </c>
+      <c r="E161" s="16" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F161" s="12" t="n">
-        <v>619200</v>
+        <v>774200</v>
       </c>
       <c r="G161" s="13" t="n">
-        <v>0.75</v>
+        <v>0.28</v>
       </c>
       <c r="H161" t="n">
-        <v>65.23</v>
+        <v>60.32</v>
       </c>
       <c r="I161" s="14" t="inlineStr">
         <is>
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="J161" s="10" t="n">
-        <v>1.818</v>
+        <v>2.781</v>
       </c>
       <c r="K161" s="10" t="n">
-        <v>1.696</v>
+        <v>2.428</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="15" t="inlineStr"/>
@@ -7764,39 +7764,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D162" s="10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E162" s="17" t="n">
-        <v>-0.0189</v>
+        <v>0.945</v>
+      </c>
+      <c r="E162" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>618400</v>
+        <v>766200</v>
       </c>
       <c r="G162" s="13" t="n">
-        <v>0.62</v>
+        <v>0.16</v>
       </c>
       <c r="H162" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="I162" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.91</v>
+      </c>
+      <c r="I162" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="10" t="n">
-        <v>1.628</v>
+        <v>0.95</v>
       </c>
       <c r="K162" s="10" t="n">
-        <v>1.693</v>
+        <v>1.023</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -7809,39 +7809,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D163" s="10" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E163" s="18" t="n">
-        <v>0.0091</v>
+        <v>0.61</v>
+      </c>
+      <c r="E163" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F163" s="12" t="n">
-        <v>600600</v>
+        <v>763900</v>
       </c>
       <c r="G163" s="13" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="H163" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="I163" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.54000000000001</v>
+      </c>
+      <c r="I163" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="10" t="n">
-        <v>0.553</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K163" s="10" t="n">
-        <v>0.587</v>
+        <v>0.494</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="15" t="inlineStr"/>
@@ -7854,28 +7854,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PJBUMI</t>
+          <t>MNRB</t>
         </is>
       </c>
       <c r="D164" s="10" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="E164" s="17" t="n">
-        <v>-0.0119</v>
+        <v>2.52</v>
+      </c>
+      <c r="E164" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>599700</v>
+        <v>763900</v>
       </c>
       <c r="G164" s="13" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="H164" t="n">
-        <v>48.33</v>
+        <v>39.16</v>
       </c>
       <c r="I164" s="14" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         </is>
       </c>
       <c r="J164" s="10" t="n">
-        <v>4.175</v>
+        <v>2.56</v>
       </c>
       <c r="K164" s="10" t="n">
-        <v>4.059</v>
+        <v>2.667</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="15" t="inlineStr"/>
@@ -7899,39 +7899,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D165" s="10" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E165" s="11" t="n">
-        <v>0</v>
+        <v>0.675</v>
+      </c>
+      <c r="E165" s="16" t="n">
+        <v>-0.0146</v>
       </c>
       <c r="F165" s="12" t="n">
-        <v>588800</v>
+        <v>759700</v>
       </c>
       <c r="G165" s="13" t="n">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="H165" t="n">
-        <v>57.26</v>
-      </c>
-      <c r="I165" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.05</v>
+      </c>
+      <c r="I165" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J165" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.659</v>
       </c>
       <c r="K165" s="10" t="n">
-        <v>0.533</v>
+        <v>0.592</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="15" t="inlineStr"/>
@@ -7944,28 +7944,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D166" s="10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E166" s="18" t="n">
-        <v>0.0132</v>
+        <v>0.51</v>
+      </c>
+      <c r="E166" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>587700</v>
+        <v>748200</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>0.42</v>
+        <v>0.27</v>
       </c>
       <c r="H166" t="n">
-        <v>61.4</v>
+        <v>58.07</v>
       </c>
       <c r="I166" s="14" t="inlineStr">
         <is>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="J166" s="10" t="n">
-        <v>2.153</v>
+        <v>0.494</v>
       </c>
       <c r="K166" s="10" t="n">
-        <v>2.218</v>
+        <v>0.485</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -7989,39 +7989,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D167" s="10" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E167" s="18" t="n">
-        <v>0.1132</v>
+        <v>1.16</v>
+      </c>
+      <c r="E167" s="16" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F167" s="12" t="n">
-        <v>587600</v>
+        <v>743300</v>
       </c>
       <c r="G167" s="13" t="n">
-        <v>1.11</v>
+        <v>0.23</v>
       </c>
       <c r="H167" t="n">
-        <v>55.11</v>
-      </c>
-      <c r="I167" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.36</v>
+      </c>
+      <c r="I167" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="10" t="n">
-        <v>0.5610000000000001</v>
+        <v>1.111</v>
       </c>
       <c r="K167" s="10" t="n">
-        <v>0.622</v>
+        <v>0.955</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="15" t="inlineStr"/>
@@ -8034,39 +8034,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D168" s="10" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E168" s="11" t="n">
-        <v>0</v>
+        <v>1.57</v>
+      </c>
+      <c r="E168" s="16" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>584100</v>
+        <v>733100</v>
       </c>
       <c r="G168" s="13" t="n">
-        <v>0.22</v>
+        <v>0.96</v>
       </c>
       <c r="H168" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="I168" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>32.35</v>
+      </c>
+      <c r="I168" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J168" s="10" t="n">
-        <v>0.825</v>
+        <v>1.683</v>
       </c>
       <c r="K168" s="10" t="n">
-        <v>0.853</v>
+        <v>1.756</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="15" t="inlineStr"/>
@@ -8079,28 +8079,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D169" s="10" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="E169" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>1.89</v>
+      </c>
+      <c r="E169" s="18" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F169" s="12" t="n">
-        <v>577000</v>
+        <v>729800</v>
       </c>
       <c r="G169" s="13" t="n">
-        <v>0.12</v>
+        <v>0.89</v>
       </c>
       <c r="H169" t="n">
-        <v>56.19</v>
+        <v>64.3</v>
       </c>
       <c r="I169" s="14" t="inlineStr">
         <is>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="J169" s="10" t="n">
-        <v>7.35</v>
+        <v>1.817</v>
       </c>
       <c r="K169" s="10" t="n">
-        <v>6.998</v>
+        <v>1.696</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="15" t="inlineStr"/>
@@ -8124,39 +8124,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SENTRAL</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D170" s="10" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E170" s="11" t="n">
-        <v>0</v>
+        <v>3.15</v>
+      </c>
+      <c r="E170" s="18" t="n">
+        <v>0.0032</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>547300</v>
+        <v>720500</v>
       </c>
       <c r="G170" s="13" t="n">
-        <v>1.26</v>
+        <v>0.19</v>
       </c>
       <c r="H170" t="n">
-        <v>24.13</v>
-      </c>
-      <c r="I170" s="16" t="inlineStr">
+        <v>34.45</v>
+      </c>
+      <c r="I170" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J170" s="10" t="n">
-        <v>0.627</v>
+        <v>3.273</v>
       </c>
       <c r="K170" s="10" t="n">
-        <v>0.65</v>
+        <v>3.506</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="15" t="inlineStr"/>
@@ -8169,39 +8169,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D171" s="10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E171" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>1.43</v>
+      </c>
+      <c r="E171" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F171" s="12" t="n">
-        <v>546000</v>
+        <v>714500</v>
       </c>
       <c r="G171" s="13" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="H171" t="n">
-        <v>49.35</v>
-      </c>
-      <c r="I171" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.53</v>
+      </c>
+      <c r="I171" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J171" s="10" t="n">
-        <v>0.633</v>
+        <v>1.383</v>
       </c>
       <c r="K171" s="10" t="n">
-        <v>0.625</v>
+        <v>1.354</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="15" t="inlineStr"/>
@@ -8214,39 +8214,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D172" s="10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E172" s="17" t="n">
-        <v>-0.0074</v>
+        <v>1.08</v>
+      </c>
+      <c r="E172" s="16" t="n">
+        <v>-0.0092</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>532500</v>
+        <v>708900</v>
       </c>
       <c r="G172" s="13" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="H172" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="I172" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.26</v>
+      </c>
+      <c r="I172" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="10" t="n">
-        <v>1.361</v>
+        <v>1.113</v>
       </c>
       <c r="K172" s="10" t="n">
-        <v>1.427</v>
+        <v>1.117</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="15" t="inlineStr"/>
@@ -8259,39 +8259,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D173" s="10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E173" s="18" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.9</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F173" s="12" t="n">
-        <v>528200</v>
+        <v>690200</v>
       </c>
       <c r="G173" s="13" t="n">
-        <v>0.14</v>
+        <v>0.84</v>
       </c>
       <c r="H173" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="I173" s="16" t="inlineStr">
+        <v>34.68</v>
+      </c>
+      <c r="I173" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J173" s="10" t="n">
-        <v>2.037</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K173" s="10" t="n">
-        <v>2.059</v>
+        <v>0.966</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="15" t="inlineStr"/>
@@ -8304,39 +8304,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D174" s="10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E174" s="11" t="n">
-        <v>0</v>
+        <v>3.57</v>
+      </c>
+      <c r="E174" s="18" t="n">
+        <v>0.0171</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>517500</v>
+        <v>683000</v>
       </c>
       <c r="G174" s="13" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H174" t="n">
-        <v>45.68</v>
-      </c>
-      <c r="I174" s="16" t="inlineStr">
+        <v>52.28</v>
+      </c>
+      <c r="I174" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J174" s="10" t="n">
-        <v>1.114</v>
+        <v>3.544</v>
       </c>
       <c r="K174" s="10" t="n">
-        <v>1.117</v>
+        <v>3.571</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="15" t="inlineStr"/>
@@ -8349,28 +8349,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D175" s="10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="E175" s="17" t="n">
-        <v>-0.0133</v>
+        <v>1.37</v>
+      </c>
+      <c r="E175" s="18" t="n">
+        <v>0.0074</v>
       </c>
       <c r="F175" s="12" t="n">
-        <v>511300</v>
+        <v>662600</v>
       </c>
       <c r="G175" s="13" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="H175" t="n">
-        <v>62.68</v>
+        <v>48.62</v>
       </c>
       <c r="I175" s="14" t="inlineStr">
         <is>
@@ -8378,10 +8378,10 @@
         </is>
       </c>
       <c r="J175" s="10" t="n">
-        <v>2.785</v>
+        <v>1.363</v>
       </c>
       <c r="K175" s="10" t="n">
-        <v>2.429</v>
+        <v>1.428</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="15" t="inlineStr"/>
@@ -8394,45 +8394,720 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D176" s="10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E176" s="11" t="n">
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="E176" s="16" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>508800</v>
+        <v>656600</v>
       </c>
       <c r="G176" s="13" t="n">
-        <v>0.86</v>
+        <v>0.24</v>
       </c>
       <c r="H176" t="n">
-        <v>49.92</v>
-      </c>
-      <c r="I176" s="16" t="inlineStr">
+        <v>47.41</v>
+      </c>
+      <c r="I176" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J176" s="10" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="K176" s="10" t="n">
-        <v>0.665</v>
+        <v>0.625</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="15" t="inlineStr"/>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>KERJAYA</t>
+        </is>
+      </c>
+      <c r="D177" s="10" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="E177" s="16" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F177" s="12" t="n">
+        <v>640600</v>
+      </c>
+      <c r="G177" s="13" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H177" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="I177" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>3.406</v>
+      </c>
+      <c r="K177" s="10" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="15" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="D178" s="10" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E178" s="16" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="F178" s="12" t="n">
+        <v>633000</v>
+      </c>
+      <c r="G178" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H178" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="I178" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J178" s="10" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="K178" s="10" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="15" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D179" s="10" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="E179" s="16" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="F179" s="12" t="n">
+        <v>622100</v>
+      </c>
+      <c r="G179" s="13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H179" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="I179" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="10" t="n">
+        <v>7.353</v>
+      </c>
+      <c r="K179" s="10" t="n">
+        <v>6.998</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="15" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>7163</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>PJBUMI</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="E180" s="16" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="F180" s="12" t="n">
+        <v>616400</v>
+      </c>
+      <c r="G180" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H180" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="I180" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J180" s="10" t="n">
+        <v>4.174</v>
+      </c>
+      <c r="K180" s="10" t="n">
+        <v>4.059</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="15" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D181" s="10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E181" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="12" t="n">
+        <v>608800</v>
+      </c>
+      <c r="G181" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H181" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="I181" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J181" s="10" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="K181" s="10" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="15" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E182" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="12" t="n">
+        <v>605200</v>
+      </c>
+      <c r="G182" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H182" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="I182" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J182" s="10" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="K182" s="10" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="15" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D183" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E183" s="16" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="F183" s="12" t="n">
+        <v>594400</v>
+      </c>
+      <c r="G183" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H183" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="I183" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="10" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="K183" s="10" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="15" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="E184" s="18" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="F184" s="12" t="n">
+        <v>590700</v>
+      </c>
+      <c r="G184" s="13" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H184" t="n">
+        <v>60.17</v>
+      </c>
+      <c r="I184" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J184" s="10" t="n">
+        <v>2.151</v>
+      </c>
+      <c r="K184" s="10" t="n">
+        <v>2.218</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="15" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>BURSA</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="E185" s="18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F185" s="12" t="n">
+        <v>576900</v>
+      </c>
+      <c r="G185" s="13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H185" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="I185" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J185" s="10" t="n">
+        <v>8.071999999999999</v>
+      </c>
+      <c r="K185" s="10" t="n">
+        <v>8.247999999999999</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="15" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5123</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>SENTRAL</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E186" s="16" t="n">
+        <v>-0.008199999999999999</v>
+      </c>
+      <c r="F186" s="12" t="n">
+        <v>562300</v>
+      </c>
+      <c r="G186" s="13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H186" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="I186" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="10" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="K186" s="10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="15" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="E187" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="12" t="n">
+        <v>542800</v>
+      </c>
+      <c r="G187" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H187" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="I187" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J187" s="10" t="n">
+        <v>1.812</v>
+      </c>
+      <c r="K187" s="10" t="n">
+        <v>1.901</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="15" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D188" s="10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E188" s="16" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="F188" s="12" t="n">
+        <v>537100</v>
+      </c>
+      <c r="G188" s="13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H188" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="I188" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J188" s="10" t="n">
+        <v>2.621</v>
+      </c>
+      <c r="K188" s="10" t="n">
+        <v>2.809</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="15" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="E189" s="16" t="n">
+        <v>-0.0208</v>
+      </c>
+      <c r="F189" s="12" t="n">
+        <v>536300</v>
+      </c>
+      <c r="G189" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H189" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="I189" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J189" s="10" t="n">
+        <v>7.574</v>
+      </c>
+      <c r="K189" s="10" t="n">
+        <v>7.677</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="15" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D190" s="10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E190" s="16" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="F190" s="12" t="n">
+        <v>530700</v>
+      </c>
+      <c r="G190" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H190" t="n">
+        <v>63.04</v>
+      </c>
+      <c r="I190" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="10" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="K190" s="10" t="n">
+        <v>2.434</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="15" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>MFLOUR</t>
+        </is>
+      </c>
+      <c r="D191" s="10" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E191" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="12" t="n">
+        <v>514600</v>
+      </c>
+      <c r="G191" s="13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H191" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="I191" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="10" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="K191" s="10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M176"/>
+  <autoFilter ref="A1:M191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>